--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -154,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -231,6 +235,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11108,14 +11113,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A3:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.88" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
@@ -11164,9 +11167,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
@@ -11191,9 +11191,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -11256,7 +11253,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
@@ -11288,7 +11284,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
@@ -11308,8 +11303,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
@@ -11340,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11697,7 +11690,26 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>CATATAN PENTING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Web original (cuaca.bmkg.go.id) TIDAK memakai API Open Data ini sama sekali — dia memakai API internal ISDP-nya sendiri (hasil scraping 159 request, 0 request ke api.bmkg.go.id/data.bmkg.go.id). Bentuk data mirip karena berasal dari sistem produksi yang sama. Pemakaian Open Data di project ini = keputusan redesign kita sendiri (jalur resmi tanpa proxy), bukan meniru original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:I15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/api/df/v1/forecast/coord</t>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/forecast/coord</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/api/df/v1/adm/coord</t>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/adm/coord</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/api/df/v1/amandemen/coord</t>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/amandemen/coord</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/api/presentwx/coord</t>
+          <t>https://cuaca.bmkg.go.id/api/presentwx/coord</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/api/public/weather/warning</t>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/warning</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/api/public/weather/warning/cyclone</t>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/warning/cyclone</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/api/public/weather/weekly-temperature</t>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/weekly-temperature</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/api/public/weather/video-latest</t>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/video-latest</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/api/public/banners</t>
+          <t>https://cuaca.bmkg.go.id/api/public/banners</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/setting/find-code</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/setting/find-code</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/sunset/json</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/sunset/json</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/tcwc/cyclone/all</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/tcwc/cyclone/all</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/public/maritim/nearest-location</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/maritim/route</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/maritim/route</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/maritim/water-area/water_area_point.geojson</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/maritim/water-area/water_area_point.geojson</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/sus/modelrun</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/sus/modelrun</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/api/signature/impact/public/list/&lt;YYYY-MM-DDT00:00:00Z&gt;</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/api/signature/impact/public/list/&lt;YYYY-MM-DDT00:00:00Z&gt;</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/maps/{general,warning,maritim,aviation,tourism}/metadata/tiles</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/tourism/tiles/data/tourism.json</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/tourism/tiles/data/tourism.json</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/sus/tiles/data/suspoi.json</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/sus/tiles/data/suspoi.json</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/spartan/pollution/{pol}/{lvl}/{t0}/{t1}/{z}/{x}/{y}.png</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/spartan/pollution/{pol}/{lvl}/{t0}/{t1}/{z}/{x}/{y}.png</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/user/subscribe-type</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/user/subscribe-type</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/api/v1/developer/{login,register,token-management,token-management/services}</t>
+          <t>https://cuaca.bmkg.go.id/api/v1/developer/{login,register,token-management,token-management/services}</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>spartan.bmkg.go.id/map/modelrun</t>
+          <t>https://spartan.bmkg.go.id/map/modelrun</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>widis.bmkg.go.id/ndf/cgms/weather/forward</t>
+          <t>https://widis.bmkg.go.id/ndf/cgms/weather/forward</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>bmkg-sus.geo.id/windmap/ecmwf/1000</t>
+          <t>https://bmkg-sus.geo.id/windmap/ecmwf/1000</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>tiles.circlegeo.com/data/{indocg,administration}.json</t>
+          <t>https://tiles.circlegeo.com/data/{indocg,administration}.json</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>cuaca.bmkg.go.id/blog/wp-json/wp/v2/</t>
+          <t>https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>data.bmkg.go.id/DataMKG/TEWS/gempadirasakan.json</t>
+          <t>https://data.bmkg.go.id/DataMKG/TEWS/gempadirasakan.json</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>nominatim.openstreetmap.org (search/reverse)</t>
+          <t>https://nominatim.openstreetmap.org (search/reverse)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>overpass-api.de/api/interpreter</t>
+          <t>https://overpass-api.de/api/interpreter</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>router.project-osrm.org/route/v1/driving</t>
+          <t>https://router.project-osrm.org/route/v1/driving</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -11333,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Belum dipakai</t>
+          <t>404 saat dicek (11 Sep 2026) — dinyatakan ada di halaman open data, path belum aktif; gempaterkini.json ✅ 200</t>
         </is>
       </c>
     </row>
@@ -11690,6 +11690,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
         <is>
@@ -11704,8 +11705,241 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Maritim: Cuaca Perairan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/perairan/{file}</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>file dari perairan_list (232 wilayah)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4 slot: 12-12-24-24 jam</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>per rilis stasiun</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>weather, weather_desc (narasi), warning_desc (pd cuaca buruk), wave_cat/desc, wind_from/to/speed. Kode wilayah F.09 = sama dgn internal nearest-location → cocok card Pesisir &amp; Laut / Pelayaran / WaveRadarMap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Maritim: index+list</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/{perairan_list|pelabuhan_list}</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>232 perairan + 294 pelabuhan</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>per rilis</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Daftar file data; sample tersimpan di baseline/open-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Maritim: GeoJSON wilayah</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/static/wilayah_perairan.json</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>GeoJSON</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>polygon 232 wilayah + kode</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>725 KB — untuk overlay peta + lookup code</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Maritim: Overview gelombang</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/overview/gelombang.json</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>kategori gelombang per wilayah (today/tmr/h2/h3)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>per rilis</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ringkas utk badge peta</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Maritim: Cuaca Pelabuhan</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/pelabuhan/{file}</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>file dari pelabuhan_list (294 pelabuhan)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2 rilis terakhir</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>per rilis</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>arus (current_*), visibility, rh, temp, PASUT low/high tide → card Pelayaran/Pelabuhan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A13:I15"/>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Mapping" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temuan API Resmi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Mapping'!$A$1:$L$33</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +97,25 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -158,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -236,6 +256,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2612,6 +2639,719 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>TEMUAN SCRAPPING API RESMI BMKG — 11 Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>Sumber: daftar API resmi dari partner BMKG (Maritim/Cuaca/Cuaca Ekstrem; Penerbangan &amp; DWT menyusul) + halaman data.bmkg.go.id. Sample asli tersimpan: scrapping_cuaca-bmkg-go-id/baseline/open-data/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Layanan</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Endpoint (full URL)</t>
+        </is>
+      </c>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>Params</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="inlineStr">
+        <is>
+          <t>Field utama respons</t>
+        </is>
+      </c>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>Contoh value (dari sample ASLI)</t>
+        </is>
+      </c>
+      <c r="G4" s="41" t="inlineStr">
+        <is>
+          <t>Pemakaian di redesign</t>
+        </is>
+      </c>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>CORS/Akses</t>
+        </is>
+      </c>
+      <c r="I4" s="41" t="inlineStr">
+        <is>
+          <t>Sample file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>A. PRAKIRAAN CUACA (api.bmkg.go.id) — resmi, 3 hari per 3 jam</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="43" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca per desa</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://api.bmkg.go.id/publik/prakiraan-cuaca?adm4=31.71.03.1001</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>adm4 (kode Kemendagri tkt IV)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>t, hu, weather_desc, weather_desc_en, ws, wd, wd_deg, tcc, tp, vs_text, image</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>t=29°C, hu=70%, weather_desc="Cerah", ws=8.6 km/h, wd="SE", tcc=36%, tp=0.1mm</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard (3-harian hourly) — jalur DIRECT pengganti proxy</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>CORS * → DIRECT, 60 req/menit/IP</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>prakiraan-cuaca_adm4-31.71.03.1001.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="42" t="inlineStr">
+        <is>
+          <t>B. MARITIM (maritim.bmkg.go.id/public_api) — resmi, dari daftar partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>Cuaca Perairan (232 wilayah)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/perairan/{file}  (list: /public_api/perairan_list)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>file (contoh F.09_Teluk Jakarta.json)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>weather, weather_desc (narasi), warning_desc, wave_cat, wave_desc, wind_from/to, wind_speed_min/max, area_remark</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>weather="Cerah Berawan", warning_desc="Waspada Angin Kencang", wave_cat="Rendah", wave_desc="0.5-1.25 m", wind 5-14 knot; 4 slot 12-12-24-24 jam</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Card Aktivitas Pesisir &amp; Laut, Pelayaran, WaveRadarMap</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>maritim_perairan_F.09_Teluk-Jakarta.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>Cuaca Pelabuhan (294 pelabuhan)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan/{file}  (list: /public_api/pelabuhan_list)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>file (contoh 0088_Sintete.json)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>semua field perairan + current_from/to, current_speed, visibility, rh_min/max, temp_min/max, low/high_tide + jam</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>visibility=2111, rh 89-100%, temp 25°C, current 0.06-0.33 cm/s, low_tide=-0.79 (15:00 UTC), high_tide=0.65 (21:00 UTC)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Card Pelayaran/Pelabuhan + info pasut</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>maritim_pelabuhan_0088_Sintete.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>Peta wilayah perairan</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/static/wilayah_perairan.json</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>GeoJSON FeatureCollection polygon 232 wilayah + kode</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>type=Polygon, koordinat teluk/ laut (725 KB)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Overlay peta + lookup kode wilayah</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>maritim_wilayah_perairan.geojson</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>Overview gelombang</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/overview/gelombang.json</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>per kode wilayah: issued, today, tomorrow, h2, h3</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>F.09: today="Rendah", tomorrow="Rendah" | U.04: "Tinggi" (11 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Badge status gelombang di peta/list</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>maritim_overview_gelombang.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>C. GEMPABUMI (data.bmkg.go.id/DataMKG/TEWS) — resmi, sudah dipakai redesign</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>Gempa terbaru M5.0+</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://data.bmkg.go.id/DataMKG/TEWS/autogempa.json</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tanggal, Jam, DateTime, Coordinates, Lintang, Bujur, Magnitude, Kedalaman, Wilayah, Potensi</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Magnitude=2.7, Kedalaman=4 km, Wilayah="...6 km barat laut Kab. Bener Meriah" (11 Sep 2026 13:00 WIB)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>EarthquakeActivity ✅ (sudah dipakai)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>gempa_autogempa.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Gempa M5.0+ terkini (15)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://data.bmkg.go.id/DataMKG/TEWS/gempaterkini.json</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>array gempa: field sama dengan autogempa</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Magnitude=5.2, "46 km Tenggara MALUKUBRTDAYA" (10 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>EarthquakeHistory ✅</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>gempa_gempaterkini.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Gempa Dirasakan</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://data.bmkg.go.id/DataMKG/TEWS/gempadirasakan.json</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>gempa + data dirasakan</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>(4.5 KB sample, beberapa peristiwa)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>EarthquakeHistory ✅</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>gempa_gempadirasakan.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Gempa Potensi Tsunami</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://data.bmkg.go.id/DataMKG/TEWS/tsunamiterkini.json</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>404 saat dicek (11 Sep 2026) — disebut di halaman open data tapi path belum aktif</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>(404)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>D. CUACA EKSTREM / PERINGATAN DINI (data.bmkg.go.id/peringatan-dini-cuaca) — resmi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>Nowcast RSS (per provinsi)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/alerts/nowcast/id</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>RSS: title, link (CAP), description, pubDate</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3 item: "Hujan Lebat disertai Petir di Sumatera Barat / Sulawesi Tengah / Aceh"</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Kandidat pengganti warning internal (butuh adapter RSS)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT (perlu cek CORS)</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>nowcast_rss.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>Nowcast CAP detail</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/alerts/nowcast/id/{kode_detail_cap}_alert.xml</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>kode_detail_cap dari RSS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>CAP 1.2: event, severity, certainty, expires, description (kecamatan terdampak), areaDesc</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>event="Hujan Lebat dan Petir", severity=Moderate, kecamatan: Bungus Teluk Kabung, Koto Xi Tarusan, Padang Selatan, Siberut Barat Daya</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Alert detail s/d kecamatan</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT (perlu cek CORS)</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>nowcast_cap_sumbab.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>E. MENYUSUL (dari daftar partner — belum tersedia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>API Penerbangan</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>menyusul</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Card Aktivitas Penerbangan</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>menunggu partner</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>API DWT (Digital Weather for Traffic)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>menyusul</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Card Weather for Traffic / TransportWeather</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>menunggu partner</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A20:I20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2761,7 +3501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11107,7 +11847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11327,7 +12067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11690,7 +12430,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
         <is>
@@ -11705,100 +12444,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Maritim: Cuaca Perairan</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GET https://maritim.bmkg.go.id/public_api/perairan/{file}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>file dari perairan_list (232 wilayah)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4 slot: 12-12-24-24 jam</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>per rilis stasiun</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>weather, weather_desc (narasi), warning_desc (pd cuaca buruk), wave_cat/desc, wind_from/to/speed. Kode wilayah F.09 = sama dgn internal nearest-location → cocok card Pesisir &amp; Laut / Pelayaran / WaveRadarMap</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Maritim: index+list</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>GET https://maritim.bmkg.go.id/public_api/{perairan_list|pelabuhan_list}</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>232 perairan + 294 pelabuhan</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>per rilis</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>DIRECT</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Daftar file data; sample tersimpan di baseline/open-data/</t>
-        </is>
-      </c>
-    </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,6 +116,11 @@
       <color rgb="001F4E79"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -178,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -263,6 +268,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2654,7 +2663,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>TEMUAN SCRAPPING API RESMI BMKG — 11 Sep 2026</t>
         </is>
@@ -2668,7 +2677,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,8 +121,52 @@
       <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF006100"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF7F6000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF9C6500"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -169,6 +213,46 @@
         <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -183,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -272,6 +356,49 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -655,62 +782,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="46" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="46" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="46" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="46" t="inlineStr">
         <is>
           <t>Params</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="46" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="46" t="inlineStr">
         <is>
           <t>Akses (dev)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="46" t="inlineStr">
         <is>
           <t>Dipakai di Original (baseline)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="46" t="inlineStr">
         <is>
           <t>Komponen Redesign</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="46" t="inlineStr">
         <is>
           <t>Status Redesign</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="46" t="inlineStr">
         <is>
           <t>Sumber Pengganti (Redesign)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="46" t="inlineStr">
         <is>
           <t>Catatan / Response Shape</t>
         </is>
@@ -745,7 +872,7 @@
           <t>Referer+Origin</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -760,7 +887,7 @@
           <t>CurrentWeather.vue, ForecastPanel.vue, ForecastTemperatureChart.vue, ForecastPrecipitationChart.vue, ForecastAirQualityChart.vue</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="J2" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -805,7 +932,7 @@
           <t>Referer+Origin</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -820,7 +947,7 @@
           <t>App.vue (geolocation handler)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -865,7 +992,7 @@
           <t>Referer+Origin</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -880,7 +1007,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>SEBAGIAN</t>
         </is>
@@ -925,7 +1052,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -940,7 +1067,7 @@
           <t>CurrentWeather.vue</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -985,7 +1112,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1000,7 +1127,7 @@
           <t>AlertsPanel.vue</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -1045,7 +1172,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1060,7 +1187,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -1105,7 +1232,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1120,7 +1247,7 @@
           <t>ForecastTemperatureChart.vue</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -1165,7 +1292,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1180,7 +1307,7 @@
           <t>NewsSection.vue</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -1225,7 +1352,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1240,7 +1367,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -1285,7 +1412,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1300,7 +1427,7 @@
           <t>src/data/cityThemes.ts</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="J11" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1345,7 +1472,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1360,7 +1487,7 @@
           <t>CurrentWeather.vue (sunrise/sunset untuk day/night)</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -1405,7 +1532,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1420,7 +1547,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -1465,7 +1592,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -1480,7 +1607,7 @@
           <t>WaveRadarMap.vue / MaritimeAdvisorDrawer.vue</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="49" t="inlineStr">
         <is>
           <t>SEBAGIAN</t>
         </is>
@@ -1525,7 +1652,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1540,7 +1667,7 @@
           <t>TransportWeather.vue</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1585,7 +1712,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1600,7 +1727,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -1645,7 +1772,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1660,7 +1787,7 @@
           <t>SatelliteMap.vue</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="J17" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1705,7 +1832,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1720,7 +1847,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -1765,7 +1892,7 @@
           <t>campuran</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1780,7 +1907,7 @@
           <t>SatelliteMap.vue, WaveRadarMap.vue</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="J19" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1825,7 +1952,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1840,7 +1967,7 @@
           <t>LandBasedActivities.vue</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1885,7 +2012,7 @@
           <t>X-API-KEY</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1900,7 +2027,7 @@
           <t>LandBasedActivities.vue</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
+      <c r="J21" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -1945,7 +2072,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -1960,7 +2087,7 @@
           <t>ForecastAirQualityChart.vue</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -2005,7 +2132,7 @@
           <t>x-public-token</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -2020,7 +2147,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -2065,7 +2192,7 @@
           <t>Akun dev</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2080,7 +2207,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -2125,7 +2252,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2140,7 +2267,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J25" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -2185,7 +2312,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2200,7 +2327,7 @@
           <t>SatelliteMap.vue</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J26" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -2245,7 +2372,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2260,7 +2387,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J27" s="51" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -2305,7 +2432,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2320,7 +2447,7 @@
           <t>SatelliteMap.vue</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr">
+      <c r="J28" s="52" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -2365,7 +2492,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="47" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -2380,7 +2507,7 @@
           <t>NewsSection.vue</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J29" s="48" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -2425,7 +2552,7 @@
           <t>Terbuka</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2440,7 +2567,7 @@
           <t>EarthquakeActivity.vue, EarthquakeHistory.vue</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J30" s="53" t="inlineStr">
         <is>
           <t>REDESIGN-ONLY</t>
         </is>
@@ -2485,7 +2612,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2500,7 +2627,7 @@
           <t>App.vue, LandBasedActivities.vue</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J31" s="53" t="inlineStr">
         <is>
           <t>REDESIGN-ONLY</t>
         </is>
@@ -2545,7 +2672,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2560,7 +2687,7 @@
           <t>LandBasedActivities.vue</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J32" s="53" t="inlineStr">
         <is>
           <t>REDESIGN-ONLY</t>
         </is>
@@ -2605,7 +2732,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="50" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -2620,7 +2747,7 @@
           <t>TransportWeather.vue</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J33" s="53" t="inlineStr">
         <is>
           <t>REDESIGN-ONLY</t>
         </is>
@@ -2663,7 +2790,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="45" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>TEMUAN SCRAPPING API RESMI BMKG — 11 Sep 2026</t>
         </is>
@@ -2676,55 +2803,56 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Layanan</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>Endpoint (full URL)</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Params</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Field utama respons</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="56" t="inlineStr">
         <is>
           <t>Contoh value (dari sample ASLI)</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="56" t="inlineStr">
         <is>
           <t>Pemakaian di redesign</t>
         </is>
       </c>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr">
         <is>
           <t>CORS/Akses</t>
         </is>
       </c>
-      <c r="I4" s="41" t="inlineStr">
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Sample file</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="57" t="inlineStr">
         <is>
           <t>A. PRAKIRAAN CUACA (api.bmkg.go.id) — resmi, 3 hari per 3 jam</t>
         </is>
@@ -2776,7 +2904,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="57" t="inlineStr">
         <is>
           <t>B. MARITIM (maritim.bmkg.go.id/public_api) — resmi, dari daftar partner</t>
         </is>
@@ -2963,7 +3091,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="inlineStr">
+      <c r="A12" s="57" t="inlineStr">
         <is>
           <t>C. GEMPABUMI (data.bmkg.go.id/DataMKG/TEWS) — resmi, sudah dipakai redesign</t>
         </is>
@@ -3150,7 +3278,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="57" t="inlineStr">
         <is>
           <t>D. CUACA EKSTREM / PERINGATAN DINI (data.bmkg.go.id/peringatan-dini-cuaca) — resmi</t>
         </is>
@@ -3247,7 +3375,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="inlineStr">
+      <c r="A20" s="57" t="inlineStr">
         <is>
           <t>E. MENYUSUL (dari daftar partner — belum tersedia)</t>
         </is>
@@ -3376,6 +3504,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3399,7 +3528,7 @@
       <c r="C4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="58" t="inlineStr">
         <is>
           <t>TERIMPLEMENTASI</t>
         </is>
@@ -3414,7 +3543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="59" t="inlineStr">
         <is>
           <t>SEBAGIAN</t>
         </is>
@@ -3429,7 +3558,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>BELUM</t>
         </is>
@@ -3444,7 +3573,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="61" t="inlineStr">
         <is>
           <t>BEDA-SUMBER</t>
         </is>
@@ -3459,7 +3588,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="62" t="inlineStr">
         <is>
           <t>REDESIGN-ONLY</t>
         </is>
@@ -3488,7 +3617,7 @@
       <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="63" t="inlineStr">
         <is>
           <t>Endpoint original terimplementasi identik (pakai API yang sama)</t>
         </is>
@@ -3498,6 +3627,7 @@
       </c>
       <c r="C12" s="2" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
@@ -3546,22 +3676,22 @@
         </is>
       </c>
       <c r="F1" s="23" t="n"/>
-      <c r="G1" s="24" t="inlineStr">
+      <c r="G1" s="64" t="inlineStr">
         <is>
           <t>API READY</t>
         </is>
       </c>
-      <c r="H1" s="24" t="inlineStr">
+      <c r="H1" s="64" t="inlineStr">
         <is>
           <t>Endpoint BMKG (path)</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="I1" s="64" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
       </c>
-      <c r="J1" s="24" t="inlineStr">
+      <c r="J1" s="64" t="inlineStr">
         <is>
           <t>Akses di Dev</t>
         </is>
@@ -3627,7 +3757,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G4" s="28" t="inlineStr">
+      <c r="G4" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -3642,7 +3772,7 @@
           <t>GPS → alamat admin; sudah dipakai redesign</t>
         </is>
       </c>
-      <c r="J4" s="30" t="inlineStr">
+      <c r="J4" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -3670,7 +3800,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -3685,7 +3815,7 @@
           <t>field lokasi.timezone (deteksi WIB/WITA/WIT)</t>
         </is>
       </c>
-      <c r="J5" s="30" t="inlineStr">
+      <c r="J5" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -3709,7 +3839,7 @@
         </is>
       </c>
       <c r="F6" s="23" t="n"/>
-      <c r="G6" s="28" t="inlineStr">
+      <c r="G6" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -3724,7 +3854,7 @@
           <t>observasi aktual kartu kondisi saat ini</t>
         </is>
       </c>
-      <c r="J6" s="31" t="inlineStr">
+      <c r="J6" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -3745,7 +3875,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G7" s="32" t="inlineStr">
+      <c r="G7" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -3788,7 +3918,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G8" s="32" t="inlineStr">
+      <c r="G8" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -3831,7 +3961,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -3846,7 +3976,7 @@
           <t>per koordinat kota</t>
         </is>
       </c>
-      <c r="J9" s="30" t="inlineStr">
+      <c r="J9" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -3874,7 +4004,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G10" s="34" t="inlineStr">
+      <c r="G10" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3917,7 +4047,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G11" s="34" t="inlineStr">
+      <c r="G11" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3932,7 +4062,7 @@
           <t>Tidak ada JSON AQI — hanya tile polusi untuk peta</t>
         </is>
       </c>
-      <c r="J11" s="31" t="inlineStr">
+      <c r="J11" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -3956,7 +4086,7 @@
         </is>
       </c>
       <c r="F12" s="23" t="n"/>
-      <c r="G12" s="28" t="inlineStr">
+      <c r="G12" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -3971,7 +4101,7 @@
           <t>sumber parameter: t, ws, wd, hu</t>
         </is>
       </c>
-      <c r="J12" s="31" t="inlineStr">
+      <c r="J12" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -3992,7 +4122,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G13" s="28" t="inlineStr">
+      <c r="G13" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4007,7 +4137,7 @@
           <t>field t (°C)</t>
         </is>
       </c>
-      <c r="J13" s="31" t="inlineStr">
+      <c r="J13" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4028,7 +4158,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G14" s="28" t="inlineStr">
+      <c r="G14" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4043,7 +4173,7 @@
           <t>field ws (km/h)</t>
         </is>
       </c>
-      <c r="J14" s="31" t="inlineStr">
+      <c r="J14" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4064,7 +4194,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
+      <c r="G15" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4079,7 +4209,7 @@
           <t>field wd / wd_deg</t>
         </is>
       </c>
-      <c r="J15" s="31" t="inlineStr">
+      <c r="J15" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4100,7 +4230,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G16" s="28" t="inlineStr">
+      <c r="G16" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4115,7 +4245,7 @@
           <t>field hu (%)</t>
         </is>
       </c>
-      <c r="J16" s="31" t="inlineStr">
+      <c r="J16" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4143,7 +4273,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G17" s="32" t="inlineStr">
+      <c r="G17" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -4182,7 +4312,7 @@
         </is>
       </c>
       <c r="F18" s="23" t="n"/>
-      <c r="G18" s="28" t="inlineStr">
+      <c r="G18" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4197,7 +4327,7 @@
           <t>data[0].cuaca[0] = grup hourly</t>
         </is>
       </c>
-      <c r="J18" s="30" t="inlineStr">
+      <c r="J18" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4218,7 +4348,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4233,7 +4363,7 @@
           <t>field t per jam</t>
         </is>
       </c>
-      <c r="J19" s="30" t="inlineStr">
+      <c r="J19" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4254,7 +4384,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G20" s="28" t="inlineStr">
+      <c r="G20" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4269,7 +4399,7 @@
           <t>field tp (mm) per jam</t>
         </is>
       </c>
-      <c r="J20" s="30" t="inlineStr">
+      <c r="J20" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4290,7 +4420,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G21" s="28" t="inlineStr">
+      <c r="G21" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4305,7 +4435,7 @@
           <t>field ws per jam</t>
         </is>
       </c>
-      <c r="J21" s="30" t="inlineStr">
+      <c r="J21" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4326,7 +4456,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G22" s="28" t="inlineStr">
+      <c r="G22" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4341,7 +4471,7 @@
           <t>field hu per jam</t>
         </is>
       </c>
-      <c r="J22" s="30" t="inlineStr">
+      <c r="J22" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4362,7 +4492,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G23" s="32" t="inlineStr">
+      <c r="G23" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -4401,7 +4531,7 @@
         </is>
       </c>
       <c r="F24" s="23" t="n"/>
-      <c r="G24" s="34" t="inlineStr">
+      <c r="G24" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4437,7 +4567,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G25" s="32" t="inlineStr">
+      <c r="G25" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -4473,7 +4603,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G26" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4488,7 +4618,7 @@
           <t>wilayah laut terdekat (code, name, wilpel, polygon)</t>
         </is>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="J26" s="66" t="inlineStr">
         <is>
           <t>PROXY</t>
         </is>
@@ -4509,7 +4639,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G27" s="28" t="inlineStr">
+      <c r="G27" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4524,7 +4654,7 @@
           <t>rute pelayaran + titik area laut</t>
         </is>
       </c>
-      <c r="J27" s="31" t="inlineStr">
+      <c r="J27" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4545,7 +4675,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G28" s="28" t="inlineStr">
+      <c r="G28" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4560,7 +4690,7 @@
           <t>layer peta penerbangan + katalog run model</t>
         </is>
       </c>
-      <c r="J28" s="31" t="inlineStr">
+      <c r="J28" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4584,7 +4714,7 @@
         </is>
       </c>
       <c r="F29" s="23" t="n"/>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G29" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4599,7 +4729,7 @@
           <t>perlu reverse-engineering param; alternatif statis: inderaja HIMA</t>
         </is>
       </c>
-      <c r="J29" s="31" t="inlineStr">
+      <c r="J29" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4620,7 +4750,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G30" s="34" t="inlineStr">
+      <c r="G30" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4635,7 +4765,7 @@
           <t>belum ada endpoint JSON terdokumentasi</t>
         </is>
       </c>
-      <c r="J30" s="31" t="inlineStr">
+      <c r="J30" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4656,7 +4786,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G31" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4671,7 +4801,7 @@
           <t>citra awan via HIMA/widis</t>
         </is>
       </c>
-      <c r="J31" s="31" t="inlineStr">
+      <c r="J31" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4692,7 +4822,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G32" s="69" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4707,7 +4837,7 @@
           <t>tile curah hujan satelit</t>
         </is>
       </c>
-      <c r="J32" s="31" t="inlineStr">
+      <c r="J32" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4728,7 +4858,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G33" s="28" t="inlineStr">
+      <c r="G33" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4743,7 +4873,7 @@
           <t>wind tiles ECMWF</t>
         </is>
       </c>
-      <c r="J33" s="31" t="inlineStr">
+      <c r="J33" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4771,7 +4901,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G34" s="28" t="inlineStr">
+      <c r="G34" s="65" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -4786,7 +4916,7 @@
           <t>metadata layer peta (sources, layers, overlays)</t>
         </is>
       </c>
-      <c r="J34" s="31" t="inlineStr">
+      <c r="J34" s="67" t="inlineStr">
         <is>
           <t>DIRECT</t>
         </is>
@@ -4814,7 +4944,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr">
+      <c r="G35" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -4857,7 +4987,7 @@
           <t>NOT YET</t>
         </is>
       </c>
-      <c r="G36" s="32" t="inlineStr">
+      <c r="G36" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -4892,7 +5022,7 @@
         </is>
       </c>
       <c r="F37" s="23" t="n"/>
-      <c r="G37" s="32" t="inlineStr">
+      <c r="G37" s="68" t="inlineStr">
         <is>
           <t>NO API</t>
         </is>
@@ -11862,12 +11992,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.88" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
@@ -11916,6 +12048,9 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
@@ -11940,6 +12075,9 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
@@ -12002,6 +12140,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="22" t="inlineStr">
         <is>
@@ -12033,6 +12172,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
@@ -12052,6 +12192,8 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
@@ -12110,48 +12252,49 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>Layanan</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="70" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="70" t="inlineStr">
         <is>
           <t>Params</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="70" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="70" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="F4" s="70" t="inlineStr">
         <is>
           <t>Update</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="G4" s="70" t="inlineStr">
         <is>
           <t>Limit</t>
         </is>
       </c>
-      <c r="H4" s="37" t="inlineStr">
+      <c r="H4" s="70" t="inlineStr">
         <is>
           <t>CORS</t>
         </is>
       </c>
-      <c r="I4" s="37" t="inlineStr">
+      <c r="I4" s="70" t="inlineStr">
         <is>
           <t>Keterangan</t>
         </is>
@@ -12439,6 +12582,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="38" t="inlineStr">
         <is>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -8,10 +8,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temuan API Resmi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Content Card" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Mapping'!$A$1:$L$33</definedName>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="39">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -312,8 +313,31 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="48">
     <fill>
       <patternFill/>
     </fill>
@@ -563,6 +587,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -820,7 +869,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -903,6 +952,25 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="42" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4221,6 +4289,839 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>AUDIT CONTENT WEB REDESIGN → SUMBER API (11 Sep 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>Pertanyaan audit: konten mana di web redesign yang bisa di-update valuenya dari hit API (knowledge base: internal BMKG + Open Data resmi + Maritim + DWT)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>Status: ✅ LIVE = sudah terpasang  |  🔄 READY = API sudah kita pegang, tinggal pasang adapter  |  ⚠️ PARTIAL = separuh data/needs narasi  |  ⏳ TUNGGU = menunggu API partner / tidak ada</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>Card / Komponen</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="inlineStr">
+        <is>
+          <t>Konten (value yang tampil di UI)</t>
+        </is>
+      </c>
+      <c r="D5" s="47" t="inlineStr">
+        <is>
+          <t>Sumber sekarang</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="inlineStr">
+        <is>
+          <t>API dari knowledge base yang bisa supply</t>
+        </is>
+      </c>
+      <c r="F5" s="47" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>─ KOLOM HERO &amp; FORECAST ─</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="43" t="inlineStr">
+        <is>
+          <t>HeroWeatherCard</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Suhu, kondisi, hujan, angin, kelembapan, peluang hujan</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>liveHourly (useBmkgWeather) — fallback mock</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord</t>
+        </is>
+      </c>
+      <c r="F7" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>HeroWeatherCard</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Chart jam-an mini di hero</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>liveHourly</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord (7 hari)</t>
+        </is>
+      </c>
+      <c r="F8" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>CurrentWeather</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Card cuaca besar per kota terpilih</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>liveWeather</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord + adm/coord (geolokasi)</t>
+        </is>
+      </c>
+      <c r="F9" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="43" t="inlineStr">
+        <is>
+          <t>ForecastPanel</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Prakiraan 7 hari (panel forecast)</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>liveHourly</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Opsi pengurang beban proxy: official api.bmkg.go.id/publik/prakiraan-cuaca?adm4 (3 hari, DIRECT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
+        <is>
+          <t>AlertsPanel</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Banner peringatan cuaca</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>liveAlerts (warning + cyclone internal)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>internal /api/public/weather/warning(+cyclone)</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Upgrade resmi: nowcast RSS/CAP (produk beda: 3-jam per kecamatan; item bisa stale)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>MajorCitiesCarousel</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kondisi terkini antar kota (carousel)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>liveWeather per kota</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>NewsSection</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Berita &amp; pengumuman</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>liveNews (WP BMKG) — fallback mock</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>blog WP BMKG (502 flaky)</t>
+        </is>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Upstream sering 502 — fallback mock jalan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>EarthquakeActivity + History</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Gempa terbaru, dirasakan, riwayat</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>live TEWS</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>data.bmkg.go.id TEWS (autogempa/gempaterkini/gempadirasakan)</t>
+        </is>
+      </c>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>SatelliteMap</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Citra satelit Himawari-9</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>live internal</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>internal citra satelit</t>
+        </is>
+      </c>
+      <c r="F15" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>ComfortIndexCard</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Indeks kenyamanan</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>dihitung dari liveWeather</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>internal df/forecast/coord</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>─ KARTU AKTIVITAS (kolom 2) &amp; TRANSPORT ─</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>TransportWeather — Jalan Raya</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Status Aman/Waspada/Awas + narasi</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>MOCK transportStatusesMap</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>DWT apiDF_Darat: kode_cuaca, hujan, angin per kecamatan per jam UTC</t>
+        </is>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Mapping: kode_cuaca 0-1→Aman, 3-7→Waspada, &gt;=10/AWS→Awas + narasi template</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>TransportWeather — Penerbangan</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Status bandara/sector udara</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>API Penerbangan = menyusul (partner); sementara: tcc/vis dari df forecast</t>
+        </is>
+      </c>
+      <c r="F19" s="51" t="inlineStr">
+        <is>
+          <t>⏳ TUNGGU</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Partial jangka pendek pakai tcc dari forecast internal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>TransportWeather — Maritim</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Status pelayaran + gelombang</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>maritim public_api: perairan wave_cat/warning_desc; pelabuhan (pasut, arus)</t>
+        </is>
+      </c>
+      <c r="F20" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Kode wilayah dari nearest-location internal sudah cocok (contoh F.09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>TransportWeather — Kereta (slot baru)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Status jalur KAI</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>belum ada slot (kandidat tambahan)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>DWT apiDF_Kereta: 178 stasiun per jam UTC</t>
+        </is>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Perlu slot UI baru kalau mau tampil</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>LandBasedActivities</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Cuaca per titik rute (aktivitas darat)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>MOCK hourlyForecastsMap (dipaksa match kota regional)</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>DWT apiDF_Darat: lat/lon kecamatan → match titik rute terdekat</t>
+        </is>
+      </c>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Rute &amp; POI tetap Overpass OSM (bukan BMKG)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>AroundActivityPanel</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Narasi analisis "Aktivitas Sekitar"</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>MOCK cityAnalysisMap (narasi fiktif per kota)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>bisa disusun generator: df forecast + DWT darat + maritim</t>
+        </is>
+      </c>
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>⚠️ PARTIAL</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Data ada semua, tapi perlu builder narasi; atau satukan konten faktual (suhu/hujan/angin) tanpa narasi fiktif</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>AirQualityCard</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>AQI, PM2.5, PM10, O3, NO2</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>PSEUDO: pm25 = f(temp)+seed — nilai fiktif</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>TIDAK ADA di knowledge base / daftar partner</t>
+        </is>
+      </c>
+      <c r="F24" s="51" t="inlineStr">
+        <is>
+          <t>⏳ TUNGGU</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Risiko etika UI: tampilan seperti data nyata padahal pseudo. Cari API ISPU BMKG (kualitas udara) terpisah atau tandai "ilustrasi"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>WaveRadarMap</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Radar tinggi gelombang</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>MOCK (label "BMKG WaveWatch III")</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>maritim overview gelombang + perairan wave_cat/wave_desc</t>
+        </is>
+      </c>
+      <c r="F25" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>WindMap + WeatherRadarMap</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Vektor angin, isobar, temperatur</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SYNTHETIC generateIndonesiaGfsWindGrid (grid prosedural)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>internal presentwx (family di baseline) / DWT angin per kecamatan</t>
+        </is>
+      </c>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>⚠️ PARTIAL</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Grid GFS asli tidak di knowledge base; DWT angin bisa jadi pengganti skala kecamatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>MaritimeAdvisorDrawer</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Sektor maritim: risiko, status cuaca, SOP, kontak</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>maritimeAdvisorData (static)</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>maritim perairan per wilayah (warning_desc, wave_cat)</t>
+        </is>
+      </c>
+      <c r="F27" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>SOP checklist &amp; kontak memang by-design static</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>AviationAdvisorDrawer</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Sektor udara: pra-terbang, SOP, kontak</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>aviationAdvisorData (static)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>API Penerbangan menyusul; sementara df forecast tcc</t>
+        </is>
+      </c>
+      <c r="F28" s="51" t="inlineStr">
+        <is>
+          <t>⏳ TUNGGU</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>MarineMap</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Peta maritim Indonesia</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>static indonesiaMapData + earthquakeData</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>maritim wilayah_perairan.geojson (polygon 232 wilayah)</t>
+        </is>
+      </c>
+      <c r="F29" s="50" t="inlineStr">
+        <is>
+          <t>🔄 READY (opsional)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Layer polygon resmi per wilayah + kode</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A17:G17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
@@ -4370,7 +5271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12715,7 +13616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12935,7 +13836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -337,7 +337,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill/>
     </fill>
@@ -614,6 +614,11 @@
         <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -869,7 +874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -971,6 +976,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4929,14 +4937,14 @@
           <t>TIDAK ADA di knowledge base / daftar partner</t>
         </is>
       </c>
-      <c r="F24" s="51" t="inlineStr">
-        <is>
-          <t>⏳ TUNGGU</t>
+      <c r="F24" s="53" t="inlineStr">
+        <is>
+          <t>⏸️ PAUSED (keputusan: urus nanti)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Risiko etika UI: tampilan seperti data nyata padahal pseudo. Cari API ISPU BMKG (kualitas udara) terpisah atau tandai "ilustrasi"</t>
+          <t>Risiko etika UI: tampilan seperti data nyata padahal pseudo. Cari API ISPU BMKG (kualitas udara) terpisah atau tandai "ilustrasi" — ⏸️ PAUSED sementara oleh keputusan (nilai pseudo dibiarkan sementara)</t>
         </is>
       </c>
     </row>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -4762,14 +4762,14 @@
           <t>API Penerbangan = menyusul (partner); sementara: tcc/vis dari df forecast</t>
         </is>
       </c>
-      <c r="F19" s="51" t="inlineStr">
-        <is>
-          <t>⏳ TUNGGU</t>
+      <c r="F19" s="53" t="inlineStr">
+        <is>
+          <t>⏸️ PAUSED (menunggu kesepakatan partner)</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Partial jangka pendek pakai tcc dari forecast internal</t>
+          <t>Keputusan: di-pause, tunggu data dari partner; jangka pendek bisa derivasi tcc</t>
         </is>
       </c>
     </row>
@@ -4902,14 +4902,14 @@
           <t>bisa disusun generator: df forecast + DWT darat + maritim</t>
         </is>
       </c>
-      <c r="F23" s="52" t="inlineStr">
-        <is>
-          <t>⚠️ PARTIAL</t>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t>✅ NARASI DINAMIS TERPASANG</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Data ada semua, tapi perlu builder narasi; atau satukan konten faktual (suhu/hujan/angin) tanpa narasi fiktif</t>
+          <t>buildCityAnalysis (analysisNarrative.ts): fakta cuaca → narasi per kondisi; fallback map statis</t>
         </is>
       </c>
     </row>
@@ -5003,14 +5003,14 @@
           <t>internal presentwx (family di baseline) / DWT angin per kecamatan</t>
         </is>
       </c>
-      <c r="F26" s="52" t="inlineStr">
-        <is>
-          <t>⚠️ PARTIAL</t>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>🔄 REAL DATA DWT TERPASANG</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Grid GFS asli tidak di knowledge base; DWT angin bisa jadi pengganti skala kecamatan</t>
+          <t>initDwtWindStations(): 1234 kecamatan DWT → IDW 3-titik di getGfsWindVectorAt; fallback sintetis bila gagal</t>
         </is>
       </c>
     </row>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -4727,14 +4727,14 @@
           <t>DWT apiDF_Darat: kode_cuaca, hujan, angin per kecamatan per jam UTC</t>
         </is>
       </c>
-      <c r="F18" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (DWT kecamatan terdekat)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Mapping: kode_cuaca 0-1→Aman, 3-7→Waspada, &gt;=10/AWS→Awas + narasi template</t>
+          <t>openData.dwtWeatherAt → status dari kode_cuaca + narasi suhu/kelembapan; fallback mock</t>
         </is>
       </c>
     </row>
@@ -4797,14 +4797,14 @@
           <t>maritim public_api: perairan wave_cat/warning_desc; pelabuhan (pasut, arus)</t>
         </is>
       </c>
-      <c r="F20" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (maritim perairan resmi)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Kode wilayah dari nearest-location internal sudah cocok (contoh F.09)</t>
+          <t>nearest-location code → perairan wave_desc/warning_desc → status + narasi; pasut nanti via pelabuhan</t>
         </is>
       </c>
     </row>
@@ -4832,14 +4832,14 @@
           <t>DWT apiDF_Kereta: 178 stasiun per jam UTC</t>
         </is>
       </c>
-      <c r="F21" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (DWT kereta)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Perlu slot UI baru kalau mau tampil</t>
+          <t>dwtKeretaAt (178 stasiun, jarak maks 0.5°) → baris Rail baru; di luar Jawa otomatis disembunyikan</t>
         </is>
       </c>
     </row>
@@ -4867,14 +4867,14 @@
           <t>DWT apiDF_Darat: lat/lon kecamatan → match titik rute terdekat</t>
         </is>
       </c>
-      <c r="F22" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (df/forecast/coord per titik rute)</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Rute &amp; POI tetap Overpass OSM (bukan BMKG)</t>
+          <t>lokasi aktif → bmkg.forecast(lat,lng) internal → 7 hari per titik; fallback peta kota mock</t>
         </is>
       </c>
     </row>
@@ -4972,12 +4972,16 @@
           <t>maritim overview gelombang + perairan wave_cat/wave_desc</t>
         </is>
       </c>
-      <c r="F25" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (geojson + overview maritim)</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>232 centroid wilayah (geojson resmi) + wave_cat overview → zone peta; wind mode ilustratif</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -5038,14 +5042,14 @@
           <t>maritim perairan per wilayah (warning_desc, wave_cat)</t>
         </is>
       </c>
-      <c r="F27" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY</t>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (parameter gelombang resmi)</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>SOP checklist &amp; kontak memang by-design static</t>
+          <t>maritimLive di-inject: parameter Tinggi Gelombang + riskLevel + advisory utk shipping/fishery</t>
         </is>
       </c>
     </row>
@@ -5104,14 +5108,14 @@
           <t>maritim wilayah_perairan.geojson (polygon 232 wilayah)</t>
         </is>
       </c>
-      <c r="F29" s="50" t="inlineStr">
-        <is>
-          <t>🔄 READY (opsional)</t>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t>✅ TERPASANG (overlay wilayah perairan)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Layer polygon resmi per wilayah + kode</t>
+          <t>L.geoJSON wilayah_perairan (232 polygon, CORS *) + popup nama/kode di MarineMap</t>
         </is>
       </c>
     </row>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -1393,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1471,6 +1471,11 @@
           <t>Catatan / Response Shape</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Diperbarui 15 Sep 2026 (Tier A &amp; B): +7 endpoint terimplementasi.</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="68" customHeight="1">
       <c r="A2" s="3" t="n">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Respons: {data:{today:{...},tomorrow:{...}}}.</t>
+          <t>Respons: {data:{today:{...},tomorrow:{...}}}. Sejak 15 Sep dilengkapi/dikalahkan prioritasnya oleh RSS nowcast resmi (lihat baris Nowcast).</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2243,7 @@
       </c>
       <c r="J14" s="37" t="inlineStr">
         <is>
-          <t>SEBAGIAN</t>
+          <t>TERIMPLEMENTASI</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -2248,7 +2253,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Respons: {data:{code:'F.09', name:'Teluk Jakarta', wilpel, geometry:Polygon}}.</t>
+          <t>Respons: {data:{code,name,wilpel,geometry}}. Sejak 15 Sep dipakai untuk narasi Aktivitas Pelayaran &amp; patch drawer maritim. BUG lama: currentSlot() baca doc.slots → API kirim doc.data, jadi data live tidak pernah masuk UI.</t>
         </is>
       </c>
     </row>
@@ -3389,6 +3394,426 @@
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Routing transportasi darat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>F. Maritim Public API (maritim.bmkg.go.id)</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan_list</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G34" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Tidak ada (API resmi BMKG Maritim)</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>PortTideCard.vue</t>
+        </is>
+      </c>
+      <c r="J34" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>294 pelabuhan; field coor = [lat, lon]; ada file_date/type (utama/pendukung). Dipakai untuk cari pelabuhan terdekat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>F. Maritim Public API (maritim.bmkg.go.id)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan/{file}.json</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>file dari pelabuhan_list</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G35" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Tidak ada</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>PortTideCard.vue</t>
+        </is>
+      </c>
+      <c r="J35" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Bentuk: {port_id,name,latitude,longitude,type,data:[4 slot]}. Slot: cuaca, gelombang, temp_min/max, rh_min/max, visibility, wind_speed_min/max, current_speed_min/max, low/high_tide(_time). PASUT SERING null → UI sembunyikan blok. current_* belum dipakai (satuan ambigu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>F. Maritim Public API (maritim.bmkg.go.id)</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/perairan/{file}.json</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>file dari perairan_list</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G36" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Tidak ada</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>WeatherActivity.vue, MaritimeAdvisorDrawer.vue, MarineMap.vue</t>
+        </is>
+      </c>
+      <c r="J36" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Bentuk: {code,name,issued,info,data:[4 slot]} (Hari ini/Besok/H+2/H+3). Slot: wave_cat, wave_desc, wind_speed_min/max, weather_desc, warning_desc. Dipakai untuk narasi pelayaran + popup peta + patch drawer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>F. Maritim Public API (maritim.bmkg.go.id)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/overview/gelombang.json</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G37" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Tidak ada</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>MarineMap.vue</t>
+        </is>
+      </c>
+      <c r="J37" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>232 wilayah × today/tomorrow/h2/h3 → warna + hitungan legend peta maritim (live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>F. Maritim Public API (maritim.bmkg.go.id)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/static/wilayah_perairan.json</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G38" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Tidak ada</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>MarineMap.vue, WaveRadarMap.vue</t>
+        </is>
+      </c>
+      <c r="J38" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>232 polygon. Properti: WP_1 (kode, mis. U.04), WP_IMM (nama), WilPel. PENTING: path .geojson = 404 (dulu dipakai kode → overlay tidak pernah muncul). Join gelombang via WP_1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>G. Resmi (Open Data / Nowcast)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/alerts/nowcast/id</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G39" s="38" t="inlineStr">
+        <is>
+          <t>PROXY (/alerts)</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Produk resmi BMKG</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>useBmkgWeather.ts (peringatan), AlertsPanel.vue</t>
+        </is>
+      </c>
+      <c r="J39" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai langsung)</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>RSS peringatan dini NASIONAL. TIDAK ADA header CORS → wajib proxy (dev: vite.config NOWCAST_PROXY; prod: api/bmkg/[...path].ts). Difilter per provinsi. Severity diinferensi dari judul (CAP tidak diambil).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>G. Resmi (Open Data / Nowcast)</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>https://api.bmkg.go.id/publik/prakiraan-cuaca</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>adm4 (kode wilayah tkt IV)</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Terbuka</t>
+        </is>
+      </c>
+      <c r="G40" s="38" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Produk resmi BMKG</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>useBmkgWeather.ts (fallback)</t>
+        </is>
+      </c>
+      <c r="J40" s="41" t="inlineStr">
+        <is>
+          <t>TERIMPLEMENTASI</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>- (dipakai sebagai fallback)</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Bentuk item IDENTIK dengan df/v1/forecast/coord (data[0].cuaca = grup hari) → forecastToHourly() dipakai ulang. Dipakai hanya bila forecast internal kosong/gagal.</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4315,6 +4740,11 @@
           <t>AUDIT CONTENT WEB REDESIGN → SUMBER API (11 Sep 2026)</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AUDIT CONTENT WEB REDESIGN → SUMBER API  (diperbarui 15 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="45" t="inlineStr">
@@ -4326,10 +4756,11 @@
     <row r="3">
       <c r="A3" s="46" t="inlineStr">
         <is>
-          <t>Status: ✅ LIVE = sudah terpasang  |  🔄 READY = API sudah kita pegang, tinggal pasang adapter  |  ⚠️ PARTIAL = separuh data/needs narasi  |  ⏳ TUNGGU = menunggu API partner / tidak ada</t>
-        </is>
-      </c>
-    </row>
+          <t>Status: ✅ LIVE = data asli live  |  ⚠️ ESTIMASI = nilai sintetis (jujur di UI)  |  ️ TIDAK DIPASANG/PAUSED  |  🔄 sebagian</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="47" t="inlineStr">
         <is>
@@ -4548,25 +4979,29 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kondisi terkini antar kota (carousel)</t>
+          <t>Landmark + nama 10 kota besar (Aktif / Pilih Kota)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>liveWeather per kota</t>
+          <t>STATIS: src/data/cityLandmarks.ts (tidak ada fetch)</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>internal df/forecast/coord</t>
+          <t>(tidak memakai API) — bila nanti mau suhu live 10 kota: df/forecast/coord per kota = 10 request</t>
         </is>
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>✅ LIVE</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
+          <t>⏸️ STATIS (keputusan 16 Sep)</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Auto-geser 10 detik &amp; fetch cuaca per kota DINONAKTIFKAN dulu (permintaan produk). Kode timer sudah dihapus dari MajorCitiesCarousel.vue. Klaim lama "liveWeather per kota" tidak akurat — kartu ini memang tidak menampilkan suhu.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -4599,7 +5034,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Upstream sering 502 — fallback mock jalan</t>
+          <t>Data WP sudah lama ter-fetch tapi prop `articles` TIDAK dirender; komponen NewsSection baru dipasang 15 Sep. Upstream sering 502 → fallback mock.</t>
         </is>
       </c>
     </row>
@@ -4799,12 +5234,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>✅ LIVE (maritim perairan resmi)</t>
+          <t>✅ LIVE (fix bug 15 Sep)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>nearest-location code → perairan wave_desc/warning_desc → status + narasi; pasut nanti via pelabuhan</t>
+          <t>BUG: openData.currentSlot() membaca doc.slots padahal API mengirim doc.data → data live tidak pernah masuk UI (status tetap mock). Diperbaiki 15 Sep; kini pakai wave_cat/wave_desc/warning_desc perairan.</t>
         </is>
       </c>
     </row>
@@ -4909,7 +5344,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>buildCityAnalysis (analysisNarrative.ts): fakta cuaca → narasi per kondisi; fallback map statis</t>
+          <t>Narasi via buildCityAnalysis; sejak 15 Sep NILAI CUACA per titik POI (comfort/hujan/UV/jam-an) diambil live dari df/forecast/coord per lat-lng POI (daftar POI tetap kurasi desain).</t>
         </is>
       </c>
     </row>
@@ -4939,12 +5374,12 @@
       </c>
       <c r="F24" s="53" t="inlineStr">
         <is>
-          <t>⏸️ PAUSED (keputusan: urus nanti)</t>
+          <t>⏸️ PAUSED (komponen mati)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Risiko etika UI: tampilan seperti data nyata padahal pseudo. Cari API ISPU BMKG (kualitas udara) terpisah atau tandai "ilustrasi" — ⏸️ PAUSED sementara oleh keputusan (nilai pseudo dibiarkan sementara)</t>
+          <t>Komponen AirQualityCard tidak dipakai. Nilai pseudo yang sama tampil di WeatherActivity; badge-nya diubah "ISPU LIVE" → "ESTIMASI" (15 Sep) karena tidak ada sumber resmi.</t>
         </is>
       </c>
     </row>
@@ -4974,12 +5409,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>✅ LIVE (geojson + overview maritim)</t>
+          <t>⏸️ TIDAK DIPASANG (diperbaiki 15 Sep)</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>232 centroid wilayah (geojson resmi) + wave_cat overview → zone peta; wind mode ilustratif</t>
+          <t>Bug: properti geojson dibaca sebagai code/kode (benar WP_1/WP_IMM) + path .geojson 404 (benar /static/wilayah_perairan.json) → semua zona kosong. Kini benar &amp; siap; sengaja tidak dipasang agar tidak duplikat peta maritim.</t>
         </is>
       </c>
     </row>
@@ -5110,12 +5545,152 @@
       </c>
       <c r="F29" s="49" t="inlineStr">
         <is>
-          <t>✅ TERPASANG (overlay wilayah perairan)</t>
+          <t>✅ LIVE (gelombang per wilayah resmi)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>L.geoJSON wilayah_perairan (232 polygon, CORS *) + popup nama/kode di MarineMap</t>
+          <t>15 Sep: overlay diganti 232 polygon wilayah perairan RESMI; warna/label/legend dari overview/gelombang.json (live, 232 wilayah); klik wilayah → popup detail perairan resmi. Layer angin &amp; mode pelabuhan masih snapshot (tidak ada endpoint bulk).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>PortTideCard (KARTU BARU 15 Sep)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Pelabuhan terdekat: nama+kode, gelombang &amp; kategori, suhu min–max, kelembapan, angin, jarak pandang, pasang/surut</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>live pelabuhan public_api (terdekat dari koordinat kota)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>maritim public_api: pelabuhan_list + pelabuhan/{file}.json</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Jam pasut UTC dikonversi ke WIB/WITA/WIT (heuristik nama kota). Pasut null di sebagian pelabuhan → blok disembunyikan + catatan. Kolom arus di-skip (satuan ambigu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>WeatherActivity — badge kualitas udara</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Badge status card kualitas udara</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>pseudo: pm25 = f(suhu)+hash(nama kota)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>TIDAK ADA sumber resmi</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t>⚠️ ESTIMASI (badge jujur)</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Dulu berlabel "ISPU LIVE" + dot berdenyut (klaim palsu). Diubah 15 Sep menjadi "ESTIMASI" + dot amber tanpa animasi. Jangan kembalikan ke LIVE tanpa sumber resmi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>WeatherActivity — Aktivitas Pelayaran</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Narasi + tinggi gelombang perairan terdekat</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>maritimLive (public_api perairan)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>maritim public_api perairan/{file}.json</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t>✅ LIVE (15 Sep)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Sebelumnya estimasi 0.3 + angin×0.04 m. Kini wave_desc/wave_cat/warning_desc resmi (bergantung fix A1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Fallback forecast resmi</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Cuaca per jam/8 hari bila API internal gagal</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>api.bmkg.go.id/publik/prakiraan-cuaca?adm4=</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Open Data resmi (DIRECT)</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t>✅ TERPASANG (fallback)</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Bentuk item identik df/forecast/coord → adapter sama. Aktif hanya bila forecast internal kosong/gagal.</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5178,11 +5753,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Sudah memanggil API asli &amp; dipakai di UI (fallback mock saat gagal)</t>
+          <t>Sudah memanggil API asli &amp; dipakai di UI (10 Sep: 8) → +7 pada 15 Sep</t>
         </is>
       </c>
     </row>
@@ -5193,11 +5768,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Sudah ter-fetch dari API, tapi UI penuh/badge menyusul</t>
+          <t>Ter-fetch tapi UI belum penuh (sisa 1; maritim/nearest-location kini TERIMPLEMENTASI)</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5831,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="n"/>
     </row>
@@ -5267,14 +5842,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Audit awal 10 Sep mencatat 0 — sudah usang. Per 15 Sep, 9 endpoint original dipanggil identik (df forecast/adm, warning, sunset, amandemen, video, cyclone, maritim-nearest, blog WP).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Official Open Data: kandidat jalur RESMI — kurangi ketergantungan proxy/internal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Diperbarui 15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tier A &amp; B (lihat sheet Audit Content Card + docs/team-notes.md §6)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Maritim &amp; pelabuhan live, peta 232 wilayah, nowcast resmi, fallback Open Data, berita dirender, kartu Pelabuhan &amp; Pasut baru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>Masih mock/estimasi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kualitas udara/ISPU</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>TIDAK ADA SUMBER resmi (ispu.bmkg.go.id &amp; ispu.menlhk.go.id tidak merespons, api.bmkg.go.id/publik/ispu 404) → badge UI diubah "LIVE" → "ESTIMASI".</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13877,7 +14490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Diperbarui: 10 Sep 2026 | Sumber: data.bmkg.go.id + sub-halamannya</t>
+          <t>Diperbarui: 15 Sep 2026 | Sumber: data.bmkg.go.id/prakiraan-cuaca + probe langsung</t>
         </is>
       </c>
     </row>
@@ -13971,7 +14584,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Resmi &amp; terdokumentasi; field hampir identik API internal (t, hu, weather_desc, ws, wd, tcc, tp, vs_text); repo contoh: github.com/infoBMKG/data-cuaca; WAJIB atribusi sumber BMKG di UI</t>
+          <t>Resmi &amp; terdokumentasi; field hampir identik df/forecast/coord. DIPAKAI sebagai FALLBACK sejak 15 Sep (useBmkgWeather).</t>
         </is>
       </c>
     </row>
@@ -14154,12 +14767,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>perlu cek</t>
+          <t>TIDAK ADA (wajib proxy)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Alternatif RESMI utk /api/public/weather/warning (internal, wajib proxy); butuh adapter RSS/CAP baru</t>
+          <t>DIPAKAI 15 Sep via proxy /alerts (dev: Vite, prod: api/bmkg/[...path].ts). Feed nasional → difilter per provinsi.</t>
         </is>
       </c>
     </row>
@@ -14201,12 +14814,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>perlu cek</t>
+          <t>TIDAK ADA (wajib proxy)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Idem</t>
+          <t>Belum dipakai (severity masih diinferensi dari judul RSS).</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14882,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>725 KB — untuk overlay peta + lookup code</t>
+          <t>725 KB, 232 polygon. Properti: WP_1 (kode, mis. U.04), WP_IMM (nama), WilPel. Path benar /static/wilayah_perairan.json — .geojson = 404 (dulu dipakai kode → overlay tak pernah muncul). DIPAKAI 15 Sep (peta maritim).</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14929,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>ringkas utk badge peta</t>
+          <t>232 wilayah × today/tomorrow/h2/h3 → warna + hitungan legend peta maritim. DIPAKAI 15 Sep (live).</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14976,101 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>arus (current_*), visibility, rh, temp, PASUT low/high tide → card Pelayaran/Pelabuhan</t>
+          <t>DIPAKAI 15 Sep di kartu "Pelabuhan &amp; Pasut" (live). arus (current_*) belum dipakai — satuan ambigu (docs cm/s, nilai 0.06-0.46 → kemungkinan m/s). PASUT low/high sering null → UI sembunyikan blok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Maritim: Perairan (detail)</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>GET https://maritim.bmkg.go.id/public_api/perairan/{file}.json</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>file dari perairan_list (mis. F.09_Teluk%20Jakarta.json)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>4 slot: hari ini/besok/H+2/H+3</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>per rilis</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>DIPAKAI 15 Sep: narasi Aktivitas Pelayaran, popup peta maritim, patch drawer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Kualitas Udara / ISPU</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ispu.bmkg.go.id · www.bmkg.go.id/kualitas-udara · api.bmkg.go.id/publik/ispu · ispu.menlhk.go.id</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>TIDAK TERSEDIA (15 Sep): 000 / 301→404 / 404 / 000. Tidak ada sumber resmi → nilai AQI di UI = estimasi.</t>
         </is>
       </c>
     </row>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -9,10 +9,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temuan API Resmi" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Content Card" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Card + Screenshot" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ringkasan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Mapping'!$A$1:$L$33</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="44">
+  <fonts count="50">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -336,8 +337,34 @@
       <color rgb="FF1F4E79"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="49">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -619,8 +646,28 @@
         <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -725,6 +772,20 @@
         <color theme="4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D5DD"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D5DD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D5DD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D5DD"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -874,7 +935,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -980,6 +1041,32 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="49" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1103,6 +1190,436 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="4543425"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="2438400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="4381500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="390525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="6572250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="8020050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="3390900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="3933825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="3067050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="26165175"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5695950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5553075"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="2362200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5238750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5238750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="5238750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6858000" cy="781050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4760,7 +5277,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="47" t="inlineStr">
         <is>
@@ -5709,6 +6225,889 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>AUDIT CONTENT CARD + SCREENSHOT — komponen, API yang dipakai, query, sample response</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="55" t="inlineStr">
+        <is>
+          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/artifacts/scripts/capture_card_screenshots.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="56" t="inlineStr">
+        <is>
+          <t>Status: ✅ LIVE = nilai kartu dari API live  |  ⚠️ CAMPURAN = sebagian live/sebagian mock  |  🔌 MOCK = statis/estimasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="57" t="inlineStr">
+        <is>
+          <t>Komponen</t>
+        </is>
+      </c>
+      <c r="C4" s="57" t="inlineStr">
+        <is>
+          <t>Screenshot</t>
+        </is>
+      </c>
+      <c r="D4" s="57" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="57" t="inlineStr">
+        <is>
+          <t>API dipakai</t>
+        </is>
+      </c>
+      <c r="F4" s="57" t="inlineStr">
+        <is>
+          <t>Query / URL terakhir</t>
+        </is>
+      </c>
+      <c r="G4" s="57" t="inlineStr">
+        <is>
+          <t>Sample Response (potongan)</t>
+        </is>
+      </c>
+      <c r="H4" s="57" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="365.75" customHeight="1">
+      <c r="A5" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="59" t="inlineStr">
+        <is>
+          <t>Hero Weather Card — Cuaca Hari Ini
+(hero)</t>
+        </is>
+      </c>
+      <c r="C5" s="60" t="n"/>
+      <c r="D5" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E5" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• Present Weather: cuaca saat ini</t>
+        </is>
+      </c>
+      <c r="F5" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+        </is>
+      </c>
+      <c r="G5" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H5" s="63" t="inlineStr">
+        <is>
+          <t>Kartu 'Hari Ini' = kondisi live saat ini; strip 7 hari = slot pertama tiap grup (df-forecast). API tidak punya tmin/tmax &amp; probabilitas hujan → keduanya di-skip (badge % = tp×20, aproksimasi).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="200" customHeight="1">
+      <c r="A6" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="59" t="inlineStr">
+        <is>
+          <t>Kondisi Saat Ini (rincian)
+(current-weather)</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="n"/>
+      <c r="D6" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E6" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• DF Adm: resolve wilayah admin
+• Present Weather: cuaca saat ini
+• API v1: waktu matahari terbit/terbenam</t>
+        </is>
+      </c>
+      <c r="F6" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+[200] /api-bmkgapi/df/v1/adm/coord&amp;lat=-6.2&amp;lon=106.816666
+[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666
+[200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+        </is>
+      </c>
+      <c r="G6" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H6" s="63" t="inlineStr">
+        <is>
+          <t>Info matahari (sunset API), wilayah (df/adm).
+– UV: proksi tcc (bukan UV asli) (est)
+– "Terasa seperti": rumus t + (hu-50)/10 (est)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="353" customHeight="1">
+      <c r="A7" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>Panel Prakiraan (Per Jam / Mingguan)
+(forecast-panel)</t>
+        </is>
+      </c>
+      <c r="C7" s="60" t="n"/>
+      <c r="D7" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E7" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• Open Data RESMI: prakiraan-cuaca (adm4)</t>
+        </is>
+      </c>
+      <c r="F7" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+(belum terekam saat capture) — Open Data RESMI: prakiraan-cuaca (adm4)</t>
+        </is>
+      </c>
+      <c r="G7" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H7" s="63" t="inlineStr">
+        <is>
+          <t>Tab Suhu = satu suhu per hari (slot pertama, tanpa min/max). Fallback resmi open-data bila df kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>Peringatan Dini (Alerts)
+(alerts)</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E8" s="59" t="inlineStr">
+        <is>
+          <t>• Public API: peringatan cuaca
+• Public API: peringatan siklon
+• Peringatan Dini Nowcast (RSS resmi)</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/public/weather/warning&amp;lat=-6.2&amp;long=106.816666
+(belum terekam saat capture) — Public API: peringatan siklon
+(belum terekam saat capture) — Peringatan Dini Nowcast (RSS resmi)</t>
+        </is>
+      </c>
+      <c r="G8" s="62" t="inlineStr">
+        <is>
+          <t>{"statusCode":200,"message":"OK!","data":{"today":{},"tomorrow":null}}</t>
+        </is>
+      </c>
+      <c r="H8" s="63" t="inlineStr">
+        <is>
+          <t>Nowcast (resmi, per provinsi) menang atas warning internal. Cyclone terdampak jarang (hanya saat ada siklon).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="525.5" customHeight="1">
+      <c r="A9" s="58" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="59" t="inlineStr">
+        <is>
+          <t>Berita &amp; Video (News Section)
+(news)</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="n"/>
+      <c r="D9" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E9" s="59" t="inlineStr">
+        <is>
+          <t>• Berita WordPress BMKG (WP REST)
+• Public API: video berita</t>
+        </is>
+      </c>
+      <c r="F9" s="62" t="inlineStr">
+        <is>
+          <t>(belum terekam saat capture) — Berita WordPress BMKG (WP REST)
+[200] /api-bmkgapi/public/weather/video-latest&amp;hashtag=infobmkgpws</t>
+        </is>
+      </c>
+      <c r="G9" s="62" t="inlineStr">
+        <is>
+          <t>[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari,  Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1Dy6sPbtzpc"},{"title":"Prakiraan Cuaca Esok Hari Kamis, 17 September 2026","videoUrl":"https://www.youtube.com/watch?v=Xx3Ddki3bHk"}]</t>
+        </is>
+      </c>
+      <c r="H9" s="63" t="inlineStr">
+        <is>
+          <t>– Fallback: artikel mock saat WP 502 (sering) (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="639.5" customHeight="1">
+      <c r="A10" s="58" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>Gempa Bumi (TEWS)
+(earthquake)</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E10" s="59" t="inlineStr">
+        <is>
+          <t>• Open Data: gempa (TEWS)</t>
+        </is>
+      </c>
+      <c r="F10" s="62" t="inlineStr">
+        <is>
+          <t>(belum terekam saat capture) — Open Data: gempa (TEWS)</t>
+        </is>
+      </c>
+      <c r="G10" s="62" t="inlineStr">
+        <is>
+          <t>— (tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H10" s="63" t="inlineStr">
+        <is>
+          <t>autogempa + gempadirasakan, 2 endpoint TEWS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="275" customHeight="1">
+      <c r="A11" s="58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>Citra Satelit Himawari-9
+(satellite)</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="n"/>
+      <c r="D11" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E11" s="59" t="inlineStr">
+        <is>
+          <t>• Citra Satelit Himawari-9 (background-image, bukan fetch)</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>(belum terekam saat capture) — Citra Satelit Himawari-9 (background-image, bukan fetch)</t>
+        </is>
+      </c>
+      <c r="G11" s="62" t="inlineStr">
+        <is>
+          <t>— (tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H11" s="63" t="inlineStr">
+        <is>
+          <t>Gambar PNG inderaja.bmkg.go.id (background-image &lt;img&gt; → TIDAK terekam patch fetch).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="317.75" customHeight="1">
+      <c r="A12" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>Carousel Kota Besar (statis)
+(major-cities)</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="n"/>
+      <c r="D12" s="64" t="inlineStr">
+        <is>
+          <t>🔌 MOCK</t>
+        </is>
+      </c>
+      <c r="E12" s="59" t="inlineStr">
+        <is>
+          <t>— (tanpa API live)</t>
+        </is>
+      </c>
+      <c r="F12" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="62" t="inlineStr">
+        <is>
+          <t>— (tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H12" s="63" t="inlineStr">
+        <is>
+          <t>– Kartu statis: landmark + nama kota (auto-geser &amp; fetch sengaja dimatikan, 16 Sep) (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="249.5" customHeight="1">
+      <c r="A13" s="58" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>Transportasi (Jalan / Kereta / Maritim)
+(transport)</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="n"/>
+      <c r="D13" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E13" s="59" t="inlineStr">
+        <is>
+          <t>• DWT: cuaca kecamatan/stasiun (jalan+kereta)
+• ISDP v1: wilayah laut terdekat
+• Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>[200] /event/source/dwt/apiDF_Kereta/manifest_times.json
+[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
+[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+        </is>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>&lt;!doctype html&gt;
+&lt;html lang="id" class="dark"&gt;
+  &lt;head&gt;
+    &lt;meta charset="UTF-8" /&gt;
+    &lt;link rel="icon" type="image/svg+xml" href="/assets/logo-BenySzP1.svg" /&gt;
+    &lt;!-- Preconnect to Google Fonts to fetch fonts faster and prevent Flash of Unstyled Text (FOUT) --&gt;
+    &lt;link rel="preconnect" href="https://fonts.googleapis.com" /&gt;
+    &lt;link rel="preconnect" href="https://fonts.gstatic.com" crossorigin /&gt;
+    &lt;link href="https://fonts.googleapis.com/css2?family=Plus+Jakarta+Sans:wght@300;400;500;600;700;800&amp;display=swap" rel="stylesheet" /&gt;
+    &lt;meta name="viewport" content="width=device-width, initial-scale=1.0, viewport-fit=cover" /&gt;
+    &lt;meta name="color-scheme" content="dark" /&gt;
+    &lt;meta name="theme-color" content="#070c19" /&gt;
+    &lt;meta name="apple-mobile-web-app-capable" content="yes" /&gt;
+    &lt;meta name="apple-mobile-web-app-status-bar-style" content="black-translucent" /&gt;
+    &lt;meta name="description" content="Portal Redesign Digital Weather Info BMKG - Layanan Informasi Cuaca Publik, Penerbangan, Maritim, Peringatan Dini Angin &amp; Hujan, dan Satelit Cuaca Himawari-9." /&gt;
+    &lt;meta name="keywords" content="BMKG, Info BMKG, Cuaca Indonesia, Radar Cuaca, Satelit Himawari-9, Gempa Megathrust, Peringatan Dini" /&gt;
+    &lt;meta name="author" content="BMKG Indonesia" /&gt;
+    &lt;title&gt;BMKG | Portal Informasi Cuaca, Iklim &amp; Geofisika Indonesia&lt;/title&gt;
+    &lt;script&gt;
+      (function() {
+        try {
+          const theme = localStorage.getItem('bmkg-theme-v2');
+          const isDark =
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H13" s="63" t="inlineStr">
+        <is>
+          <t>– Jalan Raya: DWT kecamatan terdekat (live)
+– Kereta: DWT stasiun terdekat (178 stasiun) (live)
+– Maritim: perairan resmi (fix currentSlot 15 Sep) (live)
+– Penerbangan: MOCK/PAUSED (menunggu data partner) (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="2068.25" customHeight="1">
+      <c r="A14" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>Panduan Aktivitas &amp; Analisis Cuaca
+(weather-activity)</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• ISDP v1: wilayah laut terdekat
+• Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="F14" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
+[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+        </is>
+      </c>
+      <c r="G14" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H14" s="63" t="inlineStr">
+        <is>
+          <t>– Aktivitas umum: forecast live (live)
+– Aktivitas pelayaran: gelombang perairan resmi (live)
+– ISPU/AQI: ESTIMASI sintetis (tidak ada sumber resmi) (est)
+– Indeks kenyamanan: label statis (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="456.5" customHeight="1">
+      <c r="A15" s="58" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>Peta Laut (Marine Map)
+(marine-map)</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E15" s="59" t="inlineStr">
+        <is>
+          <t>• Maritim: overview tinggi gelombang (232 wilayah)
+• Maritim: polygon 232 wilayah perairan
+• Maritim: detail cuaca/gelombang perairan
+• DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="F15" s="62" t="inlineStr">
+        <is>
+          <t>(belum terekam saat capture) — Maritim: overview tinggi gelombang (232 wilayah)
+(belum terekam saat capture) — Maritim: polygon 232 wilayah perairan
+[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json
+[200] /event/source/dwt/apiDF_Kereta/manifest_times.json</t>
+        </is>
+      </c>
+      <c r="G15" s="62" t="inlineStr">
+        <is>
+          <t>{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Selatan", "wind_to": "Barat Daya", "wind_speed_min": 5, "wind_speed_max": 18}, {"valid_from": "2026-09-22 00:00 UTC", "valid_to": "2026-09-22 12:00 UTC", "time_desc": "Besok", "weather": "Hujan Ringan", "weather_desc": "Besok untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumnya 11 - 33 knot bertiup dari arah utara, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Utara", "wind_to": "Barat Daya", "wind_speed_min": 11, "wind_speed_max": 33}, {"valid_from": "2026-09-22 12:00 UTC", "valid_to": "2026-09-23 12:00 UTC", "time_desc": "H+2", "weather": "Hujan Ringan", "weather_desc": "Lusa untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumn
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H15" s="63" t="inlineStr">
+        <is>
+          <t>– Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live (live)
+– Layer angin/cuaca: SNAPSHOT statis (sectors.json) (mock)
+– Mode Pelabuhan: snapshot ports.json (294) — hanya pelabuhan TERDEKAT yang live (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="445.25" customHeight="1">
+      <c r="A16" s="58" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>Pelabuhan &amp; Pasut
+(port-tide)</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="n"/>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="inlineStr">
+        <is>
+          <t>• Maritim: daftar pelabuhan (294)
+• Maritim: detail pelabuhan + pasut</t>
+        </is>
+      </c>
+      <c r="F16" s="62" t="inlineStr">
+        <is>
+          <t>[200] https://maritim.bmkg.go.id/public_api/pelabuhan_list
+[200] https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
+        </is>
+      </c>
+      <c r="G16" s="62" t="inlineStr">
+        <is>
+          <t>{
+  "files": [
+    {
+      "coor": [
+        1.198331,
+        109.054462
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1720,
+      "name": "0088_Sintete.json",
+      "portname": "Sintete",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.00214,
+        109.285391
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1713,
+      "name": "0310_PPP Sungai Rengas.json",
+      "portname": "PPP Sungai Rengas",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.531535,
+        110.21588
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1692,
+      "name": "0092_Kendawangan.json",
+      "portname": "Kendawangan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        4.145037,
+        117.665883
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1679,
+      "name": "0237_Nunukan.json",
+      "portname": "Nunukan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.6679806,
+        115.261925
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0603_Sanur.json",
+      "portname": "Sanur",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.35863269,
+        105.81975796
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1670,
+      "name": "0325_PPP Labuhan Maringgai.json",
+      "portname": "PPP Labuhan Maringgai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.67206,
+        115.55675
+      ],
+      "file_date": "2026-09-
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H16" s="63" t="inlineStr">
+        <is>
+          <t>Pasut null di sebagian pelabuhan → blok disembunyikan. Kolom arus di-skip (satuan ambigu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="194" customHeight="1">
+      <c r="A17" s="58" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>Aktivitas Sekitar (POI)
+(around-activity)</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• Overpass API: POI OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="F17" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="G17" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H17" s="63" t="inlineStr">
+        <is>
+          <t>Nilai cuaca per titik POI live (1 request df/coord per POI).
+– Daftar POI: kurasi statis (cityLandmarks) (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="420.5" customHeight="1">
+      <c r="A18" s="58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="59" t="inlineStr">
+        <is>
+          <t>Aktivitas Darat (Drawer)
+(land-based)</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="n"/>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>• DF Forecast: prakiraan 10 hari + per jam
+• DWT: cuaca kecamatan/stasiun (jalan+kereta)
+• Overpass API: POI OpenStreetMap
+• Nominatim: geocode OSM
+• OSRM: routing</t>
+        </is>
+      </c>
+      <c r="F18" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+[200] /event/source/dwt/apiDF_Kereta/manifest_times.json
+(belum terekam saat capture) — Overpass API: POI OpenStreetMap
+(belum terekam saat capture) — Nominatim: geocode OSM
+(belum terekam saat capture) — OSRM: routing</t>
+        </is>
+      </c>
+      <c r="G18" s="62" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+… (dipotong)</t>
+        </is>
+      </c>
+      <c r="H18" s="63" t="inlineStr">
+        <is>
+          <t>Forecast per titik rute live; fallback mock saat API gagal.
+– Pilihan lokasi awal: daftar statis (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="420.5" customHeight="1">
+      <c r="A19" s="58" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Konsultasi Pelayaran (Drawer)
+(maritime-advisor)</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>• ISDP v1: wilayah laut terdekat
+• Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
+        <is>
+          <t>[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
+[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+        </is>
+      </c>
+      <c r="G19" s="62" t="inlineStr">
+        <is>
+          <t>{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639833],[106.99055680194432,-6.087304617826876],[106.91156983292034,-6.100430027607439],[106.87701303397235,-6.098242459310679],[106.85726629171634,-6.117930573981525],[106.82270949276835,-6.124493278871807],[106.79308937938436,-6.111367869091243],[106.74372252374437,-6.106992732497721],[106.72397578148836,-6.093867322717157],[106.70422903923236,-6.052303525078705],[106.71903909592436,-6.041365683594902],[106.68448229697637,-6.015114864033774]]]},"distance":0.07574819298420225,"coordinate":{"type":"Point","coordinates":[106.83985076208779,-6.019490000627295]},"type":"area"}}</t>
+        </is>
+      </c>
+      <c r="H19" s="63" t="inlineStr">
+        <is>
+          <t>Parameter gelombang resmi di-inject ke drawer.
+– Sisa konten drawer (jenis aktivitas, tabel): statis maritimeAdvisorData.ts (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="420.5" customHeight="1">
+      <c r="A20" s="58" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="59" t="inlineStr">
+        <is>
+          <t>Konsultasi Penerbangan (Drawer)
+(aviation-advisor)</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="n"/>
+      <c r="D20" s="64" t="inlineStr">
+        <is>
+          <t>🔌 MOCK</t>
+        </is>
+      </c>
+      <c r="E20" s="59" t="inlineStr">
+        <is>
+          <t>— (tanpa API live)</t>
+        </is>
+      </c>
+      <c r="F20" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="62" t="inlineStr">
+        <is>
+          <t>— (tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H20" s="63" t="inlineStr">
+        <is>
+          <t>– 100% statis (aviationAdvisorData.ts) — API penerbangan belum ada (mock)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="58" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>Pencarian Lokasi
+(location-search)</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="n"/>
+      <c r="D21" s="64" t="inlineStr">
+        <is>
+          <t>🔌 MOCK</t>
+        </is>
+      </c>
+      <c r="E21" s="59" t="inlineStr">
+        <is>
+          <t>— (tanpa API live)</t>
+        </is>
+      </c>
+      <c r="F21" s="62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="62" t="inlineStr">
+        <is>
+          <t>— (tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H21" s="63" t="inlineStr">
+        <is>
+          <t>– POI statis (poiSearchData.ts) (mock)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
@@ -5896,7 +7295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14241,7 +15640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14461,7 +15860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -1201,7 +1201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="4543425"/>
+    <ext cx="4381500" cy="2905125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1226,7 +1226,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="2438400"/>
+    <ext cx="4381500" cy="1552575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1251,7 +1251,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="4381500"/>
+    <ext cx="4381500" cy="2800350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1276,7 +1276,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="390525"/>
+    <ext cx="4381500" cy="247650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1301,7 +1301,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="6572250"/>
+    <ext cx="4381500" cy="4200525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1326,7 +1326,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="8020050"/>
+    <ext cx="4381500" cy="5124450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1351,7 +1351,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="3390900"/>
+    <ext cx="4381500" cy="2162175"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1376,7 +1376,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="3933825"/>
+    <ext cx="4381500" cy="2514600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1401,7 +1401,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="3067050"/>
+    <ext cx="4381500" cy="1962150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1426,7 +1426,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="26165175"/>
+    <ext cx="4381500" cy="16716375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1451,7 +1451,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="5695950"/>
+    <ext cx="4381500" cy="3638550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1476,7 +1476,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="5553075"/>
+    <ext cx="4381500" cy="3552825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1501,7 +1501,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="2362200"/>
+    <ext cx="4381500" cy="1504950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -1526,7 +1526,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="5238750"/>
+    <ext cx="4381500" cy="3343275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -1551,7 +1551,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="5238750"/>
+    <ext cx="4381500" cy="3343275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -1576,7 +1576,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="5238750"/>
+    <ext cx="4381500" cy="3343275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -1601,7 +1601,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6858000" cy="781050"/>
+    <ext cx="4381500" cy="504825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -6230,11 +6230,11 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="115" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -6301,7 +6301,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="365.75" customHeight="1">
+    <row r="5" ht="236.75" customHeight="1">
       <c r="A5" s="58" t="n">
         <v>1</v>
       </c>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="200" customHeight="1">
+    <row r="6" ht="163.5" customHeight="1">
       <c r="A6" s="58" t="n">
         <v>2</v>
       </c>
@@ -6387,7 +6387,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="353" customHeight="1">
+    <row r="7" ht="228.5" customHeight="1">
       <c r="A7" s="58" t="n">
         <v>3</v>
       </c>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="120" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="58" t="n">
         <v>4</v>
       </c>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="525.5" customHeight="1">
+    <row r="9" ht="338.75" customHeight="1">
       <c r="A9" s="58" t="n">
         <v>5</v>
       </c>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="639.5" customHeight="1">
+    <row r="10" ht="409" customHeight="1">
       <c r="A10" s="58" t="n">
         <v>6</v>
       </c>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="275" customHeight="1">
+    <row r="11" ht="178.25" customHeight="1">
       <c r="A11" s="58" t="n">
         <v>7</v>
       </c>
@@ -6581,7 +6581,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="317.75" customHeight="1">
+    <row r="12" ht="206" customHeight="1">
       <c r="A12" s="58" t="n">
         <v>8</v>
       </c>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="249.5" customHeight="1">
+    <row r="13" ht="310.5" customHeight="1">
       <c r="A13" s="58" t="n">
         <v>9</v>
       </c>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="2068.25" customHeight="1">
+    <row r="14" ht="409" customHeight="1">
       <c r="A14" s="58" t="n">
         <v>10</v>
       </c>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="456.5" customHeight="1">
+    <row r="15" ht="294.5" customHeight="1">
       <c r="A15" s="58" t="n">
         <v>11</v>
       </c>
@@ -6776,7 +6776,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="445.25" customHeight="1">
+    <row r="16" ht="409" customHeight="1">
       <c r="A16" s="58" t="n">
         <v>12</v>
       </c>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="194" customHeight="1">
+    <row r="17" ht="163.5" customHeight="1">
       <c r="A17" s="58" t="n">
         <v>13</v>
       </c>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="420.5" customHeight="1">
+    <row r="18" ht="271.25" customHeight="1">
       <c r="A18" s="58" t="n">
         <v>14</v>
       </c>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="420.5" customHeight="1">
+    <row r="19" ht="271.25" customHeight="1">
       <c r="A19" s="58" t="n">
         <v>15</v>
       </c>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="420.5" customHeight="1">
+    <row r="20" ht="271.25" customHeight="1">
       <c r="A20" s="58" t="n">
         <v>16</v>
       </c>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="120" customHeight="1">
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="58" t="n">
         <v>17</v>
       </c>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -1401,7 +1401,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4381500" cy="1962150"/>
+    <ext cx="4381500" cy="4229100"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -6248,7 +6248,7 @@
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/artifacts/scripts/capture_card_screenshots.js</t>
+          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
         </is>
       </c>
     </row>
@@ -6325,13 +6325,13 @@
       </c>
       <c r="F5" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
 [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
         </is>
       </c>
       <c r="G5" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="F6" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
 [200] /api-bmkgapi/df/v1/adm/coord&amp;lat=-6.2&amp;lon=106.816666
 [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666
 [200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G6" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>
@@ -6411,13 +6411,13 @@
       </c>
       <c r="F7" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
 (belum terekam saat capture) — Open Data RESMI: prakiraan-cuaca (adm4)</t>
         </is>
       </c>
       <c r="G7" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>
@@ -6530,12 +6530,13 @@
       </c>
       <c r="F10" s="62" t="inlineStr">
         <is>
-          <t>(belum terekam saat capture) — Open Data: gempa (TEWS)</t>
+          <t>[200] https://data.bmkg.go.id/DataMKG/TEWS/gempadirasakan.json</t>
         </is>
       </c>
       <c r="G10" s="62" t="inlineStr">
         <is>
-          <t>— (tidak ada response live)</t>
+          <t>{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 76 km Barat Daya Agam","Dirasakan":"III-IV Agam, II-III Kab. Padang Pariaman, II-III Kota Pariaman, II-III Kota Padang"},{"Tanggal":"21 Sep 2026","Jam":"14:31:07 WIB","DateTime":"2026-09-21T07:31:07+00:00","Coordinates":"-0.70,122.45","Lintang":"0.70 LS","Bujur":"122.45 BT","Magnitude":"5.3","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 26 km BaratDaya Pulau Puah","Dirasakan":"IV-V Luwuk, II-III Kab. Pohuwato"},{"Tanggal":"21 Sep 2026","Jam":"12:59:25 WIB","DateTime":"2026-09-21T05:59:25+00:00","Coordinates":"-8.28,120.57","Lintang":"8.28 LS","Bujur":"120.57 BT","Magnitude":"3.5","Kedalaman":"7 km","Wilayah":"Pusat gempa berada di laut 38 km utara Ruteng, Manggarai","Dirasakan":"II-III Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"08:41:37 WIB","DateTime":"2026-09-21T01:41:37+00:00","Coordinates":"-8.33,120.59","Lintang":"8.33 LS","Bujur":"120.59 BT","Magnitude":"5.3"
+… (dipotong)</t>
         </is>
       </c>
       <c r="H10" s="63" t="inlineStr">
@@ -6618,7 +6619,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="310.5" customHeight="1">
+    <row r="13" ht="341" customHeight="1">
       <c r="A13" s="58" t="n">
         <v>9</v>
       </c>
@@ -6643,36 +6644,14 @@
       </c>
       <c r="F13" s="62" t="inlineStr">
         <is>
-          <t>[200] /event/source/dwt/apiDF_Kereta/manifest_times.json
+          <t>[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json
 [200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
 [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
         </is>
       </c>
       <c r="G13" s="62" t="inlineStr">
         <is>
-          <t>&lt;!doctype html&gt;
-&lt;html lang="id" class="dark"&gt;
-  &lt;head&gt;
-    &lt;meta charset="UTF-8" /&gt;
-    &lt;link rel="icon" type="image/svg+xml" href="/assets/logo-BenySzP1.svg" /&gt;
-    &lt;!-- Preconnect to Google Fonts to fetch fonts faster and prevent Flash of Unstyled Text (FOUT) --&gt;
-    &lt;link rel="preconnect" href="https://fonts.googleapis.com" /&gt;
-    &lt;link rel="preconnect" href="https://fonts.gstatic.com" crossorigin /&gt;
-    &lt;link href="https://fonts.googleapis.com/css2?family=Plus+Jakarta+Sans:wght@300;400;500;600;700;800&amp;display=swap" rel="stylesheet" /&gt;
-    &lt;meta name="viewport" content="width=device-width, initial-scale=1.0, viewport-fit=cover" /&gt;
-    &lt;meta name="color-scheme" content="dark" /&gt;
-    &lt;meta name="theme-color" content="#070c19" /&gt;
-    &lt;meta name="apple-mobile-web-app-capable" content="yes" /&gt;
-    &lt;meta name="apple-mobile-web-app-status-bar-style" content="black-translucent" /&gt;
-    &lt;meta name="description" content="Portal Redesign Digital Weather Info BMKG - Layanan Informasi Cuaca Publik, Penerbangan, Maritim, Peringatan Dini Angin &amp; Hujan, dan Satelit Cuaca Himawari-9." /&gt;
-    &lt;meta name="keywords" content="BMKG, Info BMKG, Cuaca Indonesia, Radar Cuaca, Satelit Himawari-9, Gempa Megathrust, Peringatan Dini" /&gt;
-    &lt;meta name="author" content="BMKG Indonesia" /&gt;
-    &lt;title&gt;BMKG | Portal Informasi Cuaca, Iklim &amp; Geofisika Indonesia&lt;/title&gt;
-    &lt;script&gt;
-      (function() {
-        try {
-          const theme = localStorage.getItem('bmkg-theme-v2');
-          const isDark =
+          <t>[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Cengkareng ",-6.158600003,106.756496988,"5005623","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Tangerang","Batuceper",-6.169660008,106.681367978,"5008776","2026-09-10 16:00:00",["85","26","2","SE","2.4"],"ndf"],["","Kota Jakarta Barat","Grogol Petamburan ",-6.161280032,106.772031002,"5005620","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Tambora",-6.155889966,106.801510993,"5005621","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.212939965,106.900340002,"501191","2026-09-10 16:00:00",["88","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Selatan","Tebet ",-6.225910038,106.858320013,"5005597","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kab. Karawang","Kotabaru",-6.406120034,107.458950011,"5009561"
 … (dipotong)</t>
         </is>
       </c>
@@ -6710,14 +6689,14 @@
       </c>
       <c r="F14" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
 [200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
 [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
         </is>
       </c>
       <c r="G14" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>
@@ -6756,15 +6735,15 @@
       </c>
       <c r="F15" s="62" t="inlineStr">
         <is>
-          <t>(belum terekam saat capture) — Maritim: overview tinggi gelombang (232 wilayah)
-(belum terekam saat capture) — Maritim: polygon 232 wilayah perairan
+          <t>[200] https://maritim.bmkg.go.id/public_api/overview/gelombang.json
+[200] https://maritim.bmkg.go.id/public_api/static/wilayah_perairan.json
 [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json
-[200] /event/source/dwt/apiDF_Kereta/manifest_times.json</t>
+[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json</t>
         </is>
       </c>
       <c r="G15" s="62" t="inlineStr">
         <is>
-          <t>{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Selatan", "wind_to": "Barat Daya", "wind_speed_min": 5, "wind_speed_max": 18}, {"valid_from": "2026-09-22 00:00 UTC", "valid_to": "2026-09-22 12:00 UTC", "time_desc": "Besok", "weather": "Hujan Ringan", "weather_desc": "Besok untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumnya 11 - 33 knot bertiup dari arah utara, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Utara", "wind_to": "Barat Daya", "wind_speed_min": 11, "wind_speed_max": 33}, {"valid_from": "2026-09-22 12:00 UTC", "valid_to": "2026-09-23 12:00 UTC", "time_desc": "H+2", "weather": "Hujan Ringan", "weather_desc": "Lusa untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumn
+          <t>{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.12": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.02": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.08": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.03": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.07": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.04": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.06": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Seda
 … (dipotong)</t>
         </is>
       </c>
@@ -6913,13 +6892,13 @@
       </c>
       <c r="F17" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
 (belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
         </is>
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>
@@ -6957,8 +6936,8 @@
       </c>
       <c r="F18" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-6.2804&amp;lon=106.9507
-[200] /event/source/dwt/apiDF_Kereta/manifest_times.json
+          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
+[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json
 (belum terekam saat capture) — Overpass API: POI OpenStreetMap
 (belum terekam saat capture) — Nominatim: geocode OSM
 (belum terekam saat capture) — OSRM: routing</t>
@@ -6966,7 +6945,7 @@
       </c>
       <c r="G18" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T06:00:00Z","t":34,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":306,"wd":"W","wd_to":"E","ws":11.5,"hu":48,"vs":null,"vs_text":null,"time_index":"5-6","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 06:00:00","local_datetime":"2026-09-22 13:00:00"},{"datetime":"2026-09-22T07:00:00Z","t":33,"tcc":50,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":48,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":30,"tcc":82,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E",
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
 … (dipotong)</t>
         </is>
       </c>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6331,8 +6331,7 @@
       </c>
       <c r="G5" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H5" s="63" t="inlineStr">
@@ -6341,7 +6340,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="163.5" customHeight="1">
+    <row r="6" ht="153" customHeight="1">
       <c r="A6" s="58" t="n">
         <v>2</v>
       </c>
@@ -6375,8 +6374,7 @@
       </c>
       <c r="G6" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H6" s="63" t="inlineStr">
@@ -6417,8 +6415,7 @@
       </c>
       <c r="G7" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H7" s="63" t="inlineStr">
@@ -6498,7 +6495,7 @@
       </c>
       <c r="G9" s="62" t="inlineStr">
         <is>
-          <t>[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari,  Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1Dy6sPbtzpc"},{"title":"Prakiraan Cuaca Esok Hari Kamis, 17 September 2026","videoUrl":"https://www.youtube.com/watch?v=Xx3Ddki3bHk"}]</t>
+          <t>[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari, Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1Dy6sPbtzpc"},{"title":"Prakiraan Cuaca Esok Hari Kamis, 17 September 2026","videoUrl":"https://www.youtube.com/watch?v=Xx3Ddki3bHk"}]</t>
         </is>
       </c>
       <c r="H9" s="63" t="inlineStr">
@@ -6535,8 +6532,7 @@
       </c>
       <c r="G10" s="62" t="inlineStr">
         <is>
-          <t>{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 76 km Barat Daya Agam","Dirasakan":"III-IV Agam, II-III Kab. Padang Pariaman, II-III Kota Pariaman, II-III Kota Padang"},{"Tanggal":"21 Sep 2026","Jam":"14:31:07 WIB","DateTime":"2026-09-21T07:31:07+00:00","Coordinates":"-0.70,122.45","Lintang":"0.70 LS","Bujur":"122.45 BT","Magnitude":"5.3","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 26 km BaratDaya Pulau Puah","Dirasakan":"IV-V Luwuk, II-III Kab. Pohuwato"},{"Tanggal":"21 Sep 2026","Jam":"12:59:25 WIB","DateTime":"2026-09-21T05:59:25+00:00","Coordinates":"-8.28,120.57","Lintang":"8.28 LS","Bujur":"120.57 BT","Magnitude":"3.5","Kedalaman":"7 km","Wilayah":"Pusat gempa berada di laut 38 km utara Ruteng, Manggarai","Dirasakan":"II-III Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"08:41:37 WIB","DateTime":"2026-09-21T01:41:37+00:00","Coordinates":"-8.33,120.59","Lintang":"8.33 LS","Bujur":"120.59 BT","Magnitude":"5.3"
-… (dipotong)</t>
+          <t>{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 76 km Barat Daya Agam","Dirasakan":"III-IV Agam, II-III Kab. Padang Pariaman, II-III Kota Pariaman, II-III Kota Padang"},{"Tanggal":"21 Sep 2026","Jam":"14:31:07 WIB","DateTime":"2026-09-21T07:31:07+00:00","Coordinates":"-0.70,122.45","Lintang":"0.70 LS","Bujur":"122.45 BT","Magnitude":"5.3","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 26 km BaratDaya Pulau Puah","Dirasakan":"IV-V Luwuk, II-III Kab. Pohuwato"},{"Tanggal":"21 Sep 2026","Jam":"12:59:25 WIB","DateTime":"2026-09-21T05:59:25+00:00","Coordinates":"-8.28,120.57","Lintang":"8.28 LS","Bujur":"120.57 BT","Magnitude":"3.5","Kedalaman":"7 km","Wilayah":"Pusat gempa berada di laut 38 km utara Ruteng, Manggarai","Dirasakan":"II-III Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"08:41:37 WIB","DateTime":"2026-09-21T01:41:37+00:00","Coordinates":"-8.33,120.59","Lintang":"8.33 LS","Bujur":"120.59 BT","Magnitude":"5.3" … (dipotong)</t>
         </is>
       </c>
       <c r="H10" s="63" t="inlineStr">
@@ -6651,8 +6647,7 @@
       </c>
       <c r="G13" s="62" t="inlineStr">
         <is>
-          <t>[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Cengkareng ",-6.158600003,106.756496988,"5005623","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Tangerang","Batuceper",-6.169660008,106.681367978,"5008776","2026-09-10 16:00:00",["85","26","2","SE","2.4"],"ndf"],["","Kota Jakarta Barat","Grogol Petamburan ",-6.161280032,106.772031002,"5005620","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Tambora",-6.155889966,106.801510993,"5005621","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.212939965,106.900340002,"501191","2026-09-10 16:00:00",["88","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Selatan","Tebet ",-6.225910038,106.858320013,"5005597","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kab. Karawang","Kotabaru",-6.406120034,107.458950011,"5009561"
-… (dipotong)</t>
+          <t>[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Cengkareng ",-6.158600003,106.756496988,"5005623","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Tangerang","Batuceper",-6.169660008,106.681367978,"5008776","2026-09-10 16:00:00",["85","26","2","SE","2.4"],"ndf"],["","Kota Jakarta Barat","Grogol Petamburan ",-6.161280032,106.772031002,"5005620","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Tambora",-6.155889966,106.801510993,"5005621","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.212939965,106.900340002,"501191","2026-09-10 16:00:00",["88","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Selatan","Tebet ",-6.225910038,106.858320013,"5005597","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kab. Karawang","Kotabaru",-6.406120034,107.458950011,"5009561" … (dipotong)</t>
         </is>
       </c>
       <c r="H13" s="63" t="inlineStr">
@@ -6696,8 +6691,7 @@
       </c>
       <c r="G14" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H14" s="63" t="inlineStr">
@@ -6743,8 +6737,7 @@
       </c>
       <c r="G15" s="62" t="inlineStr">
         <is>
-          <t>{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.12": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.02": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.08": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.03": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.07": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.04": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.06": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Seda
-… (dipotong)</t>
+          <t>{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.12": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.02": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.08": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.03": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.07": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.04": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.06": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Seda … (dipotong)</t>
         </is>
       </c>
       <c r="H15" s="63" t="inlineStr">
@@ -6755,7 +6748,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="409" customHeight="1">
+    <row r="16" ht="287.75" customHeight="1">
       <c r="A16" s="58" t="n">
         <v>12</v>
       </c>
@@ -6785,81 +6778,7 @@
       </c>
       <c r="G16" s="62" t="inlineStr">
         <is>
-          <t>{
-  "files": [
-    {
-      "coor": [
-        1.198331,
-        109.054462
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1720,
-      "name": "0088_Sintete.json",
-      "portname": "Sintete",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        0.00214,
-        109.285391
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1713,
-      "name": "0310_PPP Sungai Rengas.json",
-      "portname": "PPP Sungai Rengas",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        -2.531535,
-        110.21588
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1692,
-      "name": "0092_Kendawangan.json",
-      "portname": "Kendawangan",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        4.145037,
-        117.665883
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1679,
-      "name": "0237_Nunukan.json",
-      "portname": "Nunukan",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        -8.6679806,
-        115.261925
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1646,
-      "name": "0603_Sanur.json",
-      "portname": "Sanur",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        -5.35863269,
-        105.81975796
-      ],
-      "file_date": "2026-09-21 23:47 UTC",
-      "kb": 1670,
-      "name": "0325_PPP Labuhan Maringgai.json",
-      "portname": "PPP Labuhan Maringgai",
-      "type": "utama"
-    },
-    {
-      "coor": [
-        -8.67206,
-        115.55675
-      ],
-      "file_date": "2026-09-
-… (dipotong)</t>
+          <t>{ "files": [ { "coor": [ 1.198331, 109.054462 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1720, "name": "0088_Sintete.json", "portname": "Sintete", "type": "utama" }, { "coor": [ 0.00214, 109.285391 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1713, "name": "0310_PPP Sungai Rengas.json", "portname": "PPP Sungai Rengas", "type": "utama" }, { "coor": [ -2.531535, 110.21588 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1692, "name": "0092_Kendawangan.json", "portname": "Kendawangan", "type": "utama" }, { "coor": [ 4.145037, 117.665883 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1679, "name": "0237_Nunukan.json", "portname": "Nunukan", "type": "utama" }, { "coor": [ -8.6679806, 115.261925 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1646, "name": "0603_Sanur.json", "portname": "Sanur", "type": "utama" }, { "coor": [ -5.35863269, 105.81975796 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1670, "name": "0325_PPP Labuhan Maringgai.json", "portname": "PPP Labuhan Maringgai", "type": "utama" }, { "coor": [ -8.67206, 115.55675 ], "file_date": "2026-09- … (dipotong)</t>
         </is>
       </c>
       <c r="H16" s="63" t="inlineStr">
@@ -6868,7 +6787,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="163.5" customHeight="1">
+    <row r="17" ht="153" customHeight="1">
       <c r="A17" s="58" t="n">
         <v>13</v>
       </c>
@@ -6898,8 +6817,7 @@
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H17" s="63" t="inlineStr">
@@ -6945,8 +6863,7 @@
       </c>
       <c r="G18" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,
-… (dipotong)</t>
+          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
         </is>
       </c>
       <c r="H18" s="63" t="inlineStr">

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6225,17 +6225,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="115" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="92" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6248,7 +6249,7 @@
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
+          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Kolom "Field dipakai UI" = pemetaan response → nilai yang dirender (sumber: src/services/bmkg/adapters.ts). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
         </is>
       </c>
     </row>
@@ -6292,10 +6293,15 @@
       </c>
       <c r="G4" s="57" t="inlineStr">
         <is>
-          <t>Sample Response (potongan)</t>
+          <t>Sample Response (per API, dipotong)</t>
         </is>
       </c>
       <c r="H4" s="57" t="inlineStr">
+        <is>
+          <t>Field dipakai UI + penjelasan</t>
+        </is>
+      </c>
+      <c r="I4" s="57" t="inlineStr">
         <is>
           <t>Catatan</t>
         </is>
@@ -6331,16 +6337,27 @@
       </c>
       <c r="G5" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H5" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ Present Weather: cuaca saat ini
+{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T06:00:00.000Z","local_datetime":"2026-09-22 13:00:00","t":33,"tcc":87,"wd_deg":21,"wd":"N","wd_to":"S","ws":10.2,"hu":46,"vs":null,"vs_text":null} …</t>
+        </is>
+      </c>
+      <c r="H5" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ data.t, hu, weather_desc, ws, tcc, vs, local_datetime
+  Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.</t>
+        </is>
+      </c>
+      <c r="I5" s="63" t="inlineStr">
         <is>
           <t>Kartu 'Hari Ini' = kondisi live saat ini; strip 7 hari = slot pertama tiap grup (df-forecast). API tidak punya tmin/tmax &amp; probabilitas hujan → keduanya di-skip (badge % = tp×20, aproksimasi).</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="153" customHeight="1">
+    <row r="6" ht="331.5" customHeight="1">
       <c r="A6" s="58" t="n">
         <v>2</v>
       </c>
@@ -6374,10 +6391,29 @@
       </c>
       <c r="G6" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H6" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ DF Adm: resolve wilayah admin
+{"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","lon":106.81596823959143,"lat":-6.197052719903746,"distance":0}
+▸ Present Weather: cuaca saat ini
+{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T06:00:00.000Z","local_datetime":"2026-09-22 13:00:00","t":33,"tcc":87,"wd_deg":21,"wd":"N","wd_to":"S","ws":10.2,"hu":46,"vs":null,"vs_text":null} …
+▸ API v1: waktu matahari terbit/terbenam
+{"results":{"date":"2026-09-22","sunrise":"5:42:05 AM","sunset":"5:49:07 PM","first_light":"4:33:02 AM","last_light":"6:58:12 PM","dawn":"5:21:18 AM","dusk":"6:09:54 PM","solar_noon":"11:45:33 AM","golden_hour":"5:21:38 PM","day_length":"12:07:02","nautical_twilight_begin":"4:57:10 AM","nautical_twilight_end":"6:34:03 PM","timezone":"Asia/Jakarta","utc_offset":420,"sun_altitude":83.49,"sun_azimuth":0,"sunrise_azimuth":89.69,"sunset_azimuth":270.12,"moonrise":"2:19:27 PM","moonset":"2:15:11 AM","moon_illumination":80.06,"moon_phase":"Waxing Gibbous","moon_phase_value":0.35,"moon_always_up":fals …</t>
+        </is>
+      </c>
+      <c r="H6" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ provinsi, kotkab, kecamatan, desa
+  Resolusi koordinat → wilayah administratif; label lokasi kartu.
+▸ data.t, hu, weather_desc, ws, tcc, vs, local_datetime
+  Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.
+▸ sunrise, sunset (format 12-jam)
+  Dikonversi ke HH:mm → info matahari terbit/terbenam di CurrentWeather.</t>
+        </is>
+      </c>
+      <c r="I6" s="63" t="inlineStr">
         <is>
           <t>Info matahari (sunset API), wilayah (df/adm).
 – UV: proksi tcc (bukan UV asli) (est)
@@ -6415,16 +6451,27 @@
       </c>
       <c r="G7" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H7" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ Open Data RESMI: prakiraan-cuaca (adm4)
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H7" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ data[].cuaca[][] → t, hu, weather_desc, tp
+  Fallback prakiraan resmi (open-data) bila df kosong — bentuk item identik df.</t>
+        </is>
+      </c>
+      <c r="I7" s="63" t="inlineStr">
         <is>
           <t>Tab Suhu = satu suhu per hari (slot pertama, tanpa min/max). Fallback resmi open-data bila df kosong.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8" ht="121.5" customHeight="1">
       <c r="A8" s="58" t="n">
         <v>4</v>
       </c>
@@ -6456,10 +6503,25 @@
       </c>
       <c r="G8" s="62" t="inlineStr">
         <is>
-          <t>{"statusCode":200,"message":"OK!","data":{"today":{},"tomorrow":null}}</t>
-        </is>
-      </c>
-      <c r="H8" s="63" t="inlineStr">
+          <t>▸ Public API: peringatan cuaca
+{"statusCode":200,"message":"OK!","data":{"today":{},"tomorrow":null}}
+▸ Public API: peringatan siklon
+(tidak ada response live)
+▸ Peringatan Dini Nowcast (RSS resmi)
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H8" s="59" t="inlineStr">
+        <is>
+          <t>▸ data.today / data.tomorrow (warning_level, impact/description)
+  Peringatan hari ini/besok → severity Awas/Siaga/Waspada → AlertsPanel; kosong = tanpa peringatan.
+▸ data siklon terdampak
+  Peringatan siklon untuk wilayah — hanya muncul saat ada siklon aktif.
+▸ XML RSS: &lt;item&gt; per provinsi (title, description, pubDate)
+  Peringatan dini 3-6 jam resmi; difilter per provinsi; menang atas warning internal df.</t>
+        </is>
+      </c>
+      <c r="I8" s="63" t="inlineStr">
         <is>
           <t>Nowcast (resmi, per provinsi) menang atas warning internal. Cyclone terdampak jarang (hanya saat ada siklon).</t>
         </is>
@@ -6495,10 +6557,21 @@
       </c>
       <c r="G9" s="62" t="inlineStr">
         <is>
-          <t>[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari, Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1Dy6sPbtzpc"},{"title":"Prakiraan Cuaca Esok Hari Kamis, 17 September 2026","videoUrl":"https://www.youtube.com/watch?v=Xx3Ddki3bHk"}]</t>
-        </is>
-      </c>
-      <c r="H9" s="63" t="inlineStr">
+          <t>▸ Berita WordPress BMKG (WP REST)
+(tidak ada response live)
+▸ Public API: video berita
+[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari, Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1 …</t>
+        </is>
+      </c>
+      <c r="H9" s="59" t="inlineStr">
+        <is>
+          <t>▸ [].title.rendered, excerpt.rendered, link, _embedded (featured media)
+  Artikel berita WP → NewsSection; fallback mock saat upstream 502 (sering).
+▸ [].judul, video_url
+  Video berita terbaru (per hashtag) → tab video NewsSection.</t>
+        </is>
+      </c>
+      <c r="I9" s="63" t="inlineStr">
         <is>
           <t>– Fallback: artikel mock saat WP 502 (sering) (mock)</t>
         </is>
@@ -6532,10 +6605,17 @@
       </c>
       <c r="G10" s="62" t="inlineStr">
         <is>
-          <t>{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 76 km Barat Daya Agam","Dirasakan":"III-IV Agam, II-III Kab. Padang Pariaman, II-III Kota Pariaman, II-III Kota Padang"},{"Tanggal":"21 Sep 2026","Jam":"14:31:07 WIB","DateTime":"2026-09-21T07:31:07+00:00","Coordinates":"-0.70,122.45","Lintang":"0.70 LS","Bujur":"122.45 BT","Magnitude":"5.3","Kedalaman":"10 km","Wilayah":"Pusat gempa berada di laut 26 km BaratDaya Pulau Puah","Dirasakan":"IV-V Luwuk, II-III Kab. Pohuwato"},{"Tanggal":"21 Sep 2026","Jam":"12:59:25 WIB","DateTime":"2026-09-21T05:59:25+00:00","Coordinates":"-8.28,120.57","Lintang":"8.28 LS","Bujur":"120.57 BT","Magnitude":"3.5","Kedalaman":"7 km","Wilayah":"Pusat gempa berada di laut 38 km utara Ruteng, Manggarai","Dirasakan":"II-III Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"08:41:37 WIB","DateTime":"2026-09-21T01:41:37+00:00","Coordinates":"-8.33,120.59","Lintang":"8.33 LS","Bujur":"120.59 BT","Magnitude":"5.3" … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H10" s="63" t="inlineStr">
+          <t>▸ Open Data: gempa (TEWS)
+{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berad …</t>
+        </is>
+      </c>
+      <c r="H10" s="59" t="inlineStr">
+        <is>
+          <t>▸ features[].properties (magnitude, kedalaman, wilayah, waktu)
+  Autogempa terkini + gempa dirasakan → EarthquakePanel.</t>
+        </is>
+      </c>
+      <c r="I10" s="63" t="inlineStr">
         <is>
           <t>autogempa + gempadirasakan, 2 endpoint TEWS.</t>
         </is>
@@ -6569,10 +6649,17 @@
       </c>
       <c r="G11" s="62" t="inlineStr">
         <is>
-          <t>— (tidak ada response live)</t>
-        </is>
-      </c>
-      <c r="H11" s="63" t="inlineStr">
+          <t>▸ Citra Satelit Himawari-9 (background-image, bukan fetch)
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H11" s="59" t="inlineStr">
+        <is>
+          <t>▸ (PNG) inderaja.bmkg.go.id H08_*.png
+  Citra Himawari-9 → background panel satelit (bukan JSON; terekam sebagai request gambar).</t>
+        </is>
+      </c>
+      <c r="I11" s="63" t="inlineStr">
         <is>
           <t>Gambar PNG inderaja.bmkg.go.id (background-image &lt;img&gt; → TIDAK terekam patch fetch).</t>
         </is>
@@ -6609,7 +6696,12 @@
           <t>— (tidak ada response live)</t>
         </is>
       </c>
-      <c r="H12" s="63" t="inlineStr">
+      <c r="H12" s="59" t="inlineStr">
+        <is>
+          <t>— (kartu tanpa API live — 100% statis)</t>
+        </is>
+      </c>
+      <c r="I12" s="63" t="inlineStr">
         <is>
           <t>– Kartu statis: landmark + nama kota (auto-geser &amp; fetch sengaja dimatikan, 16 Sep) (mock)</t>
         </is>
@@ -6647,10 +6739,25 @@
       </c>
       <c r="G13" s="62" t="inlineStr">
         <is>
-          <t>[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Cengkareng ",-6.158600003,106.756496988,"5005623","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Tangerang","Batuceper",-6.169660008,106.681367978,"5008776","2026-09-10 16:00:00",["85","26","2","SE","2.4"],"ndf"],["","Kota Jakarta Barat","Grogol Petamburan ",-6.161280032,106.772031002,"5005620","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Tambora",-6.155889966,106.801510993,"5005621","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.212939965,106.900340002,"501191","2026-09-10 16:00:00",["88","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Selatan","Tebet ",-6.225910038,106.858320013,"5005597","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kab. Karawang","Kotabaru",-6.406120034,107.458950011,"5009561" … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H13" s="63" t="inlineStr">
+          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …
+▸ ISDP v1: wilayah laut terdekat
+{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
+        </is>
+      </c>
+      <c r="H13" s="59" t="inlineStr">
+        <is>
+          <t>▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ code / nama wilayah laut terdekat
+  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="inlineStr">
         <is>
           <t>– Jalan Raya: DWT kecamatan terdekat (live)
 – Kereta: DWT stasiun terdekat (178 stasiun) (live)
@@ -6691,10 +6798,25 @@
       </c>
       <c r="G14" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H14" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ ISDP v1: wilayah laut terdekat
+{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
+        </is>
+      </c>
+      <c r="H14" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ code / nama wilayah laut terdekat
+  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+        </is>
+      </c>
+      <c r="I14" s="63" t="inlineStr">
         <is>
           <t>– Aktivitas umum: forecast live (live)
 – Aktivitas pelayaran: gelombang perairan resmi (live)
@@ -6703,7 +6825,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="294.5" customHeight="1">
+    <row r="15" ht="373.5" customHeight="1">
       <c r="A15" s="58" t="n">
         <v>11</v>
       </c>
@@ -6737,10 +6859,29 @@
       </c>
       <c r="G15" s="62" t="inlineStr">
         <is>
-          <t>{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.12": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.02": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.08": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.03": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.07": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Tinggi"}, "B.04": {"issued": "2026-09-21 23:47 UTC", "today": "Sedang", "tomorrow": "Sedang", "h2": "Sedang", "h3": "Sedang"}, "B.06": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Seda … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H15" s="63" t="inlineStr">
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issu …
+▸ Maritim: polygon 232 wilayah perairan
+{"type":"FeatureCollection", "features": [ {"type":"Feature","geometry":{"type":"Polygon","coordinates":[[[106.16613031275644,-7.474222917973128],[106.15132025606444,-7.500473737534255],[106.15132025606444,-9.884923181003366],[105.85018243666048,-9.753669083197725],[104.9517056640126,-9.504286297367011],[104.1717093449007,-9.287717035987708],[103.32259942789281,-9.055834796531078],[102.82399418592888,-8.915830425538395],[102.41424928411693,-8.808639578997123],[102.39943922742495,-8.808639578997123],[105.08005948867658,-6.920768138892684],[105.12942634431657,-6.973269778014939],[105.42562747815 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …</t>
+        </is>
+      </c>
+      <c r="H15" s="59" t="inlineStr">
+        <is>
+          <t>▸ {code: issued, today, tomorrow, wave_desc}
+  Ringkasan 232 wilayah → warna peta laut + legend gelombang.
+▸ features[].geometry (polygon 232 wilayah)
+  Polygon GeoJSON → layer batas wilayah perairan di peta.
+▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.
+▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.</t>
+        </is>
+      </c>
+      <c r="I15" s="63" t="inlineStr">
         <is>
           <t>– Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live (live)
 – Layer angin/cuaca: SNAPSHOT statis (sectors.json) (mock)
@@ -6778,16 +6919,27 @@
       </c>
       <c r="G16" s="62" t="inlineStr">
         <is>
-          <t>{ "files": [ { "coor": [ 1.198331, 109.054462 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1720, "name": "0088_Sintete.json", "portname": "Sintete", "type": "utama" }, { "coor": [ 0.00214, 109.285391 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1713, "name": "0310_PPP Sungai Rengas.json", "portname": "PPP Sungai Rengas", "type": "utama" }, { "coor": [ -2.531535, 110.21588 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1692, "name": "0092_Kendawangan.json", "portname": "Kendawangan", "type": "utama" }, { "coor": [ 4.145037, 117.665883 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1679, "name": "0237_Nunukan.json", "portname": "Nunukan", "type": "utama" }, { "coor": [ -8.6679806, 115.261925 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1646, "name": "0603_Sanur.json", "portname": "Sanur", "type": "utama" }, { "coor": [ -5.35863269, 105.81975796 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1670, "name": "0325_PPP Labuhan Maringgai.json", "portname": "PPP Labuhan Maringgai", "type": "utama" }, { "coor": [ -8.67206, 115.55675 ], "file_date": "2026-09- … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H16" s="63" t="inlineStr">
+          <t>▸ Maritim: daftar pelabuhan (294)
+{ "files": [ { "coor": [ 1.198331, 109.054462 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1720, "name": "0088_Sintete.json", "portname": "Sintete", "type": "utama" }, { "coor": [ 0.00214, 109.285391 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1713, "name": "0310_PPP Sungai Rengas.json", "portname": "PPP Sungai Rengas", "type": "utama" }, { "coor": [ -2.531535, 110.21588 ], "file_date": "2026-09-21 23:47 UTC", "kb": …
+▸ Maritim: detail pelabuhan + pasut
+{"port_id": "0101", "name": "Sunda Kelapa", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "latitude": -6.11664888, "longitude": 106.80830956, "type": "utama", "data": [{"issued": "2026-09-21 23:47 UTC", "valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "weather": "Berawan", "weather_desc": "Untuk area Sunda Kelapa diperkirakan berawan, dengan kecepatan angin pada umumnya 2 - 14 knot bertiup dari arah timur", "warning_desc": "NIL", "wind_from": "Timur", "wind_to": "Utara", "wind_speed_min": 2, "wind_speed_max": 1 …</t>
+        </is>
+      </c>
+      <c r="H16" s="59" t="inlineStr">
+        <is>
+          <t>▸ files[].coor, file
+  Koordinat 294 pelabuhan → pilih terdekat → fetch detail.
+▸ detail pelabuhan + data pasut
+  Pasut (UTC → zona waktu pelabuhan) → PortTideCard; pasut null → blok disembunyikan.</t>
+        </is>
+      </c>
+      <c r="I16" s="63" t="inlineStr">
         <is>
           <t>Pasut null di sebagian pelabuhan → blok disembunyikan. Kolom arus di-skip (satuan ambigu).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="153" customHeight="1">
+    <row r="17" ht="126.5" customHeight="1">
       <c r="A17" s="58" t="n">
         <v>13</v>
       </c>
@@ -6817,17 +6969,28 @@
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H17" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ Overpass API: POI OpenStreetMap
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H17" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ elements[].lat/lon/tags
+  POI OpenStreetMap sekitar pengguna → AroundActivity.</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="inlineStr">
         <is>
           <t>Nilai cuaca per titik POI live (1 request df/coord per POI).
 – Daftar POI: kurasi statis (cityLandmarks) (mock)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="271.25" customHeight="1">
+    <row r="18" ht="279" customHeight="1">
       <c r="A18" s="58" t="n">
         <v>14</v>
       </c>
@@ -6863,10 +7026,33 @@
       </c>
       <c r="G18" s="62" t="inlineStr">
         <is>
-          <t>{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":49,"vs":null,"vs_text":null,"time_index":"6-7","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-22 07:00:00","local_datetime":"2026-09-22 14:00:00"},{"datetime":"2026-09-22T08:00:00Z","t":29,"tcc":60,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":173,"wd":"SE","wd_to":"NW","ws":14.4,"hu":56,"vs":null,"vs_text":null,"time_index":"7-8","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 08:00:00","local_datetime":"2026-09-22 15:00:00"},{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":173, … (dipotong)</t>
-        </is>
-      </c>
-      <c r="H18" s="63" t="inlineStr">
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …
+▸ Overpass API: POI OpenStreetMap
+(tidak ada response live)
+▸ Nominatim: geocode OSM
+(tidak ada response live)
+▸ OSRM: routing
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H18" s="59" t="inlineStr">
+        <is>
+          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ elements[].lat/lon/tags
+  POI OpenStreetMap sekitar pengguna → AroundActivity.
+▸ [].lat/lon/display_name
+  Geocode nama tempat → koordinat.
+▸ routes[].geometry, duration, distance
+  Rute antar titik → panel aktivitas darat.</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="inlineStr">
         <is>
           <t>Forecast per titik rute live; fallback mock saat API gagal.
 – Pilihan lokasi awal: daftar statis (mock)</t>
@@ -6903,10 +7089,21 @@
       </c>
       <c r="G19" s="62" t="inlineStr">
         <is>
-          <t>{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639833],[106.99055680194432,-6.087304617826876],[106.91156983292034,-6.100430027607439],[106.87701303397235,-6.098242459310679],[106.85726629171634,-6.117930573981525],[106.82270949276835,-6.124493278871807],[106.79308937938436,-6.111367869091243],[106.74372252374437,-6.106992732497721],[106.72397578148836,-6.093867322717157],[106.70422903923236,-6.052303525078705],[106.71903909592436,-6.041365683594902],[106.68448229697637,-6.015114864033774]]]},"distance":0.07574819298420225,"coordinate":{"type":"Point","coordinates":[106.83985076208779,-6.019490000627295]},"type":"area"}}</t>
-        </is>
-      </c>
-      <c r="H19" s="63" t="inlineStr">
+          <t>▸ ISDP v1: wilayah laut terdekat
+{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
+        </is>
+      </c>
+      <c r="H19" s="59" t="inlineStr">
+        <is>
+          <t>▸ code / nama wilayah laut terdekat
+  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+        </is>
+      </c>
+      <c r="I19" s="63" t="inlineStr">
         <is>
           <t>Parameter gelombang resmi di-inject ke drawer.
 – Sisa konten drawer (jenis aktivitas, tabel): statis maritimeAdvisorData.ts (mock)</t>
@@ -6944,7 +7141,12 @@
           <t>— (tidak ada response live)</t>
         </is>
       </c>
-      <c r="H20" s="63" t="inlineStr">
+      <c r="H20" s="59" t="inlineStr">
+        <is>
+          <t>— (kartu tanpa API live — 100% statis)</t>
+        </is>
+      </c>
+      <c r="I20" s="63" t="inlineStr">
         <is>
           <t>– 100% statis (aviationAdvisorData.ts) — API penerbangan belum ada (mock)</t>
         </is>
@@ -6981,7 +7183,12 @@
           <t>— (tidak ada response live)</t>
         </is>
       </c>
-      <c r="H21" s="63" t="inlineStr">
+      <c r="H21" s="59" t="inlineStr">
+        <is>
+          <t>— (kartu tanpa API live — 100% statis)</t>
+        </is>
+      </c>
+      <c r="I21" s="63" t="inlineStr">
         <is>
           <t>– POI statis (poiSearchData.ts) (mock)</t>
         </is>
@@ -6989,9 +7196,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -1426,7 +1426,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4381500" cy="16716375"/>
+    <ext cx="4381500" cy="15887700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -6249,7 +6249,7 @@
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Kolom "Field dipakai UI" = pemetaan response → nilai yang dirender (sumber: src/services/bmkg/adapters.ts). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
+          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Kolom "Field dipakai UI" = pemetaan response → nilai yang dirender (sumber: src/services/bmkg/adapters.ts). *(proxy) merah = API tidak bisa diakses langsung dari browser (CORS / header khusus) — harus lewat proxy/alias untuk ambil response-nya. Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
         </is>
       </c>
     </row>
@@ -6331,16 +6331,41 @@
       </c>
       <c r="F5" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+          </r>
         </is>
       </c>
       <c r="G5" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ Present Weather: cuaca saat ini
-{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T06:00:00.000Z","local_datetime":"2026-09-22 13:00:00","t":33,"tcc":87,"wd_deg":21,"wd":"N","wd_to":"S","ws":10.2,"hu":46,"vs":null,"vs_text":null} …</t>
+{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T08:20:00.000Z","local_datetime":"2026-09-22 15:20:00","t":29,"tcc":89,"wd_deg":275,"wd":"W","wd_to":"E","ws":6.5,"hu":67,"vs":null,"vs_text":null} …</t>
         </is>
       </c>
       <c r="H5" s="59" t="inlineStr">
@@ -6383,22 +6408,76 @@
       </c>
       <c r="F6" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-[200] /api-bmkgapi/df/v1/adm/coord&amp;lat=-6.2&amp;lon=106.816666
-[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666
-[200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+          </r>
         </is>
       </c>
       <c r="G6" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ DF Adm: resolve wilayah admin
 {"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","lon":106.81596823959143,"lat":-6.197052719903746,"distance":0}
 ▸ Present Weather: cuaca saat ini
-{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T06:00:00.000Z","local_datetime":"2026-09-22 13:00:00","t":33,"tcc":87,"wd_deg":21,"wd":"N","wd_to":"S","ws":10.2,"hu":46,"vs":null,"vs_text":null} …
+{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T08:20:00.000Z","local_datetime":"2026-09-22 15:20:00","t":29,"tcc":89,"wd_deg":275,"wd":"W","wd_to":"E","ws":6.5,"hu":67,"vs":null,"vs_text":null} …
 ▸ API v1: waktu matahari terbit/terbenam
-{"results":{"date":"2026-09-22","sunrise":"5:42:05 AM","sunset":"5:49:07 PM","first_light":"4:33:02 AM","last_light":"6:58:12 PM","dawn":"5:21:18 AM","dusk":"6:09:54 PM","solar_noon":"11:45:33 AM","golden_hour":"5:21:38 PM","day_length":"12:07:02","nautical_twilight_begin":"4:57:10 AM","nautical_twilight_end":"6:34:03 PM","timezone":"Asia/Jakarta","utc_offset":420,"sun_altitude":83.49,"sun_azimuth":0,"sunrise_azimuth":89.69,"sunset_azimuth":270.12,"moonrise":"2:19:27 PM","moonset":"2:15:11 AM","moon_illumination":80.06,"moon_phase":"Waxing Gibbous","moon_phase_value":0.35,"moon_always_up":fals …</t>
+{"results":{"date":"2026-09-22","sunrise":"5:42:05 AM","sunset":"5:49:07 PM","first_light":"4:33:02 AM","last_light":"6:58:12 PM","dawn":"5:21:18 AM","dusk":"6:09:54 PM","solar_noon":"11:45:33 AM","golden_hour":"5:21:38 PM","day_length":"12:07:02","nautical_twilight_begin":"4:57:10 AM","nautical_twilight_end":"6:34:03 PM","timezone":"Asia/Jakarta","utc_offset":420,"sun_altitude":83.49,"sun_azimuth":0,"sunrise_azimuth":89.69,"sunset_azimuth":270.12,"moonrise":"2:19:27 PM","moonset":"2:15:11 AM","moon_illumination":81.03,"moon_phase":"Waxing Gibbous","moon_phase_value":0.36,"moon_always_up":fals …</t>
         </is>
       </c>
       <c r="H6" s="59" t="inlineStr">
@@ -6445,14 +6524,39 @@
       </c>
       <c r="F7" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-(belum terekam saat capture) — Open Data RESMI: prakiraan-cuaca (adm4)</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Open Data RESMI: prakiraan-cuaca (adm4)</t>
+          </r>
         </is>
       </c>
       <c r="G7" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ Open Data RESMI: prakiraan-cuaca (adm4)
 (tidak ada response live)</t>
         </is>
@@ -6471,7 +6575,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="121.5" customHeight="1">
+    <row r="8" ht="142.5" customHeight="1">
       <c r="A8" s="58" t="n">
         <v>4</v>
       </c>
@@ -6496,9 +6600,53 @@
       </c>
       <c r="F8" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/public/weather/warning&amp;lat=-6.2&amp;long=106.816666
-(belum terekam saat capture) — Public API: peringatan siklon
-(belum terekam saat capture) — Peringatan Dini Nowcast (RSS resmi)</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/public/weather/warning?lat=-6.2&amp;long=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Public API: peringatan siklon</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://www.bmkg.go.id/alerts/nowcast/id</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
         </is>
       </c>
       <c r="G8" s="62" t="inlineStr">
@@ -6508,7 +6656,7 @@
 ▸ Public API: peringatan siklon
 (tidak ada response live)
 ▸ Peringatan Dini Nowcast (RSS resmi)
-(tidak ada response live)</t>
+&lt;?xml version="1.0" encoding="UTF-8"?&gt; &lt;?xml-stylesheet type="text/xsl" href="/cap/nowcast-rss-style.xsl"?&gt; &lt;rss version="2.0" xmlns:atom="http://www.w3.org/2005/Atom"&gt; &lt;channel&gt; &lt;title&gt;Peringatan Dini Cuaca BMKG&lt;/title&gt; &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/rss.xml&lt;/link&gt; &lt;description&gt;Peringatan Dini Cuaca dari BMKG (Badan Meteorologi, Klimatologi, dan Geofisika)&lt;/description&gt; &lt;atom:link href="https://www.bmkg.go.id/alerts/nowcast/id/rss.xml" rel="self" type="application/rss+xml"/&gt; &lt;language&gt;id&lt;/language&gt; …</t>
         </is>
       </c>
       <c r="H8" s="59" t="inlineStr">
@@ -6551,14 +6699,48 @@
       </c>
       <c r="F9" s="62" t="inlineStr">
         <is>
-          <t>(belum terekam saat capture) — Berita WordPress BMKG (WP REST)
-[200] /api-bmkgapi/public/weather/video-latest&amp;hashtag=infobmkgpws</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[502] https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/posts?per_page=4&amp;_embed=1</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
         </is>
       </c>
       <c r="G9" s="62" t="inlineStr">
         <is>
           <t>▸ Berita WordPress BMKG (WP REST)
-(tidak ada response live)
+{"type":"https://developers.cloudflare.com/support/troubleshooting/http-status-codes/cloudflare-5xx-errors/error-502/","title":"Error 502: Bad gateway","status":502,"detail":"The origin web server returned an invalid or incomplete response to Cloudflare. This typically indicates the origin is overloaded or misconfigured.","instance":"a3eff3f4cb3cfd32","error_code":502,"error_name":"origin_bad_gateway","error_category":"origin","ray_id":"a3eff3f4cb3cfd32","timestamp":"2026-09-22T08:31:22Z","zone":"cuaca.bmkg.go.id","cloudflare_error":true,"retryable":true,"retry_after":60,"owner_action_required …
 ▸ Public API: video berita
 [{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari, Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1 …</t>
         </is>
@@ -6600,13 +6782,13 @@
       </c>
       <c r="F10" s="62" t="inlineStr">
         <is>
-          <t>[200] https://data.bmkg.go.id/DataMKG/TEWS/gempadirasakan.json</t>
+          <t>(belum terekam saat capture) — Open Data: gempa (TEWS)</t>
         </is>
       </c>
       <c r="G10" s="62" t="inlineStr">
         <is>
           <t>▸ Open Data: gempa (TEWS)
-{"Infogempa":{"gempa":[{"Tanggal":"22 Sep 2026","Jam":"10:36:27 WIB","DateTime":"2026-09-22T03:36:27+00:00","Coordinates":"-8.43,121.44","Lintang":"8.43 LS","Bujur":"121.44 BT","Magnitude":"4.8","Kedalaman":"14 km","Wilayah":"Pusat gempa berada di laut 31 km timur laut Mbay, Nagekeo","Dirasakan":"IV Kab. Nagekeo, III Kab. Ngada, III Kab. Sikka, III Kab. Ende, II Kab. Manggarai"},{"Tanggal":"21 Sep 2026","Jam":"19:35:22 WIB","DateTime":"2026-09-21T12:35:22+00:00","Coordinates":"-0.52,99.37","Lintang":"0.52 LS","Bujur":"99.37 BT","Magnitude":"4.5","Kedalaman":"10 km","Wilayah":"Pusat gempa berad …</t>
+(tidak ada response live)</t>
         </is>
       </c>
       <c r="H10" s="59" t="inlineStr">
@@ -6732,15 +6914,59 @@
       </c>
       <c r="F13" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json
-[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
-[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
         </is>
       </c>
       <c r="G13" s="62" t="inlineStr">
         <is>
           <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
 ▸ ISDP v1: wilayah laut terdekat
 {"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
 ▸ Maritim: detail cuaca/gelombang perairan
@@ -6791,15 +7017,59 @@
       </c>
       <c r="F14" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
-[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
         </is>
       </c>
       <c r="G14" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ ISDP v1: wilayah laut terdekat
 {"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
 ▸ Maritim: detail cuaca/gelombang perairan
@@ -6825,7 +7095,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="373.5" customHeight="1">
+    <row r="15" ht="294.5" customHeight="1">
       <c r="A15" s="58" t="n">
         <v>11</v>
       </c>
@@ -6851,22 +7121,67 @@
       </c>
       <c r="F15" s="62" t="inlineStr">
         <is>
-          <t>[200] https://maritim.bmkg.go.id/public_api/overview/gelombang.json
-[200] https://maritim.bmkg.go.id/public_api/static/wilayah_perairan.json
-[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json
-[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Maritim: overview tinggi gelombang (232 wilayah)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Maritim: polygon 232 wilayah perairan</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
         </is>
       </c>
       <c r="G15" s="62" t="inlineStr">
         <is>
           <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
-{"U.04": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.02": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "U.01": {"issued": "2026-09-21 23:47 UTC", "today": "Rendah", "tomorrow": "Rendah", "h2": "Rendah", "h3": "Rendah"}, "U.03": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.09": {"issued": "2026-09-21 23:47 UTC", "today": "Tinggi", "tomorrow": "Sedang", "h2": "Tinggi", "h3": "Tinggi"}, "B.05": {"issu …
+(tidak ada response live)
 ▸ Maritim: polygon 232 wilayah perairan
-{"type":"FeatureCollection", "features": [ {"type":"Feature","geometry":{"type":"Polygon","coordinates":[[[106.16613031275644,-7.474222917973128],[106.15132025606444,-7.500473737534255],[106.15132025606444,-9.884923181003366],[105.85018243666048,-9.753669083197725],[104.9517056640126,-9.504286297367011],[104.1717093449007,-9.287717035987708],[103.32259942789281,-9.055834796531078],[102.82399418592888,-8.915830425538395],[102.41424928411693,-8.808639578997123],[102.39943922742495,-8.808639578997123],[105.08005948867658,-6.920768138892684],[105.12942634431657,-6.973269778014939],[105.42562747815 …
+(tidak ada response live)
 ▸ Maritim: detail cuaca/gelombang perairan
 {"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …
 ▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …</t>
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …</t>
         </is>
       </c>
       <c r="H15" s="59" t="inlineStr">
@@ -6963,14 +7278,39 @@
       </c>
       <c r="F17" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+          </r>
         </is>
       </c>
       <c r="G17" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ Overpass API: POI OpenStreetMap
 (tidak ada response live)</t>
         </is>
@@ -7017,19 +7357,83 @@
       </c>
       <c r="F18" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/df/v1/forecast/coord&amp;lat=-7.8385&amp;lon=110.3275
-[200] /api-bmkgevent/source/dwt/apiDF_Kereta/202609101600.json
-(belum terekam saat capture) — Overpass API: POI OpenStreetMap
-(belum terekam saat capture) — Nominatim: geocode OSM
-(belum terekam saat capture) — OSRM: routing</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — Nominatim: geocode OSM</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>(belum terekam saat capture) — OSRM: routing</t>
+          </r>
         </is>
       </c>
       <c r="G18" s="62" t="inlineStr">
         <is>
           <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.31087740815543,"lat":-7.841634455002868,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"34","adm2":"34.02","adm3":"34.02.16","adm4":"34.02.16.2001","provinsi":"Daerah Istimewa Yogyakarta","kotkab":"Bantul","kecamatan":"Kasihan","desa":"Bangunjiwo","lon":110.3108774082,"lat":-7.841634455,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T07:00:00Z","t":30,"tcc":39,"tp":0,"w …
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
 ▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-0 …
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
 ▸ Overpass API: POI OpenStreetMap
 (tidak ada response live)
 ▸ Nominatim: geocode OSM
@@ -7083,8 +7487,33 @@
       </c>
       <c r="F19" s="62" t="inlineStr">
         <is>
-          <t>[200] /api-bmkgapi/v1/public/maritim/nearest-location&amp;lat=-6.2&amp;long=106.816666
-[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
         </is>
       </c>
       <c r="G19" s="62" t="inlineStr">

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6325,8 +6325,8 @@
       </c>
       <c r="E5" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• Present Weather: cuaca saat ini</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ Present Weather: cuaca saat ini</t>
         </is>
       </c>
       <c r="F5" s="62" t="inlineStr">
@@ -6400,10 +6400,10 @@
       </c>
       <c r="E6" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• DF Adm: resolve wilayah admin
-• Present Weather: cuaca saat ini
-• API v1: waktu matahari terbit/terbenam</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ DF Adm: resolve wilayah admin
+▸ Present Weather: cuaca saat ini
+▸ API v1: waktu matahari terbit/terbenam</t>
         </is>
       </c>
       <c r="F6" s="62" t="inlineStr">
@@ -6518,8 +6518,8 @@
       </c>
       <c r="E7" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• Open Data RESMI: prakiraan-cuaca (adm4)</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ Open Data RESMI: prakiraan-cuaca (adm4)</t>
         </is>
       </c>
       <c r="F7" s="62" t="inlineStr">
@@ -6593,9 +6593,9 @@
       </c>
       <c r="E8" s="59" t="inlineStr">
         <is>
-          <t>• Public API: peringatan cuaca
-• Public API: peringatan siklon
-• Peringatan Dini Nowcast (RSS resmi)</t>
+          <t>▸ Public API: peringatan cuaca
+▸ Public API: peringatan siklon
+▸ Peringatan Dini Nowcast (RSS resmi)</t>
         </is>
       </c>
       <c r="F8" s="62" t="inlineStr">
@@ -6693,8 +6693,8 @@
       </c>
       <c r="E9" s="59" t="inlineStr">
         <is>
-          <t>• Berita WordPress BMKG (WP REST)
-• Public API: video berita</t>
+          <t>▸ Berita WordPress BMKG (WP REST)
+▸ Public API: video berita</t>
         </is>
       </c>
       <c r="F9" s="62" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="E10" s="59" t="inlineStr">
         <is>
-          <t>• Open Data: gempa (TEWS)</t>
+          <t>▸ Open Data: gempa (TEWS)</t>
         </is>
       </c>
       <c r="F10" s="62" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E11" s="59" t="inlineStr">
         <is>
-          <t>• Citra Satelit Himawari-9 (background-image, bukan fetch)</t>
+          <t>▸ Citra Satelit Himawari-9 (background-image, bukan fetch)</t>
         </is>
       </c>
       <c r="F11" s="62" t="inlineStr">
@@ -6907,9 +6907,9 @@
       </c>
       <c r="E13" s="59" t="inlineStr">
         <is>
-          <t>• DWT: cuaca kecamatan/stasiun (jalan+kereta)
-• ISDP v1: wilayah laut terdekat
-• Maritim: detail cuaca/gelombang perairan</t>
+          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+▸ ISDP v1: wilayah laut terdekat
+▸ Maritim: detail cuaca/gelombang perairan</t>
         </is>
       </c>
       <c r="F13" s="62" t="inlineStr">
@@ -7010,9 +7010,9 @@
       </c>
       <c r="E14" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• ISDP v1: wilayah laut terdekat
-• Maritim: detail cuaca/gelombang perairan</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ ISDP v1: wilayah laut terdekat
+▸ Maritim: detail cuaca/gelombang perairan</t>
         </is>
       </c>
       <c r="F14" s="62" t="inlineStr">
@@ -7113,10 +7113,10 @@
       </c>
       <c r="E15" s="59" t="inlineStr">
         <is>
-          <t>• Maritim: overview tinggi gelombang (232 wilayah)
-• Maritim: polygon 232 wilayah perairan
-• Maritim: detail cuaca/gelombang perairan
-• DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+▸ Maritim: polygon 232 wilayah perairan
+▸ Maritim: detail cuaca/gelombang perairan
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
         </is>
       </c>
       <c r="F15" s="62" t="inlineStr">
@@ -7222,8 +7222,8 @@
       </c>
       <c r="E16" s="59" t="inlineStr">
         <is>
-          <t>• Maritim: daftar pelabuhan (294)
-• Maritim: detail pelabuhan + pasut</t>
+          <t>▸ Maritim: daftar pelabuhan (294)
+▸ Maritim: detail pelabuhan + pasut</t>
         </is>
       </c>
       <c r="F16" s="62" t="inlineStr">
@@ -7272,8 +7272,8 @@
       </c>
       <c r="E17" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• Overpass API: POI OpenStreetMap</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ Overpass API: POI OpenStreetMap</t>
         </is>
       </c>
       <c r="F17" s="62" t="inlineStr">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="E18" s="59" t="inlineStr">
         <is>
-          <t>• DF Forecast: prakiraan 10 hari + per jam
-• DWT: cuaca kecamatan/stasiun (jalan+kereta)
-• Overpass API: POI OpenStreetMap
-• Nominatim: geocode OSM
-• OSRM: routing</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+▸ Overpass API: POI OpenStreetMap
+▸ Nominatim: geocode OSM
+▸ OSRM: routing</t>
         </is>
       </c>
       <c r="F18" s="62" t="inlineStr">
@@ -7481,8 +7481,8 @@
       </c>
       <c r="E19" s="59" t="inlineStr">
         <is>
-          <t>• ISDP v1: wilayah laut terdekat
-• Maritim: detail cuaca/gelombang perairan</t>
+          <t>▸ ISDP v1: wilayah laut terdekat
+▸ Maritim: detail cuaca/gelombang perairan</t>
         </is>
       </c>
       <c r="F19" s="62" t="inlineStr">

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6249,7 +6249,7 @@
     <row r="2">
       <c r="A2" s="55" t="inlineStr">
         <is>
-          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Kolom "Field dipakai UI" = pemetaan response → nilai yang dirender (sumber: src/services/bmkg/adapters.ts). *(proxy) merah = API tidak bisa diakses langsung dari browser (CORS / header khusus) — harus lewat proxy/alias untuk ambil response-nya. Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
+          <t>Screenshot diambil dari deployment prod (server.mjs + dist, data live) dengan API BOX MARKER aktif — border merah = live, amber = campuran, abu = mock (lihat kolom Status). Kolom "Field dipakai UI" = pemetaan response → nilai yang dirender (sumber: src/services/bmkg/adapters.ts). *(proxy) merah = API tidak bisa diakses langsung dari browser (CORS / header khusus) — harus lewat proxy/alias untuk ambil response-nya. live = respon asli API · estimasi = nilai turunan/konversi dari API · mock = data statis (endpoint belum tersedia). Sumber screenshot: docs/screenshots/cards/ · skrip: docs/scrapping_cuaca-bmkg-go-id/capture_card_screenshots.js</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -6356,7 +6356,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
         </is>
       </c>
@@ -6370,10 +6370,12 @@
       </c>
       <c r="H5" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ data.t, hu, weather_desc, ws, tcc, vs, local_datetime
-  Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ Present Weather: cuaca saat ini
+  Dipakai: data.t, hu, weather_desc, ws, tcc, vs, local_datetime
+  → Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.</t>
         </is>
       </c>
       <c r="I5" s="63" t="inlineStr">
@@ -6413,7 +6415,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -6433,7 +6435,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -6453,7 +6455,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
           <r>
             <t>
@@ -6464,7 +6466,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
           </r>
         </is>
       </c>
@@ -6482,21 +6484,25 @@
       </c>
       <c r="H6" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ provinsi, kotkab, kecamatan, desa
-  Resolusi koordinat → wilayah administratif; label lokasi kartu.
-▸ data.t, hu, weather_desc, ws, tcc, vs, local_datetime
-  Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.
-▸ sunrise, sunset (format 12-jam)
-  Dikonversi ke HH:mm → info matahari terbit/terbenam di CurrentWeather.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ DF Adm: resolve wilayah admin
+  Dipakai: provinsi, kotkab, kecamatan, desa
+  → Resolusi koordinat → wilayah administratif; label lokasi kartu.
+▸ Present Weather: cuaca saat ini
+  Dipakai: data.t, hu, weather_desc, ws, tcc, vs, local_datetime
+  → Kondisi terobservasi saat ini: suhu, status→ikon, "terasa seperti" = t+(hu-50)/10, UV estimasi dari tcc, jarak pandang vs m→km.
+▸ API v1: waktu matahari terbit/terbenam
+  Dipakai: sunrise, sunset (format 12-jam)
+  → Dikonversi ke HH:mm → info matahari terbit/terbenam di CurrentWeather.</t>
         </is>
       </c>
       <c r="I6" s="63" t="inlineStr">
         <is>
           <t>Info matahari (sunset API), wilayah (df/adm).
-– UV: proksi tcc (bukan UV asli) (est)
-– "Terasa seperti": rumus t + (hu-50)/10 (est)</t>
+▸ UV: proksi tcc (bukan UV asli) — estimasi/konversi dari API
+▸ "Terasa seperti": rumus t + (hu-50)/10 — estimasi/konversi dari API</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6535,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -6549,7 +6555,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Open Data RESMI: prakiraan-cuaca (adm4)</t>
+            <t>▸ Open Data RESMI: prakiraan-cuaca (adm4) — (belum terekam saat capture)</t>
           </r>
         </is>
       </c>
@@ -6563,10 +6569,12 @@
       </c>
       <c r="H7" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ data[].cuaca[][] → t, hu, weather_desc, tp
-  Fallback prakiraan resmi (open-data) bila df kosong — bentuk item identik df.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ Open Data RESMI: prakiraan-cuaca (adm4)
+  Dipakai: data[].cuaca[][] → t, hu, weather_desc, tp
+  → Fallback prakiraan resmi (open-data) bila df kosong — bentuk item identik df.</t>
         </is>
       </c>
       <c r="I7" s="63" t="inlineStr">
@@ -6575,7 +6583,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="142.5" customHeight="1">
+    <row r="8" ht="153" customHeight="1">
       <c r="A8" s="58" t="n">
         <v>4</v>
       </c>
@@ -6605,7 +6613,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/public/weather/warning?lat=-6.2&amp;long=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/public/weather/warning?lat=-6.2&amp;long=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -6625,7 +6633,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Public API: peringatan siklon</t>
+            <t>▸ Public API: peringatan siklon — (belum terekam saat capture)</t>
           </r>
           <r>
             <t>
@@ -6636,7 +6644,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://www.bmkg.go.id/alerts/nowcast/id</t>
+            <t>▸ [200] https://www.bmkg.go.id/alerts/nowcast/id</t>
           </r>
           <r>
             <rPr>
@@ -6661,12 +6669,15 @@
       </c>
       <c r="H8" s="59" t="inlineStr">
         <is>
-          <t>▸ data.today / data.tomorrow (warning_level, impact/description)
-  Peringatan hari ini/besok → severity Awas/Siaga/Waspada → AlertsPanel; kosong = tanpa peringatan.
-▸ data siklon terdampak
-  Peringatan siklon untuk wilayah — hanya muncul saat ada siklon aktif.
-▸ XML RSS: &lt;item&gt; per provinsi (title, description, pubDate)
-  Peringatan dini 3-6 jam resmi; difilter per provinsi; menang atas warning internal df.</t>
+          <t>▸ Public API: peringatan cuaca
+  Dipakai: data.today / data.tomorrow (warning_level, impact/description)
+  → Peringatan hari ini/besok → severity Awas/Siaga/Waspada → AlertsPanel; kosong = tanpa peringatan.
+▸ Public API: peringatan siklon
+  Dipakai: data siklon terdampak
+  → Peringatan siklon untuk wilayah — hanya muncul saat ada siklon aktif.
+▸ Peringatan Dini Nowcast (RSS resmi)
+  Dipakai: XML RSS: &lt;item&gt; per provinsi (title, description, pubDate)
+  → Peringatan dini 3-6 jam resmi; difilter per provinsi; menang atas warning internal df.</t>
         </is>
       </c>
       <c r="I8" s="63" t="inlineStr">
@@ -6704,7 +6715,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[502] https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/posts?per_page=4&amp;_embed=1</t>
+            <t>▸ [502] https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/posts?per_page=4&amp;_embed=1</t>
           </r>
           <r>
             <rPr>
@@ -6724,7 +6735,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
           </r>
           <r>
             <rPr>
@@ -6747,15 +6758,17 @@
       </c>
       <c r="H9" s="59" t="inlineStr">
         <is>
-          <t>▸ [].title.rendered, excerpt.rendered, link, _embedded (featured media)
-  Artikel berita WP → NewsSection; fallback mock saat upstream 502 (sering).
-▸ [].judul, video_url
-  Video berita terbaru (per hashtag) → tab video NewsSection.</t>
+          <t>▸ Berita WordPress BMKG (WP REST)
+  Dipakai: [].title.rendered, excerpt.rendered, link, _embedded (featured media)
+  → Artikel berita WP → NewsSection; fallback mock saat upstream 502 (sering).
+▸ Public API: video berita
+  Dipakai: [].judul, video_url
+  → Video berita terbaru (per hashtag) → tab video NewsSection.</t>
         </is>
       </c>
       <c r="I9" s="63" t="inlineStr">
         <is>
-          <t>– Fallback: artikel mock saat WP 502 (sering) (mock)</t>
+          <t>▸ Fallback: artikel mock saat WP 502 (sering) — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6795,7 @@
       </c>
       <c r="F10" s="62" t="inlineStr">
         <is>
-          <t>(belum terekam saat capture) — Open Data: gempa (TEWS)</t>
+          <t>▸ Open Data: gempa (TEWS) — (belum terekam saat capture)</t>
         </is>
       </c>
       <c r="G10" s="62" t="inlineStr">
@@ -6793,8 +6806,9 @@
       </c>
       <c r="H10" s="59" t="inlineStr">
         <is>
-          <t>▸ features[].properties (magnitude, kedalaman, wilayah, waktu)
-  Autogempa terkini + gempa dirasakan → EarthquakePanel.</t>
+          <t>▸ Open Data: gempa (TEWS)
+  Dipakai: features[].properties (magnitude, kedalaman, wilayah, waktu)
+  → Autogempa terkini + gempa dirasakan → EarthquakePanel.</t>
         </is>
       </c>
       <c r="I10" s="63" t="inlineStr">
@@ -6826,7 +6840,7 @@
       </c>
       <c r="F11" s="62" t="inlineStr">
         <is>
-          <t>(belum terekam saat capture) — Citra Satelit Himawari-9 (background-image, bukan fetch)</t>
+          <t>▸ Citra Satelit Himawari-9 (background-image, bukan fetch) — (belum terekam saat capture)</t>
         </is>
       </c>
       <c r="G11" s="62" t="inlineStr">
@@ -6837,8 +6851,9 @@
       </c>
       <c r="H11" s="59" t="inlineStr">
         <is>
-          <t>▸ (PNG) inderaja.bmkg.go.id H08_*.png
-  Citra Himawari-9 → background panel satelit (bukan JSON; terekam sebagai request gambar).</t>
+          <t>▸ Citra Satelit Himawari-9 (background-image, bukan fetch)
+  Dipakai: (PNG) inderaja.bmkg.go.id H08_*.png
+  → Citra Himawari-9 → background panel satelit (bukan JSON; terekam sebagai request gambar).</t>
         </is>
       </c>
       <c r="I11" s="63" t="inlineStr">
@@ -6885,7 +6900,7 @@
       </c>
       <c r="I12" s="63" t="inlineStr">
         <is>
-          <t>– Kartu statis: landmark + nama kota (auto-geser &amp; fetch sengaja dimatikan, 16 Sep) (mock)</t>
+          <t>▸ Kartu statis: landmark + nama kota (auto-geser &amp; fetch sengaja dimatikan, 16 Sep) — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6934,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+            <t>▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
           </r>
           <r>
             <rPr>
@@ -6939,7 +6954,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -6959,7 +6974,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
         </is>
       </c>
@@ -6975,20 +6990,23 @@
       </c>
       <c r="H13" s="59" t="inlineStr">
         <is>
-          <t>▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
-▸ code / nama wilayah laut terdekat
-  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
-▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ ISDP v1: wilayah laut terdekat
+  Dipakai: code / nama wilayah laut terdekat
+  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
         </is>
       </c>
       <c r="I13" s="63" t="inlineStr">
         <is>
-          <t>– Jalan Raya: DWT kecamatan terdekat (live)
-– Kereta: DWT stasiun terdekat (178 stasiun) (live)
-– Maritim: perairan resmi (fix currentSlot 15 Sep) (live)
-– Penerbangan: MOCK/PAUSED (menunggu data partner) (mock)</t>
+          <t>▸ Jalan Raya: DWT kecamatan terdekat — data asli dari API
+▸ Kereta: DWT stasiun terdekat (178 stasiun) — data asli dari API
+▸ Maritim: perairan resmi (fix currentSlot 15 Sep) — data asli dari API
+▸ Penerbangan: MOCK/PAUSED (menunggu data partner) — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7040,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -7042,7 +7060,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -7062,7 +7080,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
         </is>
       </c>
@@ -7078,20 +7096,23 @@
       </c>
       <c r="H14" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ code / nama wilayah laut terdekat
-  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
-▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ ISDP v1: wilayah laut terdekat
+  Dipakai: code / nama wilayah laut terdekat
+  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
         </is>
       </c>
       <c r="I14" s="63" t="inlineStr">
         <is>
-          <t>– Aktivitas umum: forecast live (live)
-– Aktivitas pelayaran: gelombang perairan resmi (live)
-– ISPU/AQI: ESTIMASI sintetis (tidak ada sumber resmi) (est)
-– Indeks kenyamanan: label statis (mock)</t>
+          <t>▸ Aktivitas umum: forecast live — data asli dari API
+▸ Aktivitas pelayaran: gelombang perairan resmi — data asli dari API
+▸ ISPU/AQI: ESTIMASI sintetis (tidak ada sumber resmi) — estimasi/konversi dari API
+▸ Indeks kenyamanan: label statis — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7147,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Maritim: overview tinggi gelombang (232 wilayah)</t>
+            <t>▸ Maritim: overview tinggi gelombang (232 wilayah) — (belum terekam saat capture)</t>
           </r>
           <r>
             <t>
@@ -7137,7 +7158,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Maritim: polygon 232 wilayah perairan</t>
+            <t>▸ Maritim: polygon 232 wilayah perairan — (belum terekam saat capture)</t>
           </r>
           <r>
             <t>
@@ -7148,7 +7169,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
           <r>
             <t>
@@ -7159,7 +7180,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+            <t>▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
           </r>
           <r>
             <rPr>
@@ -7186,21 +7207,25 @@
       </c>
       <c r="H15" s="59" t="inlineStr">
         <is>
-          <t>▸ {code: issued, today, tomorrow, wave_desc}
-  Ringkasan 232 wilayah → warna peta laut + legend gelombang.
-▸ features[].geometry (polygon 232 wilayah)
-  Polygon GeoJSON → layer batas wilayah perairan di peta.
-▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.
-▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.</t>
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+  Dipakai: {code: issued, today, tomorrow, wave_desc}
+  → Ringkasan 232 wilayah → warna peta laut + legend gelombang.
+▸ Maritim: polygon 232 wilayah perairan
+  Dipakai: features[].geometry (polygon 232 wilayah)
+  → Polygon GeoJSON → layer batas wilayah perairan di peta.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.</t>
         </is>
       </c>
       <c r="I15" s="63" t="inlineStr">
         <is>
-          <t>– Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live (live)
-– Layer angin/cuaca: SNAPSHOT statis (sectors.json) (mock)
-– Mode Pelabuhan: snapshot ports.json (294) — hanya pelabuhan TERDEKAT yang live (mock)</t>
+          <t>▸ Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live — data asli dari API
+▸ Layer angin/cuaca: SNAPSHOT statis (sectors.json) — data statis (belum ada endpoint)
+▸ Mode Pelabuhan: snapshot ports.json (294) — hanya pelabuhan TERDEKAT yang live — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7228,8 +7253,8 @@
       </c>
       <c r="F16" s="62" t="inlineStr">
         <is>
-          <t>[200] https://maritim.bmkg.go.id/public_api/pelabuhan_list
-[200] https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
+          <t>▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan_list
+▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
         </is>
       </c>
       <c r="G16" s="62" t="inlineStr">
@@ -7242,10 +7267,12 @@
       </c>
       <c r="H16" s="59" t="inlineStr">
         <is>
-          <t>▸ files[].coor, file
-  Koordinat 294 pelabuhan → pilih terdekat → fetch detail.
-▸ detail pelabuhan + data pasut
-  Pasut (UTC → zona waktu pelabuhan) → PortTideCard; pasut null → blok disembunyikan.</t>
+          <t>▸ Maritim: daftar pelabuhan (294)
+  Dipakai: files[].coor, file
+  → Koordinat 294 pelabuhan → pilih terdekat → fetch detail.
+▸ Maritim: detail pelabuhan + pasut
+  Dipakai: detail pelabuhan + data pasut
+  → Pasut (UTC → zona waktu pelabuhan) → PortTideCard; pasut null → blok disembunyikan.</t>
         </is>
       </c>
       <c r="I16" s="63" t="inlineStr">
@@ -7283,7 +7310,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -7303,7 +7330,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+            <t>▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
           </r>
         </is>
       </c>
@@ -7317,16 +7344,18 @@
       </c>
       <c r="H17" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ elements[].lat/lon/tags
-  POI OpenStreetMap sekitar pengguna → AroundActivity.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ Overpass API: POI OpenStreetMap
+  Dipakai: elements[].lat/lon/tags
+  → POI OpenStreetMap sekitar pengguna → AroundActivity.</t>
         </is>
       </c>
       <c r="I17" s="63" t="inlineStr">
         <is>
           <t>Nilai cuaca per titik POI live (1 request df/coord per POI).
-– Daftar POI: kurasi statis (cityLandmarks) (mock)</t>
+▸ Daftar POI: kurasi statis (cityLandmarks) — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7391,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
           </r>
           <r>
             <rPr>
@@ -7382,7 +7411,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+            <t>▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
           </r>
           <r>
             <rPr>
@@ -7402,7 +7431,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Overpass API: POI OpenStreetMap</t>
+            <t>▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
           </r>
           <r>
             <t>
@@ -7413,7 +7442,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — Nominatim: geocode OSM</t>
+            <t>▸ Nominatim: geocode OSM — (belum terekam saat capture)</t>
           </r>
           <r>
             <t>
@@ -7424,7 +7453,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>(belum terekam saat capture) — OSRM: routing</t>
+            <t>▸ OSRM: routing — (belum terekam saat capture)</t>
           </r>
         </is>
       </c>
@@ -7444,22 +7473,27 @@
       </c>
       <c r="H18" s="59" t="inlineStr">
         <is>
-          <t>▸ data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
-▸ elements[].lat/lon/tags
-  POI OpenStreetMap sekitar pengguna → AroundActivity.
-▸ [].lat/lon/display_name
-  Geocode nama tempat → koordinat.
-▸ routes[].geometry, duration, distance
-  Rute antar titik → panel aktivitas darat.</t>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ Overpass API: POI OpenStreetMap
+  Dipakai: elements[].lat/lon/tags
+  → POI OpenStreetMap sekitar pengguna → AroundActivity.
+▸ Nominatim: geocode OSM
+  Dipakai: [].lat/lon/display_name
+  → Geocode nama tempat → koordinat.
+▸ OSRM: routing
+  Dipakai: routes[].geometry, duration, distance
+  → Rute antar titik → panel aktivitas darat.</t>
         </is>
       </c>
       <c r="I18" s="63" t="inlineStr">
         <is>
           <t>Forecast per titik rute live; fallback mock saat API gagal.
-– Pilihan lokasi awal: daftar statis (mock)</t>
+▸ Pilihan lokasi awal: daftar statis — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7526,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -7512,7 +7546,7 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>[200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
         </is>
       </c>
@@ -7526,16 +7560,18 @@
       </c>
       <c r="H19" s="59" t="inlineStr">
         <is>
-          <t>▸ code / nama wilayah laut terdekat
-  Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
-▸ data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+          <t>▸ ISDP v1: wilayah laut terdekat
+  Dipakai: code / nama wilayah laut terdekat
+  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
         </is>
       </c>
       <c r="I19" s="63" t="inlineStr">
         <is>
           <t>Parameter gelombang resmi di-inject ke drawer.
-– Sisa konten drawer (jenis aktivitas, tabel): statis maritimeAdvisorData.ts (mock)</t>
+▸ Sisa konten drawer (jenis aktivitas, tabel): statis maritimeAdvisorData.ts — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7613,7 @@
       </c>
       <c r="I20" s="63" t="inlineStr">
         <is>
-          <t>– 100% statis (aviationAdvisorData.ts) — API penerbangan belum ada (mock)</t>
+          <t>▸ 100% statis (aviationAdvisorData.ts) — API penerbangan belum ada — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7655,7 @@
       </c>
       <c r="I21" s="63" t="inlineStr">
         <is>
-          <t>– POI statis (poiSearchData.ts) (mock)</t>
+          <t>▸ POI statis (poiSearchData.ts) — data statis (belum ada endpoint)</t>
         </is>
       </c>
     </row>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6348,6 +6348,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6427,6 +6431,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6447,6 +6455,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6458,6 +6470,10 @@
             <t>▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6547,6 +6563,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6625,6 +6645,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6636,6 +6660,10 @@
             <t>▸ Public API: peringatan siklon — (belum terekam saat capture)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6727,6 +6755,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6946,6 +6978,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -6966,6 +7002,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7052,6 +7092,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7072,6 +7116,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7150,6 +7198,10 @@
             <t>▸ Maritim: overview tinggi gelombang (232 wilayah) — (belum terekam saat capture)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7161,6 +7213,10 @@
             <t>▸ Maritim: polygon 232 wilayah perairan — (belum terekam saat capture)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7172,6 +7228,10 @@
             <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7322,6 +7382,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7403,6 +7467,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7423,6 +7491,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7434,6 +7506,10 @@
             <t>▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7445,6 +7521,10 @@
             <t>▸ Nominatim: geocode OSM — (belum terekam saat capture)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>
@@ -7538,6 +7618,10 @@
             <t xml:space="preserve"> *(proxy)</t>
           </r>
           <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
             <t>
 </t>
           </r>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -6352,15 +6352,8 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
         </is>
       </c>
@@ -6435,15 +6428,8 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
           <r>
             <rPr>
@@ -6459,30 +6445,16 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
           </r>
           <r>
             <rPr>
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
           </r>
         </is>
       </c>
@@ -6567,15 +6539,8 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Open Data RESMI: prakiraan-cuaca (adm4) — (belum terekam saat capture)</t>
+            <t xml:space="preserve">
+▸ Open Data RESMI: prakiraan-cuaca (adm4) — (belum terekam saat capture)</t>
           </r>
         </is>
       </c>
@@ -6649,30 +6614,16 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
+            <t xml:space="preserve">
+▸ Public API: peringatan siklon — (belum terekam saat capture)</t>
           </r>
           <r>
             <rPr>
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>▸ Public API: peringatan siklon — (belum terekam saat capture)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://www.bmkg.go.id/alerts/nowcast/id</t>
+            <t xml:space="preserve">
+▸ [200] https://www.bmkg.go.id/alerts/nowcast/id</t>
           </r>
           <r>
             <rPr>
@@ -6759,15 +6710,8 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
           </r>
           <r>
             <rPr>
@@ -6982,9 +6926,541 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
+▸ ISDP v1: wilayah laut terdekat
+{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
+        </is>
+      </c>
+      <c r="H13" s="59" t="inlineStr">
+        <is>
+          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ ISDP v1: wilayah laut terdekat
+  Dipakai: code / nama wilayah laut terdekat
+  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+        </is>
+      </c>
+      <c r="I13" s="63" t="inlineStr">
+        <is>
+          <t>▸ Jalan Raya: DWT kecamatan terdekat — data asli dari API
+▸ Kereta: DWT stasiun terdekat (178 stasiun) — data asli dari API
+▸ Maritim: perairan resmi (fix currentSlot 15 Sep) — data asli dari API
+▸ Penerbangan: MOCK/PAUSED (menunggu data partner) — data statis (belum ada endpoint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="409" customHeight="1">
+      <c r="A14" s="58" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>Panduan Aktivitas &amp; Analisis Cuaca
+(weather-activity)</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="n"/>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E14" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ ISDP v1: wilayah laut terdekat
+▸ Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="F14" s="62" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="62" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
+▸ ISDP v1: wilayah laut terdekat
+{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
+        </is>
+      </c>
+      <c r="H14" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ ISDP v1: wilayah laut terdekat
+  Dipakai: code / nama wilayah laut terdekat
+  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
+        </is>
+      </c>
+      <c r="I14" s="63" t="inlineStr">
+        <is>
+          <t>▸ Aktivitas umum: forecast live — data asli dari API
+▸ Aktivitas pelayaran: gelombang perairan resmi — data asli dari API
+▸ ISPU/AQI: ESTIMASI sintetis (tidak ada sumber resmi) — estimasi/konversi dari API
+▸ Indeks kenyamanan: label statis — data statis (belum ada endpoint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="294.5" customHeight="1">
+      <c r="A15" s="58" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>Peta Laut (Marine Map)
+(marine-map)</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="n"/>
+      <c r="D15" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E15" s="59" t="inlineStr">
+        <is>
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+▸ Maritim: polygon 232 wilayah perairan
+▸ Maritim: detail cuaca/gelombang perairan
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="F15" s="62" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>▸ Maritim: overview tinggi gelombang (232 wilayah) — (belum terekam saat capture)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ Maritim: polygon 232 wilayah perairan — (belum terekam saat capture)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G15" s="62" t="inlineStr">
+        <is>
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+(tidak ada response live)
+▸ Maritim: polygon 232 wilayah perairan
+(tidak ada response live)
+▸ Maritim: detail cuaca/gelombang perairan
+{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …</t>
+        </is>
+      </c>
+      <c r="H15" s="59" t="inlineStr">
+        <is>
+          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
+  Dipakai: {code: issued, today, tomorrow, wave_desc}
+  → Ringkasan 232 wilayah → warna peta laut + legend gelombang.
+▸ Maritim: polygon 232 wilayah perairan
+  Dipakai: features[].geometry (polygon 232 wilayah)
+  → Polygon GeoJSON → layer batas wilayah perairan di peta.
+▸ Maritim: detail cuaca/gelombang perairan
+  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
+  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.</t>
+        </is>
+      </c>
+      <c r="I15" s="63" t="inlineStr">
+        <is>
+          <t>▸ Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live — data asli dari API
+▸ Layer angin/cuaca: SNAPSHOT statis (sectors.json) — data statis (belum ada endpoint)
+▸ Mode Pelabuhan: snapshot ports.json (294) — hanya pelabuhan TERDEKAT yang live — data statis (belum ada endpoint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="287.75" customHeight="1">
+      <c r="A16" s="58" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>Pelabuhan &amp; Pasut
+(port-tide)</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="n"/>
+      <c r="D16" s="61" t="inlineStr">
+        <is>
+          <t>✅ LIVE</t>
+        </is>
+      </c>
+      <c r="E16" s="59" t="inlineStr">
+        <is>
+          <t>▸ Maritim: daftar pelabuhan (294)
+▸ Maritim: detail pelabuhan + pasut</t>
+        </is>
+      </c>
+      <c r="F16" s="62" t="inlineStr">
+        <is>
+          <t>▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan_list
+▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
+        </is>
+      </c>
+      <c r="G16" s="62" t="inlineStr">
+        <is>
+          <t>▸ Maritim: daftar pelabuhan (294)
+{ "files": [ { "coor": [ 1.198331, 109.054462 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1720, "name": "0088_Sintete.json", "portname": "Sintete", "type": "utama" }, { "coor": [ 0.00214, 109.285391 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1713, "name": "0310_PPP Sungai Rengas.json", "portname": "PPP Sungai Rengas", "type": "utama" }, { "coor": [ -2.531535, 110.21588 ], "file_date": "2026-09-21 23:47 UTC", "kb": …
+▸ Maritim: detail pelabuhan + pasut
+{"port_id": "0101", "name": "Sunda Kelapa", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "latitude": -6.11664888, "longitude": 106.80830956, "type": "utama", "data": [{"issued": "2026-09-21 23:47 UTC", "valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "weather": "Berawan", "weather_desc": "Untuk area Sunda Kelapa diperkirakan berawan, dengan kecepatan angin pada umumnya 2 - 14 knot bertiup dari arah timur", "warning_desc": "NIL", "wind_from": "Timur", "wind_to": "Utara", "wind_speed_min": 2, "wind_speed_max": 1 …</t>
+        </is>
+      </c>
+      <c r="H16" s="59" t="inlineStr">
+        <is>
+          <t>▸ Maritim: daftar pelabuhan (294)
+  Dipakai: files[].coor, file
+  → Koordinat 294 pelabuhan → pilih terdekat → fetch detail.
+▸ Maritim: detail pelabuhan + pasut
+  Dipakai: detail pelabuhan + data pasut
+  → Pasut (UTC → zona waktu pelabuhan) → PortTideCard; pasut null → blok disembunyikan.</t>
+        </is>
+      </c>
+      <c r="I16" s="63" t="inlineStr">
+        <is>
+          <t>Pasut null di sebagian pelabuhan → blok disembunyikan. Kolom arus di-skip (satuan ambigu).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="126.5" customHeight="1">
+      <c r="A17" s="58" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="59" t="inlineStr">
+        <is>
+          <t>Aktivitas Sekitar (POI)
+(around-activity)</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="n"/>
+      <c r="D17" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E17" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ Overpass API: POI OpenStreetMap</t>
+        </is>
+      </c>
+      <c r="F17" s="62" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G17" s="62" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
+▸ Overpass API: POI OpenStreetMap
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H17" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ Overpass API: POI OpenStreetMap
+  Dipakai: elements[].lat/lon/tags
+  → POI OpenStreetMap sekitar pengguna → AroundActivity.</t>
+        </is>
+      </c>
+      <c r="I17" s="63" t="inlineStr">
+        <is>
+          <t>Nilai cuaca per titik POI live (1 request df/coord per POI).
+▸ Daftar POI: kurasi statis (cityLandmarks) — data statis (belum ada endpoint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="279" customHeight="1">
+      <c r="A18" s="58" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="59" t="inlineStr">
+        <is>
+          <t>Aktivitas Darat (Drawer)
+(land-based)</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="n"/>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E18" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+▸ Overpass API: POI OpenStreetMap
+▸ Nominatim: geocode OSM
+▸ OSRM: routing</t>
+        </is>
+      </c>
+      <c r="F18" s="62" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <b val="1"/>
+              <color rgb="FFCC0000"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve"> *(proxy)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ Nominatim: geocode OSM — (belum terekam saat capture)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Courier New"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+▸ OSRM: routing — (belum terekam saat capture)</t>
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="62" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
+▸ Overpass API: POI OpenStreetMap
+(tidak ada response live)
+▸ Nominatim: geocode OSM
+(tidak ada response live)
+▸ OSRM: routing
+(tidak ada response live)</t>
+        </is>
+      </c>
+      <c r="H18" s="59" t="inlineStr">
+        <is>
+          <t>▸ DF Forecast: prakiraan 10 hari + per jam
+  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
+  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
+▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
+  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
+  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
+▸ Overpass API: POI OpenStreetMap
+  Dipakai: elements[].lat/lon/tags
+  → POI OpenStreetMap sekitar pengguna → AroundActivity.
+▸ Nominatim: geocode OSM
+  Dipakai: [].lat/lon/display_name
+  → Geocode nama tempat → koordinat.
+▸ OSRM: routing
+  Dipakai: routes[].geometry, duration, distance
+  → Rute antar titik → panel aktivitas darat.</t>
+        </is>
+      </c>
+      <c r="I18" s="63" t="inlineStr">
+        <is>
+          <t>Forecast per titik rute live; fallback mock saat API gagal.
+▸ Pilihan lokasi awal: daftar statis — data statis (belum ada endpoint)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="271.25" customHeight="1">
+      <c r="A19" s="58" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="59" t="inlineStr">
+        <is>
+          <t>Konsultasi Pelayaran (Drawer)
+(maritime-advisor)</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="n"/>
+      <c r="D19" s="65" t="inlineStr">
+        <is>
+          <t>⚠️ CAMPURAN</t>
+        </is>
+      </c>
+      <c r="E19" s="59" t="inlineStr">
+        <is>
+          <t>▸ ISDP v1: wilayah laut terdekat
+▸ Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="F19" s="62" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Courier New"/>
@@ -7006,631 +7482,8 @@
               <rFont val="Courier New"/>
               <sz val="8"/>
             </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
-          </r>
-        </is>
-      </c>
-      <c r="G13" s="62" t="inlineStr">
-        <is>
-          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
-▸ ISDP v1: wilayah laut terdekat
-{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
-▸ Maritim: detail cuaca/gelombang perairan
-{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
-        </is>
-      </c>
-      <c r="H13" s="59" t="inlineStr">
-        <is>
-          <t>▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
-▸ ISDP v1: wilayah laut terdekat
-  Dipakai: code / nama wilayah laut terdekat
-  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
-▸ Maritim: detail cuaca/gelombang perairan
-  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
-        </is>
-      </c>
-      <c r="I13" s="63" t="inlineStr">
-        <is>
-          <t>▸ Jalan Raya: DWT kecamatan terdekat — data asli dari API
-▸ Kereta: DWT stasiun terdekat (178 stasiun) — data asli dari API
-▸ Maritim: perairan resmi (fix currentSlot 15 Sep) — data asli dari API
-▸ Penerbangan: MOCK/PAUSED (menunggu data partner) — data statis (belum ada endpoint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="409" customHeight="1">
-      <c r="A14" s="58" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="59" t="inlineStr">
-        <is>
-          <t>Panduan Aktivitas &amp; Analisis Cuaca
-(weather-activity)</t>
-        </is>
-      </c>
-      <c r="C14" s="60" t="n"/>
-      <c r="D14" s="65" t="inlineStr">
-        <is>
-          <t>⚠️ CAMPURAN</t>
-        </is>
-      </c>
-      <c r="E14" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-▸ ISDP v1: wilayah laut terdekat
-▸ Maritim: detail cuaca/gelombang perairan</t>
-        </is>
-      </c>
-      <c r="F14" s="62" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
-          </r>
-        </is>
-      </c>
-      <c r="G14" s="62" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
-▸ ISDP v1: wilayah laut terdekat
-{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639 …
-▸ Maritim: detail cuaca/gelombang perairan
-{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …</t>
-        </is>
-      </c>
-      <c r="H14" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ ISDP v1: wilayah laut terdekat
-  Dipakai: code / nama wilayah laut terdekat
-  → Anchor koordinat → wilayah perairan/pelabuhan resmi terdekat.
-▸ Maritim: detail cuaca/gelombang perairan
-  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.</t>
-        </is>
-      </c>
-      <c r="I14" s="63" t="inlineStr">
-        <is>
-          <t>▸ Aktivitas umum: forecast live — data asli dari API
-▸ Aktivitas pelayaran: gelombang perairan resmi — data asli dari API
-▸ ISPU/AQI: ESTIMASI sintetis (tidak ada sumber resmi) — estimasi/konversi dari API
-▸ Indeks kenyamanan: label statis — data statis (belum ada endpoint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="294.5" customHeight="1">
-      <c r="A15" s="58" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="59" t="inlineStr">
-        <is>
-          <t>Peta Laut (Marine Map)
-(marine-map)</t>
-        </is>
-      </c>
-      <c r="C15" s="60" t="n"/>
-      <c r="D15" s="65" t="inlineStr">
-        <is>
-          <t>⚠️ CAMPURAN</t>
-        </is>
-      </c>
-      <c r="E15" s="59" t="inlineStr">
-        <is>
-          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
-▸ Maritim: polygon 232 wilayah perairan
-▸ Maritim: detail cuaca/gelombang perairan
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
-        </is>
-      </c>
-      <c r="F15" s="62" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Maritim: overview tinggi gelombang (232 wilayah) — (belum terekam saat capture)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Maritim: polygon 232 wilayah perairan — (belum terekam saat capture)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-        </is>
-      </c>
-      <c r="G15" s="62" t="inlineStr">
-        <is>
-          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
-(tidak ada response live)
-▸ Maritim: polygon 232 wilayah perairan
-(tidak ada response live)
-▸ Maritim: detail cuaca/gelombang perairan
-{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": …
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …</t>
-        </is>
-      </c>
-      <c r="H15" s="59" t="inlineStr">
-        <is>
-          <t>▸ Maritim: overview tinggi gelombang (232 wilayah)
-  Dipakai: {code: issued, today, tomorrow, wave_desc}
-  → Ringkasan 232 wilayah → warna peta laut + legend gelombang.
-▸ Maritim: polygon 232 wilayah perairan
-  Dipakai: features[].geometry (polygon 232 wilayah)
-  → Polygon GeoJSON → layer batas wilayah perairan di peta.
-▸ Maritim: detail cuaca/gelombang perairan
-  Dipakai: data[] → weather_desc, wave_desc, wind_speed_min/max, warning_desc, time_desc
-  → Slot perairan resmi (Hari ini…H+3) → kartu maritim &amp; aktivitas pelayaran; currentSlot = slot pertama yang masih berlaku.
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.</t>
-        </is>
-      </c>
-      <c r="I15" s="63" t="inlineStr">
-        <is>
-          <t>▸ Gelombang: 232 wilayah resmi (warna/legend live), klik → detail live — data asli dari API
-▸ Layer angin/cuaca: SNAPSHOT statis (sectors.json) — data statis (belum ada endpoint)
-▸ Mode Pelabuhan: snapshot ports.json (294) — hanya pelabuhan TERDEKAT yang live — data statis (belum ada endpoint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="287.75" customHeight="1">
-      <c r="A16" s="58" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="59" t="inlineStr">
-        <is>
-          <t>Pelabuhan &amp; Pasut
-(port-tide)</t>
-        </is>
-      </c>
-      <c r="C16" s="60" t="n"/>
-      <c r="D16" s="61" t="inlineStr">
-        <is>
-          <t>✅ LIVE</t>
-        </is>
-      </c>
-      <c r="E16" s="59" t="inlineStr">
-        <is>
-          <t>▸ Maritim: daftar pelabuhan (294)
-▸ Maritim: detail pelabuhan + pasut</t>
-        </is>
-      </c>
-      <c r="F16" s="62" t="inlineStr">
-        <is>
-          <t>▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan_list
-▸ [200] https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
-        </is>
-      </c>
-      <c r="G16" s="62" t="inlineStr">
-        <is>
-          <t>▸ Maritim: daftar pelabuhan (294)
-{ "files": [ { "coor": [ 1.198331, 109.054462 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1720, "name": "0088_Sintete.json", "portname": "Sintete", "type": "utama" }, { "coor": [ 0.00214, 109.285391 ], "file_date": "2026-09-21 23:47 UTC", "kb": 1713, "name": "0310_PPP Sungai Rengas.json", "portname": "PPP Sungai Rengas", "type": "utama" }, { "coor": [ -2.531535, 110.21588 ], "file_date": "2026-09-21 23:47 UTC", "kb": …
-▸ Maritim: detail pelabuhan + pasut
-{"port_id": "0101", "name": "Sunda Kelapa", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "latitude": -6.11664888, "longitude": 106.80830956, "type": "utama", "data": [{"issued": "2026-09-21 23:47 UTC", "valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "weather": "Berawan", "weather_desc": "Untuk area Sunda Kelapa diperkirakan berawan, dengan kecepatan angin pada umumnya 2 - 14 knot bertiup dari arah timur", "warning_desc": "NIL", "wind_from": "Timur", "wind_to": "Utara", "wind_speed_min": 2, "wind_speed_max": 1 …</t>
-        </is>
-      </c>
-      <c r="H16" s="59" t="inlineStr">
-        <is>
-          <t>▸ Maritim: daftar pelabuhan (294)
-  Dipakai: files[].coor, file
-  → Koordinat 294 pelabuhan → pilih terdekat → fetch detail.
-▸ Maritim: detail pelabuhan + pasut
-  Dipakai: detail pelabuhan + data pasut
-  → Pasut (UTC → zona waktu pelabuhan) → PortTideCard; pasut null → blok disembunyikan.</t>
-        </is>
-      </c>
-      <c r="I16" s="63" t="inlineStr">
-        <is>
-          <t>Pasut null di sebagian pelabuhan → blok disembunyikan. Kolom arus di-skip (satuan ambigu).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="126.5" customHeight="1">
-      <c r="A17" s="58" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="59" t="inlineStr">
-        <is>
-          <t>Aktivitas Sekitar (POI)
-(around-activity)</t>
-        </is>
-      </c>
-      <c r="C17" s="60" t="n"/>
-      <c r="D17" s="65" t="inlineStr">
-        <is>
-          <t>⚠️ CAMPURAN</t>
-        </is>
-      </c>
-      <c r="E17" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-▸ Overpass API: POI OpenStreetMap</t>
-        </is>
-      </c>
-      <c r="F17" s="62" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
-          </r>
-        </is>
-      </c>
-      <c r="G17" s="62" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
-▸ Overpass API: POI OpenStreetMap
-(tidak ada response live)</t>
-        </is>
-      </c>
-      <c r="H17" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ Overpass API: POI OpenStreetMap
-  Dipakai: elements[].lat/lon/tags
-  → POI OpenStreetMap sekitar pengguna → AroundActivity.</t>
-        </is>
-      </c>
-      <c r="I17" s="63" t="inlineStr">
-        <is>
-          <t>Nilai cuaca per titik POI live (1 request df/coord per POI).
-▸ Daftar POI: kurasi statis (cityLandmarks) — data statis (belum ada endpoint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="279" customHeight="1">
-      <c r="A18" s="58" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="59" t="inlineStr">
-        <is>
-          <t>Aktivitas Darat (Drawer)
-(land-based)</t>
-        </is>
-      </c>
-      <c r="C18" s="60" t="n"/>
-      <c r="D18" s="65" t="inlineStr">
-        <is>
-          <t>⚠️ CAMPURAN</t>
-        </is>
-      </c>
-      <c r="E18" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-▸ Overpass API: POI OpenStreetMap
-▸ Nominatim: geocode OSM
-▸ OSRM: routing</t>
-        </is>
-      </c>
-      <c r="F18" s="62" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Overpass API: POI OpenStreetMap — (belum terekam saat capture)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ Nominatim: geocode OSM — (belum terekam saat capture)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ OSRM: routing — (belum terekam saat capture)</t>
-          </r>
-        </is>
-      </c>
-      <c r="G18" s="62" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weathe …
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"nd …
-▸ Overpass API: POI OpenStreetMap
-(tidak ada response live)
-▸ Nominatim: geocode OSM
-(tidak ada response live)
-▸ OSRM: routing
-(tidak ada response live)</t>
-        </is>
-      </c>
-      <c r="H18" s="59" t="inlineStr">
-        <is>
-          <t>▸ DF Forecast: prakiraan 10 hari + per jam
-  Dipakai: data[0].cuaca[][] → t, hu, weather_desc, tp, ws, tcc, local_datetime
-  → Suhu &amp; kelembapan; weather_desc → ikon lucide (descToIcon); hujan mm → % (tp×20, aproksimasi); local_datetime → urutan jam &amp; strip 7 hari (slot pertama tiap grup). API tidak punya tmin/tmax/UV → diestimasi.
-▸ DWT: cuaca kecamatan/stasiun (jalan+kereta)
-  Dipakai: rows [kota, kecamatan/stasiun, lat, lng, id, waktu, slots cuaca[]]
-  → Cuaca kecamatan (jalan raya) &amp; stasiun (kereta) terdekat ≤2° → kartu transportasi.
-▸ Overpass API: POI OpenStreetMap
-  Dipakai: elements[].lat/lon/tags
-  → POI OpenStreetMap sekitar pengguna → AroundActivity.
-▸ Nominatim: geocode OSM
-  Dipakai: [].lat/lon/display_name
-  → Geocode nama tempat → koordinat.
-▸ OSRM: routing
-  Dipakai: routes[].geometry, duration, distance
-  → Rute antar titik → panel aktivitas darat.</t>
-        </is>
-      </c>
-      <c r="I18" s="63" t="inlineStr">
-        <is>
-          <t>Forecast per titik rute live; fallback mock saat API gagal.
-▸ Pilihan lokasi awal: daftar statis — data statis (belum ada endpoint)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="271.25" customHeight="1">
-      <c r="A19" s="58" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="59" t="inlineStr">
-        <is>
-          <t>Konsultasi Pelayaran (Drawer)
-(maritime-advisor)</t>
-        </is>
-      </c>
-      <c r="C19" s="60" t="n"/>
-      <c r="D19" s="65" t="inlineStr">
-        <is>
-          <t>⚠️ CAMPURAN</t>
-        </is>
-      </c>
-      <c r="E19" s="59" t="inlineStr">
-        <is>
-          <t>▸ ISDP v1: wilayah laut terdekat
-▸ Maritim: detail cuaca/gelombang perairan</t>
-        </is>
-      </c>
-      <c r="F19" s="62" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <b val="1"/>
-              <color rgb="FFCC0000"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve"> *(proxy)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Courier New"/>
-              <sz val="8"/>
-            </rPr>
-            <t>▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+            <t xml:space="preserve">
+▸ [200] https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
           </r>
         </is>
       </c>

--- a/docs/bmkg-api-mapping.xlsx
+++ b/docs/bmkg-api-mapping.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Official Open Data" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Full" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API Mapping'!$A$1:$L$33</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="50">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -362,6 +363,14 @@
     <font>
       <name val="Courier New"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="53">
@@ -935,7 +944,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1068,6 +1077,11 @@
     <xf numFmtId="0" fontId="0" fillId="52" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16984,4 +16998,5302 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="180" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="66" t="inlineStr">
+        <is>
+          <t>SAMPLE RESPONSE LENGKAP — respons asli utuh dari hasil fetch. Sel Excel maks 32.767 char → respons panjang dipecah per 30.000 char (kolom # = urutan potongan). Sample penuh juga tersedia di docs/screenshots/cards/dump.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="67" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="B2" s="67" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="C2" s="67" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="D2" s="67" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E2" s="67" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="F2" s="67" t="inlineStr">
+        <is>
+          <t>Response (utuh, potongan 30rb char)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="12" customHeight="1">
+      <c r="A3" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B3" s="58" t="inlineStr">
+        <is>
+          <t>DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="C3" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E3" s="58" t="inlineStr">
+        <is>
+          <t>https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+        </is>
+      </c>
+      <c r="F3" s="68" t="inlineStr">
+        <is>
+          <t>[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"ndf"],["lampung","Kab. Way Kanan","Gunung Labuhan",-4.789374036892298,104.57536485624172,"5013720","2026-09-10 16:00:00",["83","26","1","E","3.4"],"ndf"],["lampung","Kab. Way Kanan","Baradatu",-4.638040316921547,104.54443186316593,"5013716","2026-09-10 16:00:00",["79","26","1","E","10.1"],"ndf"],["lampung","Kab. Way Kanan","Blambangan Umpu",-4.475761076323806,104.45210877613977,"5013717","2026-09-10 16:00:00",["82","26","61","E","10.4"],"ndf"],["lampung","Kab. Way Kanan","Way Tuba",-4.369637115463831,104.360737473516,"5013727","2026-09-10 16:00:00",["89","25","1","E","6.1"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Lubuk Raja",-4.220206964297745,104.25604118925946,"5010811","2026-09-10 16:00:00",["89","25","1","E","2.8"],"ndf"],["lampung","Kab. Tulang Bawang Barat","Tulang Bawang Tengah",-4.547795292507033,105.09625266502826,"5013710","2026-09-10 16:00:00",["77","26","1","SE","11.1"],"ndf"],["lampung","Kab. Tulang Bawang","Gedung Meneng",-4.550000259705826,105.3567798505565,"5013697","2026-09-10 16:00:00",["82","26","1","SE","11.8"],"ndf"],["lampung","Kab. Lampung Tengah","Way Seputih",-4.726080374137268,105.42102529771392,"5013587","2026-09-10 16:00:00",["83","26","1","SE","11.8"],"ndf"],["lampung","Kab. Lampung Timur","Way Bungur (Purbolinggo Utara)",-4.893118536746499,105.52001087555635,"5013610","2026-09-10 16:00:00",["83","25","1","S","10.8"],"ndf"],["lampung","Kab. Lampung Selatan","Penengahan",-5.081095956207093,105.5228662287634,"5013552","2026-09-10 16:00:00",["85","25","1","S","10.7"],"ndf"],["lampung","Kab. Lampung Timur","Labuhan Ratu",-5.12582982311676,105.68466957715987,"5013596","2026-09-10 16:00:00",["88","24","1","S","9.9"],"ndf"],["lampung","Kab. Lampung Timur","Mataram Baru",-5.2838260339038925,105.756529299536,"5013599","2026-09-10 16:00:00",["90","24","2","SW","11.7"],"ndf"],["lampung","Kab. Lampung Timur","Labuhan Maringgai",-5.428497263058318,105.80221495084794,"5013595","2026-09-10 16:00:00",["91","24","2","SW","11.5"],"ndf"],["lampung","Kab. Lampung Selatan","Ketapang",-5.641696969180657,105.78079980179547,"5013548","2026-09-10 16:00:00",["90","24","2","SW","8.7"],"ndf"],["lampung","Kab. Lampung Selatan","Bakauheni",-5.81492173040516,105.7655712513581,"5013543","2026-09-10 16:00:00",["90","25","2","SW","11.1"],"ndf"],["lampung","Kab. Lampung Selatan","Bakauheni",-5.7606700194721725,105.69656688218902,"5013543","2026-09-10 16:00:00",["93","23","2","SW","7.3"],"ndf"],["lampung","Kab. Lampung Selatan","Way Panji",-5.642172861381937,105.54523316221827,"5013558","2026-09-10 16:00:00",["88","25","1","S","9.2"],"ndf"],["lampung","Kab. Lampung Selatan","Merbau Mataram",-5.5450908523440035,105.40294139406967,"5013549","2026-09-10 16:00:00",["86","25","1","S","14.8"],"ndf"],["lampung","Kota Bandar Lampung","Tanjung Karang Timur",-5.425166017650099,105.29824510981314,"5013741","2026-09-10 16:00:00",["87","25","10","S","10.8"],"ndf"],["lampung","Kab. Lampung Selatan","Natar",-5.285253710507391,105.1940247177576,"5013550","2026-09-10 16:00:00",["88","24","1","S","1.9"],"ndf"],["lampung","Kab. Lampung Tengah","Bumi Ratu Nuban",-5.084903093816365,105.19259704115422,"5013567","2026-09-10 16:00:00",["81","26","2","S","5.2"],"ndf"],["lampung","Kab. Lampung Tengah","Gunung Sugih",-4.891690860143001,105.2159157590113,"501375","2026-09-10 16:00:00",["79","26","2","SE","8.7"],"ndf"],["lampung","Kab. Tulang Bawang Barat","Panaragan Jaya",-4.425134077656537,104.94566252662167,"5002238","2026-09-10 16:00:00",["75","27","2","SE","11.2"],"ndf"],["lampung","Kab. Way Kanan","Pakuan Ratu",-4.3804002107468705,104.82288233872089,"5013725","2026-09-10 16:00:00",["75","27","1","SE","12.2"],"ndf"],["sumateraselatan","Kab. OKU Timur","Belitang Jaya",-4.300926213152138,104.73960120351683,"5010840","2026-09-10 16:00:00",["74","27","0","E","11.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Belitang",-4.156254983997712,104.6515611463011,"5010837","2026-09-10 16:00:00",["76","26","1","E","11.2"],"ndf"],["sumateraselatan","Kab. OKU Timur","Buay Madang",-4.2181209701493,104.50831759375006,"5010845","2026-09-10 16:00:00",["81","26","61","E","9.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Madang Suku II",-4.1039068418694455,104.4559694516218,"5010851","2026-09-10 16:00:00",["87","25","61","E","8.8"],"ndf"],["sumateraselatan","Kab. OKU Timur","Madang Suku I",-3.975415947554609,104.55019610745262,"5010850","2026-09-10 16:00:00",["86","26","61","E","9.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Semendawai Barat",-3.8316965028024583,104.61111030920199,"5010853","2026-09-10 16:00:00",["77","27","0","SE","7.6"],"ndf"],["sumateraselatan","Kab. OKU Timur","Cempaka",-3.674176184216492,104.70105393522232,"5010848","2026-09-10 16:00:00",["78","27","0","SE","7"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ilir","Teluk Gelam",-3.519987111038688,104.76244402917274,"5010805","2026-09-10 16:00:00",["78","27","0","E","5.9"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Semidang Aji",-4.0760116273443145,104.02428168729153,"5010816","2026-09-10 16:00:00",["85","25","1","E","5.3"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Pengandonan",-4.066017891119884,103.84487032745182,"5010813","2026-09-10 16:00:00",["91","23","1","SE","4.3"],"ndf"],["sumateraselatan","Kab. Muaraenim","Tanjung Agung",-3.9137323867467444,103.79823289173765,"5010738","2026-09-10 16:00:00",["94","24","2","SE","5.9"],"ndf"],["sumateraselatan","Kab. Muaraenim","Lawang Kidul",-3.7295621048954786,103.79918467614004,"5010727","2026-09-10 16:00:00",["97","24","1","E","5.6"],"ndf"],["bengkulu","Kota Bengkulu","Selebar",-3.882543799999894,102.35218700000013,"5011019","2026-09-10 16:00:00",["87","25","10","SE","8.3"],"ndf"],["bengkulu","Kab. Seluma","Air Periukkan",-4.00379229999993,102.46548350000012,"5011000","2026-09-10 16:00:00",["87","25","10","E","9.7"],"ndf"],["bengkulu","Kab. Seluma","Seluma Timur",-4.093860799999959,102.6000661000001,"5011006","2026-09-10 16:00:00",["89","25","1","E","8.2"],"ndf"],["bengkulu","Kab. Seluma","Talo Kecil",-4.204463399999895,102.73121540000005,"5011012","2026-09-10 16:00:00",["89","25","1","E","10.2"],"ndf"],["bengkulu","Kab. Seluma","Semidang Alas Maras",-4.333194599999956,102.76795090000019,"5011009","2026-09-10 16:00:00",["88","25","1","E","11.8"],"ndf"],["bengkulu","Kab. Bengkulu Selatan","Kota Manna",-4.437247899999875,102.8829103000001,"5010899","2026-09-10 16:00:00",["89","25","10","E","13.5"],"ndf"],["bengkulu","Kab. Bengkulu Selatan","Kedurang Ilir",-4.517169199999955,103.00564820000005,"5010898","2026-09-10 16:00:00",["89","25","1","E","15.9"],"ndf"],["bengkulu","Kab. Kaur","Tanjung Kemuning",-4.595883799999967,103.16220340000012,"5010948","2026-09-10 16:00:00",["89","25","1","SE","13.1"],"ndf"],["bengkulu","Kab. Kaur","Kaur Tengah",-4.704700999999943,103.28957610000003,"5010936","2026-09-10 16:00:00",["89","24","10","E","16"],"ndf"],["bengkulu","Kab. Kaur","Maje",-4.81059329999988,103.40355930000004,"5010942","2026-09-10 16:00:00",["89","25","2","E","17.7"],"ndf"],["bengkulu","Kab. Kaur","Nasal",-4.893037599999957,103.53041710000014,"5010944","2026-09-10 16:00:00",["90","25","10","SE","12.9"],"ndf"],["lampung","Kab. Pesisir Barat","Lemong",-4.893037599999957,103.6734110000001,"5013655","2026-09-10 16:00:00",["96","23","10","SE","5.8"],"ndf"],["lampung","Kab. Pesisir Barat","Pesisir Utara",-5.0134358999999336,103.75134520000006,"5013659","2026-09-10 16:00:00",["94","23","2","SE","8.7"],"ndf"],["lampung","Kab. Pesisir Barat","Pulau Pisang",-5.10034909999996,103.86499870000011,"5013660","2026-09-10 16:00:00",["94","23","1","E","9.1"],"ndf"],["lampung","Kab. Pesisir Barat","Krui Selatan",-5.227717699999971,103.9176988000001,"5013654","2026-09-10 16:00:00",["88","25","1","E","15.7"],"ndf"],["lampung","Kab. Pesisir Barat","Pesisir Selatan",-5.326004599999919,104.0217256000002,"5013657","2026-09-10 16:00:00",["88","24","1","E","14.2"],"ndf"],["lampung","Kab. Pesisir Barat","Ngambur",-5.4565736999999785,104.12506570000005,"5013656","2026-09-10 16:00:00",["89","24","1","E","18.4"],"ndf"],["lampung","Kab. Pesisir Barat","Bengkunat Belimbing",-5.519113799999957,104.26565640000013,"5013652","2026-09-10 16:00:00",["90","24","1","E","7.4"],"ndf"],["lampung","Kab. Pesisir Barat","Bengkunat Belimbing",-5.6252117999998745,104.38770760000011,"5013652","2026-09-10 16:00:00",["91","24","2","SE","5.4"],"ndf"],["lampung","Kab. Tanggamus","Semaka",-5.519626399999936,104.4520806000001,"5013686","2026-09-10 16:00:00",["94","23","3","SE","6.1"],"ndf"],["lampung","Kab. Tanggamus","Kota Agung Barat",-5.472978299999909,104.53104490000004,"5013680","2026-09-10 16:00:00",["96","22","10","SE","6.1"],"ndf"],["lampung","Kab. Tanggamus","Kota Agung Timur",-5.484768799999813,104.68845830000004,"5013681","2026-09-10 16:00:00",["98","23","10","SE","7.7"],"ndf"],["lampung","Kab. Tanggamus","Gunung Alip",-5.362067699999955,104.7852754000001,"5013676","2026-09-10 16:00:00",["92","23","2","SW","6.5"],"ndf"],["lampung","Kab. Pringsewu","Gading Rejo",-5.35642769999987,104.96363150000008,"5013665","2026-09-10 16:00:00",["85","24","1","S","8.4"],"ndf"],["lampung","Kab. Pesawaran","Gedong Tataan",-5.373176799999953,105.13117300000016,"5013642","2026-09-10 16:00:00",["91","23","10","SE","4.4"],"ndf"],["bengkulu","Kab. Bengkulu Utara","Air Napal",-3.616926352416101,102.18066538555348,"5010917","2026-09-10 16:00:00",["87","25","1","E","5.7"],"ndf"],["bengkulu","Kab. Bengkulu Utara","Ketahun",-3.3970641554774943,101.85991404196756,"5010926","2026-09-10 16:00:00",["86","26","1","E","10.2"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Basa Ampek Balai Tapan",-2.1388051755944275,101.07707137104939,"5013357","2026-09-10 16:00:00",["92","24","10","NE","4.1"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Linggo Sari Baganti",-1.9008590750113967,100.86672701813393,"5013364","2026-09-10 16:00:00",["96","24","2","NE","1.2"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Batang Kapas",-1.4025999403904734,100.59737203227394,"5013358","2026-09-10 16:00:00",["90","25","2","NE","1.3"],"ndf"],["sumateraselatan","Kab. Lahat","Merapi Barat",-3.741610109121666,103.67829814262313,"5010708","2026-09-10 16:00:00",["97","24","2","E","4.1"],"ndf"],["sumateraselatan","Kab. Lahat","Gumay Talang",-3.778729700812562,103.52363317724416,"5010700","2026-09-10 16:00:00",["98","24","1","SW","1.8"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ilir","Mesuji",-4.002724228364855,105.08409361928841,"5010795","2026-09-10 16:00:00",["78","27","1","SE","11"],"ndf"],["sumateraselatan","Kab. Muaraenim","Lubai",-3.7394527311431034,104.22896887166553,"5010729","2026-09-10 16:00:00",["90","25","61","SE","8.6"],"ndf"],["sumateraselatan","Kota Lubuk Linggau","Lubuklinggau Utara I ?",-3.1277588999999466,102.81657850000005,"5010866","2026-09-10 16:00:00",["97","24","3","W","8"],"ndf"],["sumateraselatan","Kab. Muaraenim","Kelekar",-3.2226338006767037,104.49499261211736,"5010726","2026-09-10 16:00:00",["76","27","1","E","9.6"],"ndf"],["jambi","Kab. Tebo","Tebo Tengah",-1.4767471163646633,102.46032468195699,"5010653","2026-09-10 16:00:00",["99","23","61","E","6.4"],"ndf"],["jambi","Kab. Batanghari","Muara Tembesi",-1.723735168769906,103.14085052962446,"5010549","2026-09-10 16:00:00",["97","24","61","N","4.3"],"ndf"],["sumaterabarat","Kab. Padang Pariaman","2x11 Enam Lingkung",-0.5355243498658524,100.33670207908523,"5013317","2026-09-10 16:00:00",["97","21","2","NE","2.2"],"ndf"],["sumaterabarat","Kab. Sijunjung","Kamang Baru",-0.8766470506943165,101.32199053676788,"5013372","2026-09-10 16:00:00",["98","23","10","S","1.9"],"ndf"],["sumaterabarat","Kab. Dharmasraya","Sungai Rumbai",-1.1945430410731888,101.72554712335665,"5013259","2026-09-10 16:00:00",["99","24","10","E","4.3"],"ndf"],["sumaterabarat","Kab. Tanah Datar","Tanjung Emas",-0.491785099999845,100.6741378000001,"5013412","2026-09-10 16:00:00",["94","22","10","N","1.6"],"ndf"],["sumaterabarat","Kab. Pasaman","Lubuk Sikaping",0.15118809641677444,100.16776034767128,"501543","2026-09-10 16:00:00",["99","19","45","NE","1"],"ndf"],["sumaterabarat","Kab. Pasaman","Rao",0.5304741807460687,100.03213107033895,"5013340","2026-09-10 16:00:00",["96","21","2","SW","5.9"],"ndf"],["sumaterautara","Kab. Mandailing Natal","Kotanopan",0.6722900566936119,99.69424760751104,"5011926","2026-09-10 16:00:00",["98","19","3","NE","0.7"],"ndf"],["sumaterautara","Kab. Tapanuli Selatan","Tanotombangan Angkola",1.0929787625244103,99.4543979381234,"5012118","2026-09-10 16:00:00",["99","21","3","SW","2.4"],"ndf"],["riau","Kab. Pelalawan","Pangkalan Kerinci",0.3599183816165237,101.90091017221368,"501476","2026-09-10 16:00:00",["98","24","10","E","6.3"],"ndf"],["riau","Kab. Pelalawan","Pangkalan Lesung",0.026317948599057672,102.11173041733036,"5010481","2026-09-10 16:00:00",["99","24","61","E","3.3"],"ndf"],["jambi","Kab. Tanjung Jabung Barat","Tungkal Ulu",-1.1039260291702249,103.03400950319013,"5010634","2026-09-10 16:00:00",["98","24","61","S","4.8"],"ndf"],["jambi","Kab. Tanjung Jabung Barat","Merlung",-1.2552597491409756,103.05209340683433,"5010627","2026-09-10 16:00:00",["99","23","61","N","3.1"],"ndf"],["jambi","Kab. Tanjung Jabung Timur","Mendahara Ulu",-1.3394926687474253,103.3704652894146,"5010640","2026-09-10 16:00:00",["99","24","61","NE","1.7"],"ndf"],["jambi","Kab. Muaro Jambi","Sakernan",-1.4337193245782487,103.50038386033287,"501210","2026-09-10 16:00:00",["97","24","61","W","9.7"],"ndf"],["jambi","Kota Jambi","Danau Teluk",-1.5755352005258487,103.56748466069729,"5010671","2026-09-10 16:00:00",["97","25","61","SW","1.4"],"ndf"],["sumaterautara","Kab. Tapanuli Tengah","Sibabangun",1.5198540669704244,98.96518075532475,"5012129","2026-09-10 16:00:00",["99","24","3","NE","2.9"],"ndf"],["sumaterautara","Kab. Tapanuli Tengah","Badiri",1.6350199796524976,98.84620770503324,"5012120","2026-09-10 16:00:00",["91","24","3","NE","2.3"],"ndf"],["sumaterautara","Kab. Tapanuli Selatan","Marancar",1.6430110028638296,99.1889492340814,"5012114","2026-09-10 16:00:00",["99","21","3","SW","2.3"],"ndf"],["riau","Kab. Siak","Kandis",0.7279020261682376,101.44964539245808,"5010518","2026-09-10 16:00:00",["99","24","10","E","6.7"],"ndf"],["riau","Kota Dumai","Dumai Barat",1.6187722267511617,101.33638304858044,"5010531","2026-09-10 16:00:00",["97","25","10","SE","4.5"],"ndf"],["sumaterautara","Kab. Toba Samosir","Tampahan",2.3326779465620007,99.07225650058712,"5012169","2026-09-10 16:00:00",["92","20","3","SE","4.9"],"ndf"],["sumaterautara","Kab. Samosir","Pangururan",2.5125057120776546,98.64444924058057,"501583","2026-09-10 16:00:00",["96","17","3","SW","5.8"],"ndf"],["sumaterautara","Kab. Labuhanbatu","Bilah Barat",2.1867793121053296,99.77132231525815,"5011883","2026-09-10 16:00:00",["96","25","3","E","0.1"],"ndf"],["sumaterautara","Kab. Labuhanbatu Selatan","Kota Pinang",2.0421080829509037,100.04115319331925,"5002211","2026-09-10 16:00:00",["96","25","2","SE","5.5"],"ndf"],["riau","Kab. Rokan Hilir","Bangko Pusako",1.6242747303271585,101.02149112772133,"5010487","2026-09-10 16:00:00",["98","25","10","S","0.7"],"ndf"],["sumaterautara","Kab. Deli Serdang","Pancur Batu",3.4431624835622756,98.60141470540583,"5011843","2026-09-10 16:00:00",["97","24","3","S","2"],"ndf"],["sumaterautara","Kab. Deli Serdang","Sibolangit",3.2782658358581216,98.55323062003777,"5011848","2026-09-10 16:00:00",["94","20","3","S","5.3"],"ndf"],["aceh","Kab. Aceh Utara","Aceh Utara",5.070186364360438,97.30967472628646,"501408","2026-09-10 16:00:00",["98","24","3","SW","5.6"],"ndf"],["aceh","Kota Lhokseumawe","Blang Mangat",5.130624673908642,97.14882316229244,"5012856","2026-09-10 16:00:00",["97","24","3","SW","5.6"],"ndf"],["aceh","Kab. Bireuen","Simpang Mamplam",5.189635306853177,96.48114640405635,"5012778","2026-09-10 16:00:00",["84","26","3","SE","6.8"],"ndf"],["aceh","Kab. Aceh Besar","Lembah Seulawah",5.367714168529517,95.64214845340064,"5012612","2026-09-10 16:00:00",["93","23","3","SE","2.6"],"ndf"],["aceh","Kab. Nagan Raya","Kuala Pesisir",4.10755261128395,96.19836729235533,"5012794","2026-09-10 16:00:00",["97","25","3","N","7.1"],"ndf"],["aceh","Kab. Nagan Raya","Darul Makmur",4.0361687811090405,96.46914995481876,"5012792","2026-09-10 16:00:00",["98","24","3","W","2.3"],"ndf"],["aceh","Kab. Aceh Selatan","Trumon Timur",2.863570397435751,97.75548657457057,"5012647","2026-09-10 16:00:00",["99","23","3","NW","2"],"ndf"],["aceh","Kab. Aceh Barat","Woyla",4.366913860919453,96.07939424206381,"5012586","2026-09-10 16:00:00",["99","24","3","NE","2.1"],"ndf"],["aceh","Kab. Aceh Jaya","Indra Jaya",5.082179839271987,95.36174880270528,"5012623","2026-09-10 16:00:00",["89","25","3","NE","3.5"],"ndf"],["aceh","Kab. Aceh Barat","Samatiga",4.231104891967991,96.00768848190984,"5012584","2026-09-10 16:00:00",["97","26","3","N","8.8"],"ndf"],["sumaterautara","Kab. Dairi","Gunung Sitember",3.0358924913035437,98.15857700719724,"5011820","2026-09-10 16:00:00",["99","20","3","SE","1.5"],"ndf"],["sumaterautara","Kab. Labuhanbatu Utara","Kualuh Leidong",2.7478372097551804,99.9606086067617,"5011897","2026-09-10 16:00:00",["98","25","3","W","0.3"],"ndf"],["sumaterautara","Kab. Padanglawas Utara","Dolok",1.8146469559800216,99.677669247752,"5012024","2026-09-10 16:00:00",["98","22","3","SW","3"],"ndf"],["sumaterautara","Kab. Padanglawas Utara","Halongonan",1.5702810614967202,99.7216209928409,"5012026","2026-09-10 16:00:00",["83","25","3","SW","7.9"],"ndf"],["sumaterabarat","Kab. Pasaman Barat","Koto Balingka",0.2931021322718861,99.52131750259426,"5013347","2026-09-10 16:00:00",["98","23","10","SW","1.5"],"ndf"],["sumaterabarat","Kab. Agam","Tanjung Mutiara",-0.37438688568208195,99.9251241605984,"5013249","2026-09-10 16:00:00",["97","24","10","N","6.5"],"ndf"],["sumaterabarat","Kota Solok","Lubuk Sikarah",-0.8056238864892095,100.65582192270112,"5013302","2026-09-10 16:00:00",["95","21","10","S","1.9"],"ndf"],["sumaterabarat","Kab. Solok Selatan","Koto Parik Gadang Diateh",-1.4400291488376946,101.01292985154838,"5013394","2026-09-10 16:00:00",["98","19","10","S","0.8"],"ndf"],["jambi","Kab. Kerinci","Batang Merangin",-2.2444437264668298,101.72439872517472,"5010570","2026-09-10 16:00:00",["98","19","45","SW","4.1"],"ndf"],["jambi","Kab. Merangin","Renah Pemberap",-2.134648578462278,102.02381998859273,"5010592","2026-09-10 16:00:00",["98","22","61","E","1.9"],"ndf"],["jambi","Kab. Sarolangun","Pauh",-2.1264136211880253,102.8259393364649,"5010620","2026-09-10 16:00:00",["97","24","61","E","4.9"],"ndf"],["jambi","Kab. Tanjung Jabung Timur","Muara Sabak Timur",-1.1554980908004486,103.83610930892148,"5010642","2026-09-10 16:00:00",["99","24","61","SW","7.1"],"ndf"],["kepulauanriau","Kota Batam","Galang",0.7300927288910626,104.21189839179495,"5012398","2026-09-10 16:00:00",["80","28","2","E","10"],"ndf"],["kepulauanbangkabelitung","Kab. Bangka","Puding Besar",-2.0223774065063744,105.92979855405717,"5011028","2026-09-10 16:00:00",["86","23","1","SE","6.9"],"ndf"],["kepulauanbangkabelitung","Kab. Bangka Tengah","Koba",-2.5191715374900148,106.39403886155856,"501362","2026-09-10 16:00:00",["78","25","1","E","4.5"],"ndf"],["riau","Kab. Kuantan Sengingi","Singingi Hilir",-0.24011737986285892,101.32332980439209,"5010473","2026-09-10 16:00:00",["98","24","10","SE","2.4"],"ndf"],["sumaterabarat","Kab. Kepulauan Mentawai","Sikakap",-2.7726252574708035,100.2143287823482,"5013269","2026-09-10 16:00:00",["87","26","2","E","7.5"],"ndf"],["sumaterautara","Kab. Nias Barat","Sirombu",0.9659768999641882,97.41151473543331,"5011978","2026-09-10 16:00:00",["84","26","3","E","6.3"],"ndf"],["jawatimur","Kab. Jember","Sumber Baru",-8.118434441419254,113.3540335906813,"5008259","2026-09-10 16:00:00",["99","22","10","SW","3.5"],"ndf"],["jawatimur","Kab. Jember","Sumber Sari",-8.176136370810639,113.68656326624614,"5008261","2026-09-10 16:00:00",["94","23","3","W","2.7"],"ndf"],["jawatimur","Kab. Banyuwangi","Kalibaru",-8.196956654611654,113.89476610425629,"5008127","2026-09-10 16:00:00",["95","21","10","SE","10.2"],"ndf"],["jawatimur","Kab. Banyuwangi","Kalibaru",-8.243951009476802,113.91618125330876,"5008127","2026-09-10 16:00:00",["97","20","45","E","12.8"],"ndf"],["jawatimur","Kab. Banyuwangi","Banyuwangi",-8.24454587472826,114.35400207838154,"501273","2026-09-10 16:00:00",["95","24","3","S","6.5"],"ndf"],["jawatimur","Kab. Banyuwangi","Banyuwangi",-8.176136370810639,114.38136587994859,"501273","2026-09-10 16:00:00",["94","23","10","SW","8.2"],"ndf"],["jawatimur","Kota Blitar","Alun - Alun Kota Blitar",-8.108369321364535,112.16028179866623,"5008317","2026-09-10 16:00:00",["92","23","3","SE","7"],"ndf"],["daerahistimewayogyakarta","Kab. Bantul","Piyungan",-7.832351844688219,110.45040111987669,"5008072","2026-09-10 16:00:00",["90","23","3","S","4.7"],"ndf"],["daerahistimewayogyakarta","Kab. Gunung Kidul","Gunung Kidul",-7.9679811220205465,110.60363840865222,"501189","2026-09-10 16:00:00",["91","22","3","SE","8.8"],"ndf"],["jawatengah","Kab. Wonogiri","Giritontro",-8.098375585140104,110.91534780041599,"5010364","2026-09-10 16:00:00",["95","22","1","SE","6.6"],"ndf"],["jawatimur","Kab. Ponorogo","Slahung",-8.036985491189625,111.41075158182969,"5008612","2026-09-10 16:00:00",["93","21","10","S","4.7"],"ndf"],["daerahistimewayogyakarta","Kab. Bantul","Kasihan",-7.828068814877668,110.35284321863764,"5008046","2026-09-10 16:00:00",["88","23","3","W","3.4"],"ndf"],["jawatimur","Kab. Situbondo","Banyuputih",-7.786130814649994,114.30556021807126,"5008672","2026-09-10 16:00:00",["85","24","3","SE","3.8"],"ndf"],["jawatimur","Kab. Situbondo","Banyuputih",-7.834195926967709,114.30889146347931,"5008672","2026-09-10 16:00:00",["85","24","3","SE","3.8"],"ndf"],["jawatimur","Kab. Banyuwangi","Wongsorejo",-8.018366208819032,114.40882882572419,"5008143","2026-09-10 16:00:00",["91","24","3","S","17.4"],"ndf"],["jawatengah","Kab. Kebumen","Sempor",-7.61153786334711,109.50956223817127,"5010067","2026-09-10 16:00:00",["95","22","1","SE","2.9"],"ndf"],["jawatengah","Kab. Kebumen","Karanganyar",-7.632477120198473,109.5723800087253,"5010052","2026-09-10 16:00:00",["91","23","1","S","2.5"],"ndf"],["jawatengah","Kab. Purworejo","Butuh",-7.722420746218916,109.83316893496419,"5010252","2026-09-10 16:00:00",["88","24","1","NW","0.3"],"ndf"],["jawatimur","Kota Malang","Kedungkandang",-8.028213211614855,112.61394190250121,"5008333","2026-09-10 16:00:00",["93","22","3","SW","3.1"],"ndf"],["jawatimur","Kab. Malang","Kabupaten Malang",-8.12755570860827,112.57111160439626,"501284","2026-09-10 16:00:00",["94","22","3","SE","4.5"],"ndf"],["jawatimur","Kab. Jombang","Perak",-7.5817668403959715,112.16041663479007,"5008281","2026-09-10 16:00:00",["86","24","3","SW","11.1"],"ndf"],["jawatimur","Kab. Mojokerto","Jetis",-7.43045776770731,112.44390250224751,"5008499","2026-09-10 16:00:00",["79","25","2","W","6.9"],"ndf"],["jawatimur","Kab. Nganjuk","Bagor",-7.555592769331838,111.79278990938923,"5008511","2026-09-10 16:00:00",["82","24","2","W","3.9"],"ndf"],["jawatengah","Kab. Banyumas","Jatilawang",-7.537159878073226,109.13536820039445,"5009872","2026-09-10 16:00:00",["84","25","1","SE","3.1"],"ndf"],["jawatengah","Kab. Banyumas","Sokaraja",-7.440791707337098,109.26742828621803,"5009888","2026-09-10 16:00:00",["87","24","1","E","3.8"],"ndf"],["jawatengah","Kab. Banjarnegara","Purworejo Klampok",-7.461017125886656,109.44350840064948,"5009861","2026-09-10 16:00:00",["88","24","1","S","2.7"],"ndf"],["jawatimur","Kota Mojokerto","Magersari",-7.461009194350083,112.45903899102177,"5008337","2026-09-10 16:00:00",["76","26","2","SW","5.2"],"ndf"],["jawatimur","Kab. Madiun","Mejayan",-7.553356075986358,111.64272523528831,"5008436","2026-09-10 16:00:00",["81","24","2","W","3.2"],"ndf"],["jawatimur","Kab. Ngawi","Kasreman",-7.418178896245138,111.49654701416335,"5008536","2026-09-10 16:00:00",["78","24","2","SE","11"],"ndf"],["daerahistimewayogyakarta","Kab. Sleman","Sleman",-7.713826926219554,110.35797492287355,"501187","2026-09-10 16:00:00",["89","23","10","NW","3"],"ndf"],["jawatengah","Kab. Cilacap","Cipari",-7.440184199999976,108.76107340000016,"5009964","2026-09-10 16:00:00",["84","25","1","S","3.3"],"ndf"],["jawatimur","Kota Surabaya","Surabaya",-7.279277860029765,112.70971520798605,"501306","2026-09-10 16:00:00",["76","27","2","E","6.6"],"ndf"],["jawatimur","Kab. Bojonegoro","Bojonegoro",-7.157770683767069,111.8667911466705,"501277","2026-09-10 16:00:00",["78","25","2","SE","6.7"],"ndf"],["jawabarat","Kab. Pangandaran","Cijulang",-7.734162599999934,108.4657916000001,"5009361","2026-09-10 16:00:00",["90","24","3","NE","4.4"],"ndf"],["jawatengah","Kota Semarang","Semarang Utara",-6.958050624242674,110.41531993311418,"5010138","2026-09-10 16:00:00",["73","27","1","SE","2.3"],"ndf"],["jawatengah","Kab. Kudus","Kudus",-6.802790793612246,110.86801238947339,"501250","2026-09-10 16:00:00",["74","26","1","S","3.3"],"ndf"],["jawabarat","Kab. Tasikmalaya","Pagerageung",-7.10885689702377,108.10565645012139,"5009639","2026-09-10 16:00:00",["99","19","3","SE","4"],"ndf"],["banten","Kab. Lebak","Panggarangan",-6.875927493394784,106.10496697017805,"5008819","2026-09-10 16:00:00",["90","23","2","SE","14.1"],"ndf"],["jawabarat","Kota Bandung","Bandung Kidul",-6.947036621274037,107.61004316015442,"5009239","2026-09-10 16:00:00",["88","22","3","SE","3.7"],"ndf"],["jawabarat","Kab. Cirebon","Pabedilan",-6.828457246328412,108.74908650070802,"5009627","2026-09-10 16:00:00",["76","26","3","S","12.9"],"ndf"],["jawabarat","Kab. Cirebon","Gebang",-6.813585615041973,108.69554862807684,"5009469","2026-09-10 16:00:00",["76","26","3","S","17.2"],"ndf"],["jawabarat","Kab. Cirebon","Astanajapura",-6.7942236062342545,108.60541475410236,"5009232","2026-09-10 16:00:00",["74","25","3","S","11.3"],"ndf"],["jawabarat","Kab. Cirebon","Karangsembung",-6.830391413522818,108.64158256139103,"5009534","2026-09-10 16:00:00",["75","26","3","S","17.2"],"ndf"],["jawabarat","Kab. Cirebon","Weru",-6.702077059376336,108.4675473687829,"5009845","2026-09-10 16:00:00",["78","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Kedawung (Cirebon Barat)",-6.721112747422978,108.50657052927858,"5009546","2026-09-10 16:00:00",["81","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Jamblang",-6.689793026001496,108.44131299157277,"5009493","2026-09-10 16:00:00",["78","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Klangenan",-6.6888412415992775,108.39657912466316,"5009557","2026-09-10 16:00:00",["78","26","3","S","0.1"],"ndf"],["jawabarat","Kab. Indramayu","Terisi",-6.573623776383727,107.94915346004183,"5009830","2026-09-10 16:00:00",["93","25","3","S","4.3"],"ndf"],["jawabarat","Kab. Cirebon","Ciwaringin",-6.694262449379266,108.36853346231942,"5009446","2026-09-10 16:00:00",["78","26","3","S","0.1"],"ndf"],["jawabarat","Kab. Cirebon","Arjawinangun",-6.623506338359618,108.37730365008366,"5009230","2026-09-10 16:00:00",["75","27","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Suranenggala",-6.603280919810061,108.5141226579189,"5009790","2026-09-10 16:00:00",["71","27","3","E","1.8"],"ndf"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="12" customHeight="1">
+      <c r="A4" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B4" s="58" t="inlineStr">
+        <is>
+          <t>DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="C4" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" s="58" t="inlineStr">
+        <is>
+          <t>https://publik.bmkg.go.id/event/source/dwt/apiDF_Kereta/202609101600.json</t>
+        </is>
+      </c>
+      <c r="F4" s="68" t="inlineStr">
+        <is>
+          <t>[["","Kota Jakarta Pusat","Menteng ",-6.19809917164,106.84108701,"5005610","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.149180001,106.827000026,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Taman Sari",-6.141079981,106.822740007,"5005622","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Pusat","Senen ",-6.193899969,106.856519999,"5005611","2026-09-10 16:00:00",["85","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Pusat","Kemayoran ",-6.174619999,106.844179993,"5005614","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Barat","Cengkareng ",-6.158600003,106.756496988,"5005623","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Tangerang","Batuceper",-6.169660008,106.681367978,"5008776","2026-09-10 16:00:00",["85","26","2","SE","2.4"],"ndf"],["","Kota Jakarta Barat","Grogol Petamburan ",-6.161280032,106.772031002,"5005620","2026-09-10 16:00:00",["82","26","2","E","0.5"],"ndf"],["","Kota Jakarta Barat","Tambora",-6.155889966,106.801510993,"5005621","2026-09-10 16:00:00",["81","26","2","E","0.5"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.212939965,106.900340002,"501191","2026-09-10 16:00:00",["88","26","2","SE","2.5"],"ndf"],["","Kota Jakarta Selatan","Tebet ",-6.225910038,106.858320013,"5005597","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kab. Karawang","Kotabaru",-6.406120034,107.458950011,"5009561","2026-09-10 16:00:00",["92","26","3","SW","1.3"],"ndf"],["","Kab. Serang","Jawilan",-6.334949965,106.33276253,"5008873","2026-09-10 16:00:00",["89","24","3","S","3.9"],"ndf"],["","Kab. Bekasi","Kedungwaringin",-6.270000022,107.261150004,"5009548","2026-09-10 16:00:00",["90","25","3","SW","2.3"],"ndf"],["","Kota Depok","Sawangan",-6.368989963,106.832360001,"5009727","2026-09-10 16:00:00",["93","25","2","SE","1.8"],"ndf"],["","Kota Jakarta Selatan","Jagakarsa ",-6.360730017,106.831639996,"5005589","2026-09-10 16:00:00",["93","25","2","SE","1.8"],"ndf"],["","Kab. Tangerang","Cisauk",-6.329640029,106.61896999,"5008894","2026-09-10 16:00:00",["89","25","2","E","4.6"],"ndf"],["","Kota Cilegon","Citangkil",-6.009779982,106.023030421,"5008764","2026-09-10 16:00:00",["87","26","3","E","4.5"],"ndf"],["","Kota Bekasi","Bekasi Barat",-6.219139975,106.952000018,"5009262","2026-09-10 16:00:00",["92","25","2","SE","3"],"ndf"],["","Kab. Sukabumi","Parungkuda",-6.846540011,106.76064997,"5009670","2026-09-10 16:00:00",["93","21","3","S","0.6"],"ndf"],["","Kab. Sukabumi","Cibadak",-6.905019963,106.853160029,"5009310","2026-09-10 16:00:00",["90","22","3","SW","2"],"ndf"],["","Kota Jakarta Selatan","Pancoran ",-6.242699996,106.858750004,"5005596","2026-09-10 16:00:00",["89","26","2","SE","3.1"],"ndf"],["","Kota Jakarta Selatan","Pasar Minggu ",-6.309420029,106.83846999,"5005590","2026-09-10 16:00:00",["92","25","2","SE","1.4"],"ndf"],["","Kota Jakarta Timur","Jakarta Timur",-6.214249972,106.88500003,"501191","2026-09-10 16:00:00",["87","26","2","SE","2.5"],"ndf"],["","Kota Bekasi","Bekasi",-6.236720011,106.999240005,"5002228","2026-09-10 16:00:00",["96","25","2","S","1.4"],"ndf"],["","Kab. Tangerang","Jambe",-6.338020004,106.492464608,"5008898","2026-09-10 16:00:00",["90","24","2","E","3.2"],"ndf"],["","Kota Jakarta Timur","Kramat Jati ",-6.284359982,106.844479982,"5005603","2026-09-10 16:00:00",["90","25","2","SE","3.1"],"ndf"],["","Kab. Sukabumi","Parungkuda",-6.817680029,106.76002996,"5009670","2026-09-10 16:00:00",["95","21","3","SE","2.2"],"ndf"],["","Kota Depok","Cipayung",-6.448809989,106.802580021,"5009421","2026-09-10 16:00:00",["92","25","2","S","3"],"ndf"],["","Kab. Serang","Kramatwatu",-6.039119996,106.162011176,"5008877","2026-09-10 16:00:00",["83","26","3","SE","4.9"],"ndf"],["","Kab. Sukabumi","Sukalarang",-6.89644997,106.822449993,"5009761","2026-09-10 16:00:00",["88","22","3","S","0.6"],"ndf"],["","Kota Serang","Walantaka",-6.155480007,106.218802007,"5008775","2026-09-10 16:00:00",["92","25","3","S","2.5"],"ndf"],["","Kab. Tangerang","Solear",-6.328520039,106.434704075,"5008916","2026-09-10 16:00:00",["89","24","3","SE","3"],"ndf"],["","Kab. Tangerang","Solear",-6.335620014,106.411984004,"5008916","2026-09-10 16:00:00",["89","24","3","SE","3"],"ndf"],["","Kab. Tangerang","Solear",-6.332230037,106.39606325,"5008916","2026-09-10 16:00:00",["90","24","3","S","2.9"],"ndf"],["","Kab. Serang","Pamarayan",-6.26566004,106.267939992,"5008882","2026-09-10 16:00:00",["90","24","2","S","4.6"],"ndf"],["","Kab. Sukabumi","Ciambar",-6.79041001,106.779489974,"5009300","2026-09-10 16:00:00",["98","20","3","SE","2.2"],"ndf"],["","Kab. Sukabumi","Sukabumi",-6.92388,106.924769981,"501222","2026-09-10 16:00:00",["95","20","3","SW","2"],"ndf"],["","Kab. Serang","Serang",-6.112409011,106.158660008,"501174","2026-09-10 16:00:00",["89","25","3","SE","4.1"],"ndf"],["","Kab. Sukabumi","Cisaat",-6.913860021,106.887530023,"5009431","2026-09-10 16:00:00",["94","21","3","SW","2"],"ndf"],["","Kab. Karawang","Kotabaru",-6.393169994,107.433280014,"5009561","2026-09-10 16:00:00",["93","26","3","W","0.5"],"ndf"],["","Kab. Serang","Petir",-6.216999991,106.244602175,"5008883","2026-09-10 16:00:00",["92","24","2","S","5.5"],"ndf"],["","Kab. Serang","Kramatwatu",-6.031319965,106.121480567,"5008877","2026-09-10 16:00:00",["84","26","3","SE","5.9"],"ndf"],["","Kota Bekasi","Bekasi Barat",-6.224300042,106.979159983,"5009262","2026-09-10 16:00:00",["93","25","2","SE","3"],"ndf"],["","Kota Jakarta Pusat","Tanah Abang ",-6.200801041,106.816016966,"5005609","2026-09-10 16:00:00",["84","26","2","E","0.5"],"ndf"],["","Kab. Nganjuk","Kertosono",-7.602842,112.038984,"5008516","2026-09-10 16:00:00",["84","24","3","S","21.2"],"ndf"],["","Kota Surabaya","Wonokromo",-7.30213001992,112.73931,"5008377","2026-09-10 16:00:00",["74","27","3","SW","2"],"ndf"],["","Kab. Brebes","Peguyangan",-7.285556,109.029722,"5009950","2026-09-10 16:00:00",["94","20","2","E","4.2"],"ndf"],["","Kab. Brebes","Bumiayu",-7.237436,109.009813,"5002225","2026-09-10 16:00:00",["89","22","2","SE","6.9"],"ndf"],["","Kab. Sragen","Sragen",-7.419102,111.063886,"501264","2026-09-10 16:00:00",["78","24","3","S","8.7"],"ndf"],["","Kab. Gresik","Driyorejo",-7.38783998956,112.61956716,"5008222","2026-09-10 16:00:00",["74","26","3","W","6.9"],"ndf"],["","Kab. Jombang","Perak",-7.5826728,112.1670949,"5008281","2026-09-10 16:00:00",["85","24","3","S","11.8"],"ndf"],["","Kab. Pemalang","Pemalang",-6.887265969,109.388038578,"5010222","2026-09-10 16:00:00",["77","26","2","S","5.2"],"ndf"],["","Kab. Pemalang","Petarukan",-6.897705545,109.449630924,"5010223","2026-09-10 16:00:00",["78","25","2","S","5.7"],"ndf"],["","Kab. Batang","Banyuputih",-6.919783422,109.956013426,"5009895","2026-09-10 16:00:00",["83","25","3","SE","6.2"],"ndf"],["","Kota Surabaya","Benowo",-7.25084999972,112.657248,"5008348","2026-09-10 16:00:00",["77","27","3","W","4.2"],"ndf"],["","Kab. Gresik","Cerme",-7.22436048014,112.57091604,"5008221","2026-09-10 16:00:00",["79","26","3","W","5.2"],"ndf"],["","Kab. Tegal","Margasari",-7.121994,108.985115,"5010333","2026-09-10 16:00:00",["81","24","2","S","13.9"],"ndf"],["","Kab. Jember","Sumber Baru",-8.123967,113.385083,"5008259","2026-09-10 16:00:00",["99","22","3","SW","3.8"],"ndf"],["","Kota Tegal","Tegal",-6.86742121,109.142810615,"501267","2026-09-10 16:00:00",["79","25","2","SW","7.4"],"ndf"],["","Kab. Tegal","Kramat",-6.868139231,109.18580803,"5010331","2026-09-10 16:00:00",["79","25","2","SW","7.4"],"ndf"],["","Kab. Tegal","Suradadi",-6.880565915,109.275933786,"5010336","2026-09-10 16:00:00",["79","26","2","SW","3.6"],"ndf"],["","Kab. Klaten","Klaten",-7.71235,110.603033,"501249","2026-09-10 16:00:00",["85","23","3","SW","13.3"],"ndf"],["","Kab. Klaten","Jogonalan",-7.741322,110.549333,"5010094","2026-09-10 16:00:00",["88","22","3","SW","13.3"],"ndf"],["","Kab. Cianjur","Sukaluyu",-6.8179338,107.175619,"5009762","2026-09-10 16:00:00",["93","23","3","S","1.4"],"ndf"],["","Kab. Cianjur","Sukaluyu",-6.8136729,107.2226246,"5009762","2026-09-10 16:00:00",["91","24","3","S","1.4"],"ndf"],["","Kab. Cianjur","Ciranjang",-6.8141668,107.2512413,"5009429","2026-09-10 16:00:00",["91","23","3","SE","1.6"],"ndf"],["","Kab. Bandung Barat","Cipatat",-6.8220192,107.3860532,"5009419","2026-09-10 16:00:00",["96","22","3","SE","4.1"],"ndf"],["","Kab. Bandung Barat","Padalarang",-6.8110784,107.4649216,"5009635","2026-09-10 16:00:00",["98","21","3","SE","5.7"],"ndf"],["","Kab. Bandung Barat","Padalarang",-6.8034182,107.4634242,"5009635","2026-09-10 16:00:00",["98","21","3","SE","5.7"],"ndf"],["","Kota Cimahi","Cimahi Tengah",-6.8648797,107.5151502,"5009400","2026-09-10 16:00:00",["92","21","3","SE","1.9"],"ndf"],["","Kota Bandung","Cicendo",-6.8960709,107.5611395,"5009335","2026-09-10 16:00:00",["87","21","3","E","2.5"],"ndf"],["","Kota Bandung","Andir",-6.90803,107.57927,"5009223","2026-09-10 16:00:00",["87","21","3","E","2.5"],"ndf"],["","Kota Bandung","Sumurbandung",-6.91393,107.60268,"5009788","2026-09-10 16:00:00",["85","22","3","E","2.5"],"ndf"],["","Kab. Tasikmalaya","Manonjaya",-7.3532039,108.3026407,"5009611","2026-09-10 16:00:00",["98","21","3","NW","2.6"],"ndf"],["","Kab. Ciamis","Ciamis",-7.3535172,108.4940313,"501216","2026-09-10 16:00:00",["91","23","3","SW","0.2"],"ndf"],["","Kota Banjar","Banjar",-7.3762116,108.5423314,"501213","2026-09-10 16:00:00",["89","23","3","SW","0.5"],"ndf"],["","Kab. Purwakarta","Purwakarta",-6.510684,107.4563938,"5009699","2026-09-10 16:00:00",["95","25","3","S","2.1"],"ndf"],["","Kab. Purwakarta","Purwakarta",-6.573477,107.4308163,"501230","2026-09-10 16:00:00",["95","24","3","S","2.5"],"ndf"],["","Kab. Purwakarta","Sukatani",-6.610963,107.4085941,"5009779","2026-09-10 16:00:00",["96","24","3","S","2.5"],"ndf"],["","Kab. Purwakarta","Sukatani",-6.6409712,107.3912405,"5009779","2026-09-10 16:00:00",["97","24","3","SE","4.3"],"ndf"],["","Kab. Purwakarta","Darangdan",-6.6861412,107.398012,"5009455","2026-09-10 16:00:00",["97","23","3","SE","4.3"],"ndf"],["","Kab. Bandung Barat","Cipeundeuy",-6.7157413,107.3908245,"5009423","2026-09-10 16:00:00",["97","23","3","SE","4.3"],"ndf"],["","Kab. Bandung Barat","Cipeundeuy",-6.7361248,107.3985416,"5009423","2026-09-10 16:00:00",["97","23","3","SE","4.3"],"ndf"],["","Kab. Bandung Barat","Cikalongwetan",-6.761064,107.4089756,"5009367","2026-09-10 16:00:00",["97","22","3","SE","4.1"],"ndf"],["","Kab. Bandung Barat","Cikalongwetan",-6.7802002,107.4321373,"5009367","2026-09-10 16:00:00",["98","21","3","SE","5.7"],"ndf"],["","Kab. Ciamis","Cijeungjing",-7.3473119,108.4293405,"5009360","2026-09-10 16:00:00",["93","22","3","SW","0.2"],"ndf"],["","Kab. Purwakarta","Purwakarta",-6.5527265,107.4463949,"501230","2026-09-10 16:00:00",["95","25","3","S","2.7"],"ndf"],["","Kab. Brebes","Losari",-6.8461356,108.8017949,"5009949","2026-09-10 16:00:00",["75","26","2","SW","6.1"],"ndf"],["","Kab. Brebes","Tanjung",-6.8767333,108.8610446,"5009954","2026-09-10 16:00:00",["75","26","2","S","5.6"],"ndf"],["","Kab. Cirebon","Babakan",-6.8606738,108.7198821,"5009233","2026-09-10 16:00:00",["75","26","2","S","14.9"],"ndf"],["","Kab. Cirebon","Pangenan",-6.7837655,108.6224466,"5009658","2026-09-10 16:00:00",["74","26","3","S","14"],"ndf"],["","Kota Cirebon","Pekalipan",-6.7192609,108.5587694,"5009686","2026-09-10 16:00:00",["78","26","3","SE","12.9"],"ndf"],["","Kab. Cirebon","Astanajapura",-6.7776446,108.5930791,"5009232","2026-09-10 16:00:00",["74","26","3","S","14"],"ndf"],["","Kab. Cirebon","Lemahabang",-6.8328027,108.6260332,"5009576","2026-09-10 16:00:00",["75","25","3","S","14"],"ndf"],["","Kab. Cirebon","Karangsembung",-6.8578551,108.6477938,"5009534","2026-09-10 16:00:00",["75","25","2","S","14.9"],"ndf"],["","Kab. Cirebon","Ciledug",-6.9028773,108.7439659,"5009391","2026-09-10 16:00:00",["74","26","2","SW","6.1"],"ndf"],["","Kab. Subang","Patok Beusi",-6.408455903,107.540660491,"5009682","2026-09-10 16:00:00",["91","25","3","SW","1.3"],"ndf"],["","Kab. Subang","Compreng",-6.453814572,107.817123905,"5009450","2026-09-10 16:00:00",["92","25","3","SW","4.5"],"ndf"],["","Kab. Indramayu","Lelea",-6.467708582,108.10685344,"5009573","2026-09-10 16:00:00",["90","26","3","S","5.7"],"ndf"],["","Kab. Indramayu","Lelea",-6.46984404,108.161010928,"5009573","2026-09-10 16:00:00",["89","26","3","S","4.9"],"ndf"],["","Kab. Indramayu","Sliyeg",-6.472979793,108.306044424,"5009746","2026-09-10 16:00:00",["90","26","3","SW","3"],"ndf"],["","Kota Semarang","Gayamsari",-6.984391976,110.475850012,"5010128","2026-09-10 16:00:00",["76","26","2","E","4.6"],"ndf"],["","Kota Semarang","Semarang Timur",-6.964542959,110.428085988,"5010137","2026-09-10 16:00:00",["78","26","3","SE","2.2"],"ndf"],["","Kab. Grobogan","Toroh",-7.143887021,110.915013962,"5010011","2026-09-10 16:00:00",["74","25","3","SE","9"],"ndf"],["","Kab. Grobogan","Toroh",-7.145303981,110.900379997,"5010011","2026-09-10 16:00:00",["74","25","3","SE","9"],"ndf"],["","Kab. Demak","Mranggen",-7.025586013,110.522176037,"5009991","2026-09-10 16:00:00",["75","26","2","E","4.6"],"ndf"],["","Kota Semarang","Tugu",-6.971060978,110.30304702,"5010140","2026-09-10 16:00:00",["78","26","3","SE","5.6"],"ndf"],["","Kota Semarang","Tugu",-6.959852027,110.254847975,"5010140","2026-09-10 16:00:00",["77","26","3","SE","5.6"],"ndf"],["","Kab. Grobogan","Purwodadi",-7.140626963,110.848459974,"501257","2026-09-10 16:00:00",["74","25","2","SE","9"],"ndf"],["","Kab. Grobogan","Karangrayung",-7.101384988,110.779111041,"5010001","2026-09-10 16:00:00",["73","25","2","SE","5.9"],"ndf"],["","Kab. Grobogan","Tegowanu",-7.053010007,110.602395963,"5010010","2026-09-10 16:00:00",["69","26","2","E","7.6"],"ndf"],["","Kab. Grobogan","Gubug",-7.06102998,110.669580018,"5010000","2026-09-10 16:00:00",["70","26","2","SE","9.1"],"ndf"],["","Kab. Grobogan","Pulokulon",-7.150300015,111.010150993,"5010007","2026-09-10 16:00:00",["77","25","3","SE","8.3"],"ndf"],["","Kab. Grobogan","Pulokulon",-7.152650971,111.060671993,"5010007","2026-09-10 16:00:00",["78","25","3","S","7"],"ndf"],["","Kab. Grobogan","Gabus",-7.149901036,111.144983964,"5009996","2026-09-10 16:00:00",["80","24","3","SW","4.3"],"ndf"],["","Kab. Grobogan","Gabus",-7.174126999,111.222775988,"5009996","2026-09-10 16:00:00",["78","25","3","SW","4.3"],"ndf"],["","Kab. Kudus","Jati",-7.182936966,111.288036983,"5009913","2026-09-10 16:00:00",["74","25","3","S","2.7"],"ndf"],["","Kab. Blora","Sambong",-7.192292009,111.398060024,"5009921","2026-09-10 16:00:00",["73","25","3","SE","6.8"],"ndf"],["","Kab. Blora","Kedungtuban",-7.196411965,111.500484031,"5009916","2026-09-10 16:00:00",["75","25","3","SE","8.9"],"ndf"],["","Kab. Bojonegoro","Ngraho",-7.188726012,111.555191036,"5008184","2026-09-10 16:00:00",["75","25","3","S","6.6"],"ndf"],["","Kab. Bojonegoro","Kasiman",-7.172408961,111.655173982,"5008176","2026-09-10 16:00:00",["76","25","3","W","3.2"],"ndf"],["","Kab. Bojonegoro","Kalitidu",-7.131720018,111.767349998,"5008173","2026-09-10 16:00:00",["79","25","3","E","4.2"],"ndf"],["","Kab. Kendal","Pegandon",-6.973611005,110.148090022,"5010081","2026-09-10 16:00:00",["76","25","3","SE","7.8"],"ndf"],["","Kab. Kendal","Rowosari",-6.952457009,110.027920017,"5010084","2026-09-10 16:00:00",["83","25","3","S","3.3"],"ndf"],["","Kab. Batang","Banyuputih",-6.923748991,109.894299991,"5009895","2026-09-10 16:00:00",["85","25","2","S","7.8"],"ndf"],["","Kab. Batang","Kandeman",-6.908717975,109.789191009,"5009899","2026-09-10 16:00:00",["86","26","2","S","6.1"],"ndf"],["","Kab. Batang","Kandeman",-6.906473972,109.732592041,"5009899","2026-09-10 16:00:00",["87","26","2","S","3.3"],"ndf"],["","Kota Pekalongan","Pekalongan Timur",-6.889760038,109.664269974,"5010119","2026-09-10 16:00:00",["86","26","2","S","3.3"],"ndf"],["","Kab. Pekalongan","Sragi",-6.92375402,109.570989031,"5010210","2026-09-10 16:00:00",["82","26","2","S","4.5"],"ndf"],["","Kab. Wonosobo","Mojotengah",-7.3600667,109.8983833,"5010391","2026-09-10 16:00:00",["99","18","3","N","2.6"],"ndf"],["","Kab. Wonosobo","Leksono",-7.42378,109.86053,"5010390","2026-09-10 16:00:00",["99","19","3","N","2.6"],"ndf"],["","Kab. Banjarnegara","Banjarnegara",-7.3981837,109.6543405,"5009848","2026-09-10 16:00:00",["94","22","3","E","0.9"],"ndf"],["","Kab. Banjarnegara","Purwonegoro",-7.4339534,109.5625715,"5009860","2026-09-10 16:00:00",["90","23","3","S","1.1"],"ndf"],["","Kab. Cilacap","Jeruklegi",-7.6230254,109.0181518,"5009967","2026-09-10 16:00:00",["88","24","3","E","7.6"],"ndf"],["","Kab. Klaten","Ceper",-7.66903460036,110.6748584,"5010090","2026-09-10 16:00:00",["83","24","3","SW","11.7"],"ndf"],["","Kab. Sragen","Masaran",-7.46807199986,110.947673,"5010300","2026-09-10 16:00:00",["79","24","3","S","7"],"ndf"],["","Kab. Kulon Progo","Wates",-7.85952360387,110.157952923,"501188","2026-09-10 16:00:00",["90","22","3","W","1.4"],"ndf"],["","Kota Surakarta","Pasar Kliwon",-7.59602204873,110.853347965,"5010144","2026-09-10 16:00:00",["79","24","3","SW","7.8"],"ndf"],["","Kab. Sukoharjo","Polokerto",-7.62640225664,110.84280814,"5010320","2026-09-10 16:00:00",["80","24","3","SW","7.8"],"ndf"],["","Kab. Sukoharjo","Sukoharjo",-7.67978416779,110.843247855,"501265","2026-09-10 16:00:00",["81","24","3","SW","6.5"],"ndf"],["","Kota Surakarta","Surakarta",-7.55718802129,110.821369998,"501266","2026-09-10 16:00:00",["79","24","3","SW","11.5"],"ndf"],["","Kab. Sleman","Godean",-7.79599489587,110.284247752,"5008037","2026-09-10 16:00:00",["89","22","3","NW","4.2"],"ndf"],["","Kab. Klaten","Delanggu",-7.62213704206,110.706564998,"5010091","2026-09-10 16:00:00",["79","24","3","S","13.2"],"ndf"],["","Kab. Sukoharjo","Gatak",-7.5894109904,110.744451033,"5010315","2026-09-10 16:00:00",["79","24","3","SW","11.5"],"ndf"],["","Kota Surakarta","Banjarsari",-7.56180301279,110.796471974,"5010141","2026-09-10 16:00:00",["79","24","3","SW","11.5"],"ndf"],["","Kab. Wonogiri","Wonogiri",-7.81607097864,110.921867341,"501270","2026-09-10 16:00:00",["85","23","3","S","5.4"],"ndf"],["","Kab. Sleman","Prambanan",-7.75654119418,110.500449557,"5008076","2026-09-10 16:00:00",["90","22","3","SW","6.2"],"ndf"],["","Kab. Karanganyar","Gondangrejo",-7.46617597542,110.805201977,"5010029","2026-09-10 16:00:00",["78","24","3","S","11.3"],"ndf"],["","Kota Surakarta","Surakarta",-7.56210702501,110.839417996,"501266","2026-09-10 16:00:00",["79","24","3","SW","11.5"],"ndf"],["","Kab. Banyumas","Kebasen",-7.570097,109.220034,"5009875","2026-09-10 16:00:00",["87","24","2","E","6.2"],"ndf"],["","Kab. Banyumas","Kebasen",-7.530255,109.203144,"5009875","2026-09-10 16:00:00",["87","24","2","SE","3.1"],"ndf"],["","Kab. Purworejo","Bagelen",-7.802009,110.000648,"5010247","2026-09-10 16:00:00",["90","23","2","NE","3.2"],"ndf"],["","Kab. Karanganyar","Jaten",-7.56818600036,110.875482978,"5010030","2026-09-10 16:00:00",["79","24","3","SW","7.8"],"ndf"],["","Kab. Sragen","Gondang",-7.40523995797,111.117098965,"5010295","2026-09-10 16:00:00",["78","24","3","S","8.7"],"ndf"],["","Kab. Sragen","Sragen",-7.42936802068,111.017872989,"501264","2026-09-10 16:00:00",["79","24","3","S","9.3"],"ndf"],["","Kab. Pasuruan","Purwosari",-7.75504502989,112.72450608,"5008586","2026-09-10 16:00:00",["88","21","3","SW","10"],"ndf"],["","Kab. Pasuruan","Purwodadi",-7.83667206043,112.6978938,"5008585","2026-09-10 16:00:00",["96","19","10","SW","10"],"ndf"],["","Kab. Ngawi","Paron",-7.442181,111.386552,"5008544","2026-09-10 16:00:00",["70","26","3","SE","5.7"],"ndf"],["","Kab. Ngawi","Widodaren",-7.398737,111.224633,"5008547","2026-09-10 16:00:00",["77","25","3","SW","5.8"],"ndf"],["","Kab. Blitar","Sanan Kulon",-8.120967,112.081182,"5008156","2026-09-10 16:00:00",["92","23","3","SE","8"],"ndf"],["","Kab. Tulungagung","Ngunut",-8.102826,112.012138,"5008754","2026-09-10 16:00:00",["91","23","3","S","4.1"],"ndf"],["","Kab. Jombang","Sumobito",-7.519442,112.339314,"5008285","2026-09-10 16:00:00",["80","25","3","SW","6.2"],"ndf"],["","Kab. Jombang","Sumobito",-7.50694,112.370384,"5008285","2026-09-10 16:00:00",["79","25","3","SW","6.2"],"ndf"],["","Kab. Jombang","Peterongan",-7.54184,112.279167,"5008282","2026-09-10 16:00:00",["82","24","3","SW","2"],"ndf"],["","Kab. Jombang","Jombang",-7.557891,112.233435,"501281","2026-09-10 16:00:00",["84","24","3","S","11.8"],"ndf"],["","Kab. Kediri","Purwoasri",-7.591899,112.100745,"5008309","2026-09-10 16:00:00",["87","23","3","S","21.2"],"ndf"],["","Kab. Nganjuk","Tanjunganom",-7.602583,111.942601,"5008528","2026-09-10 16:00:00",["80","25","3","SE","17.2"],"ndf"],["","Kab. Madiun","Mejayan",-7.55099,111.654719,"5008436","2026-09-10 16:00:00",["82","24","3","W","5.5"],"ndf"],["","Kab. Kediri","Kras",-7.948749,111.960368,"5008297","2026-09-10 16:00:00",["90","23","3","S","7"],"ndf"],["","Kab. Kediri","Papar",-7.728122,112.05746,"5008304","2026-09-10 16:00:00",["84","24","3","S","21.2"],"ndf"],["","Kab. Kediri","Ngadiluwih",-7.89843,111.988011,"5008300","2026-09-10 16:00:00",["88","23","3","S","13.3"],"ndf"],["","Kab. Tulungagung","Ngantru",-8.01054,111.92707,"5008753","2026-09-10 16:00:00",["91","23","10","W","6.2"],"ndf"],["","Kab. Kediri","Papar",-7.697579,112.079537,"5008304","2026-09-10 16:00:00",["84","24","3","S","21.2"],"ndf"],["","Kab. Kediri","Purwoasri",-7.64735,112.100101,"5008309","2026-09-10 16:00:00",["86","24","3","S","21.2"],"ndf"],["","Kab. Kediri","Gampengrejo",-7.771188,112.02601,"5008291","2026-09-10 16:00:00",["83","24","3","S","19.3"],"ndf"],["","Kab. Madiun","Wonoasri",-7.587101,111.588602,"5008440","2026-09-10 16:00:00",["80","24","3","S","5.2"],"ndf"],["","Kab. Tulungagung","Tulungagung",-8.082419,111.944644,"501309","2026-09-10 16:00:00",["90","24","3","S","4.1"],"ndf"],["","Kota Surabaya","Simokerto",-7.23526298988,112.757373,"5008368","2026-09-10 16:00:00",["75","27","3","SW","2"],"ndf"],["","Kota Surabaya","Krembangan",-7.24300397979,112.74051312,"5008359","2026-09-10 16:00:00",["75","27","3","SW","2"],"ndf"],["","Kota Surabaya","Tandes",-7.25903100002,112.68693108,"5008372","2026-09-10 16:00:00",["76","27","3","W","4.2"],"ndf"],["","Kab. Lamongan","Deket",-7.11255995985,112.42018188,"5008381","2026-09-10 16:00:00",["81","25","3","SW","7.5"],"ndf"],["","Kab. Gresik","Duduk Sampeyan",-7.1546270401,112.52051604,"5008223","2026-09-10 16:00:00",["81","26","3","W","7.2"],"ndf"],["","Kab. Lamongan","Deket",-7.13123999986,112.48018812,"5008381","2026-09-10 16:00:00",["82","25","3","W","6.3"],"ndf"],["","Kab. Lamongan","Turi",-7.10302256969,112.36968072,"5008403","2026-09-10 16:00:00",["81","25","3","SW","7.5"],"ndf"],["","Kab. Lamongan","Pucuk",-7.09746687026,112.26979584,"5008394","2026-09-10 16:00:00",["80","25","3","S","5.6"],"ndf"],["","Kab. Lamongan","Turi",-7.09364375968,112.32194868,"5008403","2026-09-10 16:00:00",["80","25","3","S","5.6"],"ndf"],["","Kab. Lamongan","Babat",-7.10230400959,112.2223842,"5008378","2026-09-10 16:00:00",["80","25","3","S","5.8"],"ndf"],["","Kab. Bojonegoro","Baureno",-7.13114342976,112.099743,"5008169","2026-09-10 16:00:00",["82","24","3","S","6.3"],"ndf"],["","Kab. Bojonegoro","Sumberrejo",-7.17767622034,112.00149828,"5008190","2026-09-10 16:00:00",["79","25","3","SE","10.2"],"ndf"],["","Kab. Bojonegoro","Sumberrejo",-7.16381909959,112.04384328,"5008190","2026-09-10 16:00:00",["80","25","3","SE","11.1"],"ndf"],["","Kota Cirebon","Pekalipan",-6.705497559,108.555365726,"5009686","2026-09-10 16:00:00",["76","27","3","SE","12.9"],"ndf"],["","Kab. Grobogan","Tanggungharjo",-7.091487972,110.603208002,"5010008","2026-09-10 16:00:00",["70","26","2","E","7.6"],"ndf"],["","Kab. Grobogan","Kedungjati",-7.163538979,110.635558963,"5010002","2026-09-10 16:00:00",["72","25","2","SE","9"],"ndf"],["","Kab. Grobogan","Kedungjati",-7.17923996,110.671880012,"5010002","2026-09-10 16:00:00",["73","25","3","SE","9"],"ndf"],["","Kab. Boyolali","Juwangi",-7.185745994,110.751916962,"5009928","2026-09-10 16:00:00",["74","25","2","S","10.2"],"ndf"],["","Kab. Grobogan","Karangrayung",-7.19627,110.825626,"5010001","2026-09-10 16:00:00",["75","25","2","S","10.2"],"ndf"],["","Kab. Grobogan","Geyer",-7.218683017,110.899931984,"5009997","2026-09-10 16:00:00",["75","25","3","SE","9"],"ndf"],["","Kab. Sukoharjo","Nguter",-7.741429,110.878615,"5010319","2026-09-10 16:00:00",["83","23","3","S","5.4"],"ndf"],["","Kota Malang","Alun - alun kota Malang",-7.99481196041,112.63247892,"5008330","2026-09-10 16:00:00",["97","21","3","W","3.3"],"ndf"],["","Kab. Malang","Kepanjen",-8.15189301033,112.51696212,"5008472","2026-09-10 16:00:00",["94","22","3","E","9.9"],"ndf"],["","Kab. Malang","Sumberpucung",-8.15840603986,112.47844896,"5008485","2026-09-10 16:00:00",["95","21","3","E","9.9"],"ndf"],["","Kab. Blitar","Selorejo",-8.157271,112.420497,"5008158","2026-09-10 16:00:00",["95","22","3","E","7.9"],"ndf"],["","Kab. Blitar","Kesamben",-8.14927,112.363465,"5008151","2026-09-10 16:00:00",["94","22","3","E","7.9"],"ndf"],["","Kab. Blitar","Talun",-8.091522,112.288545,"5008161","2026-09-10 16:00:00",["93","22","3","E","5.9"],"ndf"],["","Kab. Blitar","Garum",-8.073538,112.216941,"5008148","2026-09-10 16:00:00",["93","22","3","SE","7.9"],"ndf"],["","Kab. Bojonegoro","Balen",-7.19920233038,111.93336,"5008168","2026-09-10 16:00:00",["77","25","3","SE","2.8"],"ndf"],["","Kab. Cianjur","Cibeber",-6.8880473,107.1264719,"5009316","2026-09-10 16:00:00",["96","21","3","SW","3.7"],"ndf"],["","Kab. Cianjur","Cibeber",-6.9375809,107.1211052,"5009316","2026-09-10 16:00:00",["97","21","3","S","2.5"],"ndf"],["","Kab. Sukabumi","Cireunghas",-6.9498736,107.0615343,"5009430","2026-09-10 16:00:00",["98","20","3","S","2.5"],"ndf"],["","Kab. Sukabumi","Cireunghas",-6.958476659,107.03677227,"5009430","2026-09-10 16:00:00",["98","20","3","S","1.8"],"ndf"],["","Kab. Sukabumi","Kebonpedes",-6.9415406,106.9920296,"5009545","2026-09-10 16:00:00",["98","20","3","S","1.8"],"ndf"],["","Kota Jakarta Pusat","Johar Baru ",-6.186271,106.850973,"5005612","2026-09-10 16:00:00",["83","26","2","SE","2.5"],"ndf"],["","Kab. Banyumas","Purwokerto Barat",-7.41915,109.221842,"5009883","2026-09-10 16:00:00",["91","22","2","SE","1.2"],"ndf"],["","Kab. Banyumas","Karang Lewas",-7.388056,109.185833,"5009874","2026-09-10 16:00:00",["95","21","2","SE","1.2"],"ndf"],["","Kab. Banyumas","Cilongok",-7.382222,109.120833,"5009870","2026-09-10 16:00:00",["95","21","2","SE","4.6"],"ndf"],["","Kab. Banyumas","Pakuncen",-7.355556,109.087222,"5009880","2026-09-10 16:00:00",["95","21","2","SE","4.6"],"ndf"],["","Kab. Brebes","Peguyangan",-7.32815,109.057755,"5009950","2026-09-10 16:00:00",["93","20","2","E","4.2"],"ndf"],["","Kab. Cilacap","Cilacap Tengah",-7.73614,109.006986,"5009961","2026-09-10 16:00:00",["87","25","3","E","17.9"],"ndf"],["","Kab. Cilacap","Cilacap Tengah",-7.684992,109.042481,"5009961","2026-09-10 16:00:00",["88","24","3","E","14.1"],"ndf"],["","Kab. Banyumas","Tambak",-7.6130742,109.4086317,"5009892","2026-09-10 16:00:00",["95","21","2","E","2.8"],"ndf"],["","Kab. Banyumas","Sumpiuh",-7.615358,109.360625,"5009891","2026-09-10 16:00:00",["93","22","2","E","2.8"],"ndf"],["","Kab. Banyumas","Kemranjen",-7.621933,109.312955,"5009878","2026-09-10 16:00:00",["91","22","2","E","5.6"],"ndf"],["","Kab. Cilacap","Binangun",-7.630011,109.253651,"5009959","2026-09-10 16:00:00",["88","23","2","E","5.6"],"ndf"],["","Kab. Cilacap","Maos",-7.62587,109.197645,"5009975","2026-09-10 16:00:00",["87","24","2","E","6.2"],"ndf"],["","Kab. Cilacap","Maos",-7.6191362,109.1397207,"5009975","2026-09-10 16:00:00",["87","24","2","E","6.2"],"ndf"],["","Kab. Cilacap","Kesugihan",-7.6213364,109.0768866,"5009972","2026-09-10 16:00:00",["88","24","2","E","8.2"],"ndf"],["","Kab. Cilacap","Kawungaten",-7.59097,108.91944,"5009970","2026-09-10 16:00:00",["88","24","3","SE","4.1"],"ndf"],["","Kab. Cilacap","Gandrungmangu",-7.52812,108.85913,"5009966","2026-09-10 16:00:00",["89","23","2","SE","4.1"],"ndf"],["","Kab. Cilacap","Sidareja",-7.48653,108.80761,"5009980","2026-09-10 16:00:00",["89","23","2","S","2.6"],"ndf"],["","Kota Banjar","Langensari",-7.3601271,108.6370424,"5009569","2026-09-10 16:00:00",["89","23","3","SW","0.5"],"ndf"],["","Kab. Tasikmalaya","Manonjaya",-7.35378,108.27434,"5009611","2026-09-10 16:00:00",["98","21","3","NW","2.6"],"ndf"],["","Kota Tasikmalaya","Purbaratu",-7.322216,108.2237434,"5009695","2026-09-10 16:00:00",["98","21","3","N","1.2"],"ndf"],["","Kab. Ciamis","Sindangkasih",-7.28679,108.20084,"5009740","2026-09-10 16:00:00",["98","21","3","N","1.2"],"ndf"],["","Kab. Ciamis","Cihaurbeuti",-7.21957,108.1912,"5009354","2026-09-10 16:00:00",["99","19","3","E","2.8"],"ndf"],["","Kab. Tasikmalaya","Sukaresik",-7.1574,108.14579,"5009771","2026-09-10 16:00:00",["98","19","3","E","2.8"],"ndf"],["","Kab. Ciamis","Panumbangan",-7.134236,108.118429,"5009662","2026-09-10 16:00:00",["97","19","3","S","5.2"],"ndf"],["","Kab. Tasikmalaya","Pagerageung",-7.09365,108.10065,"5009639","2026-09-10 16:00:00",["97","19","3","S","5.2"],"ndf"],["","Kab. Garut","Malangbong",-7.05863,108.07049,"5009601","2026-09-10 16:00:00",["95","20","3","S","5.2"],"ndf"],["","Kab. Garut","Kersamanah",-7.06474,108.007,"5009551","2026-09-10 16:00:00",["97","20","3","S","4.7"],"ndf"],["","Kab. Garut","Cibatu",-7.10013,107.97948,"5009314","2026-09-10 16:00:00",["96","19","3","S","4.7"],"ndf"],["","Kab. Garut","Cibatu",-7.1033,107.9582,"5009314","2026-09-10 16:00:00",["96","19","3","S","4.7"],"ndf"],["","Kab. Garut","Leuwigoong",-7.09826,107.93114,"5009584","2026-09-10 16:00:00",["96","19","3","SE","4"],"ndf"],["","Kab. Garut","Cibiuk",-7.08438,107.89971,"5009328","2026-09-10 16:00:00",["97","19","3","SE","4"],"ndf"],["","Kab. Garut","Cibiuk",-7.05362,107.89393,"5009328","2026-09-10 16:00:00",["98","19","3","SE","4"],"ndf"],["","Kab. Bandung","Cikancung",-6.980719779,107.799545752,"5009369","2026-09-10 16:00:00",["98","20","3","E","3"],"ndf"],["","Kab. Bandung","Rancaekek",-6.96481,107.75589,"5009709","2026-09-10 16:00:00",["96","20","3","E","3"],"ndf"],["","Kota Bandung","Panyileukan",-6.94094,107.69003,"5009663","2026-09-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="12" customHeight="1">
+      <c r="A5" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>https://publik.bmkg.go.id/event/source/dwt/apiDF_Kereta/202609101600.json</t>
+        </is>
+      </c>
+      <c r="F5" s="68" t="inlineStr">
+        <is>
+          <t>10 16:00:00",["94","20","3","NE","2.7"],"ndf"],["","Kota Bandung","Antapani",-6.92508,107.64638,"5009225","2026-09-10 16:00:00",["89","21","3","NE","2.7"],"ndf"],["","Kota Bandung","Kiaracondong",-6.9187208,107.6259428,"5009556","2026-09-10 16:00:00",["87","21","3","E","2.5"],"ndf"],["","Kab. Bandung Barat","Cipatat",-6.8244598,107.3465944,"5009419","2026-09-10 16:00:00",["92","23","3","SE","1.6"],"ndf"],["","Kab. Cianjur","Haurwangi",-6.818544595,107.298120594,"5009486","2026-09-10 16:00:00",["91","24","3","SE","1.6"],"ndf"],["","Kab. Cianjur","Cianjur",-6.8247459,107.1428413,"501217","2026-09-10 16:00:00",["94","22","3","S","1.4"],"ndf"],["","Kab. Purworejo","Kutoarjo",-7.72617,109.90734,"5010257","2026-09-10 16:00:00",["89","23","3","NW","1.5"],"ndf"],["","Kab. Purworejo","Butuh",-7.72444,109.8584,"5010252","2026-09-10 16:00:00",["89","23","3","NW","1.5"],"ndf"],["","Kab. Kebumen","Pejagoan",-7.72441,109.79812,"5010060","2026-09-10 16:00:00",["88","23","2","NW","1.4"],"ndf"],["","Kab. Kebumen","Kutowinangun",-7.71682,109.73428,"5010056","2026-09-10 16:00:00",["88","23","2","NW","1.4"],"ndf"],["","Kab. Kebumen","Kebumen",-7.69734,109.70138,"501247","2026-09-10 16:00:00",["89","23","2","NW","0.9"],"ndf"],["","Kab. Kebumen","Klirong",-7.681881,109.662137,"5010055","2026-09-10 16:00:00",["90","23","2","NW","0.9"],"ndf"],["","Kab. Kebumen","Klirong",-7.679147,109.639593,"5010055","2026-09-10 16:00:00",["90","23","2","NE","0.8"],"ndf"],["","Kab. Kebumen","Sruweng",-7.65466,109.60238,"5010068","2026-09-10 16:00:00",["91","23","2","NE","0.8"],"ndf"],["","Kab. Kebumen","Karanganyar",-7.63331,109.57328,"5010052","2026-09-10 16:00:00",["93","22","2","W","1.8"],"ndf"],["","Kab. Kebumen","Sempor",-7.6107716,109.507697,"5010067","2026-09-10 16:00:00",["95","22","2","SW","0.7"],"ndf"],["","Kab. Sidoarjo","Tarik",-7.45932996021,112.51880604,"5008665","2026-09-10 16:00:00",["75","26","3","SW","5.6"],"ndf"],["","Kab. Sidoarjo","Balongbendo",-7.43667102008,112.55321484,"5008652","2026-09-10 16:00:00",["75","26","3","SW","2.5"],"ndf"],["","Kab. Pasuruan","Beji",-7.58486285989,112.72479264,"5008572","2026-09-10 16:00:00",["82","25","3","SW","2.5"],"ndf"],["","Kab. Sidoarjo","Tanggulangin",-7.50682997974,112.70808,"5008664","2026-09-10 16:00:00",["75","27","3","SW","4.2"],"ndf"],["","Kab. Sidoarjo","Buduran",-7.44135002982,112.71566016,"5008653","2026-09-10 16:00:00",["74","27","3","SW","4.2"],"ndf"],["","Kab. Sidoarjo","Buduran",-7.42788999032,112.72298004,"5008653","2026-09-10 16:00:00",["74","27","3","SW","7.3"],"ndf"],["","Kab. Sidoarjo","Gedangan",-7.41187997987,112.72610988,"5008655","2026-09-10 16:00:00",["74","27","3","SW","7.3"],"ndf"],["","Kab. Sidoarjo","Gedangan",-7.38897002996,112.72858992,"5008655","2026-09-10 16:00:00",["73","27","3","SW","7.3"],"ndf"],["","Kab. Sidoarjo","Waru",-7.36793000977,112.72934016,"5008667","2026-09-10 16:00:00",["73","27","3","SW","7.3"],"ndf"],["","Kota Surabaya","Gayungan",-7.3406399398,112.72944996,"5008352","2026-09-10 16:00:00",["74","27","3","SW","7.3"],"ndf"],["","Kota Surabaya","Tenggilis Mejoyo",-7.31478995959,112.73442012,"5008374","2026-09-10 16:00:00",["74","27","3","SW","2"],"ndf"],["","Kab. Banyuwangi","Tegalsari",-7.28781002982,112.74809004,"5008373","2026-09-10 16:00:00",["75","27","3","SW","2"],"ndf"],["","Kab. Nganjuk","Wilangan",-7.547541,111.732129,"5008529","2026-09-10 16:00:00",["84","23","3","W","5.5"],"ndf"],["","Kab. Karanganyar","Kebakkramat",-7.533983,110.9014356,"5010037","2026-09-10 16:00:00",["78","24","3","SW","7.9"],"ndf"],["","Kab. Ngawi","Geneng",-7.4978954,111.4187735,"5008531","2026-09-10 16:00:00",["70","26","3","SE","5.7"],"ndf"],["","Kab. Magetan","Barat",-7.5622107,111.4512161,"5008442","2026-09-10 16:00:00",["73","25","3","S","11.7"],"ndf"],["","Kab. Nganjuk","Nganjuk",-7.571655,111.852785,"501293","2026-09-10 16:00:00",["80","24","3","SE","4.4"],"ndf"],["","Kab. Nganjuk","Bagor",-7.561238,111.803695,"5008511","2026-09-10 16:00:00",["81","24","3","W","5.4"],"ndf"],["","Kota Pasuruan","BugulKidul",-7.637970541,112.910014959,"5008339","2026-09-10 16:00:00",["71","26","3","S","3.6"],"ndf"],["","Kab. Pasuruan","Nguling",-7.717542462,113.012092542,"5008580","2026-09-10 16:00:00",["74","25","3","SE","1.7"],"ndf"],["","Kab. Probolinggo","Sumberasih",-7.734690662,113.11881437,"5008634","2026-09-10 16:00:00",["74","26","3","SE","5.6"],"ndf"],["","Kota Probolinggo","Mayangan",-7.742985561,113.216005806,"5008345","2026-09-10 16:00:00",["77","26","3","SE","15.2"],"ndf"],["","Kab. Probolinggo","Tegalsiwalan",-7.84642864,113.229060369,"5008635","2026-09-10 16:00:00",["82","24","3","S","13.1"],"ndf"],["","Kab. Lumajang","Klakah",-7.993944939,113.249508524,"5008410","2026-09-10 16:00:00",["96","22","3","S","10.4"],"ndf"],["","Kab. Jember","Sumber Baru",-8.070051614,113.305296293,"5008259","2026-09-10 16:00:00",["98","22","3","W","5.9"],"ndf"],["","Kab. Jember","Sumber Baru",-8.123424,113.364089,"5008259","2026-09-10 16:00:00",["98","23","3","SW","0.4"],"ndf"],["","Kab. Jember","Tanggul",-8.162801,113.448266,"5008263","2026-09-10 16:00:00",["98","23","2","SW","0.5"],"ndf"],["","Kab. Jember","Bangsalsari",-8.202992,113.533284,"5008239","2026-09-10 16:00:00",["96","23","2","SW","0.5"],"ndf"],["","Kab. Jember","Kaliwates",-8.2034,113.614447,"5008245","2026-09-10 16:00:00",["96","23","3","NW","1.2"],"ndf"],["","Kab. Jember","Jember",-8.177444,113.677412,"501280","2026-09-10 16:00:00",["95","22","3","W","4.3"],"ndf"],["","Kab. Jember","Ledokombo",-8.126981,113.812212,"5008247","2026-09-10 16:00:00",["91","22","3","SW","9.6"],"ndf"],["","Kab. Jember","Ledokombo",-8.140581,113.875548,"5008247","2026-09-10 16:00:00",["95","21","3","SE","8.7"],"ndf"],["","Kab. Jember","Ledokombo",-8.157286,113.894375,"5008247","2026-09-10 16:00:00",["96","20","3","SE","8.7"],"ndf"],["","Kab. Banyuwangi","Kalibaru",-8.192625968,113.896233039,"5008127","2026-09-10 16:00:00",["96","20","3","SE","8.7"],"ndf"],["","Kab. Banyuwangi","Kalibaru",-8.224905012,113.895763988,"5008127","2026-09-10 16:00:00",["96","20","3","SE","8.7"],"ndf"],["","Kab. Banyuwangi","Kalibaru",-8.272413975,113.926810976,"5008127","2026-09-10 16:00:00",["99","21","10","E","11.4"],"ndf"],["","Kab. Banyuwangi","Genteng",-8.29963496,114.049456995,"5008122","2026-09-10 16:00:00",["98","21","10","NE","4"],"ndf"],["","Kab. Banyuwangi","Genteng",-8.302907003,114.076372962,"5008122","2026-09-10 16:00:00",["98","21","10","NE","4"],"ndf"],["","Kab. Banyuwangi","Genteng",-8.301849961,114.105320033,"5008122","2026-09-10 16:00:00",["95","22","10","NE","4"],"ndf"],["","Kab. Banyuwangi","Rogojampi",-8.306452967,114.240533961,"5008133","2026-09-10 16:00:00",["94","23","3","E","5"],"ndf"],["","Kab. Banyuwangi","Kabat",-8.30481397,114.292555992,"5008126","2026-09-10 16:00:00",["95","24","3","E","5"],"ndf"],["","Kab. Banyuwangi","Kabat",-8.278078968,114.315241026,"5008126","2026-09-10 16:00:00",["95","23","3","E","5"],"ndf"],["","Kab. Banyuwangi","Kabat",-8.276021965,114.315913003,"5008126","2026-09-10 16:00:00",["95","23","3","E","5"],"ndf"],["","Kab. Banyuwangi","Banyuwangi",-8.222945994,114.340870036,"501273","2026-09-10 16:00:00",["95","23","3","S","6.6"],"ndf"],["","Kab. Banyuwangi","Banyuwangi",-8.183635036,114.369383007,"501273","2026-09-10 16:00:00",["95","23","3","S","6.6"],"ndf"],["","Kab. Gilimanuk","Gilimanuk",-8.14124004,114.397388035,"1100024","2026-09-10 16:00:00",["95","23","10","S","6.6"],"ndf"],["","Kab. Bandung","Baleendah",-6.9892228,107.6280233,"5009237","2026-09-10 16:00:00",["85","22","3","E","2.4"],"ndf"],["","Kab. Bandung","Paseh",-7.0476227,107.7583964,"5009675","2026-09-10 16:00:00",["97","19","3","SE","2.4"],"ndf"],["","Kab. Garut","Leles",-7.2054231,107.8848186,"5009575","2026-09-10 16:00:00",["95","18","3","SE","4"],"ndf"],["","Kab. Garut","Cigedug",-7.3108773,107.7954336,"5009348","2026-09-10 16:00:00",["97","17","3","N","1"],"ndf"],["","Kab. Demak","Sayung",-6.941152001,110.510082962,"5009992","2026-09-10 16:00:00",["73","27","2","E","4.6"],"ndf"],["","Kab. Demak","Karang Tengah",-6.919498025,110.597589025,"5009986","2026-09-10 16:00:00",["71","26","2","E","9.2"],"ndf"],["","Kab. Demak","Gajah",-6.871038973,110.729289008,"5009984","2026-09-10 16:00:00",["70","26","2","SE","9.9"],"ndf"],["","Kab. Demak","Sayung",-6.952358019,110.478759035,"5009992","2026-09-10 16:00:00",["74","27","2","E","4.6"],"ndf"],["","Kab. Demak","Demak",-6.901154984,110.634335959,"501243","2026-09-10 16:00:00",["71","26","2","E","9.2"],"ndf"],["","Kab. Blora","Jati",-6.814773018,110.844665989,"5010153","2026-09-10 16:00:00",["73","26","3","S","3"],"ndf"],["","Kab. Pati","Winong",-6.750228005,111.02760002,"5010197","2026-09-10 16:00:00",["81","25","3","S","1.6"],"ndf"],["","Kota Semarang","Semarang Timur",-6.969476966,110.430268971,"5010137","2026-09-10 16:00:00",["78","26","3","SE","2.2"],"ndf"],["","Kab. Rembang","Kaliori",-6.703347014,111.245066989,"5010264","2026-09-10 16:00:00",["73","26","3","SE","9.4"],"ndf"],["","Kab. Rembang","Pamotan",-6.763367979,111.491077021,"5010267","2026-09-10 16:00:00",["81","25","3","SE","4.9"],"ndf"],["","Kab. Tuban","Jatirogo",-6.884233011,111.654543998,"5008728","2026-09-10 16:00:00",["78","25","3","E","5.3"],"ndf"],["","Kab. Pati","Margoyoso",-6.611124035,111.064681979,"5010189","2026-09-10 16:00:00",["81","25","3","SE","8.7"],"ndf"],["","Kab. Pati","Tayu",-6.535506025,111.050598035,"5010193","2026-09-10 16:00:00",["83","26","3","SE","14.5"],"ndf"],["","Kab. Grobogan","Godong",-7.022553692,110.772768036,"5009998","2026-09-10 16:00:00",["74","25","2","SE","6.9"],"ndf"],["","Kab. Grobogan","Wirosari",-7.078767009,111.093678335,"5010012","2026-09-10 16:00:00",["78","25","3","S","4.5"],"ndf"],["","Kab. Blora","Kunduran",-7.050729124,111.240727343,"5009918","2026-09-10 16:00:00",["77","25","3","SW","1.9"],"ndf"],["","Kab. Klaten","Ngawen",-7.00495597,111.313639591,"5009919","2026-09-10 16:00:00",["74","25","3","SE","5.2"],"ndf"],["","Kab. Blora","Blora",-6.971194502,111.424123971,"501239","2026-09-10 16:00:00",["77","24","3","SE","7.7"],"ndf"],["","Kab. Rembang","Rembang",-6.70958885,111.342362445,"501260","2026-09-10 16:00:00",["77","26","3","SE","5.3"],"ndf"],["","Kab. Rembang","Bulu",-6.863782173,111.424391354,"5010262","2026-09-10 16:00:00",["79","24","3","SE","8.6"],"ndf"],["","Kab. Bojonegoro","Padangan",-7.15421034,111.591248475,"5008185","2026-09-10 16:00:00",["75","25","3","S","6.6"],"ndf"],["","Kab. Grobogan","Purwodadi",-7.083449895,110.911473278,"501257","2026-09-10 16:00:00",["75","25","3","SE","5"],"ndf"],["","Kab. Grobogan","Ngaringan",-7.084891666,111.119229058,"5010005","2026-09-10 16:00:00",["77","25","3","S","4.5"],"ndf"],["","Kab. Kendal","Weleri",-6.970801977,110.069790054,"5010087","2026-09-10 16:00:00",["80","25","3","S","3.2"],"ndf"],["","Kab. Kendal","Weleri",-7.000741633,110.06930952,"5010087","2026-09-10 16:00:00",["82","24","3","S","3.2"],"ndf"],["","Kab. Tuban","Senori",-7.045893017,111.784472968,"5008739","2026-09-10 16:00:00",["79","24","3","E","4.2"],"ndf"],["","Kab. Semarang","Bringin",-7.253319975,110.523518315,"5010280","2026-09-10 16:00:00",["80","24","3","SW","3.3"],"ndf"],["","Kab. Semarang","Bawen",-7.260701163,110.454160664,"5010278","2026-09-10 16:00:00",["89","22","3","SW","3.3"],"ndf"],["","Kab. Semarang","Ambarawa",-7.265596194,110.401347969,"5002226","2026-09-10 16:00:00",["93","20","3","SW","5.1"],"ndf"],["","Kab. Semarang","Jambu",-7.279839395,110.368804224,"5010282","2026-09-10 16:00:00",["94","20","3","SW","5.1"],"ndf"],["","Kab. Semarang","Jambu",-7.309188461,110.353019424,"5010282","2026-09-10 16:00:00",["96","20","3","SW","5.1"],"ndf"],["","Kota Semarang","Mijen",-6.788115297,110.724938801,"5009990","2026-09-10 16:00:00",["69","27","3","E","7.5"],"ndf"],["","Kab. Kendal","Cepiring",-6.920889337,110.19236357,"5010071","2026-09-10 16:00:00",["73","26","3","S","7.4"],"ndf"],["","Kab. Jepara","Pecangaan",-6.692340234,110.706827603,"5010025","2026-09-10 16:00:00",["73","26","3","E","9.4"],"ndf"],["","Kab. Purworejo","Banyuurip",-7.75362730986,109.949849294,"5010248","2026-09-10 16:00:00",["91","23","2","NE","3.2"],"ndf"],["","Kab. Kulon Progo","Sentolo",-7.85919251936,110.20937942,"5008086","2026-09-10 16:00:00",["89","23","3","W","1.4"],"ndf"],["","Kab. Jombang","Ngoro",-7.673074,112.225367,"5008279","2026-09-10 16:00:00",["82","24","3","S","10.1"],"ndf"],["","Kab. Lamongan","Kedungpring",-7.186355,112.19573,"5008386","2026-09-10 16:00:00",["80","25","3","S","9.5"],"ndf"],["","Kab. Lamongan","Buluk",-7.276501,112.13474,"5008380","2026-09-10 16:00:00",["82","24","3","SE","14.8"],"ndf"],["","Kab. Jombang","Kabuh",-7.387555,112.21203,"5008273","2026-09-10 16:00:00",["84","24","3","S","12.1"],"ndf"],["","Kab. Jombang","Ploso",-7.453772,112.226718,"5008284","2026-09-10 16:00:00",["84","24","3","S","11.8"],"ndf"],["","Kab. Lamongan","Ngimbang",-7.283789,112.21544,"5008392","2026-09-10 16:00:00",["82","24","3","S","11.6"],"ndf"],["","Kab. Kediri","Kandangan",-7.754698,112.28212,"5008294","2026-09-10 16:00:00",["82","23","3","SE","2.9"],"ndf"],["","Kota Kediri","Pesantren",-7.83585,112.053249,"5008324","2026-09-10 16:00:00",["85","24","3","S","19.1"],"ndf"],["","Kab. Kediri","Puncu",-7.86756,112.150574,"5008308","2026-09-10 16:00:00",["87","23","3","SE","12.5"],"ndf"],["","Kab. Kediri","Puncu",-7.829332,112.134426,"5008308","2026-09-10 16:00:00",["87","23","3","S","19.1"],"ndf"],["","Kab. Malang","Poncokusumo",-8.00828599966,112.762388,"5008481","2026-09-10 16:00:00",["98","18","3","NE","2.3"],"ndf"],["","Kab. Sidoarjo","Prambon",-7.46135699969,112.564282,"5008660","2026-09-10 16:00:00",["74","26","3","SW","2.5"],"ndf"],["","Kab. Gresik","Gresik",-7.15288000004,112.65781,"501279","2026-09-10 16:00:00",["80","27","3","N","2"],"ndf"],["","Kab. Sidoarjo","Tulangan",-7.46575099989,112.651053,"5008666","2026-09-10 16:00:00",["74","26","3","SW","4.2"],"ndf"],["","Kab. Tuban","Plumpang",-7.02338999979,112.09996,"5008736","2026-09-10 16:00:00",["86","24","3","S","5.2"],"ndf"],["","Kab. Tuban","Tuban",-6.90002999973,112.05813,"501308","2026-09-10 16:00:00",["83","24","3","S","9.9"],"ndf"],["","Kota Mojokerto","Kota Mojokerto",-7.45740490026,112.4323264,"501291","2026-09-10 16:00:00",["78","25","3","SW","6.2"],"ndf"],["","Kab. Mojokerto","Gedeg",-7.45669100044,112.3875241,"5008496","2026-09-10 16:00:00",["81","25","3","SW","6.2"],"ndf"],["","Kab. Serang","Anyer",-6.069849981,105.889949016,"5008861","2026-09-10 16:00:00",["85","25","3","E","2.9"],"ndf"],["","Kab. Pandeglang","Cipeucang",-6.404519258,105.991272144,"5008837","2026-09-10 16:00:00",["93","24","3","NW","0.8"],"ndf"],["","Kab. Pandeglang","Labuan",-6.375210006,105.82492196,"5008843","2026-09-10 16:00:00",["87","24","3","SE","14.5"],"ndf"],["","Kab. Lebak","Bayah",-6.963043436,106.261703353,"5008798","2026-09-10 16:00:00",["86","25","3","SE","6.1"],"ndf"],["","Kab. Bogor","Gunung Putri",-6.46506358,106.908963981,"5009478","2026-09-10 16:00:00",["92","25","2","S","1.5"],"ndf"],["","Kab. Tasikmalaya","Sukaratu",-7.352534912,108.112664318,"5009770","2026-09-10 16:00:00",["98","20","3","N","1.9"],"ndf"],["","Kota Tasikmalaya","Bungursari",-7.288330073,108.136465497,"5009289","2026-09-10 16:00:00",["99","20","3","E","1.3"],"ndf"],["","Kab. Karawang","Rengasdengklok",-6.159549002,107.299416997,"5009716","2026-09-10 16:00:00",["85","26","3","S","4.1"],"ndf"],["","Kab. Karawang","Lemahabang",-6.285241004,107.454903983,"5009577","2026-09-10 16:00:00",["91","26","3","SW","3.6"],"ndf"],["","Kab. Karawang","Cilamaya Kulon",-6.249833331,107.595294993,"5009386","2026-09-10 16:00:00",["90","26","3","SW","3.5"],"ndf"],["","Kab. Pangandaran","Cijulang",-7.727001947,108.474412624,"5009361","2026-09-10 16:00:00",["89","24","3","NE","6.8"],"ndf"],["","Kab. Pangandaran","Pangandaran",-7.676011674,108.630918161,"5009656","2026-09-10 16:00:00",["89","24","3","NE","9.7"],"ndf"],["","Kab. Cilacap","Sampang",-7.635019103,108.750901937,"5009979","2026-09-10 16:00:00",["90","24","3","E","9.2"],"ndf"],["","Kab. Indramayu","Indramayu",-6.349135574,108.321413261,"501225","2026-09-10 16:00:00",["79","27","2","SW","5.9"],"ndf"],["","Kab. Cirebon","Depok",-6.752579243,108.425806875,"5009461","2026-09-10 16:00:00",["90","24","3","SE","2.8"],"ndf"],["","Kab. Purbalingga","Kalimanah",-7.389399477,109.358153604,"5010234","2026-09-10 16:00:00",["85","24","2","E","0.8"],"ndf"],["","Kab. Purbalingga","Kemangkon",-7.443698777,109.328761312,"5010240","2026-09-10 16:00:00",["87","23","2","SE","4.3"],"ndf"],["","Kab. Banyumas","Sokaraja",-7.460949869,109.29009507,"5009888","2026-09-10 16:00:00",["87","23","2","SE","4.3"],"ndf"],["","Kab. Banyumas","Purwokerto Timur",-7.424377553,109.240102594,"5009885","2026-09-10 16:00:00",["91","22","2","SE","1.2"],"ndf"],["","Kab. Banyumas","Patikraja",-7.497177788,109.226513889,"5009881","2026-09-10 16:00:00",["87","24","2","SE","3.1"],"ndf"],["","Kab. Pekalongan","Kedungwuni",-6.992543968,109.633176454,"5010204","2026-09-10 16:00:00",["83","25","2","S","3.7"],"ndf"],["","Kab. Purworejo","Loano",-7.688638344,110.060283804,"5010258","2026-09-10 16:00:00",["98","21","2","NE","4.2"],"ndf"],["","Kota Magelang","Magelang",-7.468492402,110.218304767,"501251","2026-09-10 16:00:00",["97","20","2","NW","1.3"],"ndf"],["","Kab. Magelang","Secang",-7.392101294,110.241696356,"5010173","2026-09-10 16:00:00",["98","19","3","E","1.1"],"ndf"],["","Kota Yogyakarta","Ngampilan",-7.811809521,110.354963103,"5008059","2026-09-10 16:00:00",["89","23","3","W","4.4"],"ndf"],["","Kota Yogyakarta","Kotagede",-7.823016782,110.39964938,"5008048","2026-09-10 16:00:00",["90","22","3","W","4.4"],"ndf"],["","Kab. Bantul","Pundong",-7.96176125,110.342545171,"5008077","2026-09-10 16:00:00",["90","23","3","E","3.5"],"ndf"],["","Kab. Bantul","Bantul",-7.906866628,110.319450411,"501186","2026-09-10 16:00:00",["90","23","3","W","3.1"],"ndf"],["","Kab. Bantul","Srandakan",-7.940417029,110.24705531,"5008090","2026-09-10 16:00:00",["88","23","3","E","3.7"],"ndf"],["","Kab. Kulon Progo","Lendah",-7.942510954,110.205034029,"5008051","2026-09-10 16:00:00",["88","24","3","E","5.2"],"ndf"],["","Kab. Temanggung","Bulu",-7.279885428,110.101276079,"5010342","2026-09-10 16:00:00",["94","18","3","SW","3.4"],"ndf"],["","Kab. Ponorogo","Jambon",-7.879234689,111.335249757,"5008599","2026-09-10 16:00:00",["87","22","3","SW","1.5"],"ndf"],["","Kab. Ponorogo","Sukorejo",-7.869895305,111.418699834,"5008321","2026-09-10 16:00:00",["83","23","3","S","4.5"],"ndf"],["","Kab. Ponorogo","Ponorogo",-7.867846392,111.470181281,"501299","2026-09-10 16:00:00",["84","24","3","SE","8.1"],"ndf"],["","Kab. Ponorogo","Balong",-7.959803042,111.44038567,"5008597","2026-09-10 16:00:00",["88","22","10","SE","7.8"],"ndf"],["","Kab. Ponorogo","Slahung",-8.03131299,111.416251416,"5008612","2026-09-10 16:00:00",["94","21","10","S","5.5"],"ndf"],["","Kab. Trenggalek","Trenggalek",-8.053465559,111.708486027,"501307","2026-09-10 16:00:00",["95","22","3","SE","5.4"],"ndf"],["","Kab. Trenggalek","Karangan",-8.031513,111.6378353,"5008717","2026-09-10 16:00:00",["95","22","3","E","5"],"ndf"],["","Kab. Mojokerto","Sooko",-7.53244,112.40713,"5008508","2026-09-10 16:00:00",["79","25","3","SW","6.2"],"ndf"],["","Kab. Jombang","Ngoro",-7.690841,112.2686,"5008279","2026-09-10 16:00:00",["81","24","3","SE","0.6"],"ndf"],["","Kab. Kediri","Kandangan",-7.760787615,112.263404164,"5008294","2026-09-10 16:00:00",["82","23","3","SE","2.9"],"ndf"],["","Kab. Kediri","Kayen Kidul",-7.920396613,112.126312655,"5008295","2026-09-10 16:00:00",["90","22","3","S","15.1"],"ndf"],["","Kab. Tuban","Merakurak",-6.886665369,111.999234786,"5008732","2026-09-10 16:00:00",["82","24","3","S","8.9"],"ndf"],["","Kab. Pasuruan","Pandaan",-7.654107394,112.702816398,"5008581","2026-09-10 16:00:00",["86","22","3","SW","6"],"ndf"],["","Kab. Mojokerto","Bangsal",-7.495332815,112.478661372,"5008493","2026-09-10 16:00:00",["75","26","3","SW","5.6"],"ndf"],["","Kab. Tulungagung","Gondang",-7.606365492,112.472326934,"5008497","2026-09-10 16:00:00",["84","23","3","S","2.3"],"ndf"],["","Kab. Pasuruan","Grati",-7.727654,112.959446,"5008575","2026-09-10 16:00:00",["74","25","3","SE","1.7"],"ndf"],["","Kota Pasuruan","Purworejo",-7.675324,112.887568,"5008341","2026-09-10 16:00:00",["72","26","3","SE","1.7"],"ndf"],["","Kab. Pasuruan","Poh Jentrek",-7.665517104,112.854816978,"5008583","2026-09-10 16:00:00",["73","25","3","SE","1.7"],"ndf"],["","Kab. Pasuruan","Kejayan",-7.718021,112.802803,"5008576","2026-09-10 16:00:00",["77","24","3","SW","6.1"],"ndf"],["","Kab. Bangkalan","Kamal",-7.165229692,112.71896531,"5008106","2026-09-10 16:00:00",["78","27","3","N","2"],"ndf"],["","Kab. Bangkalan","Bangkalan",-7.025260305,112.747956975,"501272","2026-09-10 16:00:00",["83","26","3","NE","9"],"ndf"],["","Kab. Bangkalan","Tanah Merah",-7.090009833,112.888294387,"5008115","2026-09-10 16:00:00",["83","26","3","E","10.4"],"ndf"],["","Kab. Bangkalan","Kwanyar",-7.151984376,112.867502366,"5008110","2026-09-10 16:00:00",["81","26","3","E","11.9"],"ndf"],["","Kab. Bangkalan","Blega",-7.129919,113.062638,"5008102","2026-09-10 16:00:00",["80","26","3","SE","18.3"],"ndf"],["","Kab. Sampang","Sampang",-7.2031402,113.2490578,"501302","2026-09-10 16:00:00",["77","27","3","SE","13.8"],"ndf"],["","Kab. Pamekasan","Pamekasan",-7.161089099,113.486967199,"501296","2026-09-10 16:00:00",["87","26","3","SW","4.8"],"ndf"],["","Kab. Pamekasan","Tlanakan",-7.215425021,113.408272152,"5008569","2026-09-10 16:00:00",["84","26","2","S","7.4"],"ndf"],["","Kab. Sumenep","Kalianget",-7.053456989,113.942461483,"5008698","2026-09-10 16:00:00",["81","27","3","E","21.5"],"ndf"],["","Kab. Sumenep","Kota Sumenep",-7.006222376,113.863924627,"5008700","2026-09-10 16:00:00",["82","26","3","E","12.3"],"ndf"],["","Kab. Probolinggo","Paiton",-7.715921,113.510282,"5008629","2026-09-10 16:00:00",["77","26","3","S","7.7"],"ndf"],["","Kab. Probolinggo","Paiton",-7.74495,113.451937,"5008629","2026-09-10 16:00:00",["79","25","3","SE","0.7"],"ndf"],["","Kab. Malang","Tirtoyudo",-8.213929,112.75227,"5008487","2026-09-10 16:00:00",["96","20","3","E","12.5"],"ndf"],["","Kab. Malang","Turen",-8.171022,112.642412,"5008489","2026-09-10 16:00:00",["93","22","3","E","10"],"ndf"],["","Kab. Lumajang","Lumajang",-8.139456702,113.212026181,"501286","2026-09-10 16:00:00",["96","23","3","S","1"],"ndf"],["","Kab. Lumajang","Pasirian",-8.216462951,113.115375026,"5008414","2026-09-10 16:00:00",["94","23","3","SW","1"],"ndf"],["","Kab. Jember","Puger",-8.37220606,113.473873968,"5008253","2026-09-10 16:00:00",["89","24","2","E","13.9"],"ndf"],["","Kab. Jember","Wuluhan",-8.31538929,113.484243659,"5008267","2026-09-10 16:00:00",["89","24","2","SE","6.7"],"ndf"],["","Kab. Jember","Rambipuji",-8.272947558,113.538310009,"5008254","2026-09-10 16:00:00",["92","24","2","SE","2.4"],"ndf"],["","Kab. Jember","Ambulu",-8.347506223,113.593803006,"5008236","2026-09-10 16:00:00",["90","24","2","SE","9.5"],"ndf"],["","Kab. Situbondo","Panarukan",-7.700275222,113.932236567,"5008681","2026-09-10 16:00:00",["84","24","3","S","5.9"],"ndf"],["","Kab. Situbondo","Kapongan",-7.697300896,114.032768794,"5008677","2026-09-10 16:00:00",["80","25","3","S","5.9"],"ndf"],["","Kab. Bondowoso","Bondowoso",-7.916230027,113.833381859,"501278","2026-09-10 16:00:00",["86","22","3","S","7.8"],"ndf"],["","Kab. Banyuwangi","Cluring",-8.433642,114.226833,"5008120","2026-09-10 16:00:00",["93","23","3","NE","0.9"],"ndf"],["","Kab. Banyuwangi","Srono",-8.402225,114.262621,"5008139","2026-09-10 16:00:00",["93","24","3","E","6.3"],"ndf"],["","Kab. Malang","Bululawang",-8.10876,112.6359965,"5008462","2026-09-10 16:00:00",["93","22","3","NW","1"],"ndf"],["","Kab. Boyolali","Boyolali",-7.537513297,110.599672461,"501240","2026-09-10 16:00:00",["82","22","3","SW","11.9"],"ndf"],["","Kab. Cilacap","Cilacap Tengah",-7.685,109.022989,"5009961","2026-09-10 16:00:00",["88","24","3","E","12.5"],"ndf"],["","Kab. Tegal","Adiwerna",-6.982,109.137,"5010323","2026-09-10 16:00:00",["78","25","2","S","11.3"],"ndf"],["","Kab. Sleman","Kalasan",-7.775,110.464982,"5008043","2026-09-10 16:00:00",["90","22","3","SW","6.2"],"ndf"],["","Kota Surakarta","Pasar Kliwon",-7.576,110.836,"5010144","2026-09-10 16:00:00",["79","24","3","SW","11.5"],"ndf"],["","Kota Malang","Alun - alun kota Malang",-7.989,112.63,"5008330","2026-09-10 16:00:00",["97","21","3","W","3.3"],"ndf"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12" customHeight="1">
+      <c r="A6" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>DWT: cuaca kecamatan/stasiun (jalan+kereta)</t>
+        </is>
+      </c>
+      <c r="C6" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="58" t="inlineStr">
+        <is>
+          <t>https://publik.bmkg.go.id/event/source/dwt/apiDF_Darat/202609101600.json</t>
+        </is>
+      </c>
+      <c r="F6" s="68" t="inlineStr">
+        <is>
+          <t>[["lampung","Kab. Lampung Tengah","Terusan Nunyai",-4.699604904679063,105.20665965569867,"5013584","2026-09-10 16:00:00",["78","26","1","SE","9.5"],"ndf"],["lampung","Kab. Lampung Tengah","Seputih Agung",-4.89787745875816,105.05458830281606,"5013578","2026-09-10 16:00:00",["80","26","3","SE","9.2"],"ndf"],["lampung","Kab. Lampung Utara","Kotabumi",-4.846956993233334,104.85804482373453,"501378","2026-09-10 16:00:00",["81","26","1","SE","11.7"],"ndf"],["lampung","Kab. Lampung Utara","Abung Barat",-4.865040896877758,104.69148255332641,"5013612","2026-09-10 16:00:00",["87","24","1","SE","5.5"],"ndf"],["lampung","Kab. Way Kanan","Gunung Labuhan",-4.789374036892298,104.57536485624172,"5013720","2026-09-10 16:00:00",["83","26","1","E","3.4"],"ndf"],["lampung","Kab. Way Kanan","Baradatu",-4.638040316921547,104.54443186316593,"5013716","2026-09-10 16:00:00",["79","26","1","E","10.1"],"ndf"],["lampung","Kab. Way Kanan","Blambangan Umpu",-4.475761076323806,104.45210877613977,"5013717","2026-09-10 16:00:00",["82","26","61","E","10.4"],"ndf"],["lampung","Kab. Way Kanan","Way Tuba",-4.369637115463831,104.360737473516,"5013727","2026-09-10 16:00:00",["89","25","1","E","6.1"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Lubuk Raja",-4.220206964297745,104.25604118925946,"5010811","2026-09-10 16:00:00",["89","25","1","E","2.8"],"ndf"],["lampung","Kab. Tulang Bawang Barat","Tulang Bawang Tengah",-4.547795292507033,105.09625266502826,"5013710","2026-09-10 16:00:00",["77","26","1","SE","11.1"],"ndf"],["lampung","Kab. Tulang Bawang","Gedung Meneng",-4.550000259705826,105.3567798505565,"5013697","2026-09-10 16:00:00",["82","26","1","SE","11.8"],"ndf"],["lampung","Kab. Lampung Tengah","Way Seputih",-4.726080374137268,105.42102529771392,"5013587","2026-09-10 16:00:00",["83","26","1","SE","11.8"],"ndf"],["lampung","Kab. Lampung Timur","Way Bungur (Purbolinggo Utara)",-4.893118536746499,105.52001087555635,"5013610","2026-09-10 16:00:00",["83","25","1","S","10.8"],"ndf"],["lampung","Kab. Lampung Selatan","Penengahan",-5.081095956207093,105.5228662287634,"5013552","2026-09-10 16:00:00",["85","25","1","S","10.7"],"ndf"],["lampung","Kab. Lampung Timur","Labuhan Ratu",-5.12582982311676,105.68466957715987,"5013596","2026-09-10 16:00:00",["88","24","1","S","9.9"],"ndf"],["lampung","Kab. Lampung Timur","Mataram Baru",-5.2838260339038925,105.756529299536,"5013599","2026-09-10 16:00:00",["90","24","2","SW","11.7"],"ndf"],["lampung","Kab. Lampung Timur","Labuhan Maringgai",-5.428497263058318,105.80221495084794,"5013595","2026-09-10 16:00:00",["91","24","2","SW","11.5"],"ndf"],["lampung","Kab. Lampung Selatan","Ketapang",-5.641696969180657,105.78079980179547,"5013548","2026-09-10 16:00:00",["90","24","2","SW","8.7"],"ndf"],["lampung","Kab. Lampung Selatan","Bakauheni",-5.81492173040516,105.7655712513581,"5013543","2026-09-10 16:00:00",["90","25","2","SW","11.1"],"ndf"],["lampung","Kab. Lampung Selatan","Bakauheni",-5.7606700194721725,105.69656688218902,"5013543","2026-09-10 16:00:00",["93","23","2","SW","7.3"],"ndf"],["lampung","Kab. Lampung Selatan","Way Panji",-5.642172861381937,105.54523316221827,"5013558","2026-09-10 16:00:00",["88","25","1","S","9.2"],"ndf"],["lampung","Kab. Lampung Selatan","Merbau Mataram",-5.5450908523440035,105.40294139406967,"5013549","2026-09-10 16:00:00",["86","25","1","S","14.8"],"ndf"],["lampung","Kota Bandar Lampung","Tanjung Karang Timur",-5.425166017650099,105.29824510981314,"5013741","2026-09-10 16:00:00",["87","25","10","S","10.8"],"ndf"],["lampung","Kab. Lampung Selatan","Natar",-5.285253710507391,105.1940247177576,"5013550","2026-09-10 16:00:00",["88","24","1","S","1.9"],"ndf"],["lampung","Kab. Lampung Tengah","Bumi Ratu Nuban",-5.084903093816365,105.19259704115422,"5013567","2026-09-10 16:00:00",["81","26","2","S","5.2"],"ndf"],["lampung","Kab. Lampung Tengah","Gunung Sugih",-4.891690860143001,105.2159157590113,"501375","2026-09-10 16:00:00",["79","26","2","SE","8.7"],"ndf"],["lampung","Kab. Tulang Bawang Barat","Panaragan Jaya",-4.425134077656537,104.94566252662167,"5002238","2026-09-10 16:00:00",["75","27","2","SE","11.2"],"ndf"],["lampung","Kab. Way Kanan","Pakuan Ratu",-4.3804002107468705,104.82288233872089,"5013725","2026-09-10 16:00:00",["75","27","1","SE","12.2"],"ndf"],["sumateraselatan","Kab. OKU Timur","Belitang Jaya",-4.300926213152138,104.73960120351683,"5010840","2026-09-10 16:00:00",["74","27","0","E","11.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Belitang",-4.156254983997712,104.6515611463011,"5010837","2026-09-10 16:00:00",["76","26","1","E","11.2"],"ndf"],["sumateraselatan","Kab. OKU Timur","Buay Madang",-4.2181209701493,104.50831759375006,"5010845","2026-09-10 16:00:00",["81","26","61","E","9.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Madang Suku II",-4.1039068418694455,104.4559694516218,"5010851","2026-09-10 16:00:00",["87","25","61","E","8.8"],"ndf"],["sumateraselatan","Kab. OKU Timur","Madang Suku I",-3.975415947554609,104.55019610745262,"5010850","2026-09-10 16:00:00",["86","26","61","E","9.5"],"ndf"],["sumateraselatan","Kab. OKU Timur","Semendawai Barat",-3.8316965028024583,104.61111030920199,"5010853","2026-09-10 16:00:00",["77","27","0","SE","7.6"],"ndf"],["sumateraselatan","Kab. OKU Timur","Cempaka",-3.674176184216492,104.70105393522232,"5010848","2026-09-10 16:00:00",["78","27","0","SE","7"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ilir","Teluk Gelam",-3.519987111038688,104.76244402917274,"5010805","2026-09-10 16:00:00",["78","27","0","E","5.9"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Semidang Aji",-4.0760116273443145,104.02428168729153,"5010816","2026-09-10 16:00:00",["85","25","1","E","5.3"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ulu","Pengandonan",-4.066017891119884,103.84487032745182,"5010813","2026-09-10 16:00:00",["91","23","1","SE","4.3"],"ndf"],["sumateraselatan","Kab. Muaraenim","Tanjung Agung",-3.9137323867467444,103.79823289173765,"5010738","2026-09-10 16:00:00",["94","24","2","SE","5.9"],"ndf"],["sumateraselatan","Kab. Muaraenim","Lawang Kidul",-3.7295621048954786,103.79918467614004,"5010727","2026-09-10 16:00:00",["97","24","1","E","5.6"],"ndf"],["bengkulu","Kota Bengkulu","Selebar",-3.882543799999894,102.35218700000013,"5011019","2026-09-10 16:00:00",["87","25","10","SE","8.3"],"ndf"],["bengkulu","Kab. Seluma","Air Periukkan",-4.00379229999993,102.46548350000012,"5011000","2026-09-10 16:00:00",["87","25","10","E","9.7"],"ndf"],["bengkulu","Kab. Seluma","Seluma Timur",-4.093860799999959,102.6000661000001,"5011006","2026-09-10 16:00:00",["89","25","1","E","8.2"],"ndf"],["bengkulu","Kab. Seluma","Talo Kecil",-4.204463399999895,102.73121540000005,"5011012","2026-09-10 16:00:00",["89","25","1","E","10.2"],"ndf"],["bengkulu","Kab. Seluma","Semidang Alas Maras",-4.333194599999956,102.76795090000019,"5011009","2026-09-10 16:00:00",["88","25","1","E","11.8"],"ndf"],["bengkulu","Kab. Bengkulu Selatan","Kota Manna",-4.437247899999875,102.8829103000001,"5010899","2026-09-10 16:00:00",["89","25","10","E","13.5"],"ndf"],["bengkulu","Kab. Bengkulu Selatan","Kedurang Ilir",-4.517169199999955,103.00564820000005,"5010898","2026-09-10 16:00:00",["89","25","1","E","15.9"],"ndf"],["bengkulu","Kab. Kaur","Tanjung Kemuning",-4.595883799999967,103.16220340000012,"5010948","2026-09-10 16:00:00",["89","25","1","SE","13.1"],"ndf"],["bengkulu","Kab. Kaur","Kaur Tengah",-4.704700999999943,103.28957610000003,"5010936","2026-09-10 16:00:00",["89","24","10","E","16"],"ndf"],["bengkulu","Kab. Kaur","Maje",-4.81059329999988,103.40355930000004,"5010942","2026-09-10 16:00:00",["89","25","2","E","17.7"],"ndf"],["bengkulu","Kab. Kaur","Nasal",-4.893037599999957,103.53041710000014,"5010944","2026-09-10 16:00:00",["90","25","10","SE","12.9"],"ndf"],["lampung","Kab. Pesisir Barat","Lemong",-4.893037599999957,103.6734110000001,"5013655","2026-09-10 16:00:00",["96","23","10","SE","5.8"],"ndf"],["lampung","Kab. Pesisir Barat","Pesisir Utara",-5.0134358999999336,103.75134520000006,"5013659","2026-09-10 16:00:00",["94","23","2","SE","8.7"],"ndf"],["lampung","Kab. Pesisir Barat","Pulau Pisang",-5.10034909999996,103.86499870000011,"5013660","2026-09-10 16:00:00",["94","23","1","E","9.1"],"ndf"],["lampung","Kab. Pesisir Barat","Krui Selatan",-5.227717699999971,103.9176988000001,"5013654","2026-09-10 16:00:00",["88","25","1","E","15.7"],"ndf"],["lampung","Kab. Pesisir Barat","Pesisir Selatan",-5.326004599999919,104.0217256000002,"5013657","2026-09-10 16:00:00",["88","24","1","E","14.2"],"ndf"],["lampung","Kab. Pesisir Barat","Ngambur",-5.4565736999999785,104.12506570000005,"5013656","2026-09-10 16:00:00",["89","24","1","E","18.4"],"ndf"],["lampung","Kab. Pesisir Barat","Bengkunat Belimbing",-5.519113799999957,104.26565640000013,"5013652","2026-09-10 16:00:00",["90","24","1","E","7.4"],"ndf"],["lampung","Kab. Pesisir Barat","Bengkunat Belimbing",-5.6252117999998745,104.38770760000011,"5013652","2026-09-10 16:00:00",["91","24","2","SE","5.4"],"ndf"],["lampung","Kab. Tanggamus","Semaka",-5.519626399999936,104.4520806000001,"5013686","2026-09-10 16:00:00",["94","23","3","SE","6.1"],"ndf"],["lampung","Kab. Tanggamus","Kota Agung Barat",-5.472978299999909,104.53104490000004,"5013680","2026-09-10 16:00:00",["96","22","10","SE","6.1"],"ndf"],["lampung","Kab. Tanggamus","Kota Agung Timur",-5.484768799999813,104.68845830000004,"5013681","2026-09-10 16:00:00",["98","23","10","SE","7.7"],"ndf"],["lampung","Kab. Tanggamus","Gunung Alip",-5.362067699999955,104.7852754000001,"5013676","2026-09-10 16:00:00",["92","23","2","SW","6.5"],"ndf"],["lampung","Kab. Pringsewu","Gading Rejo",-5.35642769999987,104.96363150000008,"5013665","2026-09-10 16:00:00",["85","24","1","S","8.4"],"ndf"],["lampung","Kab. Pesawaran","Gedong Tataan",-5.373176799999953,105.13117300000016,"5013642","2026-09-10 16:00:00",["91","23","10","SE","4.4"],"ndf"],["bengkulu","Kab. Bengkulu Utara","Air Napal",-3.616926352416101,102.18066538555348,"5010917","2026-09-10 16:00:00",["87","25","1","E","5.7"],"ndf"],["bengkulu","Kab. Bengkulu Utara","Ketahun",-3.3970641554774943,101.85991404196756,"5010926","2026-09-10 16:00:00",["86","26","1","E","10.2"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Basa Ampek Balai Tapan",-2.1388051755944275,101.07707137104939,"5013357","2026-09-10 16:00:00",["92","24","10","NE","4.1"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Linggo Sari Baganti",-1.9008590750113967,100.86672701813393,"5013364","2026-09-10 16:00:00",["96","24","2","NE","1.2"],"ndf"],["sumaterabarat","Kab. Pesisir Selatan","Batang Kapas",-1.4025999403904734,100.59737203227394,"5013358","2026-09-10 16:00:00",["90","25","2","NE","1.3"],"ndf"],["sumateraselatan","Kab. Lahat","Merapi Barat",-3.741610109121666,103.67829814262313,"5010708","2026-09-10 16:00:00",["97","24","2","E","4.1"],"ndf"],["sumateraselatan","Kab. Lahat","Gumay Talang",-3.778729700812562,103.52363317724416,"5010700","2026-09-10 16:00:00",["98","24","1","SW","1.8"],"ndf"],["sumateraselatan","Kab. Ogan Komering Ilir","Mesuji",-4.002724228364855,105.08409361928841,"5010795","2026-09-10 16:00:00",["78","27","1","SE","11"],"ndf"],["sumateraselatan","Kab. Muaraenim","Lubai",-3.7394527311431034,104.22896887166553,"5010729","2026-09-10 16:00:00",["90","25","61","SE","8.6"],"ndf"],["sumateraselatan","Kota Lubuk Linggau","Lubuklinggau Utara I ?",-3.1277588999999466,102.81657850000005,"5010866","2026-09-10 16:00:00",["97","24","3","W","8"],"ndf"],["sumateraselatan","Kab. Muaraenim","Kelekar",-3.2226338006767037,104.49499261211736,"5010726","2026-09-10 16:00:00",["76","27","1","E","9.6"],"ndf"],["jambi","Kab. Tebo","Tebo Tengah",-1.4767471163646633,102.46032468195699,"5010653","2026-09-10 16:00:00",["99","23","61","E","6.4"],"ndf"],["jambi","Kab. Batanghari","Muara Tembesi",-1.723735168769906,103.14085052962446,"5010549","2026-09-10 16:00:00",["97","24","61","N","4.3"],"ndf"],["sumaterabarat","Kab. Padang Pariaman","2x11 Enam Lingkung",-0.5355243498658524,100.33670207908523,"5013317","2026-09-10 16:00:00",["97","21","2","NE","2.2"],"ndf"],["sumaterabarat","Kab. Sijunjung","Kamang Baru",-0.8766470506943165,101.32199053676788,"5013372","2026-09-10 16:00:00",["98","23","10","S","1.9"],"ndf"],["sumaterabarat","Kab. Dharmasraya","Sungai Rumbai",-1.1945430410731888,101.72554712335665,"5013259","2026-09-10 16:00:00",["99","24","10","E","4.3"],"ndf"],["sumaterabarat","Kab. Tanah Datar","Tanjung Emas",-0.491785099999845,100.6741378000001,"5013412","2026-09-10 16:00:00",["94","22","10","N","1.6"],"ndf"],["sumaterabarat","Kab. Pasaman","Lubuk Sikaping",0.15118809641677444,100.16776034767128,"501543","2026-09-10 16:00:00",["99","19","45","NE","1"],"ndf"],["sumaterabarat","Kab. Pasaman","Rao",0.5304741807460687,100.03213107033895,"5013340","2026-09-10 16:00:00",["96","21","2","SW","5.9"],"ndf"],["sumaterautara","Kab. Mandailing Natal","Kotanopan",0.6722900566936119,99.69424760751104,"5011926","2026-09-10 16:00:00",["98","19","3","NE","0.7"],"ndf"],["sumaterautara","Kab. Tapanuli Selatan","Tanotombangan Angkola",1.0929787625244103,99.4543979381234,"5012118","2026-09-10 16:00:00",["99","21","3","SW","2.4"],"ndf"],["riau","Kab. Pelalawan","Pangkalan Kerinci",0.3599183816165237,101.90091017221368,"501476","2026-09-10 16:00:00",["98","24","10","E","6.3"],"ndf"],["riau","Kab. Pelalawan","Pangkalan Lesung",0.026317948599057672,102.11173041733036,"5010481","2026-09-10 16:00:00",["99","24","61","E","3.3"],"ndf"],["jambi","Kab. Tanjung Jabung Barat","Tungkal Ulu",-1.1039260291702249,103.03400950319013,"5010634","2026-09-10 16:00:00",["98","24","61","S","4.8"],"ndf"],["jambi","Kab. Tanjung Jabung Barat","Merlung",-1.2552597491409756,103.05209340683433,"5010627","2026-09-10 16:00:00",["99","23","61","N","3.1"],"ndf"],["jambi","Kab. Tanjung Jabung Timur","Mendahara Ulu",-1.3394926687474253,103.3704652894146,"5010640","2026-09-10 16:00:00",["99","24","61","NE","1.7"],"ndf"],["jambi","Kab. Muaro Jambi","Sakernan",-1.4337193245782487,103.50038386033287,"501210","2026-09-10 16:00:00",["97","24","61","W","9.7"],"ndf"],["jambi","Kota Jambi","Danau Teluk",-1.5755352005258487,103.56748466069729,"5010671","2026-09-10 16:00:00",["97","25","61","SW","1.4"],"ndf"],["sumaterautara","Kab. Tapanuli Tengah","Sibabangun",1.5198540669704244,98.96518075532475,"5012129","2026-09-10 16:00:00",["99","24","3","NE","2.9"],"ndf"],["sumaterautara","Kab. Tapanuli Tengah","Badiri",1.6350199796524976,98.84620770503324,"5012120","2026-09-10 16:00:00",["91","24","3","NE","2.3"],"ndf"],["sumaterautara","Kab. Tapanuli Selatan","Marancar",1.6430110028638296,99.1889492340814,"5012114","2026-09-10 16:00:00",["99","21","3","SW","2.3"],"ndf"],["riau","Kab. Siak","Kandis",0.7279020261682376,101.44964539245808,"5010518","2026-09-10 16:00:00",["99","24","10","E","6.7"],"ndf"],["riau","Kota Dumai","Dumai Barat",1.6187722267511617,101.33638304858044,"5010531","2026-09-10 16:00:00",["97","25","10","SE","4.5"],"ndf"],["sumaterautara","Kab. Toba Samosir","Tampahan",2.3326779465620007,99.07225650058712,"5012169","2026-09-10 16:00:00",["92","20","3","SE","4.9"],"ndf"],["sumaterautara","Kab. Samosir","Pangururan",2.5125057120776546,98.64444924058057,"501583","2026-09-10 16:00:00",["96","17","3","SW","5.8"],"ndf"],["sumaterautara","Kab. Labuhanbatu","Bilah Barat",2.1867793121053296,99.77132231525815,"5011883","2026-09-10 16:00:00",["96","25","3","E","0.1"],"ndf"],["sumaterautara","Kab. Labuhanbatu Selatan","Kota Pinang",2.0421080829509037,100.04115319331925,"5002211","2026-09-10 16:00:00",["96","25","2","SE","5.5"],"ndf"],["riau","Kab. Rokan Hilir","Bangko Pusako",1.6242747303271585,101.02149112772133,"5010487","2026-09-10 16:00:00",["98","25","10","S","0.7"],"ndf"],["sumaterautara","Kab. Deli Serdang","Pancur Batu",3.4431624835622756,98.60141470540583,"5011843","2026-09-10 16:00:00",["97","24","3","S","2"],"ndf"],["sumaterautara","Kab. Deli Serdang","Sibolangit",3.2782658358581216,98.55323062003777,"5011848","2026-09-10 16:00:00",["94","20","3","S","5.3"],"ndf"],["aceh","Kab. Aceh Utara","Aceh Utara",5.070186364360438,97.30967472628646,"501408","2026-09-10 16:00:00",["98","24","3","SW","5.6"],"ndf"],["aceh","Kota Lhokseumawe","Blang Mangat",5.130624673908642,97.14882316229244,"5012856","2026-09-10 16:00:00",["97","24","3","SW","5.6"],"ndf"],["aceh","Kab. Bireuen","Simpang Mamplam",5.189635306853177,96.48114640405635,"5012778","2026-09-10 16:00:00",["84","26","3","SE","6.8"],"ndf"],["aceh","Kab. Aceh Besar","Lembah Seulawah",5.367714168529517,95.64214845340064,"5012612","2026-09-10 16:00:00",["93","23","3","SE","2.6"],"ndf"],["aceh","Kab. Nagan Raya","Kuala Pesisir",4.10755261128395,96.19836729235533,"5012794","2026-09-10 16:00:00",["97","25","3","N","7.1"],"ndf"],["aceh","Kab. Nagan Raya","Darul Makmur",4.0361687811090405,96.46914995481876,"5012792","2026-09-10 16:00:00",["98","24","3","W","2.3"],"ndf"],["aceh","Kab. Aceh Selatan","Trumon Timur",2.863570397435751,97.75548657457057,"5012647","2026-09-10 16:00:00",["99","23","3","NW","2"],"ndf"],["aceh","Kab. Aceh Barat","Woyla",4.366913860919453,96.07939424206381,"5012586","2026-09-10 16:00:00",["99","24","3","NE","2.1"],"ndf"],["aceh","Kab. Aceh Jaya","Indra Jaya",5.082179839271987,95.36174880270528,"5012623","2026-09-10 16:00:00",["89","25","3","NE","3.5"],"ndf"],["aceh","Kab. Aceh Barat","Samatiga",4.231104891967991,96.00768848190984,"5012584","2026-09-10 16:00:00",["97","26","3","N","8.8"],"ndf"],["sumaterautara","Kab. Dairi","Gunung Sitember",3.0358924913035437,98.15857700719724,"5011820","2026-09-10 16:00:00",["99","20","3","SE","1.5"],"ndf"],["sumaterautara","Kab. Labuhanbatu Utara","Kualuh Leidong",2.7478372097551804,99.9606086067617,"5011897","2026-09-10 16:00:00",["98","25","3","W","0.3"],"ndf"],["sumaterautara","Kab. Padanglawas Utara","Dolok",1.8146469559800216,99.677669247752,"5012024","2026-09-10 16:00:00",["98","22","3","SW","3"],"ndf"],["sumaterautara","Kab. Padanglawas Utara","Halongonan",1.5702810614967202,99.7216209928409,"5012026","2026-09-10 16:00:00",["83","25","3","SW","7.9"],"ndf"],["sumaterabarat","Kab. Pasaman Barat","Koto Balingka",0.2931021322718861,99.52131750259426,"5013347","2026-09-10 16:00:00",["98","23","10","SW","1.5"],"ndf"],["sumaterabarat","Kab. Agam","Tanjung Mutiara",-0.37438688568208195,99.9251241605984,"5013249","2026-09-10 16:00:00",["97","24","10","N","6.5"],"ndf"],["sumaterabarat","Kota Solok","Lubuk Sikarah",-0.8056238864892095,100.65582192270112,"5013302","2026-09-10 16:00:00",["95","21","10","S","1.9"],"ndf"],["sumaterabarat","Kab. Solok Selatan","Koto Parik Gadang Diateh",-1.4400291488376946,101.01292985154838,"5013394","2026-09-10 16:00:00",["98","19","10","S","0.8"],"ndf"],["jambi","Kab. Kerinci","Batang Merangin",-2.2444437264668298,101.72439872517472,"5010570","2026-09-10 16:00:00",["98","19","45","SW","4.1"],"ndf"],["jambi","Kab. Merangin","Renah Pemberap",-2.134648578462278,102.02381998859273,"5010592","2026-09-10 16:00:00",["98","22","61","E","1.9"],"ndf"],["jambi","Kab. Sarolangun","Pauh",-2.1264136211880253,102.8259393364649,"5010620","2026-09-10 16:00:00",["97","24","61","E","4.9"],"ndf"],["jambi","Kab. Tanjung Jabung Timur","Muara Sabak Timur",-1.1554980908004486,103.83610930892148,"5010642","2026-09-10 16:00:00",["99","24","61","SW","7.1"],"ndf"],["kepulauanriau","Kota Batam","Galang",0.7300927288910626,104.21189839179495,"5012398","2026-09-10 16:00:00",["80","28","2","E","10"],"ndf"],["kepulauanbangkabelitung","Kab. Bangka","Puding Besar",-2.0223774065063744,105.92979855405717,"5011028","2026-09-10 16:00:00",["86","23","1","SE","6.9"],"ndf"],["kepulauanbangkabelitung","Kab. Bangka Tengah","Koba",-2.5191715374900148,106.39403886155856,"501362","2026-09-10 16:00:00",["78","25","1","E","4.5"],"ndf"],["riau","Kab. Kuantan Sengingi","Singingi Hilir",-0.24011737986285892,101.32332980439209,"5010473","2026-09-10 16:00:00",["98","24","10","SE","2.4"],"ndf"],["sumaterabarat","Kab. Kepulauan Mentawai","Sikakap",-2.7726252574708035,100.2143287823482,"5013269","2026-09-10 16:00:00",["87","26","2","E","7.5"],"ndf"],["sumaterautara","Kab. Nias Barat","Sirombu",0.9659768999641882,97.41151473543331,"5011978","2026-09-10 16:00:00",["84","26","3","E","6.3"],"ndf"],["jawatimur","Kab. Jember","Sumber Baru",-8.118434441419254,113.3540335906813,"5008259","2026-09-10 16:00:00",["99","22","10","SW","3.5"],"ndf"],["jawatimur","Kab. Jember","Sumber Sari",-8.176136370810639,113.68656326624614,"5008261","2026-09-10 16:00:00",["94","23","3","W","2.7"],"ndf"],["jawatimur","Kab. Banyuwangi","Kalibaru",-8.196956654611654,113.89476610425629,"5008127","2026-09-10 16:00:00",["95","21","10","SE","10.2"],"ndf"],["jawatimur","Kab. Banyuwangi","Kalibaru",-8.243951009476802,113.91618125330876,"5008127","2026-09-10 16:00:00",["97","20","45","E","12.8"],"ndf"],["jawatimur","Kab. Banyuwangi","Banyuwangi",-8.24454587472826,114.35400207838154,"501273","2026-09-10 16:00:00",["95","24","3","S","6.5"],"ndf"],["jawatimur","Kab. Banyuwangi","Banyuwangi",-8.176136370810639,114.38136587994859,"501273","2026-09-10 16:00:00",["94","23","10","SW","8.2"],"ndf"],["jawatimur","Kota Blitar","Alun - Alun Kota Blitar",-8.108369321364535,112.16028179866623,"5008317","2026-09-10 16:00:00",["92","23","3","SE","7"],"ndf"],["daerahistimewayogyakarta","Kab. Bantul","Piyungan",-7.832351844688219,110.45040111987669,"5008072","2026-09-10 16:00:00",["90","23","3","S","4.7"],"ndf"],["daerahistimewayogyakarta","Kab. Gunung Kidul","Gunung Kidul",-7.9679811220205465,110.60363840865222,"501189","2026-09-10 16:00:00",["91","22","3","SE","8.8"],"ndf"],["jawatengah","Kab. Wonogiri","Giritontro",-8.098375585140104,110.91534780041599,"5010364","2026-09-10 16:00:00",["95","22","1","SE","6.6"],"ndf"],["jawatimur","Kab. Ponorogo","Slahung",-8.036985491189625,111.41075158182969,"5008612","2026-09-10 16:00:00",["93","21","10","S","4.7"],"ndf"],["daerahistimewayogyakarta","Kab. Bantul","Kasihan",-7.828068814877668,110.35284321863764,"5008046","2026-09-10 16:00:00",["88","23","3","W","3.4"],"ndf"],["jawatimur","Kab. Situbondo","Banyuputih",-7.786130814649994,114.30556021807126,"5008672","2026-09-10 16:00:00",["85","24","3","SE","3.8"],"ndf"],["jawatimur","Kab. Situbondo","Banyuputih",-7.834195926967709,114.30889146347931,"5008672","2026-09-10 16:00:00",["85","24","3","SE","3.8"],"ndf"],["jawatimur","Kab. Banyuwangi","Wongsorejo",-8.018366208819032,114.40882882572419,"5008143","2026-09-10 16:00:00",["91","24","3","S","17.4"],"ndf"],["jawatengah","Kab. Kebumen","Sempor",-7.61153786334711,109.50956223817127,"5010067","2026-09-10 16:00:00",["95","22","1","SE","2.9"],"ndf"],["jawatengah","Kab. Kebumen","Karanganyar",-7.632477120198473,109.5723800087253,"5010052","2026-09-10 16:00:00",["91","23","1","S","2.5"],"ndf"],["jawatengah","Kab. Purworejo","Butuh",-7.722420746218916,109.83316893496419,"5010252","2026-09-10 16:00:00",["88","24","1","NW","0.3"],"ndf"],["jawatimur","Kota Malang","Kedungkandang",-8.028213211614855,112.61394190250121,"5008333","2026-09-10 16:00:00",["93","22","3","SW","3.1"],"ndf"],["jawatimur","Kab. Malang","Kabupaten Malang",-8.12755570860827,112.57111160439626,"501284","2026-09-10 16:00:00",["94","22","3","SE","4.5"],"ndf"],["jawatimur","Kab. Jombang","Perak",-7.5817668403959715,112.16041663479007,"5008281","2026-09-10 16:00:00",["86","24","3","SW","11.1"],"ndf"],["jawatimur","Kab. Mojokerto","Jetis",-7.43045776770731,112.44390250224751,"5008499","2026-09-10 16:00:00",["79","25","2","W","6.9"],"ndf"],["jawatimur","Kab. Nganjuk","Bagor",-7.555592769331838,111.79278990938923,"5008511","2026-09-10 16:00:00",["82","24","2","W","3.9"],"ndf"],["jawatengah","Kab. Banyumas","Jatilawang",-7.537159878073226,109.13536820039445,"5009872","2026-09-10 16:00:00",["84","25","1","SE","3.1"],"ndf"],["jawatengah","Kab. Banyumas","Sokaraja",-7.440791707337098,109.26742828621803,"5009888","2026-09-10 16:00:00",["87","24","1","E","3.8"],"ndf"],["jawatengah","Kab. Banjarnegara","Purworejo Klampok",-7.461017125886656,109.44350840064948,"5009861","2026-09-10 16:00:00",["88","24","1","S","2.7"],"ndf"],["jawatimur","Kota Mojokerto","Magersari",-7.461009194350083,112.45903899102177,"5008337","2026-09-10 16:00:00",["76","26","2","SW","5.2"],"ndf"],["jawatimur","Kab. Madiun","Mejayan",-7.553356075986358,111.64272523528831,"5008436","2026-09-10 16:00:00",["81","24","2","W","3.2"],"ndf"],["jawatimur","Kab. Ngawi","Kasreman",-7.418178896245138,111.49654701416335,"5008536","2026-09-10 16:00:00",["78","24","2","SE","11"],"ndf"],["daerahistimewayogyakarta","Kab. Sleman","Sleman",-7.713826926219554,110.35797492287355,"501187","2026-09-10 16:00:00",["89","23","10","NW","3"],"ndf"],["jawatengah","Kab. Cilacap","Cipari",-7.440184199999976,108.76107340000016,"5009964","2026-09-10 16:00:00",["84","25","1","S","3.3"],"ndf"],["jawatimur","Kota Surabaya","Surabaya",-7.279277860029765,112.70971520798605,"501306","2026-09-10 16:00:00",["76","27","2","E","6.6"],"ndf"],["jawatimur","Kab. Bojonegoro","Bojonegoro",-7.157770683767069,111.8667911466705,"501277","2026-09-10 16:00:00",["78","25","2","SE","6.7"],"ndf"],["jawabarat","Kab. Pangandaran","Cijulang",-7.734162599999934,108.4657916000001,"5009361","2026-09-10 16:00:00",["90","24","3","NE","4.4"],"ndf"],["jawatengah","Kota Semarang","Semarang Utara",-6.958050624242674,110.41531993311418,"5010138","2026-09-10 16:00:00",["73","27","1","SE","2.3"],"ndf"],["jawatengah","Kab. Kudus","Kudus",-6.802790793612246,110.86801238947339,"501250","2026-09-10 16:00:00",["74","26","1","S","3.3"],"ndf"],["jawabarat","Kab. Tasikmalaya","Pagerageung",-7.10885689702377,108.10565645012139,"5009639","2026-09-10 16:00:00",["99","19","3","SE","4"],"ndf"],["banten","Kab. Lebak","Panggarangan",-6.875927493394784,106.10496697017805,"5008819","2026-09-10 16:00:00",["90","23","2","SE","14.1"],"ndf"],["jawabarat","Kota Bandung","Bandung Kidul",-6.947036621274037,107.61004316015442,"5009239","2026-09-10 16:00:00",["88","22","3","SE","3.7"],"ndf"],["jawabarat","Kab. Cirebon","Pabedilan",-6.828457246328412,108.74908650070802,"5009627","2026-09-10 16:00:00",["76","26","3","S","12.9"],"ndf"],["jawabarat","Kab. Cirebon","Gebang",-6.813585615041973,108.69554862807684,"5009469","2026-09-10 16:00:00",["76","26","3","S","17.2"],"ndf"],["jawabarat","Kab. Cirebon","Astanajapura",-6.7942236062342545,108.60541475410236,"5009232","2026-09-10 16:00:00",["74","25","3","S","11.3"],"ndf"],["jawabarat","Kab. Cirebon","Karangsembung",-6.830391413522818,108.64158256139103,"5009534","2026-09-10 16:00:00",["75","26","3","S","17.2"],"ndf"],["jawabarat","Kab. Cirebon","Weru",-6.702077059376336,108.4675473687829,"5009845","2026-09-10 16:00:00",["78","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Kedawung (Cirebon Barat)",-6.721112747422978,108.50657052927858,"5009546","2026-09-10 16:00:00",["81","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Jamblang",-6.689793026001496,108.44131299157277,"5009493","2026-09-10 16:00:00",["78","26","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Klangenan",-6.6888412415992775,108.39657912466316,"5009557","2026-09-10 16:00:00",["78","26","3","S","0.1"],"ndf"],["jawabarat","Kab. Indramayu","Terisi",-6.573623776383727,107.94915346004183,"5009830","2026-09-10 16:00:00",["93","25","3","S","4.3"],"ndf"],["jawabarat","Kab. Cirebon","Ciwaringin",-6.694262449379266,108.36853346231942,"5009446","2026-09-10 16:00:00",["78","26","3","S","0.1"],"ndf"],["jawabarat","Kab. Cirebon","Arjawinangun",-6.623506338359618,108.37730365008366,"5009230","2026-09-10 16:00:00",["75","27","3","NW","0.5"],"ndf"],["jawabarat","Kab. Cirebon","Suranenggala",-6.603280919810061,108.5141226579189,"5009790","2026-09-10 16:00:00",["71","27","3","E","1.8"],"ndf"]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="12" customHeight="1">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>port-tide</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Maritim: daftar pelabuhan (294)</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan_list</t>
+        </is>
+      </c>
+      <c r="F7" s="68" t="inlineStr">
+        <is>
+          <t>{
+  "files": [
+    {
+      "coor": [
+        1.198331,
+        109.054462
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1720,
+      "name": "0088_Sintete.json",
+      "portname": "Sintete",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.00214,
+        109.285391
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1713,
+      "name": "0310_PPP Sungai Rengas.json",
+      "portname": "PPP Sungai Rengas",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.531535,
+        110.21588
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1692,
+      "name": "0092_Kendawangan.json",
+      "portname": "Kendawangan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        4.145037,
+        117.665883
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1679,
+      "name": "0237_Nunukan.json",
+      "portname": "Nunukan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.6679806,
+        115.261925
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0603_Sanur.json",
+      "portname": "Sanur",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.35863269,
+        105.81975796
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1670,
+      "name": "0325_PPP Labuhan Maringgai.json",
+      "portname": "PPP Labuhan Maringgai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.67206,
+        115.55675
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1649,
+      "name": "0559_Mentigi.json",
+      "portname": "Mentigi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.024312,
+        131.242495
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1595,
+      "name": "0452_Arar.json",
+      "portname": "Arar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.8161046,
+        119.49650816
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1669,
+      "name": "0219_Biringkasi.json",
+      "portname": "Biringkasi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.47938659,
+        140.37922382
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1660,
+      "name": "0505_PPN Merauke.json",
+      "portname": "PPN Merauke",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.638437,
+        108.087731
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1628,
+      "name": "0475_Pulau Tiga.json",
+      "portname": "Pulau Tiga",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.673501,
+        125.061763
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1652,
+      "name": "0465_Likupang.json",
+      "portname": "Likupang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.671619,
+        115.553233
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1675,
+      "name": "0169_Nusa Penida.json",
+      "portname": "Nusa Penida",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.835036,
+        120.517619
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1726,
+      "name": "0531_Pamamata, Selayar.json",
+      "portname": "Pamamata, Selayar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.02081413,
+        122.98861477
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1612,
+      "name": "0231_Langara.json",
+      "portname": "Langara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.84083214,
+        122.73105567
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1639,
+      "name": "0229_Raha.json",
+      "portname": "Raha",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.17656,
+        123.067995
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1641,
+      "name": "0581_Kamaru.json",
+      "portname": "Kamaru",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.0333892,
+        117.53464771
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1629,
+      "name": "0198_Tanjung Santan.json",
+      "portname": "Tanjung Santan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.534242,
+        115.509335
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1613,
+      "name": "0167_Padangbai.json",
+      "portname": "Padangbai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.71162106,
+        108.56879081
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0107_Cirebon.json",
+      "portname": "Cirebon",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.986576,
+        117.988101
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1619,
+      "name": "0199_Sangkuliran.json",
+      "portname": "Sangkuliran",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.2861781,
+        122.28710175
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1655,
+      "name": "0416_Mawasangka.json",
+      "portname": "Mawasangka",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.24655186,
+        108.07697534
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1740,
+      "name": "0383_Tanjung Batu.json",
+      "portname": "Tanjung Batu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.735789,
+        123.893262
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1678,
+      "name": "0598_Tomia.json",
+      "portname": "Tomia",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.411223,
+        121.868417
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1600,
+      "name": "0543_Wakai.json",
+      "portname": "Wakai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.534335,
+        103.660082
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1592,
+      "name": "0537_Talang Duku.json",
+      "portname": "Talang Duku",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        5.89595662,
+        95.33580541
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1666,
+      "name": "0490_TPI Ie Meulle.json",
+      "portname": "TPI Ie Meulle",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.009895,
+        127.41111
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1637,
+      "name": "0432_Kayoa.json",
+      "portname": "Kayoa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.510711,
+        108.851915
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1674,
+      "name": "0566_Pulau Temajo.json",
+      "portname": "Pulau Temajo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.370889,
+        123.404532
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1608,
+      "name": "0401_Lewoleba.json",
+      "portname": "Lewoleba",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.288288,
+        123.766172
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1603,
+      "name": "0553_Wowong.json",
+      "portname": "Wowong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.059416,
+        119.465604
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1678,
+      "name": "1001_Untia-Makassar.json",
+      "portname": "Untia-Makassar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.12278919,
+        119.40804005
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1689,
+      "name": "0010_Soekarno - Hatta.json",
+      "portname": "Soekarno - Hatta",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.508771,
+        123.063138
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1685,
+      "name": "0245_Gorontalo.json",
+      "portname": "Gorontalo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.334359,
+        127.881913
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1596,
+      "name": "0584_Weda.json",
+      "portname": "Weda",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.99766,
+        100.371432
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1734,
+      "name": "0002_Teluk Bayur.json",
+      "portname": "Teluk Bayur",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.662733,
+        119.740983
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1658,
+      "name": "0427_PPN Donggala.json",
+      "portname": "PPN Donggala",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.411231,
+        121.86843
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1599,
+      "name": "0606_Wakai.json",
+      "portname": "Wakai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.491755,
+        105.796904
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1658,
+      "name": "0486_TPI Panimbang.json",
+      "portname": "TPI Panimbang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.87053874,
+        105.75480299
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1629,
+      "name": "0371_ASDP Bakauheni.json",
+      "portname": "ASDP Bakauheni",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.676427,
+        127.456607
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1670,
+      "name": "0593_Goto.json",
+      "portname": "Goto",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.013554,
+        108.864955
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1632,
+      "name": "0477_Subi.json",
+      "portname": "Subi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.703193,
+        120.096647
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1681,
+      "name": "0544_Toboli.json",
+      "portname": "Toboli",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.9093817,
+        106.0920656
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0116_Bojonegara.json",
+      "portname": "Bojonegara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.746072,
+        107.628461
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1663,
+      "name": "0099_Tanjung Pandan.json",
+      "portname": "Tanjung Pandan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.12440269,
+        103.92746488
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1662,
+      "name": "0084_Sekupang.json",
+      "portname": "Sekupang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.472095,
+        122.904247
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1678,
+      "name": "0572_Labuan, Buton Utara.json",
+      "portname": "Labuan, Buton Utara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.071389,
+        104.200898
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1689,
+      "name": "0540_PPI Nipah Panjang.json",
+      "portname": "PPI Nipah Panjang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.42702113,
+        122.59972591
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1602,
+      "name": "0577_Waara.json",
+      "portname": "Waara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.508104,
+        117.155324
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1568,
+      "name": "0194_Samarinda.json",
+      "portname": "Samarinda",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.360455,
+        99.45252
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1628,
+      "name": "0491_Kuala Tanjung.json",
+      "portname": "Kuala Tanjung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.446696,
+        125.208082
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1652,
+      "name": "0356_PPS Bitung.json",
+      "portname": "PPS Bitung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.431713,
+        130.804737
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1604,
+      "name": "0451_Waesai.json",
+      "portname": "Waesai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.50543731,
+        108.90792797
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1719,
+      "name": "0587_Kijing International Port.json",
+      "portname": "Kijing International Port",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.318312,
+        122.049219
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1633,
+      "name": "0414_Dongkala.json",
+      "portname": "Dongkala",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.792772,
+        109.958201
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0089_Sukabangun.json",
+      "portname": "Sukabangun",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.45477862,
+        122.61016846
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1605,
+      "name": "0232_Baubau.json",
+      "portname": "Baubau",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.759426,
+        108.713653
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1683,
+      "name": "0564_Pulau Lemukutan.json",
+      "portname": "Pulau Lemukutan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        4.631485,
+        95.571466
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1653,
+      "name": "0493_Calang.json",
+      "portname": "Calang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.88394883,
+        131.26274482
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0428_Klademak.json",
+      "portname": "Klademak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.0028824,
+        119.6213947
+      ],
+      "file_date": "2025-07-15 07:35 UTC",
+      "kb": 1739,
+      "name": "1002_Pelabuhan Nusantara Pare Pare.json",
+      "portname": "Pelabuhan Nusantara Pare Pare",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.72370295,
+        128.01508784
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0605_Tobelo.json",
+      "portname": "Tobelo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.27075,
+        127.083845
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1609,
+      "name": "0268_Namlea.json",
+      "portname": "Namlea",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.056907,
+        125.98203
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1604,
+      "name": "0585_Sanana.json",
+      "portname": "Sanana",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.741121,
+        127.559672
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1676,
+      "name": "0435_Sofifi.json",
+      "portname": "Sofifi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.38139691,
+        120.75485229
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1718,
+      "name": "0243_Poso.json",
+      "portname": "Poso",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.379997,
+        119.612159
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1653,
+      "name": "0387_Garongkong.json",
+      "portname": "Garongkong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.121565,
+        103.843134
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1614,
+      "name": "0539_Muara Sabak.json",
+      "portname": "Muara Sabak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.02253056,
+        109.34044361
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1574,
+      "name": "0009_Dwikora.json",
+      "portname": "Dwikora",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.671997,
+        115.559211
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0560_Sampalan.json",
+      "portname": "Sampalan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.76756089,
+        127.37779498
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1697,
+      "name": "0359_PPN Ternate.json",
+      "portname": "PPN Ternate",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.704359,
+        111.153891
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1631,
+      "name": "0331_PPP Bajomulyo.json",
+      "portname": "PPP Bajomulyo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.73154157,
+        116.07712462
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1680,
+      "name": "0172_Lembar.json",
+      "portname": "Lembar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.55874,
+        115.45797
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1632,
+      "name": "0561_Tribuana Kusamba.json",
+      "portname": "Tribuana Kusamba",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -9.638949,
+        120.250733
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0189_Waingapu.json",
+      "portname": "Waingapu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.049674,
+        128.291256
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1627,
+      "name": "0448_Daruba-Morotai.json",
+      "portname": "Daruba-Morotai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.73916881,
+        108.98891423
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1671,
+      "name": "0005_Tanjung Intan.json",
+      "portname": "Tanjung Intan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.1981949,
+        124.55118656
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1650,
+      "name": "0464_Amurang.json",
+      "portname": "Amurang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.305703,
+        97.609921
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0027_Gunung Sitoli.json",
+      "portname": "Gunung Sitoli",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.01807244,
+        105.95240196
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0480_Ciwandan.json",
+      "portname": "Ciwandan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.74416252,
+        107.63367282
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1679,
+      "name": "0313_PPN Tanjung Pandan.json",
+      "portname": "PPN Tanjung Pandan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.72896842,
+        98.79120827
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1619,
+      "name": "0026_Sibolga.json",
+      "portname": "Sibolga",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.989044,
+        121.340938
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0225_Kolonodale.json",
+      "portname": "Kolonodale",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.410665,
+        105.851227
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1664,
+      "name": "0328_PPP Teladas.json",
+      "portname": "PPP Teladas",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.69953453,
+        132.44125843
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1645,
+      "name": "0297_Kokas.json",
+      "portname": "Kokas",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.3240778,
+        119.35595556
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1699,
+      "name": "0499_Galesong.json",
+      "portname": "Galesong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.23951,
+        109.138895
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1602,
+      "name": "0389_Tebas Kuala.json",
+      "portname": "Tebas Kuala",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.37186,
+        105.822128
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1648,
+      "name": "0114_PP Labuan.json",
+      "portname": "PP Labuan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.0075,
+        109.76861111
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1631,
+      "name": "0311_PPP Teluk Batang.json",
+      "portname": "PPP Teluk Batang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.886864,
+        136.245077
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1613,
+      "name": "0280_Serui.json",
+      "portname": "Serui",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.78379143,
+        98.71509089
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1675,
+      "name": "0301_PPS Belawan.json",
+      "portname": "PPS Belawan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.43848505,
+        125.19146058
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1650,
+      "name": "0012_Samudera.json",
+      "portname": "Samudera",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.47926077,
+        96.38215542
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1698,
+      "name": "0023_Sinabang.json",
+      "portname": "Sinabang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.842346,
+        120.85443
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1640,
+      "name": "0399_Aimere.json",
+      "portname": "Aimere",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.338727,
+        128.920555
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1605,
+      "name": "0269_Amahai.json",
+      "portname": "Amahai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.867442,
+        121.583612
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1603,
+      "name": "0546_Ampana.json",
+      "portname": "Ampana",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.466321,
+        105.317403
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0003_Panjang.json",
+      "portname": "Panjang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.549392,
+        120.385968
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1600,
+      "name": "0215_Bajoe.json",
+      "portname": "Bajoe",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.73345473,
+        108.58246019
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1665,
+      "name": "0315_PPN Kejawanan.json",
+      "portname": "PPN Kejawanan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.682824,
+        98.833334
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1581,
+      "name": "0597_Ambarita.json",
+      "portname": "Ambarita",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.10265793,
+        106.77192271
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0105_Muara Angke.json",
+      "portname": "Muara Angke",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.521837,
+        116.832732
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0567_Pototano.json",
+      "portname": "Pototano",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.15365576,
+        103.99702308
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1727,
+      "name": "0082_Ferry Harbour Bay.json",
+      "portname": "Ferry Harbour Bay",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.606118,
+        120.463574
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1687,
+      "name": "0576_Bira.json",
+      "portname": "Bira",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.556885,
+        122.50823
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1644,
+      "name": "0579_Kadatua.json",
+      "portname": "Kadatua",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.724771,
+        109.022811
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1661,
+      "name": "0340_PPS Cilacap.json",
+      "portname": "PPS Cilacap",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.419529,
+        122.851327
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1682,
+      "name": "0463_Amolengo.json",
+      "portname": "Amolengo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.93117697,
+        105.99667387
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1625,
+      "name": "0370_ASDP Merak.json",
+      "portname": "ASDP Merak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.309155,
+        123.289117
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1606,
+      "name": "0224_Banggai.json",
+      "portname": "Banggai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.07691,
+        129.427012
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1592,
+      "name": "0583_Gebe.json",
+      "portname": "Gebe",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.69409066,
+        128.17694306
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0015_Yos Sudarso.json",
+      "portname": "Yos Sudarso",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.569548,
+        119.501546
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1667,
+      "name": "0541_Taman Nasional Pulau Komodo.json",
+      "portname": "Taman Nasional Pulau Komodo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.720384,
+        109.394682
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1663,
+      "name": "0591_Logending.json",
+      "portname": "Logending",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.4966929,
+        124.84156844
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1679,
+      "name": "0250_Manado.json",
+      "portname": "Manado",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.85237534,
+        122.89703006
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1624,
+      "name": "0246_PPN Kwandang.json",
+      "portname": "PPN Kwandang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.826585,
+        122.487367
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0501_Muara Sampara.json",
+      "portname": "Muara Sampara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.226395,
+        111.074326
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1749,
+      "name": "0346_PPP Tamperan.json",
+      "portname": "PPP Tamperan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.86799,
+        134.075913
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0284_Manokwari.json",
+      "portname": "Manokwari",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.366166,
+        122.616713
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0578_Tolandano.json",
+      "portname": "Tolandano",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.95137,
+        124.382145
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1602,
+      "name": "0586_Bobong.json",
+      "portname": "Bobong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.988322,
+        103.436404
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1772,
+      "name": "0534_Internasional Tanjung Balai Karimun.json",
+      "portname": "Internasional Tanjung Balai Karimun",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.700589,
+        111.337487
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1652,
+      "name": "0334_PPP Tasik Agung.json",
+      "portname": "PPP Tasik Agung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.66891,
+        127.474399
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1672,
+      "name": "0569_Kupal.json",
+      "portname": "Kupal",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.97210568,
+        122.57823944
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1614,
+      "name": "0011_Kendari.json",
+      "portname": "Kendari",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.677366,
+        128.189243
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1614,
+      "name": "0361_PPN Ambon.json",
+      "portname": "PPN Ambon",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.490192,
+        121.838667
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1661,
+      "name": "0185_Seba.json",
+      "portname": "Seba",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.235773,
+        123.706065
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0554_Balauring.json",
+      "portname": "Balauring",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.15537846,
+        112.66200542
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1605,
+      "name": "0151_Gresik.json",
+      "portname": "Gresik",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.724984,
+        123.045189
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1674,
+      "name": "0186_Rote.json",
+      "portname": "Rote",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.862661,
+        109.193709
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0590_Larangan Tegal.json",
+      "portname": "Larangan Tegal",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.3635357,
+        104.81446266
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1645,
+      "name": "0380_</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="12" customHeight="1">
+      <c r="A8" s="58" t="inlineStr">
+        <is>
+          <t>port-tide</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>Maritim: daftar pelabuhan (294)</t>
+        </is>
+      </c>
+      <c r="C8" s="58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E8" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan_list</t>
+        </is>
+      </c>
+      <c r="F8" s="68" t="inlineStr">
+        <is>
+          <t>Tanjung Api Api.json",
+      "portname": "Tanjung Api Api",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.49982623,
+        104.62030828
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1632,
+      "name": "0119_Kota Agung.json",
+      "portname": "Kota Agung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.09631135,
+        106.88499342
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1669,
+      "name": "0004_Tanjung Priok.json",
+      "portname": "Tanjung Priok",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.88133,
+        109.749869
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1632,
+      "name": "0496_PPP Klidang Lor.json",
+      "portname": "PPP Klidang Lor",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.434228,
+        98.89858
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1584,
+      "name": "0594_Sipinggan.json",
+      "portname": "Sipinggan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.43376903,
+        125.54899053
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1618,
+      "name": "0466_Pananaru.json",
+      "portname": "Pananaru",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.089688,
+        105.65221
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1566,
+      "name": "0121_Mesuji.json",
+      "portname": "Mesuji",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.47685963,
+        140.39037672
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1648,
+      "name": "0286_Merauke.json",
+      "portname": "Merauke",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.285497,
+        120.453565
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1635,
+      "name": "0557_Reo.json",
+      "portname": "Reo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.545231,
+        129.896066
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1616,
+      "name": "0267_Banda Neira.json",
+      "portname": "Banda Neira",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.635889,
+        123.8599
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1697,
+      "name": "0599_Kaledupa.json",
+      "portname": "Kaledupa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.68331466,
+        120.4281571
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1617,
+      "name": "0500_Bangsalae.json",
+      "portname": "Bangsalae",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.886465,
+        127.500218
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1685,
+      "name": "0433_Sidangole.json",
+      "portname": "Sidangole",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.495754,
+        108.907979
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1670,
+      "name": "0565_Sui Kunyit.json",
+      "portname": "Sui Kunyit",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.845037,
+        109.622093
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1615,
+      "name": "0589_Wonokerto.json",
+      "portname": "Wonokerto",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.283845,
+        117.595787
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1697,
+      "name": "0195_Tarakan.json",
+      "portname": "Tarakan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.508409,
+        132.083196
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0457_Sausapor.json",
+      "portname": "Sausapor",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.194908,
+        123.465465
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1645,
+      "name": "0552_Hansisi.json",
+      "portname": "Hansisi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.16858959,
+        104.00032645
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1706,
+      "name": "0014_Batu Ampar.json",
+      "portname": "Batu Ampar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.071434,
+        121.896798
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1665,
+      "name": "0574_Tanjung Pising.json",
+      "portname": "Tanjung Pising",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.91644,
+        110.049838
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1619,
+      "name": "0335_PPP Tawang.json",
+      "portname": "PPP Tawang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.002246,
+        107.746951
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1604,
+      "name": "0476_Midai.json",
+      "portname": "Midai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.533717,
+        133.45158
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0458_Babo.json",
+      "portname": "Babo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.005917,
+        124.0266
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1722,
+      "name": "0600_Binongko.json",
+      "portname": "Binongko",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.742516,
+        109.010018
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1667,
+      "name": "0592_Sentolo Kawat.json",
+      "portname": "Sentolo Kawat",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.3372936,
+        99.06226158
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1580,
+      "name": "0595_Balige.json",
+      "portname": "Balige",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.16306547,
+        114.4373703
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1628,
+      "name": "0170_ASDP Gilimanuk.json",
+      "portname": "ASDP Gilimanuk",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.6143169,
+        122.2201454
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0551_Maumere.json",
+      "portname": "Maumere",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.329298,
+        123.304496
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1606,
+      "name": "0555_Adonara.json",
+      "portname": "Adonara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.987696,
+        105.704647
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1635,
+      "name": "0471_Letung.json",
+      "portname": "Letung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.772425,
+        122.053221
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0573_Kasipute.json",
+      "portname": "Kasipute",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.307223,
+        121.735213
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1652,
+      "name": "0556_Pulau Palue.json",
+      "portname": "Pulau Palue",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.058509,
+        113.942093
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1690,
+      "name": "0154_Kalianget.json",
+      "portname": "Kalianget",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.43203,
+        127.303143
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1639,
+      "name": "0571_Indari.json",
+      "portname": "Indari",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.795806,
+        108.035645
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1650,
+      "name": "0474_Sedanau.json",
+      "portname": "Sedanau",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.849603,
+        109.128758
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1627,
+      "name": "0336_PPP Tegalsari.json",
+      "portname": "PPP Tegalsari",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.82141,
+        110.544755
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1651,
+      "name": "0333_Morodemak.json",
+      "portname": "Morodemak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.74817785,
+        115.21384763
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1717,
+      "name": "0165_Benoa, Bali.json",
+      "portname": "Benoa, Bali",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.796252,
+        122.659326
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1615,
+      "name": "0545_Pagimana.json",
+      "portname": "Pagimana",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        4.73687959,
+        107.99857339
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1693,
+      "name": "0473_Pulau Laut.json",
+      "portname": "Pulau Laut",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.183621,
+        103.932807
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0450_Krui.json",
+      "portname": "Krui",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        4.960279,
+        97.773104
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1636,
+      "name": "0492_Idi.json",
+      "portname": "Idi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.585532,
+        128.328544
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1605,
+      "name": "0270_Tulehu.json",
+      "portname": "Tulehu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.125613,
+        128.132325
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0443_Subaim.json",
+      "portname": "Subaim",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.133242,
+        104.055774
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1732,
+      "name": "0441_Ferry Batam Centre International.json",
+      "portname": "Ferry Batam Centre International",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.19980282,
+        108.9921124
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1669,
+      "name": "0309_PPN Pemangkat.json",
+      "portname": "PPN Pemangkat",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.273526,
+        116.805177
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1645,
+      "name": "0193_Semayang, Balikpapan.json",
+      "portname": "Semayang, Balikpapan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.03223,
+        106.5777
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1639,
+      "name": "0533_Cituis Rawa Saban.json",
+      "portname": "Cituis Rawa Saban",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.56445639,
+        97.82642841
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1717,
+      "name": "0028_Teluk Dalam.json",
+      "portname": "Teluk Dalam",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.8384073,
+        105.8837909
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1751,
+      "name": "0487_PPI Binuangen.json",
+      "portname": "PPI Binuangen",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.90446413,
+        115.259113
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1706,
+      "name": "0502_PP Muara Kintap.json",
+      "portname": "PP Muara Kintap",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.14333278,
+        114.40050602
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1626,
+      "name": "0164_ASDP Ketapang.json",
+      "portname": "ASDP Ketapang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.629291,
+        122.525663
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1657,
+      "name": "0580_Siompu.json",
+      "portname": "Siompu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        5.59648867,
+        95.52610159
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0016_Malahayati.json",
+      "portname": "Malahayati",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.859299,
+        109.692574
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1630,
+      "name": "0329_PPN Pekalongan.json",
+      "portname": "PPN Pekalongan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.904529,
+        105.813229
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1614,
+      "name": "0472_Kuala Maras.json",
+      "portname": "Kuala Maras",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.19420248,
+        114.83583927
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1708,
+      "name": "0168_Celukan Bawang.json",
+      "portname": "Celukan Bawang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.659294,
+        98.933163
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1578,
+      "name": "0596_Ajibata.json",
+      "portname": "Ajibata",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.602492,
+        121.61773
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1721,
+      "name": "0542_Raijua.json",
+      "portname": "Raijua",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.165333,
+        117.487031
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1608,
+      "name": "0200_Lok Tuan.json",
+      "portname": "Lok Tuan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.85295,
+        109.414665
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1622,
+      "name": "0588_Asem Doyong.json",
+      "portname": "Asem Doyong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.790323,
+        108.860189
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1666,
+      "name": "0563_Teluk Suak.json",
+      "portname": "Teluk Suak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.24324578,
+        116.77685738
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0418_Penajam.json",
+      "portname": "Penajam",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.342309,
+        122.990058
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1612,
+      "name": "0191_Larantuka.json",
+      "portname": "Larantuka",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.87794933,
+        131.24533899
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1641,
+      "name": "0291_Sorong.json",
+      "portname": "Sorong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.757183,
+        134.238152
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1595,
+      "name": "0272_Dobo.json",
+      "portname": "Dobo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.97305982,
+        122.58288042
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1626,
+      "name": "0353_PPS Kendari.json",
+      "portname": "PPS Kendari",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.485069,
+        116.674471
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1648,
+      "name": "0568_Kayangan.json",
+      "portname": "Kayangan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.22166304,
+        124.51181173
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1656,
+      "name": "0188_Kalabahi.json",
+      "portname": "Kalabahi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.710507,
+        119.856685
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1648,
+      "name": "0429_Pantoloan.json",
+      "portname": "Pantoloan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.716452,
+        114.21209
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1612,
+      "name": "0524_Jangkar.json",
+      "portname": "Jangkar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.454163,
+        140.360198
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1640,
+      "name": "0602_Depapre.json",
+      "portname": "Depapre",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.65205,
+        105.589752
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1645,
+      "name": "0489_PP Sumur.json",
+      "portname": "PP Sumur",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.73229936,
+        113.2241243
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1693,
+      "name": "0497_PP Mayangan.json",
+      "portname": "PP Mayangan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.626368,
+        127.604025
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0438_Babang.json",
+      "portname": "Babang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.21640226,
+        106.21736526
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1616,
+      "name": "0085_Tarempa.json",
+      "portname": "Tarempa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.200851,
+        116.817897
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1609,
+      "name": "0419_Karingau.json",
+      "portname": "Karingau",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.11664888,
+        106.80830956
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1641,
+      "name": "0101_Sunda Kelapa.json",
+      "portname": "Sunda Kelapa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.445471,
+        122.454548
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1608,
+      "name": "0412_Torobulu.json",
+      "portname": "Torobulu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.49493945,
+        119.87450525
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1619,
+      "name": "0182_Labuan Bajo.json",
+      "portname": "Labuan Bajo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.738616,
+        122.373896
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1679,
+      "name": "0406_Tondasi, Muna Barat.json",
+      "portname": "Tondasi, Muna Barat",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.88430863,
+        110.44014931
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1701,
+      "name": "0129_Karimun Jawa.json",
+      "portname": "Karimun Jawa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.207475,
+        127.128711
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1639,
+      "name": "0570_Busua.json",
+      "portname": "Busua",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.74519487,
+        111.72436022
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1558,
+      "name": "0142_Kumai.json",
+      "portname": "Kumai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.54456149,
+        140.71397329
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1612,
+      "name": "0278_Jayapura.json",
+      "portname": "Jayapura",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.262231,
+        121.794872
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1639,
+      "name": "0407_Sikeli.json",
+      "portname": "Sikeli",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.271081,
+        109.357903
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1579,
+      "name": "0479_Rasau Jaya.json",
+      "portname": "Rasau Jaya",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.496876,
+        109.007436
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1649,
+      "name": "0478_Serasan.json",
+      "portname": "Serasan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.735581,
+        127.384544
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1669,
+      "name": "0434_Rum.json",
+      "portname": "Rum",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.262342,
+        122.217122
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1607,
+      "name": "0548_Dolong.json",
+      "portname": "Dolong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.09908809,
+        106.91655602
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1701,
+      "name": "0104_Kalibaru.json",
+      "portname": "Kalibaru",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.09331454,
+        106.95871257
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1661,
+      "name": "0102_Marunda.json",
+      "portname": "Marunda",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.659133,
+        123.196979
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1626,
+      "name": "0444_Wa Ode Buri.json",
+      "portname": "Wa Ode Buri",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.833,
+        117.506048
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1733,
+      "name": "0483_Pelabuhan di DKI Jakartaa.json",
+      "portname": "Pelabuhan di DKI Jakartaa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.48678446,
+        105.25295724
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0326_PPP Lempasing.json",
+      "portname": "PPP Lempasing",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.219626,
+        123.519203
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0398_Bolok.json",
+      "portname": "Bolok",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.0470224,
+        105.9231226
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1666,
+      "name": "0481_Pelabuhan ANyer.json",
+      "portname": "Pelabuhan ANyer",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -10.19545133,
+        123.52778435
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1715,
+      "name": "0008_Tenau.json",
+      "portname": "Tenau",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.807368,
+        103.479706
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1694,
+      "name": "0538_Roro Kuala Tungkal.json",
+      "portname": "Roro Kuala Tungkal",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.931989,
+        132.309951
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1611,
+      "name": "0292_Fak-fak.json",
+      "portname": "Fak-fak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.391221,
+        123.162871
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1616,
+      "name": "0402_Waiwerang.json",
+      "portname": "Waiwerang",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.624076,
+        122.709582
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1636,
+      "name": "0413_Tampo.json",
+      "portname": "Tampo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.993126,
+        103.394044
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1677,
+      "name": "0536_Khusus Bea Cukai.json",
+      "portname": "Khusus Bea Cukai",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.590774,
+        110.647769
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1651,
+      "name": "0128_Jepara.json",
+      "portname": "Jepara",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.837115,
+        120.515563
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1699,
+      "name": "0405_Pamamata.json",
+      "portname": "Pamamata",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.606929,
+        120.463409
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1711,
+      "name": "0404_Tanjung Bira.json",
+      "portname": "Tanjung Bira",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.93952487,
+        110.42057889
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1662,
+      "name": "0006_Tanjung Mas.json",
+      "portname": "Tanjung Mas",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.302438,
+        122.344018
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1634,
+      "name": "0547_Pasokan.json",
+      "portname": "Pasokan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.38685396,
+        114.57486712
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1672,
+      "name": "0350_PPN Pengambengan.json",
+      "portname": "PPN Pengambengan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.828108,
+        129.84614
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1637,
+      "name": "0459_Misool.json",
+      "portname": "Misool",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.23078,
+        135.583111
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1649,
+      "name": "0281_Nabire.json",
+      "portname": "Nabire",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.243992,
+        107.90422
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1610,
+      "name": "0504_Patimban.json",
+      "portname": "Patimban",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.02945523,
+        99.59292093
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1712,
+      "name": "0379_Tua Pejat.json",
+      "portname": "Tua Pejat",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.02868,
+        106.16404
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1626,
+      "name": "0115_PP Karangantu.json",
+      "portname": "PP Karangantu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.720323,
+        96.80962
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1634,
+      "name": "0494_Susoh Blang Pidie.json",
+      "portname": "Susoh Blang Pidie",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.030085,
+        100.399527
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1738,
+      "name": "0377_Teluk Bungus.json",
+      "portname": "Teluk Bungus",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.883831,
+        128.29712
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1593,
+      "name": "0582_Buli.json",
+      "portname": "Buli",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.727733,
+        134.505521
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0285_Wasior.json",
+      "portname": "Wasior",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.897189,
+        122.83118
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1707,
+      "name": "0575_Pure.json",
+      "portname": "Pure",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.633466,
+        132.74224
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1600,
+      "name": "0271_Tual.json",
+      "portname": "Tual",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.18718719,
+        136.07521794
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1641,
+      "name": "0013_Biak.json",
+      "portname": "Biak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.93923591,
+        126.6945076
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1613,
+      "name": "0252_Lirung.json",
+      "portname": "Lirung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.0028824,
+        119.6213947
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1717,
+      "name": "1002_Nusantara Pare Pare.json",
+      "portname": "Nusantara Pare Pare",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.475617,
+        127.419959
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1659,
+      "name": "0446_Pulau Moti.json",
+      "portname": "Pulau Moti",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.80648,
+        116.250342
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1581,
+      "name": "0430_Pondong.json",
+      "portname": "Pondong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.335101,
+        128.341853
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1687,
+      "name": "0276_Waipirit.json",
+      "portname": "Waipirit",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.76631645,
+        127.37747312
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1688,
+      "name": "0431_Bastiong.json",
+      "portname": "Bastiong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.486327,
+        122.109028
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0549_Marisa.json",
+      "portname": "Marisa",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.05663,
+        121.590237
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1644,
+      "name": "0409_Kolaka.json",
+      "portname": "Kolaka",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.476201,
+        119.446938
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1668,
+      "name": "0498_Tanjung Silopo.json",
+      "portname": "Tanjung Silopo",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.996277,
+        124.86189
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1607,
+      "name": "0187_Atapupu.json",
+      "portname": "Atapupu",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.72370295,
+        128.01508784
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0437_Tobelo.json",
+      "portname": "Tobelo",
+      "type": "utama"
+    },
+    {
+      "co</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="12" customHeight="1">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>port-tide</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Maritim: daftar pelabuhan (294)</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan_list</t>
+        </is>
+      </c>
+      <c r="F9" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">or": [
+        2.999271,
+        99.81489
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1646,
+      "name": "0047_Tanjung Balai Asahan.json",
+      "portname": "Tanjung Balai Asahan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.338528,
+        123.534933
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1638,
+      "name": "0423_Wanci.json",
+      "portname": "Wanci",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.8919444,
+        108.39166667
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1648,
+      "name": "0469_Penagi.json",
+      "portname": "Penagi",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.8541274,
+        121.6618024
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1673,
+      "name": "0550_Ende, Flores.json",
+      "portname": "Ende, Flores",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.47948304,
+        105.65361857
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1690,
+      "name": "0528_Marina Tanjung Lesung.json",
+      "portname": "Marina Tanjung Lesung",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.792076,
+        98.713921
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1659,
+      "name": "0001_Belawan.json",
+      "portname": "Belawan",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.541114,
+        112.964655
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1557,
+      "name": "0470_Sampit.json",
+      "portname": "Sampit",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        3.601774,
+        125.50099
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1603,
+      "name": "0251_Tahuna.json",
+      "portname": "Tahuna",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.71432,
+        108.500161
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1658,
+      "name": "0601_Pangandaran.json",
+      "portname": "Pangandaran",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.9214811,
+        105.995156
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1622,
+      "name": "0485_Indah Kiat.json",
+      "portname": "Indah Kiat",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.677746,
+        109.274602
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1681,
+      "name": "0529_Padang Tikar.json",
+      "portname": "Padang Tikar",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.431965,
+        116.008538
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1608,
+      "name": "0532_Batulicin.json",
+      "portname": "Batulicin",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.779036,
+        127.388334
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1717,
+      "name": "0257_Ahmad Yani, Ternate.json",
+      "portname": "Ahmad Yani, Ternate",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.23256,
+        105.831963
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0488_PP Pasauran.json",
+      "portname": "PP Pasauran",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.004734,
+        103.353545
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1667,
+      "name": "0535_Parit Rampak.json",
+      "portname": "Parit Rampak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        2.732797,
+        125.415955
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1606,
+      "name": "0562_Ulu Siau.json",
+      "portname": "Ulu Siau",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -4.00335803,
+        119.62197304
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1689,
+      "name": "0207_Pare-pare.json",
+      "portname": "Pare-pare",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -1.246666,
+        100.43175
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1722,
+      "name": "0495_PPP Carocok.json",
+      "portname": "PPP Carocok",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -6.10004959,
+        106.80178433
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1647,
+      "name": "0106_PPS Muara Baru.json",
+      "portname": "PPS Muara Baru",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -2.08458195,
+        105.13225079
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1667,
+      "name": "0382_Tanjung Kelian.json",
+      "portname": "Tanjung Kelian",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.608187,
+        120.463669
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1687,
+      "name": "0530_Bira.json",
+      "portname": "Bira",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -5.85141424,
+        112.6431676
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1726,
+      "name": "0391_Sangkapura.json",
+      "portname": "Sangkapura",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.877424,
+        131.251758
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1673,
+      "name": "0456_Dermaga Usaha Mina.json",
+      "portname": "Dermaga Usaha Mina",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.953008,
+        122.796361
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1672,
+      "name": "0417_Luwuk.json",
+      "portname": "Luwuk",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        0.331076,
+        127.439021
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1694,
+      "name": "0449_Pulau Makian.json",
+      "portname": "Pulau Makian",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -0.88944867,
+        131.26801931
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1654,
+      "name": "0455_Pelayaran Rakyat Sorong.json",
+      "portname": "Pelayaran Rakyat Sorong",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -7.18647042,
+        112.72228342
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1628,
+      "name": "0007_Tanjung Perak.json",
+      "portname": "Tanjung Perak",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -3.320286,
+        114.561909
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1593,
+      "name": "0339_PP Banjarmasin.json",
+      "portname": "PP Banjarmasin",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.434639,
+        123.060462
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1602,
+      "name": "0558_Solor.json",
+      "portname": "Solor",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.36253,
+        124.096535
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1664,
+      "name": "0183_Baranusa, Alor.json",
+      "portname": "Baranusa, Alor",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        1.319809,
+        126.363889
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1656,
+      "name": "0439_Batang Dua.json",
+      "portname": "Batang Dua",
+      "type": "utama"
+    },
+    {
+      "coor": [
+        -8.448176,
+        118.714063
+      ],
+      "file_date": "2026-09-21 23:47 UTC",
+      "kb": 1612,
+      "name": "0173_Bima, NTB.json",
+      "portname": "Bima, NTB",
+      "type": "utama"
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="12" customHeight="1">
+      <c r="A10" s="58" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>Present Weather: cuaca saat ini</t>
+        </is>
+      </c>
+      <c r="C10" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/presentwx/coord?lat=-6.2&amp;lon=106.816666</t>
+        </is>
+      </c>
+      <c r="F10" s="68" t="inlineStr">
+        <is>
+          <t>{"status":200,"data":{"lokasi":{"lon":106.81596823959143,"lat":-6.197052719903746,"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","distance":0},"cuaca":{"weather":4,"weather_desc":"Berawan Tebal","weather_desc_en":"Overcast","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan tebal-am.svg","datetime":"2026-09-22T08:20:00.000Z","local_datetime":"2026-09-22 15:20:00","t":29,"tcc":89,"wd_deg":275,"wd":"W","wd_to":"E","ws":6.5,"hu":67,"vs":null,"vs_text":null}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="12" customHeight="1">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>current-weather</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>API v1: waktu matahari terbit/terbenam</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/v1/sunset/json?lat=-6.2&amp;lng=106.816666</t>
+        </is>
+      </c>
+      <c r="F11" s="68" t="inlineStr">
+        <is>
+          <t>{"results":{"date":"2026-09-22","sunrise":"5:42:05 AM","sunset":"5:49:07 PM","first_light":"4:33:02 AM","last_light":"6:58:12 PM","dawn":"5:21:18 AM","dusk":"6:09:54 PM","solar_noon":"11:45:33 AM","golden_hour":"5:21:38 PM","day_length":"12:07:02","nautical_twilight_begin":"4:57:10 AM","nautical_twilight_end":"6:34:03 PM","timezone":"Asia/Jakarta","utc_offset":420,"sun_altitude":83.49,"sun_azimuth":0,"sunrise_azimuth":89.69,"sunset_azimuth":270.12,"moonrise":"2:19:27 PM","moonset":"2:15:11 AM","moon_illumination":81.03,"moon_phase":"Waxing Gibbous","moon_phase_value":0.36,"moon_always_up":false,"moon_always_down":false,"elevation":8,"sun_status":"normal","golden_hour_morning":{"begin":"5:29:21 AM","end":"6:09:34 AM"},"golden_hour_evening":{"begin":"5:21:38 PM","end":"6:01:52 PM"},"blue_hour_morning":{"begin":"5:21:18 AM","end":"5:29:21 AM"},"blue_hour_evening":{"begin":"6:01:52 PM","end":"6:09:54 PM"}},"status":"OK","tzid":"Asia/Jakarta"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>port-tide</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>Maritim: detail pelabuhan + pasut</t>
+        </is>
+      </c>
+      <c r="C12" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/pelabuhan/0101_Sunda%20Kelapa.json</t>
+        </is>
+      </c>
+      <c r="F12" s="68" t="inlineStr">
+        <is>
+          <t>{"port_id": "0101", "name": "Sunda Kelapa", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "latitude": -6.11664888, "longitude": 106.80830956, "type": "utama", "data": [{"issued": "2026-09-21 23:47 UTC", "valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "weather": "Berawan", "weather_desc": "Untuk area Sunda Kelapa diperkirakan berawan, dengan kecepatan angin pada umumnya 2 - 14 knot bertiup dari arah timur", "warning_desc": "NIL", "wind_from": "Timur", "wind_to": "Utara", "wind_speed_min": 2, "wind_speed_max": 14, "current_from": "Timur Laut", "current_to": "Tenggara", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "current_speed_min": 0.01, "current_speed_max": 0.07, "visibility": 8611, "rh_min": 74, "rh_max": 93, "temp_min": 26, "temp_max": 29, "low_tide": null, "low_tide_time": null, "high_tide": null, "high_tide_time": null}, {"issued": "2026-09-21 23:47 UTC", "valid_from": "2026-09-22 00:00 UTC", "valid_to": "2026-09-22 12:00 UTC", "weather": "Hujan Ringan", "weather_desc": "Untuk area Sunda Kelapa diperkirakan hujan ringan, dengan kecepatan angin pada umumnya 2 - 14 knot bertiup dari arah utara", "warning_desc": "NIL", "wind_from": "Utara", "wind_to": "Timur", "wind_speed_min": 2, "wind_speed_max": 14, "current_from": "Timur Laut", "current_to": "Tenggara", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "current_speed_min": 0.01, "current_speed_max": 0.07, "visibility": 8527, "rh_min": 60, "rh_max": 85, "temp_min": 28, "temp_max": 34, "low_tide": null, "low_tide_time": null, "high_tide": null, "high_tide_time": null}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="12" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Public API: video berita</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/video-latest?hashtag=infobmkgpws</t>
+        </is>
+      </c>
+      <c r="F13" s="68" t="inlineStr">
+        <is>
+          <t>[{"title":"Prakiraan Cuaca Esok Hari, Selasa, 22 September 2026.","videoUrl":"https://www.youtube.com/watch?v=l6NWtkthnzU"},{"title":"Prakiraan Cuaca Esok Hari,  Senin, 21 September 2026.","videoUrl":"https://www.youtube.com/watch?v=GNIhEbJS8q4"},{"title":"Prakiraan Cuaca Esok Hari, Minggu, 20 September 2026","videoUrl":"https://www.youtube.com/watch?v=kCepZRm8uIQ"},{"title":"Prakiraan Cuaca Esok Hari, Sabtu, 19 September 2026.","videoUrl":"https://www.youtube.com/watch?v=9egb1zLG0PM"},{"title":"Prakiraan Cuaca Esok Hari, Jumat, 18 September 2026.","videoUrl":"https://www.youtube.com/watch?v=1Dy6sPbtzpc"},{"title":"Prakiraan Cuaca Esok Hari Kamis, 17 September 2026","videoUrl":"https://www.youtube.com/watch?v=Xx3Ddki3bHk"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="12" customHeight="1">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="B14" s="58" t="inlineStr">
+        <is>
+          <t>DF Forecast: prakiraan 10 hari + per jam</t>
+        </is>
+      </c>
+      <c r="C14" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.2804&amp;lon=106.9507</t>
+        </is>
+      </c>
+      <c r="F14" s="68" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.94655786745837,"lat":-6.277639992667722,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"32","adm2":"32.75","adm3":"32.75.09","adm4":"32.75.09.1003","provinsi":"Jawa Barat","kotkab":"Kota Bekasi","kecamatan":"Jatiasih","desa":"Jatikramat","lon":106.9465578675,"lat":-6.2776399927,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":80,"tp":0.3,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":290,"wd":"W","wd_to":"E","ws":14,"hu":73,"vs":null,"vs_text":null,"time_index":"8-9","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 09:00:00","local_datetime":"2026-09-22 16:00:00"},{"datetime":"2026-09-22T10:00:00Z","t":27,"tcc":82,"tp":0.3,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":326,"wd":"NW","wd_to":"SE","ws":3.7,"hu":78,"vs":null,"vs_text":null,"time_index":"9-10","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 10:00:00","local_datetime":"2026-09-22 17:00:00"},{"datetime":"2026-09-22T11:00:00Z","t":28,"tcc":84,"tp":0.3,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":326,"wd":"NW","wd_to":"SE","ws":3.7,"hu":78,"vs":null,"vs_text":null,"time_index":"10-11","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 11:00:00","local_datetime":"2026-09-22 18:00:00"},{"datetime":"2026-09-22T12:00:00Z","t":28,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":326,"wd":"NW","wd_to":"SE","ws":3.7,"hu":79,"vs":null,"vs_text":null,"time_index":"11-12","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 12:00:00","local_datetime":"2026-09-22 19:00:00"},{"datetime":"2026-09-22T13:00:00Z","t":27,"tcc":69,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":124,"wd":"E","wd_to":"W","ws":3.3,"hu":80,"vs":null,"vs_text":null,"time_index":"12-13","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 13:00:00","local_datetime":"2026-09-22 20:00:00"},{"datetime":"2026-09-22T14:00:00Z","t":27,"tcc":31,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":124,"wd":"E","wd_to":"W","ws":3.3,"hu":82,"vs":null,"vs_text":null,"time_index":"13-14","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 14:00:00","local_datetime":"2026-09-22 21:00:00"},{"datetime":"2026-09-22T15:00:00Z","t":27,"tcc":19,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":124,"wd":"E","wd_to":"W","ws":3.3,"hu":84,"vs":null,"vs_text":null,"time_index":"14-15","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 15:00:00","local_datetime":"2026-09-22 22:00:00"},{"datetime":"2026-09-22T16:00:00Z","t":26,"tcc":46,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":169,"wd":"SE","wd_to":"NW","ws":2.5,"hu":87,"vs":null,"vs_text":null,"time_index":"15-16","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 16:00:00","local_datetime":"2026-09-22 23:00:00"}],[{"datetime":"2026-09-22T17:00:00Z","t":26,"tcc":92,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":169,"wd":"SE","wd_to":"NW","ws":2.5,"hu":89,"vs":null,"vs_text":null,"time_index":"16-17","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 17:00:00","local_datetime":"2026-09-23 00:00:00"},{"datetime":"2026-09-22T18:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":169,"wd":"SE","wd_to":"NW","ws":2.5,"hu":91,"vs":null,"vs_text":null,"time_index":"17-18","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 18:00:00","local_datetime":"2026-09-23 01:00:00"},{"datetime":"2026-09-22T19:00:00Z","t":25,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":163,"wd":"SE","wd_to":"NW","ws":2.9,"hu":92,"vs":null,"vs_text":null,"time_index":"18-19","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 19:00:00","local_datetime":"2026-09-23 02:00:00"},{"datetime":"2026-09-22T20:00:00Z","t":25,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":163,"wd":"SE","wd_to":"NW","ws":2.9,"hu":92,"vs":null,"vs_text":null,"time_index":"19-20","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 20:00:00","local_datetime":"2026-09-23 03:00:00"},{"datetime":"2026-09-22T21:00:00Z","t":25,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":163,"wd":"SE","wd_to":"NW","ws":2.9,"hu":92,"vs":null,"vs_text":null,"time_index":"20-21","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 21:00:00","local_datetime":"2026-09-23 04:00:00"},{"datetime":"2026-09-22T22:00:00Z","t":25,"tcc":100,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":142,"wd":"SE","wd_to":"NW","ws":1.6,"hu":92,"vs":null,"vs_text":null,"time_index":"21-22","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 22:00:00","local_datetime":"2026-09-23 05:00:00"},{"datetime":"2026-09-22T23:00:00Z","t":26,"tcc":98,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":142,"wd":"SE","wd_to":"NW","ws":1.6,"hu":83,"vs":null,"vs_text":null,"time_index":"22-23","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 23:00:00","local_datetime":"2026-09-23 06:00:00"},{"datetime":"2026-09-23T00:00:00Z","t":28,"tcc":97,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":142,"wd":"SE","wd_to":"NW","ws":1.6,"hu":70,"vs":null,"vs_text":null,"time_index":"23-24","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-23 00:00:00","local_datetime":"2026-09-23 07:00:00"},{"datetime":"2026-09-23T03:00:00Z","t":33,"tcc":53,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":107,"wd":"E","wd_to":"W","ws":3.6,"hu":50,"vs":null,"vs_text":null,"time_index":"26-27","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 03:00:00","local_datetime":"2026-09-23 10:00:00"},{"datetime":"2026-09-23T06:00:00Z","t":33,"tcc":51,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":353,"wd":"NW","wd_to":"SE","ws":5.3,"hu":52,"vs":null,"vs_text":null,"time_index":"29-30","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 06:00:00","local_datetime":"2026-09-23 13:00:00"},{"datetime":"2026-09-23T09:00:00Z","t":30,"tcc":27,"tp":0.3,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":344,"wd":"NW","wd_to":"SE","ws":9.1,"hu":65,"vs":null,"vs_text":null,"time_index":"32-33","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 09:00:00","local_datetime":"2026-09-23 16:00:00"},{"datetime":"2026-09-23T12:00:00Z","t":28,"tcc":27,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":18,"wd":"N","wd_to":"S","ws":4.3,"hu":75,"vs":null,"vs_text":null,"time_index":"35-36","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 12:00:00","local_datetime":"2026-09-23 19:00:00"},{"datetime":"2026-09-23T15:00:00Z","t":27,"tcc":33,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":104,"wd":"E","wd_to":"W","ws":3.7,"hu":82,"vs":null,"vs_text":null,"time_index":"38-39","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 15:00:00","local_datetime":"2026-09-23 22:00:00"}],[{"datetime":"2026-09-23T18:00:00Z","t":26,"tcc":49,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":136,"wd":"SE","wd_to":"NW","ws":3.7,"hu":89,"vs":null,"vs_text":null,"time_index":"41-42","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 18:00:00","local_datetime":"2026-09-24 01:00:00"},{"datetime":"2026-09-23T21:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":121,"wd":"E","wd_to":"W","ws":4.8,"hu":88,"vs":null,"vs_text":null,"time_index":"44-45","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-23 21:00:00","local_datetime":"2026-09-24 04:00:00"},{"datetime":"2026-09-24T00:00:00Z","t":28,"tcc":44,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":123,"wd":"E","wd_to":"W","ws":4.6,"hu":72,"vs":null,"vs_text":null,"time_index":"47-48","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 00:00:00","local_datetime":"2026-09-24 07:00:00"},{"datetime":"2026-09-24T03:00:00Z","t":32,"tcc":25,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":111,"wd":"E","wd_to":"W","ws":6.6,"hu":52,"vs":null,"vs_text":null,"time_index":"50-51","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 03:00:00","local_datetime":"2026-09-24 10:00:00"},{"datetime":"2026-09-24T06:00:00Z","t":35,"tcc":97,"tp":0.5,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":111,"wd":"E","wd_to":"W","ws":6.6,"hu":43,"vs":null,"vs_text":null,"time_index":"53-54","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 06:00:00","local_datetime":"2026-09-24 13:00:00"},{"datetime":"2026-09-24T09:00:00Z","t":30,"tcc":97,"tp":0.5,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":252,"wd":"SW","wd_to":"NE","ws":2.1,"hu":61,"vs":null,"vs_text":null,"time_index":"56-57","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 09:00:00","local_datetime":"2026-09-24 16:00:00"},{"datetime":"2026-09-24T12:00:00Z","t":28,"tcc":76,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":252,"wd":"SW","wd_to":"NE","ws":2.1,"hu":78,"vs":null,"vs_text":null,"time_index":"59-60","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-24 12:00:00","local_datetime":"2026-09-24 19:00:00"},{"datetime":"2026-09-24T15:00:00Z","t":27,"tcc":30,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":213,"wd":"S","wd_to":"N","ws":0.8,"hu":84,"vs":null,"vs_text":null,"time_index":"62-63","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 15:00:00","local_datetime":"2026-09-24 22:00:00"}],[{"datetime":"2026-09-24T18:00:00Z","t":26,"tcc":6,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":213,"wd":"S","wd_to":"N","ws":0.8,"hu":92,"vs":null,"vs_text":null,"time_index":"65-66","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 18:00:00","local_datetime":"2026-09-25 01:00:00"},{"datetime":"2026-09-24T21:00:00Z","t":25,"tcc":8,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":176,"wd":"SE","wd_to":"NW","ws":3.6,"hu":90,"vs":null,"vs_text":null,"time_index":"68-69","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 21:00:00","local_datetime":"2026-09-25 04:00:00"},{"datetime":"2026-09-25T00:00:00Z","t":28,"tcc":57,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":176,"wd":"SE","wd_to":"NW","ws":3.6,"hu":72,"vs":null,"vs_text":null,"time_index":"71-72","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-25 00:00:00","local_datetime":"2026-09-25 07:00:00"},{"datetime":"2026-09-25T03:00:00Z","t":33,"tcc":94,"tp":0.1,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":348,"wd":"NW","wd_to":"SE","ws":8.8,"hu":53,"vs":null,"vs_text":null,"time_index":"74-75","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-25 03:00:00","local_datetime":"2026-09-25 10:00:00"},{"datetime":"2026-09-25T06:00:00Z","t":32,"tcc":98,"tp":0.9,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":348,"wd":"NW","wd_to":"SE","ws":8.8,"hu":58,"vs":null,"vs_text":null,"time_index":"77-78","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-25 06:00:00","local_datetime":"2026-09-25 13:00:00"},{"datetime":"2026-09-25T09:00:00Z","t":30,"tcc":77,"tp":0.9,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":164,"wd":"SE","wd_to":"NW","ws":3.2,"hu":59,"vs":null,"vs_text":null,"time_index":"80-81","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-25 09:00:00","local_datetime":"2026-09-25 16:00:00"},{"datetime":"2026-09-25T12:00:00Z","t":26,"tcc":10,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":164,"wd":"SE","wd_to":"NW","ws":3.2,"hu":88,"vs":null,"vs_text":null,"time_index":"83-84","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 12:00:00","local_datetime":"2026-09-25 19:00:00"},{"datetime":"2026-09-25T15:00:00Z","t":26,"tcc":8,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":172,"wd":"SE","wd_to":"NW","ws":1.9,"hu":88,"vs":null,"vs_text":null,"time_index":"86-87","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 15:00:00","local_datetime":"2026-09-25 22:00:00"}],[{"datetime":"2026-09-25T18:00:00Z","t":26,"tcc":2,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":172,"wd":"SE","wd_to":"NW","ws":1.9,"hu":89,"vs":null,"vs_text":null,"time_index":"89-90","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 18:00:00","local_datetime":"2026-09-26 01:00:00"},{"datetime":"2026-09-25T21:00:00Z","t":25,"tcc":9,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":186,"wd":"S","wd_to":"N","ws":3.8,"hu":92,"vs":null,"vs_text":null,"time_index":"92-93","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 21:00:00","local_datetime":"2026-09-26 04:00:00"},{"datetime":"2026-09-26T00:00:00Z","t":26,"tcc":24,"tp":0.3,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":186,"wd":"S","wd_to":"N","ws":3.8,"hu":83,"vs":null,"vs_text":null,"time_index":"95-96","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-26 00:00:00","local_datetime":"2026-09-26 07:00:00"},{"datetime":"2026-09-26T06:00:00Z","t":32,"tcc":100,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":168,"wd":"SE","wd_to":"NW","ws":0.6,"hu":56,"vs":null,"vs_text":null,"time_index":"101-102","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-26 06:00:00","local_datetime":"2026-09-26 13:00:00"},{"datetime":"2026-09-26T12:00:00Z","t":27,"tcc":88,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":168,"wd":"SE","wd_to":"NW","ws":0.6,"hu":83,"vs":null,"vs_text":null,"time_index":"107-108","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-26 12:00:00","local_datetime":"2026-09-26 19:00:00"}],[{"datetime":"2026-09-26T18:00:00Z","t":25,"tcc":7,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":4.1,"hu":90,"vs":null,"vs_text":null,"time_index":"113-114","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-26 18:00:00","local_datetime":"2026-09-27 01:00:00"},{"datetime":"2026-09-27T00:00:00Z","t":26,"tcc":3,"tp":0.2,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":4.1,"hu":80,"vs":null,"vs_text":null,"time_index":"119-120","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 00:00:00","local_datetime":"2026-09-27 07:00:00"},{"datetime":"2026-09-27T06:00:00Z","t":33,"tcc":33,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":67,"wd":"NE","wd_to":"SW","ws":7.2,"hu":51,"vs":null,"vs_text":null,"time_index":"125-126","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 06:00:00","local_datetime":"2026-09-27 13:00:00"},{"datetime":"2026-09-27T12:00:00Z","t":28,"tcc":76,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":67,"wd":"NE","wd_to":"SW","ws":7.2,"hu":66,"vs":null,"vs_text":null,"time_index":"131-132","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-27 12:00:00","local_datetime":"2026-09-27 19:00:00"}],[{"datetime":"2026-09-27T18:00:00Z","t":26,"tcc":0,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":161,"wd":"SE","wd_to":"NW","ws":3.7,"hu":83,"vs":null,"vs_text":null,"time_index":"137-138","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-27 18:00:00","local_datetime":"2026-09-28 01:00:00"},{"datetime":"2026-09-28T00:00:00Z","t":26,"tcc":8,"tp":0.3,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":161,"wd":"SE","wd_to":"NW","ws":3.7,"hu":80,"vs":null,"vs_text":null,"time_index":"143-144","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-28 00:00:00","local_datetime":"2026-09-28 07:00:00"},{"datetime":"2026-09-28T06:00:00Z","t":34,"tcc":72,"tp":0.3,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":47,"vs":null,"vs_text":null,"time_index":"149-150","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-28 06:00:00","local_datetime":"2026-09-28 13:00:00"},{"datetime":"2026-09-28T12:00:00Z","t":29,"tcc":2,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":68,"vs":null,"vs_text":null,"time_index":"155-156","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 12:00:00","local_datetime":"2026-09-28 19:00:00"}],[{"datetime":"2026-09-28T18:00:00Z","t":26,"tcc":2,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":160,"wd":"SE","wd_to":"NW","ws":3.4,"hu":84,"vs":null,"vs_text":null,"time_index":"161-162","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 18:00:00","local_datetime":"2026-09-29 01:00:00"},{"datetime":"2026-09-29T00:00:00Z","t":26,"tcc":64,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":160,"wd":"SE","wd_to":"NW","ws":3.4,"hu":79,"vs":null,"vs_text":null,"time_index":"167-168","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 00:00:00","local_datetime":"2026-09-29 07:00:00"},{"datetime":"2026-09-29T06:00:00Z","t":35,"tcc":61,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":68,"wd":"NE","wd_to":"SW","ws":7.9,"hu":45,"vs":null,"vs_text":null,"time_index":"173-174","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 06:00:00","local_datetime":"2026-09-29 13:00:00"},{"datetime":"2026-09-29T12:00:00Z","t":28,"tcc":100,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":68,"wd":"NE","wd_to":"SW","ws":7.9,"hu":64,"vs":null,"vs_text":null,"time_index":"179-180","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-29 12:00:00","local_datetime":"2026-09-29 19:00:00"}],[{"datetime":"2026-09-29T18:00:00Z","t":26,"tcc":88,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":199,"wd":"S","wd_to":"N","ws":4.5,"hu":83,"vs":null,"vs_text":null,"time_index":"185-186","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-29 18:00:00","local_datetime":"2026-09-30 01:00:00"},{"datetime":"2026-09-30T00:00:00Z","t":26,"tcc":13,"tp":0.4,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":199,"wd":"S","wd_to":"N","ws":4.5,"hu":78,"vs":null,"vs_text":null,"time_index":"191-192","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-30 00:00:00","local_datetime":"2026-09-30 07:00:00"},{"datetime":"2026-09-30T06:00:00Z","t":35,"tcc":94,"tp":0.4,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":67,"wd":"NE","wd_to":"SW","ws":5.8,"hu":42,"vs":null,"vs_text":null,"time_index":"197-198","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-30 06:00:00","local_datetime":"2026-09-30 13:00:00"},{"datetime":"2026-09-30T12:00:00Z","t":29,"tcc":91,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":67,"wd":"NE","wd_to":"SW","ws":5.8,"hu":65,"vs":null,"vs_text":null,"time_index":"203-204","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-30 12:00:00","local_datetime":"2026-09-30 19:00:00"}],[{"datetime":"2026-09-30T18:00:00Z","t":25,"tcc":89,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":183,"wd":"S","wd_to":"N","ws":3.6,"hu":86,"vs":null,"vs_text":null,"time_index":"209-210","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-30 18:00:00","local_datetime":"2026-10-01 01:00:00"},{"datetime":"2026-10-01T00:00:00Z","t":26,"tcc":99,"tp":0.4,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":183,"wd":"S","wd_to":"N","ws":3.6,"hu":83,"vs":null,"vs_text":null,"time_index":"215-216","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-10-01 00:00:00","local_datetime":"2026-10-01 07:00:00"}]]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="12" customHeight="1">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>DF Forecast: prakiraan 10 hari + per jam</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.2271&amp;lon=106.7994</t>
+        </is>
+      </c>
+      <c r="F15" s="68" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Gelora","lon":106.80150533961634,"lat":-6.216258882675461,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Gelora","lon":106.8015053396,"lat":-6.2162588827,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":27,"tcc":94,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":275,"wd":"W","wd_to":"E","ws":6.5,"hu":83,"vs":null,"vs_text":null,"time_index":"8-9","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 09:00:00","local_datetime":"2026-09-22 16:00:00"},{"datetime":"2026-09-22T10:00:00Z","t":27,"tcc":98,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":85,"vs":null,"vs_text":null,"time_index":"9-10","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 10:00:00","local_datetime":"2026-09-22 17:00:00"},{"datetime":"2026-09-22T11:00:00Z","t":27,"tcc":72,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":84,"vs":null,"vs_text":null,"time_index":"10-11","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 11:00:00","local_datetime":"2026-09-22 18:00:00"},{"datetime":"2026-09-22T12:00:00Z","t":27,"tcc":42,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":83,"vs":null,"vs_text":null,"time_index":"11-12","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 12:00:00","local_datetime":"2026-09-22 19:00:00"},{"datetime":"2026-09-22T13:00:00Z","t":28,"tcc":71,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":82,"vs":null,"vs_text":null,"time_index":"12-13","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 13:00:00","local_datetime":"2026-09-22 20:00:00"},{"datetime":"2026-09-22T14:00:00Z","t":28,"tcc":21,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":82,"vs":null,"vs_text":null,"time_index":"13-14","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 14:00:00","local_datetime":"2026-09-22 21:00:00"},{"datetime":"2026-09-22T15:00:00Z","t":27,"tcc":31,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":83,"vs":null,"vs_text":null,"time_index":"14-15","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 15:00:00","local_datetime":"2026-09-22 22:00:00"},{"datetime":"2026-09-22T16:00:00Z","t":27,"tcc":52,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":86,"vs":null,"vs_text":null,"time_index":"15-16","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 16:00:00","local_datetime":"2026-09-22 23:00:00"}],[{"datetime":"2026-09-22T17:00:00Z","t":26,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":87,"vs":null,"vs_text":null,"time_index":"16-17","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 17:00:00","local_datetime":"2026-09-23 00:00:00"},{"datetime":"2026-09-22T18:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":88,"vs":null,"vs_text":null,"time_index":"17-18","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 18:00:00","local_datetime":"2026-09-23 01:00:00"},{"datetime":"2026-09-22T19:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":90,"vs":null,"vs_text":null,"time_index":"18-19","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 19:00:00","local_datetime":"2026-09-23 02:00:00"},{"datetime":"2026-09-22T20:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":91,"vs":null,"vs_text":null,"time_index":"19-20","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 20:00:00","local_datetime":"2026-09-23 03:00:00"},{"datetime":"2026-09-22T21:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":91,"vs":null,"vs_text":null,"time_index":"20-21","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 21:00:00","local_datetime":"2026-09-23 04:00:00"},{"datetime":"2026-09-22T22:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":91,"vs":null,"vs_text":null,"time_index":"21-22","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 22:00:00","local_datetime":"2026-09-23 05:00:00"},{"datetime":"2026-09-22T23:00:00Z","t":26,"tcc":98,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":84,"vs":null,"vs_text":null,"time_index":"22-23","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 23:00:00","local_datetime":"2026-09-23 06:00:00"},{"datetime":"2026-09-23T00:00:00Z","t":28,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":75,"vs":null,"vs_text":null,"time_index":"23-24","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-23 00:00:00","local_datetime":"2026-09-23 07:00:00"},{"datetime":"2026-09-23T03:00:00Z","t":32,"tcc":42,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":85,"wd":"NE","wd_to":"SW","ws":1.4,"hu":56,"vs":null,"vs_text":null,"time_index":"26-27","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 03:00:00","local_datetime":"2026-09-23 10:00:00"},{"datetime":"2026-09-23T06:00:00Z","t":32,"tcc":46,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":3,"wd":"N","wd_to":"S","ws":7.4,"hu":57,"vs":null,"vs_text":null,"time_index":"29-30","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 06:00:00","local_datetime":"2026-09-23 13:00:00"},{"datetime":"2026-09-23T09:00:00Z","t":30,"tcc":51,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":5,"wd":"N","wd_to":"S","ws":11.1,"hu":68,"vs":null,"vs_text":null,"time_index":"32-33","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 09:00:00","local_datetime":"2026-09-23 16:00:00"},{"datetime":"2026-09-23T12:00:00Z","t":28,"tcc":65,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":16,"wd":"N","wd_to":"S","ws":5,"hu":76,"vs":null,"vs_text":null,"time_index":"35-36","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-23 12:00:00","local_datetime":"2026-09-23 19:00:00"},{"datetime":"2026-09-23T15:00:00Z","t":28,"tcc":20,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":56,"wd":"NE","wd_to":"SW","ws":4.7,"hu":78,"vs":null,"vs_text":null,"time_index":"38-39","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 15:00:00","local_datetime":"2026-09-23 22:00:00"}],[{"datetime":"2026-09-23T18:00:00Z","t":26,"tcc":32,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":118,"wd":"E","wd_to":"W","ws":3.3,"hu":85,"vs":null,"vs_text":null,"time_index":"41-42","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 18:00:00","local_datetime":"2026-09-24 01:00:00"},{"datetime":"2026-09-23T21:00:00Z","t":26,"tcc":85,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":142,"wd":"SE","wd_to":"NW","ws":3.2,"hu":88,"vs":null,"vs_text":null,"time_index":"44-45","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-23 21:00:00","local_datetime":"2026-09-24 04:00:00"},{"datetime":"2026-09-24T00:00:00Z","t":28,"tcc":20,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":109,"wd":"E","wd_to":"W","ws":4.6,"hu":73,"vs":null,"vs_text":null,"time_index":"47-48","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 00:00:00","local_datetime":"2026-09-24 07:00:00"},{"datetime":"2026-09-24T03:00:00Z","t":33,"tcc":31,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":1,"wd":"N","wd_to":"S","ws":8.8,"hu":52,"vs":null,"vs_text":null,"time_index":"50-51","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 03:00:00","local_datetime":"2026-09-24 10:00:00"},{"datetime":"2026-09-24T06:00:00Z","t":32,"tcc":100,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":1,"wd":"N","wd_to":"S","ws":8.8,"hu":58,"vs":null,"vs_text":null,"time_index":"53-54","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 06:00:00","local_datetime":"2026-09-24 13:00:00"},{"datetime":"2026-09-24T09:00:00Z","t":30,"tcc":100,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":192,"wd":"S","wd_to":"N","ws":5.9,"hu":65,"vs":null,"vs_text":null,"time_index":"56-57","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 09:00:00","local_datetime":"2026-09-24 16:00:00"},{"datetime":"2026-09-24T12:00:00Z","t":27,"tcc":87,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":192,"wd":"S","wd_to":"N","ws":5.9,"hu":81,"vs":null,"vs_text":null,"time_index":"59-60","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-24 12:00:00","local_datetime":"2026-09-24 19:00:00"},{"datetime":"2026-09-24T15:00:00Z","t":27,"tcc":13,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":257,"wd":"SW","wd_to":"NE","ws":1.1,"hu":84,"vs":null,"vs_text":null,"time_index":"62-63","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 15:00:00","local_datetime":"2026-09-24 22:00:00"}],[{"datetime":"2026-09-24T18:00:00Z","t":26,"tcc":18,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":257,"wd":"SW","wd_to":"NE","ws":1.1,"hu":90,"vs":null,"vs_text":null,"time_index":"65-66","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 18:00:00","local_datetime":"2026-09-25 01:00:00"},{"datetime":"2026-09-24T21:00:00Z","t":25,"tcc":10,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":224,"wd":"S","wd_to":"N","ws":1.7,"hu":91,"vs":null,"vs_text":null,"time_index":"68-69","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 21:00:00","local_datetime":"2026-09-25 04:00:00"},{"datetime":"2026-09-25T00:00:00Z","t":28,"tcc":59,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":224,"wd":"S","wd_to":"N","ws":1.7,"hu":74,"vs":null,"vs_text":null,"time_index":"71-72","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-25 00:00:00","local_datetime":"2026-09-25 07:00:00"},{"datetime":"2026-09-25T03:00:00Z","t":33,"tcc":67,"tp":0.2,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":20,"wd":"N","wd_to":"S","ws":11.7,"hu":55,"vs":null,"vs_text":null,"time_index":"74-75","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-25 03:00:00","local_datetime":"2026-09-25 10:00:00"},{"datetime":"2026-09-25T06:00:00Z","t":30,"tcc":94,"tp":0.4,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":20,"wd":"N","wd_to":"S","ws":11.7,"hu":65,"vs":null,"vs_text":null,"time_index":"77-78","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-25 06:00:00","local_datetime":"2026-09-25 13:00:00"},{"datetime":"2026-09-25T09:00:00Z","t":30,"tcc":97,"tp":0.4,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":203,"wd":"S","wd_to":"N","ws":1.6,"hu":65,"vs":null,"vs_text":null,"time_index":"80-81","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-25 09:00:00","local_datetime":"2026-09-25 16:00:00"},{"datetime":"2026-09-25T12:00:00Z","t":26,"tcc":3,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":203,"wd":"S","wd_to":"N","ws":1.6,"hu":86,"vs":null,"vs_text":null,"time_index":"83-84","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 12:00:00","local_datetime":"2026-09-25 19:00:00"},{"datetime":"2026-09-25T15:00:00Z","t":26,"tcc":11,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":167,"wd":"SE","wd_to":"NW","ws":2,"hu":89,"vs":null,"vs_text":null,"time_index":"86-87","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 15:00:00","local_datetime":"2026-09-25 22:00:00"}],[{"datetime":"2026-09-25T18:00:00Z","t":26,"tcc":4,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":167,"wd":"SE","wd_to":"NW","ws":2,"hu":91,"vs":null,"vs_text":null,"time_index":"89-90","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 18:00:00","local_datetime":"2026-09-26 01:00:00"},{"datetime":"2026-09-25T21:00:00Z","t":25,"tcc":12,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":3.5,"hu":89,"vs":null,"vs_text":null,"time_index":"92-93","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 21:00:00","local_datetime":"2026-09-26 04:00:00"},{"datetime":"2026-09-26T00:00:00Z","t":26,"tcc":13,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":3.5,"hu":84,"vs":null,"vs_text":null,"time_index":"95-96","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-26 00:00:00","local_datetime":"2026-09-26 07:00:00"},{"datetime":"2026-09-26T06:00:00Z","t":31,"tcc":100,"tp":0.2,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":178,"wd":"SE","wd_to":"NW","ws":0.5,"hu":61,"vs":null,"vs_text":null,"time_index":"101-102","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-26 06:00:00","local_datetime":"2026-09-26 13:00:00"},{"datetime":"2026-09-26T12:00:00Z","t":28,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":178,"wd":"SE","wd_to":"NW","ws":0.5,"hu":77,"vs":null,"vs_text":null,"time_index":"107-108","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-26 12:00:00","local_datetime":"2026-09-26 19:00:00"}],[{"datetime":"2026-09-26T18:00:00Z","t":26,"tcc":8,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":147,"wd":"SE","wd_to":"NW","ws":4,"hu":89,"vs":null,"vs_text":null,"time_index":"113-114","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-26 18:00:00","local_datetime":"2026-09-27 01:00:00"},{"datetime":"2026-09-27T00:00:00Z","t":26,"tcc":7,"tp":0.1,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":147,"wd":"SE","wd_to":"NW","ws":4,"hu":80,"vs":null,"vs_text":null,"time_index":"119-120","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 00:00:00","local_datetime":"2026-09-27 07:00:00"},{"datetime":"2026-09-27T06:00:00Z","t":32,"tcc":31,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":56,"vs":null,"vs_text":null,"time_index":"125-126","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 06:00:00","local_datetime":"2026-09-27 13:00:00"},{"datetime":"2026-09-27T12:00:00Z","t":30,"tcc":88,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":63,"vs":null,"vs_text":null,"time_index":"131-132","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-27 12:00:00","local_datetime":"2026-09-27 19:00:00"}],[{"datetime":"2026-09-27T18:00:00Z","t":26,"tcc":0,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":139,"wd":"SE","wd_to":"NW","ws":4,"hu":79,"vs":null,"vs_text":null,"time_index":"137-138","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-27 18:00:00","local_datetime":"2026-09-28 01:00:00"},{"datetime":"2026-09-28T00:00:00Z","t":26,"tcc":6,"tp":0.3,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":139,"wd":"SE","wd_to":"NW","ws":4,"hu":80,"vs":null,"vs_text":null,"time_index":"143-144","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-28 00:00:00","local_datetime":"2026-09-28 07:00:00"},{"datetime":"2026-09-28T06:00:00Z","t":33,"tcc":66,"tp":0.3,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":105,"wd":"E","wd_to":"W","ws":2.5,"hu":55,"vs":null,"vs_text":null,"time_index":"149-150","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-28 06:00:00","local_datetime":"2026-09-28 13:00:00"},{"datetime":"2026-09-28T12:00:00Z","t":29,"tcc":8,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":105,"wd":"E","wd_to":"W","ws":2.5,"hu":70,"vs":null,"vs_text":null,"time_index":"155-156","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 12:00:00","local_datetime":"2026-09-28 19:00:00"}],[{"datetime":"2026-09-28T18:00:00Z","t":26,"tcc":2,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":138,"wd":"SE","wd_to":"NW","ws":2.7,"hu":84,"vs":null,"vs_text":null,"time_index":"161-162","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 18:00:00","local_datetime":"2026-09-29 01:00:00"},{"datetime":"2026-09-29T00:00:00Z","t":27,"tcc":71,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":138,"wd":"SE","wd_to":"NW","ws":2.7,"hu":79,"vs":null,"vs_text":null,"time_index":"167-168","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 00:00:00","local_datetime":"2026-09-29 07:00:00"},{"datetime":"2026-09-29T06:00:00Z","t":34,"tcc":70,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":65,"wd":"NE","wd_to":"SW","ws":9.6,"hu":49,"vs":null,"vs_text":null,"time_index":"173-174","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 06:00:00","local_datetime":"2026-09-29 13:00:00"},{"datetime":"2026-09-29T12:00:00Z","t":29,"tcc":100,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":65,"wd":"NE","wd_to":"SW","ws":9.6,"hu":59,"vs":null,"vs_text":null,"time_index":"179-180","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-29 12:00:00","local_datetime":"2026-09-29 19:00:00"}],[{"datetime":"2026-09-29T18:00:00Z","t":26,"tcc":94,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":190,"wd":"S","wd_to":"N","ws":3.2,"hu":81,"vs":null,"vs_text":null,"time_index":"185-186","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-29 18:00:00","local_datetime":"2026-09-30 01:00:00"},{"datetime":"2026-09-30T00:00:00Z","t":26,"tcc":21,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":190,"wd":"S","wd_to":"N","ws":3.2,"hu":79,"vs":null,"vs_text":null,"time_index":"191-192","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-30 00:00:00","local_datetime":"2026-09-30 07:00:00"},{"datetime":"2026-09-30T06:00:00Z","t":33,"tcc":98,"tp":0.2,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":90,"wd":"E","wd_to":"W","ws":7,"hu":52,"vs":null,"vs_text":null,"time_index":"197-198","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-30 06:00:00","local_datetime":"2026-09-30 13:00:00"},{"datetime":"2026-09-30T12:00:00Z","t":30,"tcc":89,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":90,"wd":"E","wd_to":"W","ws":7,"hu":61,"vs":null,"vs_text":null,"time_index":"203-204","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-30 12:00:00","local_datetime":"2026-09-30 19:00:00"}],[{"datetime":"2026-09-30T18:00:00Z","t":26,"tcc":94,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":152,"wd":"SE","wd_to":"NW","ws":0.9,"hu":81,"vs":null,"vs_text":null,"time_index":"209-210","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-30 18:00:00","local_datetime":"2026-10-01 01:00:00"},{"datetime":"2026-10-01T00:00:00Z","t":26,"tcc":99,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":152,"wd":"SE","wd_to":"NW","ws":0.9,"hu":80,"vs":null,"vs_text":null,"time_index":"215-216","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-10-01 00:00:00","local_datetime":"2026-10-01 07:00:00"}]]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>DF Forecast: prakiraan 10 hari + per jam</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/forecast/coord?lat=-6.1754&amp;lon=106.8272</t>
+        </is>
+      </c>
+      <c r="F16" s="68" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.82670735619568,"lat":-6.176384269281675,"distance":0,"timezone":"Asia/Jakarta"},"data":[{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.01","adm4":"31.71.01.1001","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Gambir","desa":"Gambir","lon":106.8267073562,"lat":-6.1763842693,"timezone":"+0700","type":"adm4"},"cuaca":[[{"datetime":"2026-09-22T09:00:00Z","t":28,"tcc":90,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":275,"wd":"W","wd_to":"E","ws":6.5,"hu":77,"vs":null,"vs_text":null,"time_index":"8-9","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-22 09:00:00","local_datetime":"2026-09-22 16:00:00"},{"datetime":"2026-09-22T10:00:00Z","t":28,"tcc":96,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":80,"vs":null,"vs_text":null,"time_index":"9-10","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 10:00:00","local_datetime":"2026-09-22 17:00:00"},{"datetime":"2026-09-22T11:00:00Z","t":28,"tcc":87,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":79,"vs":null,"vs_text":null,"time_index":"10-11","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 11:00:00","local_datetime":"2026-09-22 18:00:00"},{"datetime":"2026-09-22T12:00:00Z","t":28,"tcc":59,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":35,"wd":"N","wd_to":"S","ws":3.8,"hu":77,"vs":null,"vs_text":null,"time_index":"11-12","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 12:00:00","local_datetime":"2026-09-22 19:00:00"},{"datetime":"2026-09-22T13:00:00Z","t":28,"tcc":72,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":77,"vs":null,"vs_text":null,"time_index":"12-13","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-22 13:00:00","local_datetime":"2026-09-22 20:00:00"},{"datetime":"2026-09-22T14:00:00Z","t":28,"tcc":24,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":77,"vs":null,"vs_text":null,"time_index":"13-14","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 14:00:00","local_datetime":"2026-09-22 21:00:00"},{"datetime":"2026-09-22T15:00:00Z","t":28,"tcc":29,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":90,"wd":"NE","wd_to":"SW","ws":1.9,"hu":79,"vs":null,"vs_text":null,"time_index":"14-15","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 15:00:00","local_datetime":"2026-09-22 22:00:00"},{"datetime":"2026-09-22T16:00:00Z","t":27,"tcc":58,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":81,"vs":null,"vs_text":null,"time_index":"15-16","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-22 16:00:00","local_datetime":"2026-09-22 23:00:00"}],[{"datetime":"2026-09-22T17:00:00Z","t":27,"tcc":94,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":83,"vs":null,"vs_text":null,"time_index":"16-17","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 17:00:00","local_datetime":"2026-09-23 00:00:00"},{"datetime":"2026-09-22T18:00:00Z","t":26,"tcc":99,"tp":0.1,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":154,"wd":"SE","wd_to":"NW","ws":1.1,"hu":85,"vs":null,"vs_text":null,"time_index":"17-18","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 18:00:00","local_datetime":"2026-09-23 01:00:00"},{"datetime":"2026-09-22T19:00:00Z","t":26,"tcc":99,"tp":0.1,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":86,"vs":null,"vs_text":null,"time_index":"18-19","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 19:00:00","local_datetime":"2026-09-23 02:00:00"},{"datetime":"2026-09-22T20:00:00Z","t":26,"tcc":98,"tp":0.1,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":87,"vs":null,"vs_text":null,"time_index":"19-20","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 20:00:00","local_datetime":"2026-09-23 03:00:00"},{"datetime":"2026-09-22T21:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":167,"wd":"SE","wd_to":"NW","ws":1.5,"hu":88,"vs":null,"vs_text":null,"time_index":"20-21","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 21:00:00","local_datetime":"2026-09-23 04:00:00"},{"datetime":"2026-09-22T22:00:00Z","t":26,"tcc":99,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":89,"vs":null,"vs_text":null,"time_index":"21-22","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-22 22:00:00","local_datetime":"2026-09-23 05:00:00"},{"datetime":"2026-09-22T23:00:00Z","t":27,"tcc":98,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":82,"vs":null,"vs_text":null,"time_index":"22-23","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-22 23:00:00","local_datetime":"2026-09-23 06:00:00"},{"datetime":"2026-09-23T00:00:00Z","t":28,"tcc":95,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":161,"wd":"SE","wd_to":"NW","ws":2.6,"hu":72,"vs":null,"vs_text":null,"time_index":"23-24","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-23 00:00:00","local_datetime":"2026-09-23 07:00:00"},{"datetime":"2026-09-23T03:00:00Z","t":32,"tcc":47,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":85,"wd":"NE","wd_to":"SW","ws":1.4,"hu":57,"vs":null,"vs_text":null,"time_index":"26-27","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 03:00:00","local_datetime":"2026-09-23 10:00:00"},{"datetime":"2026-09-23T06:00:00Z","t":31,"tcc":41,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":3,"wd":"N","wd_to":"S","ws":7.4,"hu":61,"vs":null,"vs_text":null,"time_index":"29-30","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 06:00:00","local_datetime":"2026-09-23 13:00:00"},{"datetime":"2026-09-23T09:00:00Z","t":30,"tcc":43,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":5,"wd":"N","wd_to":"S","ws":11.1,"hu":68,"vs":null,"vs_text":null,"time_index":"32-33","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-23 09:00:00","local_datetime":"2026-09-23 16:00:00"},{"datetime":"2026-09-23T12:00:00Z","t":29,"tcc":57,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":16,"wd":"N","wd_to":"S","ws":5,"hu":73,"vs":null,"vs_text":null,"time_index":"35-36","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 12:00:00","local_datetime":"2026-09-23 19:00:00"},{"datetime":"2026-09-23T15:00:00Z","t":28,"tcc":24,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":56,"wd":"NE","wd_to":"SW","ws":4.7,"hu":76,"vs":null,"vs_text":null,"time_index":"38-39","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 15:00:00","local_datetime":"2026-09-23 22:00:00"}],[{"datetime":"2026-09-23T18:00:00Z","t":27,"tcc":42,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":118,"wd":"E","wd_to":"W","ws":3.3,"hu":81,"vs":null,"vs_text":null,"time_index":"41-42","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-23 18:00:00","local_datetime":"2026-09-24 01:00:00"},{"datetime":"2026-09-23T21:00:00Z","t":26,"tcc":86,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":142,"wd":"SE","wd_to":"NW","ws":3.2,"hu":86,"vs":null,"vs_text":null,"time_index":"44-45","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-23 21:00:00","local_datetime":"2026-09-24 04:00:00"},{"datetime":"2026-09-24T00:00:00Z","t":28,"tcc":19,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":109,"wd":"E","wd_to":"W","ws":4.6,"hu":72,"vs":null,"vs_text":null,"time_index":"47-48","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 00:00:00","local_datetime":"2026-09-24 07:00:00"},{"datetime":"2026-09-24T03:00:00Z","t":33,"tcc":40,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":1,"wd":"N","wd_to":"S","ws":8.8,"hu":52,"vs":null,"vs_text":null,"time_index":"50-51","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-24 03:00:00","local_datetime":"2026-09-24 10:00:00"},{"datetime":"2026-09-24T06:00:00Z","t":32,"tcc":99,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":1,"wd":"N","wd_to":"S","ws":8.8,"hu":61,"vs":null,"vs_text":null,"time_index":"53-54","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 06:00:00","local_datetime":"2026-09-24 13:00:00"},{"datetime":"2026-09-24T09:00:00Z","t":30,"tcc":99,"tp":0.3,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":192,"wd":"S","wd_to":"N","ws":5.9,"hu":63,"vs":null,"vs_text":null,"time_index":"56-57","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-24 09:00:00","local_datetime":"2026-09-24 16:00:00"},{"datetime":"2026-09-24T12:00:00Z","t":28,"tcc":90,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":192,"wd":"S","wd_to":"N","ws":5.9,"hu":76,"vs":null,"vs_text":null,"time_index":"59-60","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-24 12:00:00","local_datetime":"2026-09-24 19:00:00"},{"datetime":"2026-09-24T15:00:00Z","t":27,"tcc":16,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":257,"wd":"SW","wd_to":"NE","ws":1.1,"hu":80,"vs":null,"vs_text":null,"time_index":"62-63","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 15:00:00","local_datetime":"2026-09-24 22:00:00"}],[{"datetime":"2026-09-24T18:00:00Z","t":26,"tcc":16,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":257,"wd":"SW","wd_to":"NE","ws":1.1,"hu":86,"vs":null,"vs_text":null,"time_index":"65-66","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 18:00:00","local_datetime":"2026-09-25 01:00:00"},{"datetime":"2026-09-24T21:00:00Z","t":26,"tcc":14,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":224,"wd":"S","wd_to":"N","ws":1.7,"hu":88,"vs":null,"vs_text":null,"time_index":"68-69","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-24 21:00:00","local_datetime":"2026-09-25 04:00:00"},{"datetime":"2026-09-25T00:00:00Z","t":28,"tcc":62,"tp":0.2,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":224,"wd":"S","wd_to":"N","ws":1.7,"hu":73,"vs":null,"vs_text":null,"time_index":"71-72","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-25 00:00:00","local_datetime":"2026-09-25 07:00:00"},{"datetime":"2026-09-25T03:00:00Z","t":32,"tcc":72,"tp":0.2,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":20,"wd":"N","wd_to":"S","ws":11.7,"hu":55,"vs":null,"vs_text":null,"time_index":"74-75","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-25 03:00:00","local_datetime":"2026-09-25 10:00:00"},{"datetime":"2026-09-25T06:00:00Z","t":29,"tcc":90,"tp":0.2,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":20,"wd":"N","wd_to":"S","ws":11.7,"hu":71,"vs":null,"vs_text":null,"time_index":"77-78","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-25 06:00:00","local_datetime":"2026-09-25 13:00:00"},{"datetime":"2026-09-25T09:00:00Z","t":31,"tcc":92,"tp":0.2,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":203,"wd":"S","wd_to":"N","ws":1.6,"hu":60,"vs":null,"vs_text":null,"time_index":"80-81","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-25 09:00:00","local_datetime":"2026-09-25 16:00:00"},{"datetime":"2026-09-25T12:00:00Z","t":27,"tcc":8,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":203,"wd":"S","wd_to":"N","ws":1.6,"hu":80,"vs":null,"vs_text":null,"time_index":"83-84","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 12:00:00","local_datetime":"2026-09-25 19:00:00"},{"datetime":"2026-09-25T15:00:00Z","t":27,"tcc":10,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":167,"wd":"SE","wd_to":"NW","ws":2,"hu":83,"vs":null,"vs_text":null,"time_index":"86-87","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 15:00:00","local_datetime":"2026-09-25 22:00:00"}],[{"datetime":"2026-09-25T18:00:00Z","t":26,"tcc":3,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":167,"wd":"SE","wd_to":"NW","ws":2,"hu":86,"vs":null,"vs_text":null,"time_index":"89-90","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 18:00:00","local_datetime":"2026-09-26 01:00:00"},{"datetime":"2026-09-25T21:00:00Z","t":26,"tcc":14,"tp":0,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":3.5,"hu":87,"vs":null,"vs_text":null,"time_index":"92-93","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-25 21:00:00","local_datetime":"2026-09-26 04:00:00"},{"datetime":"2026-09-26T00:00:00Z","t":26,"tcc":17,"tp":0.2,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":165,"wd":"SE","wd_to":"NW","ws":3.5,"hu":82,"vs":null,"vs_text":null,"time_index":"95-96","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-26 00:00:00","local_datetime":"2026-09-26 07:00:00"},{"datetime":"2026-09-26T06:00:00Z","t":30,"tcc":100,"tp":0.2,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":178,"wd":"SE","wd_to":"NW","ws":0.5,"hu":66,"vs":null,"vs_text":null,"time_index":"101-102","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-26 06:00:00","local_datetime":"2026-09-26 13:00:00"},{"datetime":"2026-09-26T12:00:00Z","t":29,"tcc":91,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":178,"wd":"SE","wd_to":"NW","ws":0.5,"hu":73,"vs":null,"vs_text":null,"time_index":"107-108","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-26 12:00:00","local_datetime":"2026-09-26 19:00:00"}],[{"datetime":"2026-09-26T18:00:00Z","t":26,"tcc":4,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":147,"wd":"SE","wd_to":"NW","ws":4,"hu":84,"vs":null,"vs_text":null,"time_index":"113-114","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-26 18:00:00","local_datetime":"2026-09-27 01:00:00"},{"datetime":"2026-09-27T00:00:00Z","t":26,"tcc":12,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":147,"wd":"SE","wd_to":"NW","ws":4,"hu":77,"vs":null,"vs_text":null,"time_index":"119-120","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 00:00:00","local_datetime":"2026-09-27 07:00:00"},{"datetime":"2026-09-27T06:00:00Z","t":32,"tcc":31,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":59,"vs":null,"vs_text":null,"time_index":"125-126","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-27 06:00:00","local_datetime":"2026-09-27 13:00:00"},{"datetime":"2026-09-27T12:00:00Z","t":29,"tcc":83,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":62,"wd":"NE","wd_to":"SW","ws":6.9,"hu":62,"vs":null,"vs_text":null,"time_index":"131-132","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-27 12:00:00","local_datetime":"2026-09-27 19:00:00"}],[{"datetime":"2026-09-27T18:00:00Z","t":27,"tcc":0,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":139,"wd":"SE","wd_to":"NW","ws":4,"hu":78,"vs":null,"vs_text":null,"time_index":"137-138","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-27 18:00:00","local_datetime":"2026-09-28 01:00:00"},{"datetime":"2026-09-28T00:00:00Z","t":27,"tcc":7,"tp":0.2,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":139,"wd":"SE","wd_to":"NW","ws":4,"hu":79,"vs":null,"vs_text":null,"time_index":"143-144","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-28 00:00:00","local_datetime":"2026-09-28 07:00:00"},{"datetime":"2026-09-28T06:00:00Z","t":32,"tcc":65,"tp":0.2,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":105,"wd":"E","wd_to":"W","ws":2.5,"hu":60,"vs":null,"vs_text":null,"time_index":"149-150","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-28 06:00:00","local_datetime":"2026-09-28 13:00:00"},{"datetime":"2026-09-28T12:00:00Z","t":30,"tcc":5,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":105,"wd":"E","wd_to":"W","ws":2.5,"hu":66,"vs":null,"vs_text":null,"time_index":"155-156","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 12:00:00","local_datetime":"2026-09-28 19:00:00"}],[{"datetime":"2026-09-28T18:00:00Z","t":27,"tcc":4,"tp":0,"weather":0,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":138,"wd":"SE","wd_to":"NW","ws":2.7,"hu":81,"vs":null,"vs_text":null,"time_index":"161-162","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-pm.svg","utc_datetime":"2026-09-28 18:00:00","local_datetime":"2026-09-29 01:00:00"},{"datetime":"2026-09-29T00:00:00Z","t":27,"tcc":74,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":138,"wd":"SE","wd_to":"NW","ws":2.7,"hu":78,"vs":null,"vs_text":null,"time_index":"167-168","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 00:00:00","local_datetime":"2026-09-29 07:00:00"},{"datetime":"2026-09-29T06:00:00Z","t":34,"tcc":63,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":65,"wd":"NE","wd_to":"SW","ws":9.6,"hu":52,"vs":null,"vs_text":null,"time_index":"173-174","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-am.svg","utc_datetime":"2026-09-29 06:00:00","local_datetime":"2026-09-29 13:00:00"},{"datetime":"2026-09-29T12:00:00Z","t":29,"tcc":100,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":65,"wd":"NE","wd_to":"SW","ws":9.6,"hu":63,"vs":null,"vs_text":null,"time_index":"179-180","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-29 12:00:00","local_datetime":"2026-09-29 19:00:00"}],[{"datetime":"2026-09-29T18:00:00Z","t":27,"tcc":93,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":190,"wd":"S","wd_to":"N","ws":3.2,"hu":79,"vs":null,"vs_text":null,"time_index":"185-186","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-29 18:00:00","local_datetime":"2026-09-30 01:00:00"},{"datetime":"2026-09-30T00:00:00Z","t":26,"tcc":22,"tp":0.1,"weather":1,"weather_desc":"Cerah","weather_desc_en":"Sunny","wd_deg":190,"wd":"S","wd_to":"N","ws":3.2,"hu":78,"vs":null,"vs_text":null,"time_index":"191-192","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah-am.svg","utc_datetime":"2026-09-30 00:00:00","local_datetime":"2026-09-30 07:00:00"},{"datetime":"2026-09-30T06:00:00Z","t":32,"tcc":97,"tp":0.1,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":90,"wd":"E","wd_to":"W","ws":7,"hu":61,"vs":null,"vs_text":null,"time_index":"197-198","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-09-30 06:00:00","local_datetime":"2026-09-30 13:00:00"},{"datetime":"2026-09-30T12:00:00Z","t":30,"tcc":89,"tp":0,"weather":2,"weather_desc":"Cerah Berawan","weather_desc_en":"Partly Cloudy","wd_deg":90,"wd":"E","wd_to":"W","ws":7,"hu":59,"vs":null,"vs_text":null,"time_index":"203-204","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/cerah berawan-pm.svg","utc_datetime":"2026-09-30 12:00:00","local_datetime":"2026-09-30 19:00:00"}],[{"datetime":"2026-09-30T18:00:00Z","t":27,"tcc":94,"tp":0,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":152,"wd":"SE","wd_to":"NW","ws":0.9,"hu":79,"vs":null,"vs_text":null,"time_index":"209-210","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-pm.svg","utc_datetime":"2026-09-30 18:00:00","local_datetime":"2026-10-01 01:00:00"},{"datetime":"2026-10-01T00:00:00Z","t":26,"tcc":99,"tp":0.2,"weather":3,"weather_desc":"Berawan","weather_desc_en":"Mostly Cloudy","wd_deg":152,"wd":"SE","wd_to":"NW","ws":0.9,"hu":80,"vs":null,"vs_text":null,"time_index":"215-216","analysis_date":"2026-09-22T00:00:00","image":"https://api-apps.bmkg.go.id/storage/icon/cuaca/berawan-am.svg","utc_datetime":"2026-10-01 00:00:00","local_datetime":"2026-10-01 07:00:00"}]]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="12" customHeight="1">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>Berita WordPress BMKG (WP REST)</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="58" t="n">
+        <v>502</v>
+      </c>
+      <c r="E17" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/posts?per_page=4&amp;_embed=1</t>
+        </is>
+      </c>
+      <c r="F17" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"type":"https://developers.cloudflare.com/support/troubleshooting/http-status-codes/cloudflare-5xx-errors/error-502/","title":"Error 502: Bad gateway","status":502,"detail":"The origin web server returned an invalid or incomplete response to Cloudflare. This typically indicates the origin is overloaded or misconfigured.","instance":"a3eff3f3e8e6fd32","error_code":502,"error_name":"origin_bad_gateway","error_category":"origin","ray_id":"a3eff3f3e8e6fd32","timestamp":"2026-09-22T08:31:22Z","zone":"cuaca.bmkg.go.id","cloudflare_error":true,"retryable":true,"retry_after":60,"owner_action_required":true,"what_you_should_do":"**Wait and retry.** Back off for at least 60 seconds. If the error persists, the website operator should check their origin server health and configuration.","footer":"This error was generated by Cloudflare on behalf of the website owner."}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>Berita WordPress BMKG (WP REST)</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="58" t="n">
+        <v>502</v>
+      </c>
+      <c r="E18" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/blog/wp-json/wp/v2/posts?per_page=4&amp;_embed=1</t>
+        </is>
+      </c>
+      <c r="F18" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"type":"https://developers.cloudflare.com/support/troubleshooting/http-status-codes/cloudflare-5xx-errors/error-502/","title":"Error 502: Bad gateway","status":502,"detail":"The origin web server returned an invalid or incomplete response to Cloudflare. This typically indicates the origin is overloaded or misconfigured.","instance":"a3eff3f4cb3cfd32","error_code":502,"error_name":"origin_bad_gateway","error_category":"origin","ray_id":"a3eff3f4cb3cfd32","timestamp":"2026-09-22T08:31:22Z","zone":"cuaca.bmkg.go.id","cloudflare_error":true,"retryable":true,"retry_after":60,"owner_action_required":true,"what_you_should_do":"**Wait and retry.** Back off for at least 60 seconds. If the error persists, the website operator should check their origin server health and configuration.","footer":"This error was generated by Cloudflare on behalf of the website owner."}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>alerts</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>Peringatan Dini Nowcast (RSS resmi)</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E19" s="58" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/alerts/nowcast/id</t>
+        </is>
+      </c>
+      <c r="F19" s="68" t="inlineStr">
+        <is>
+          <t>&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+    &lt;?xml-stylesheet type="text/xsl" href="/cap/nowcast-rss-style.xsl"?&gt;
+    &lt;rss version="2.0" xmlns:atom="http://www.w3.org/2005/Atom"&gt;
+        &lt;channel&gt;
+            &lt;title&gt;Peringatan Dini Cuaca BMKG&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/rss.xml&lt;/link&gt;
+            &lt;description&gt;Peringatan Dini Cuaca dari BMKG (Badan Meteorologi, Klimatologi, dan Geofisika)&lt;/description&gt;
+            &lt;atom:link href="https://www.bmkg.go.id/alerts/nowcast/id/rss.xml" rel="self" type="application/rss+xml"/&gt;
+            &lt;language&gt;id&lt;/language&gt;
+            &lt;copyright&gt;public domain&lt;/copyright&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 08:15:34 +0000&lt;/pubDate&gt;
+            &lt;lastBuildDate&gt;Tue, 22 Sep 2026 08:15:34 +0000&lt;/lastBuildDate&gt;
+            &lt;docs&gt;http://blogs.law.harvard.edu/tech/rss&lt;/docs&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Kalimantan Barat&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CKB20260922001_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 15:15 WIB di sebagian wilayah Kalimantan Barat, khususnya di HULU SUNGAI, KUBU, TUJUH BELAS.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 17:15 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.61.001&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 15:05:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Kep. Riau&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CKR20260922006_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 15:15 WIB di sebagian wilayah Kep. Riau, khususnya di BUNGURAN TIMUR LAUT, BUNGURAN UTARA, GALANG, KEPULAUAN POSEK, SENAYANG.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 17:15 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.21.006&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 15:05:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Nusa Tenggara Timur&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CNT20260922001_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 16:30 WITA di sebagian wilayah Nusa Tenggara Timur, khususnya di BORONG, LANGKE REMBONG, LELAK, RANA MESE, RUTENG, SATAR MESE, SATAR MESE BARAT, SATAR MESE BARAT, WAE RII.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 19:30 WITA.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.53.001&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 16:00:00 +0800&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Lampung&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CLG20260922007_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 14:40 WIB di sebagian wilayah Lampung, khususnya di ABUNG SEMULI, ANAK RATU AJI, ANAK TUHA, BANGUN REJO, BATANGHARI, BLAMBANGAN PAGAR, CANDIPURO, GEDONG TATAAN, JATI AGUNG, KALIANDA, KEMILING, KETAPANG, KOTABUMI, MARGA TIGA, NATAR, NEGERI KATON, PALAS, PENENGAHAN, SEKAMPUNG, SEKAMPUNG UDIK, SEPUTIH AGUNG, TANJUNG BINTANG, TANJUNG SARI, TEGINENENG, TELUK PANDAN, TERBANGGI BESAR, TERUSAN NUNYAI, WAWAY KARYA, WAY PANGUBUAN, WAY PANJI, WAY SULAN.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 16:00 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.18.007&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 14:30:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Sulawesi Tengah&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CSG20260922003_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 15:42 WITA di sebagian wilayah Sulawesi Tengah, khususnya di BANAWA SELATAN, LABUAN, SINDUE TOMBUSABORA, TILOAN.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 18:00 WITA.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.72.003&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 15:30:00 +0800&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Kep. Bangka Belitung&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CBB20260922004_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 14:15 WIB di sebagian wilayah Kep. Bangka Belitung, khususnya di MENDO BARAT, SUNGAI SELAN.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 16:00 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.19.004&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 14:00:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Jakarta&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CJK20260922001_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 14:00 WIB di sebagian wilayah Jakarta, khususnya di CIBINONG, JAMBE, KEPULAUAN SERIBU UTARA, PARUNG PANJANG, SERPONG.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 16:00 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.31.001&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 13:50:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Bengkulu&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CBK20260922003_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 13:40 WIB di sebagian wilayah Bengkulu, khususnya di AIR BESI, AIR DIKIT, AIR NAPAL, AIR NIPIS, AIR PADANG, AIR PERIUKAN, AIR RAMI, AMEN, ARMA JAYA, BANG HAJI, BATIK NAU, BERMANI ILIR, BINGIN KUNING, GIRI MULYA, HULU PALIK, ILIR TALO, IPUH, KARANG TINGGI, KAUR SELATAN, KAUR UTARA, KEDURANG, KELAM TENGAH, KERKAP, KETAHUN, KINAL, KOTA ARGA MAKMUR, KOTA MUKOMUKO, LAIS, LEBONG ATAS, LEBONG SAKTI, LEBONG SELATAN, LEBONG TENGAH, LEBONG UTARA, LUAS, LUBUK SANDI, MALIN DEMAN, MARGA SAKTI SEBELAT, MERIGI KELINDANG, MERIGI SAKTI, MUARA KEMUMU, MUARA SAHUNG, NAPAL PUTIH, NASAL, PADANG GUCI HULU, PADANG JAYA, PAGAR JATI, PELABAI, PEMATANG TIGA, PENARIK, PINANG BELAPIS, PINANG RAYA, PINO, PINO RAYA, PONDOK KELAPA, PONDOK KUBANG, PONDOK SUGUH, PUTRI HIJAU, SEBERANG MUSI, SEGINIM, SELAGAN RAYA, SELUMA SELATAN, SELUMA TIMUR, SELUMA UTARA, SEMIDANG ALAS, SEMIDANG ALAS MARAS, SINDANG BELITI ILIR, SINDANG BELITI ULU, SUKARAJA, SUNGAI RUMBAI, TABA PENANJUNG, TALO, TALO KECIL, TANJUNG AGUNG PALIK, TERAMANG JAYA, TETAP, TOPOS, UJAN MAS, ULOK KUPAI, ULU MANNA, ULU TALO, URAM JAYA.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 17:00 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.17.003&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 13:37:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Sumatera Utara&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CSU20260922003_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 13:45 WIB di sebagian wilayah Sumatera Utara, khususnya di AMANDRAYA, ANGKOLA TIMUR, ARAMO, BATANG ANGKOLA, BAWOLATO, BORONADU, FANAYAMA, GOMO, HILIMEGAI, IDANOTAE, KUALUH HULU, KUALUH LEIDONG, LAHUSA, LUAHAGUNDRE MANIAMOLO, MANIAMOLO, MARANCAR, MAZINO, MAZO, MUARA BATANG GADIS, O'O'U, ONOLALU, PADANGSIDIMPUAN ANGKOLA JULU, PADANGSIDIMPUAN BATUNADUA, PADANGSIDIMPUAN HUTAIMBARU, PADANGSIDIMPUAN SELATAN, PADANGSIDIMPUAN TENGGARA, PADANGSIDIMPUAN UTARA, SAYUR MATINGGI, SIABU, SIDUA'ORI, SOMAMBAWA, SUSUA, TANO TOMBANGAN ANGKOLA, TELUK DALAM, TOMA, ULU IDANOTAE, ULUNOYO, ULUSUSUA, UMBUNASI.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 16:45 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.12.003&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 13:35:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Kep. Riau&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CKR20260922005_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 13:30 WIB di sebagian wilayah Kep. Riau, khususnya di GALANG, PULAU LAUT, SENAYANG, SERI KUALA LOBAM, TELUK BINTAN.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 15:30 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.21.005&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 13:20:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Banten&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CBT20260922001_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 13:30 WIB di sebagian wilayah Banten, khususnya di CIBEBER, GUNUNG SARI, LEBAKGEDONG, MANCAK, PABUARAN, SOBANG, TAKTAKAN, WARINGINKURUNG.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 16:00 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.36.001&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 13:00:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;item&gt;
+            &lt;title&gt;Hujan Lebat disertai Petir di Sumatera Selatan&lt;/title&gt;
+            &lt;link&gt;https://www.bmkg.go.id/alerts/nowcast/id/CSS20260922005_alert.xml&lt;/link&gt;
+            &lt;description&gt;Hujan lebat disertai petir akan terjadi pada 22 September 2026, 13:20 WIB di sebagian wilayah Sumatera Selatan, khususnya di BABAT TOMAN, BATANG HARI LEKO, BAYUNG LENCIR, KARANG JAYA, LAWANG WETAN, LEMPUING JAYA, LINTANG KANAN, LUBUK LINGGAU SELATAN I, MEGANG SAKTI, MESUJI RAYA, MUARA BELITI, MUARA KELINGI, MUARA LAKITAN, MUARA SUGIHAN, PAJAR BULAN, PENDOPO, PSEKSU, PURWODADI, RAWAS ILIR, SANGA DESA, SEMENDE DARAT ULU, SINDANG DANAU, STL ULU TERAWAS, SUMBER HARTA, SUNGAI ARE, TANJUNG SAKTI PUMI, TANJUNGSAKTI PUMU, TIANG PUMPUNG KEPUNGUT, TUAH NEGERI, TUNGKAL JAYA, ULU MUSI, ULU OGAN.
+ Kondisi ini berpotensi menimbulkan dampak berupa jarak pandang berkurang, angin kencang, dan banjir lokal.
+ Masyarakat dihimbau untuk tetap waspada, mengurangi aktivitas di luar ruangan, serta mengambil langkah-langkah pencegahan yang diperlukan guna menjaga keselamatan.
+ Kondisi diperkirakan dapat berlangsung hingga 22 September 2026, 15:20 WIB.&lt;/description&gt;
+            &lt;author&gt;cuaca.ekstrem@bmkg.go.id (BMKG)&lt;/author&gt;
+            &lt;category&gt;Met&lt;/category&gt;
+            &lt;guid isPermaLink="false"&gt;2.49.0.1.360.0.2026.09.22.08.16.005&lt;/guid&gt;
+            &lt;pubDate&gt;Tue, 22 Sep 2026 12:50:00 +0700&lt;/pubDate&gt;
+        &lt;/item&gt;
+        &lt;/channel&gt;
+    &lt;/rss&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="12" customHeight="1">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>DF Amandemen: update peringatan</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E20" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/amandemen/coord?lat=-6.2&amp;lon=106.816666</t>
+        </is>
+      </c>
+      <c r="F20" s="68" t="inlineStr">
+        <is>
+          <t>{"lokasi":{"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","lon":106.81596823959143,"lat":-6.197052719903746,"distance":0},"amandemen":[]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>ISDP v1: wilayah laut terdekat</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E21" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/v1/public/maritim/nearest-location?lat=-6.2&amp;long=106.816666</t>
+        </is>
+      </c>
+      <c r="F21" s="68" t="inlineStr">
+        <is>
+          <t>{"statusCode":200,"message":"OK!","data":{"code":"F.09","name":"Teluk Jakarta","wilpel":"Stamar Tanjung Priok - Jakarta","geometry":{"type":"Polygon","coordinates":[[[106.68448229697637,-6.015114864033774],[106.68448229697637,-5.910111585789263],[107.03498697202032,-5.910111585789263],[106.99055680194432,-5.931987268756869],[107.01030354420033,-5.940737541943912],[107.02017691532832,-5.960425656614758],[107.01030354420033,-5.984488907879126],[106.98562011638033,-6.004177022549971],[106.99055680194432,-6.023865137220817],[107.02017691532832,-6.03480297870462],[107.02017691532832,-6.078554344639833],[106.99055680194432,-6.087304617826876],[106.91156983292034,-6.100430027607439],[106.87701303397235,-6.098242459310679],[106.85726629171634,-6.117930573981525],[106.82270949276835,-6.124493278871807],[106.79308937938436,-6.111367869091243],[106.74372252374437,-6.106992732497721],[106.72397578148836,-6.093867322717157],[106.70422903923236,-6.052303525078705],[106.71903909592436,-6.041365683594902],[106.68448229697637,-6.015114864033774]]]},"distance":0.07574819298420225,"coordinate":{"type":"Point","coordinates":[106.83985076208779,-6.019490000627295]},"type":"area"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>current-weather</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>DF Adm: resolve wilayah admin</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E22" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/df/v1/adm/coord?lat=-6.2&amp;lon=106.816666</t>
+        </is>
+      </c>
+      <c r="F22" s="68" t="inlineStr">
+        <is>
+          <t>{"adm1":"31","adm2":"31.71","adm3":"31.71.07","adm4":"31.71.07.1005","provinsi":"DKI Jakarta","kotkab":"Kota Adm. Jakarta Pusat","kecamatan":"Tanah Abang","desa":"Kebon Melati","lon":106.81596823959143,"lat":-6.197052719903746,"distance":0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>alerts</t>
+        </is>
+      </c>
+      <c r="B23" s="58" t="inlineStr">
+        <is>
+          <t>Public API: peringatan cuaca</t>
+        </is>
+      </c>
+      <c r="C23" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E23" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/public/weather/warning?lat=-6.2&amp;long=106.816666</t>
+        </is>
+      </c>
+      <c r="F23" s="68" t="inlineStr">
+        <is>
+          <t>{"statusCode":200,"message":"OK!","data":{"today":{},"tomorrow":null}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>lainnya</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E24" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/perairan_list</t>
+        </is>
+      </c>
+      <c r="F24" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{
+  "files": [
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2373,
+      "name": "R.07_Perairan Merauke.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2419,
+      "name": "I.07_Perairan Gresik - Surabaya.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2366,
+      "name": "N.02_Laut Sulawesi bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2368,
+      "name": "O.14_Perairan timur Obi.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2504,
+      "name": "L.15_Perairan P. Bonerate - Kalaotoa bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2469,
+      "name": "C.06_Perairan timur Lampung bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2547,
+      "name": "H.03_Samudera Hindia selatan Jawa Barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2382,
+      "name": "E.01_Perairan Riau.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2518,
+      "name": "U.04_Samudera Hindia selatan Banten.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2548,
+      "name": "I.14_Samudera Hindia selatan Jawa Timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2492,
+      "name": "H.05_Perairan Kebumen - Purworejo.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2416,
+      "name": "E.02_Perairan Kep. Batam.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2444,
+      "name": "T.09_Laut Banda selatan bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2327,
+      "name": "O.11_Teluk Weda.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2554,
+      "name": "T.10_Perairan Kep. Sermata - Kep. Leti.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2402,
+      "name": "K.05_Selat Sumba bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2555,
+      "name": "L.05_Perairan Spermonde Makassar bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2478,
+      "name": "I.06_Perairan Tuban - Lamongan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2536,
+      "name": "I.03_Laut Jawa bagian selatan Bawean.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2441,
+      "name": "T.06_Laut Banda utara bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2408,
+      "name": "K.15_Selat Wetar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2494,
+      "name": "L.14_Perairan P. Bonerate - Kalaotoa bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2587,
+      "name": "O.02_Samudera Pasifik utara Halmahera bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2372,
+      "name": "M.05_Perairan Sulawesi Barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2389,
+      "name": "A.02_Selat Malaka bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2476,
+      "name": "R.06_Laut Arafuru bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2481,
+      "name": "K.07_Laut Sawu bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2448,
+      "name": "T.08_Laut Banda selatan bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2337,
+      "name": "O.06_Perairan Bacan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2394,
+      "name": "L.16_Laut Flores bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2461,
+      "name": "O.13_Perairan timur Halmahera.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2408,
+      "name": "M.09_Perairan Kalimantan Utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2394,
+      "name": "Q.05_Perairan selatan Biak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2519,
+      "name": "I.02_Laut Jawa bagian utara Bawean.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2491,
+      "name": "A.07_Perairan Meulaboh - Kep. Sinabang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2437,
+      "name": "S.02_Perairan Banggai bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2466,
+      "name": "H.06_Perairan Yogyakarta.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2492,
+      "name": "R.02_Perairan Amamapare - Agats bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2407,
+      "name": "N.13_Teluk Tomini bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2526,
+      "name": "R.08_Laut Arafuru selatan Merauke.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2463,
+      "name": "S.06_Perairan Manui Kendari bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2428,
+      "name": "G.05_Perairan Pekalongan - Kendal.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2390,
+      "name": "J.10_Perairan utara Sumbawa.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2401,
+      "name": "L.06_Perairan Spermonde Makassar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2452,
+      "name": "T.01_Laut Seram bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2524,
+      "name": "K.13_Perairan selatan Kupang - P. Rote.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2376,
+      "name": "M.07_Selat Makassar bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2492,
+      "name": "N.08_Perairan Bitung - Likupang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2513,
+      "name": "H.01_Perairan Sukabumi - Cianjur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2421,
+      "name": "F.01_Selat Karimata bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2420,
+      "name": "A.03_Perairan Sabang - Banda Aceh.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2515,
+      "name": "S.07_Laut Banda timur Sulawesi Tenggara bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2368,
+      "name": "G.07_Perairan Jepara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2469,
+      "name": "A.01_Perairan utara Sabang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2422,
+      "name": "O.15_Perairan Kep. Sula bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2363,
+      "name": "T.14_Perairan Kep. Kai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2426,
+      "name": "A.05_Selat Malaka bagian tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2416,
+      "name": "D.03_Perairan utara Kep. Anambas.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2470,
+      "name": "N.07_Perairan Kep. Sitaro.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2376,
+      "name": "P.08_Perairan Fak-Fak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2401,
+      "name": "C.04_Teluk Lampung bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2565,
+      "name": "S.16_Laut Banda timur Sulawesi Tenggara bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2445,
+      "name": "K.10_Selat Alor - Pantar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2387,
+      "name": "D.12_Perairan Kendawangan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2510,
+      "name": "R.05_Perairan Yos Sudarso bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2349,
+      "name": "Q.02_Perairan barat Biak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2403,
+      "name": "F.10_Perairan Karawang - Subang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2309,
+      "name": "O.10_Teluk Kau.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2480,
+      "name": "K.04_Selat Sumba bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2454,
+      "name": "S.04_Perairan Teluk Tolo bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2472,
+      "name": "U.03_Perairan selatan Banten.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2405,
+      "name": "M.08_Perairan barat Sulawesi Tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2417,
+      "name": "N.01_Perairan utara Sulawesi Utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2421,
+      "name": "D.02_Perairan selatan Kep. Anambas.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2550,
+      "name": "S.08_Laut Banda timur Sulawesi Tengara bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2415,
+      "name": "J.07_Selat Lombok bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2483,
+      "name": "G.03_Perairan Kep. Karimun Jawa.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2415,
+      "name": "S.01_Perairan Banggai bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2415,
+      "name": "F.03_Perairan utara P. Belitung.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2489,
+      "name": "J.03_Selat Bali bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2519,
+      "name": "B.03_Perairan timur P. Siberut.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2500,
+      "name": "T.13_Laut Arafuru bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2429,
+      "name": "A.06_Perairan barat Aceh.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2474,
+      "name": "S.15_Perairan selatan Wakatobi bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2363,
+      "name": "T.15_Perairan Kep. Aru.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2381,
+      "name": "U.01_Selat Sunda bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2415,
+      "name": "I.11_Selat Madura bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2552,
+      "name": "K.14_Samudera Hindia selatan Kupang - P. Rote.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2487,
+      "name": "K.03_Selat Sape bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2386,
+      "name": "Q.06_Teluk Cenderawasih.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2442,
+      "name": "H.04_Perairan Cilacap.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2482,
+      "name": "O.09_Perairan Morotai bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2344,
+      "name": "P.03_Perairan Manokwari.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2479,
+      "name": "I.08_Perairan utara Madura.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2360,
+      "name": "P.07_Teluk Bintuni.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2514,
+      "name": "O.03_Perairan Halmahera Barat bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2385,
+      "name": "L.09_Teluk Bone bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2351,
+      "name": "F.09_Teluk Jakarta.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2473,
+      "name": "I.10_Perairan Kep. Kangean.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2509,
+      "name": "C.05_Samudera Hindia barat Lampung.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2529,
+      "name": "B.12_Samudera Hindia barat Bengkulu.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2391,
+      "name": "D.05_Perairan utara Kep. Natuna.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2337,
+      "name": "F.02_Selat Gelasa.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2582,
+      "name": "K.08_Samudera Hindia selatan P. Sumba - P. Sabu.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2508,
+      "name": "J.12_Samudera Hindia selatan NTB.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2466,
+      "name": "L.11_Perairan timur Kep. Selayar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2504,
+      "name": "B.11_Perairan timur P. Enggano.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2577,
+      "name": "B.09_Samudera Hindia barat Kep. Mentawai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2451,
+      "name": "P.02_Perairan Raja Ampat bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2435,
+      "name": "I.09_Perairan Kep. Sapudi.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2490,
+      "name": "B.06_Perairan barat P. Pagai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2411,
+      "name": "J.08_Laut Sumbawa.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2544,
+      "name": "H.07_Samudera Hindia selatan Jawa Tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2393,
+      "name": "D.04_Perairan barat Kep. Natuna.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2436,
+      "name": "R.03_Laut Arafuru timur Kepulauan Aru.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2371,
+      "name": "K.02_Selat Sape bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2457,
+      "name": "P.06_Perairan Sorong bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2494,
+      "name": "B.05_Perairan timur P. Pagai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2433,
+      "name": "O.04_Perairan Kep. Loloda.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2503,
+      "name": "J.05_Selat Lombok bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2440,
+      "name": "S.03_Perairan Teluk Tolo bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2396,
+      "name": "K.11_Selat Ombai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2492,
+      "name": "B.10_Perairan barat Bengkulu.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2409,
+      "name": "F.11_Perairan Indramayu - Cirebon.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2441,
+      "name": "D.10_Perairan Pontianak - Mempawah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2445,
+      "name": "M.01_Perairan Kota Baru bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2433,
+      "name": "F.04_Perairan selatan P. Belitung.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2374,
+      "name": "Q.03_Perairan utara Biak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2423,
+      "name": "C.08_Selat Bangka bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2530,
+      "name": "B.01_Perairan barat Sumatera Barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2483,
+      "name": "T.12_Perairan Kep. Tanimbar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2396,
+      "name": "J.09_Selat Alas bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2381,
+      "name": "E.05_Selat Berhala.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2430,
+      "name": "F.06_Laut Jawa bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2478,
+      "name": "A.08_Samudera Hindia barat Aceh.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2389,
+      "name": "F.08_Perairan Kep. Seribu.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2469,
+      "name": "S.14_Perairan selatan Wakatobi bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2490,
+      "name": "S.11_Perairan Bau-bau bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2546,
+      "name": "I.05_Laut Jawa bagian timur Masalembo.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2527,
+      "name": "K.12_Perairan utara Kupang - P. Rote.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2401,
+      "name": "T.05_Perairan selatan P. Seram.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2410,
+      "name": "O.12_Laut Halmahera.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2510,
+      "name": "T.16_Laut Arafuru bagian tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2478,
+      "name": "T.11_Perairan Kep. Babar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2371,
+      "name": "K.01_Perairan utara Flores.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2418,
+      "name": "N.11_Perairan selatan Sulawesi Utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2372,
+      "name": "M.03_Perairan Balikpapan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2399,
+      "name": "L.13_Laut Flores bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2341,
+      "name": "N.03_Laut Sulawesi bagian tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2431,
+      "name": "L.03_Perairan Spermonde Pangkep bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2507,
+      "name": "A.09_Perairan Kep. Nias - Sibolga.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2364,
+      "name": "P.09_Perairan Kaimana.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2490,
+      "name": "C.01_Perairan barat Lampung.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2502,
+      "name": "I.13_Perairan selatan Jawa Timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2452,
+      "name": "K.06_Laut Sawu bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2432,
+      "name": "T.04_Perairan P. Ambon - Kep. Lease.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2514,
+      "name": "P.01_Samudera Pasifik utara Papua Barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2385,
+      "name": "D.01_Laut Natuna Utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2505,
+      "name": "L.01_Selat Makassar bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2476,
+      "name": "S.12_Perairan utara Wakatobi bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2511,
+      "name": "B.04_Perairan timur P. Sipora.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2486,
+      "name": "J.11_Selat Alas bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2392,
+      "name": "N.04_Laut Sulawesi bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2368,
+      "name": "J.01_Laut Bali.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2433,
+      "name": "T.03_Perairan P. Buru.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2355,
+      "name": "D.11_Perairan Ketapang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2488,
+      "name": "U.02_Selat Sunda bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2420,
+      "name": "D.13_Perairan Kepulauan Karimata.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2433,
+      "name": "N.12_Teluk Tomini bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2412,
+      "name": "T.02_Laut Seram bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2342,
+      "name": "O.07_Perairan Obi.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2457,
+      "name": "G.08_Perairan Pati - Rembang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2431,
+      "name": "T.07_Laut Banda utara bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2490,
+      "name": "H.02_Perairan Garut - Pangandaran.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2523,
+      "name": "J.06_Samudera Hindia selatan Bali.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2372,
+      "name": "P.05_Perairan Misool.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2482,
+      "name": "C.07_Perairan timur Lampung bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2388,
+      "name": "L.04_Perairan Spermonde Pangkep.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2402,
+      "name": "N.10_Laut Maluku bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2591,
+      "name": "O.01_Samudera Pasifik utara Halmahera bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2506,
+      "name": "G.01_Perairan Kalimantan Tengah bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2424,
+      "name": "G.04_Perairan Brebes - Pemalang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2441,
+      "name": "L.12_Laut Flores bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2365,
+      "name": "D.08_Laut Natuna.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2444,
+      "name": "D.06_Perairan selatan Kep. Natuna - Pulau Midai.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2530,
+      "name": "A.10_Samudera Hindia barat Kep. Nias.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2544,
+      "name": "I.01_Perairan Kalimantan Tengah bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2413,
+      "name": "G.06_Perairan Semarang - Demak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2438,
+      "name": "R.04_Perairan Yos Sudarso bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2379,
+      "name": "D.07_Perairan Kep. Subi - Serasan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2385,
+      "name": "Q.01_Samudera Pasifik utara Biak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2458,
+      "name": "N.09_Laut Maluku bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2469,
+      "name": "N.05_Perairan Kep. Sangihe.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2395,
+      "name": "J.02_Selat Bali bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2408,
+      "name": "E.03_Perairan Kep. Bintan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2418,
+      "name": "I.12_Selat Madura bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2439,
+      "name": "O.16_Perairan Kep. Sula bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2423,
+      "name": "E.04_Perairan Kep. Lingga.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2481,
+      "name": "L.10_Teluk Bone bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2513,
+      "name": "L.07_Perairan barat Kep. Selayar.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2366,
+      "name": "L.02_Perairan Pare - pare.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2434,
+      "name": "D.09_Perairan Singkawang - Sambas.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2459,
+      "name": "S.05_Perairan Manui Kendari bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2394,
+      "name": "Q.04_Perairan timur Biak.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2462,
+      "name": "N.06_Perairan Kep. Talaud.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2375,
+      "name": "F.07_Perairan utara Banten.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2411,
+      "name": "S.10_Perairan Bau-bau bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2426,
+      "name": "O.05_Perairan Ternate - Batang Dua.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2414,
+      "name": "M.04_Selat Makassar bagian tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2510,
+      "name": "Q.08_Samudera Pasifik utara Jayapura.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2498,
+      "name": "B.07_Perairan barat P. Sipora.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2435,
+      "name": "F.05_Selat Karimata bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2431,
+      "name": "E.06_Perairan utara P. Bangka.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2486,
+      "name": "R.01_Perairan Amamapare - Agats bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2537,
+      "name": "I.04_Laut Jawa bagian barat Masalembo.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2367,
+      "name": "A.04_Perairan Lhokseumawe.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2431,
+      "name": "L.08_Perairan Kep. Sabalana.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2353,
+      "name": "K.09_Selat Flores - Lamakera.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2525,
+      "name": "S.09_Laut Banda timur Sulawesi Tenggara bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2492,
+      "name": "G.02_Laut Jawa bagian tengah.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2415,
+      "name": "P.04_Perairan Raja Ampat - Sorong.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2475,
+      "name": "C.02_Selat Sunda bagian barat.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2432,
+      "name": "M.02_Perairan Kota Baru bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2520,
+      "name": "B.08_Perairan barat P. Siberut.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2517,
+      "name": "B.02_Perairan utara P. Siberut.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2420,
+      "name": "C.09_Selat Bangka bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2480,
+      "name": "S.13_Perairan utara Wakatobi bagian timur.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2487,
+      "name": "O.08_Perairan Morotai bagian utara.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2406,
+      "name": "M.06_Perairan Samarinda - Bontang.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2504,
+      "name": "C.03_Teluk Lampung bagian selatan.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2428,
+      "name": "Q.07_Perairan Jayapura - Sarmi.json"
+    },
+    {
+      "file_date": "2026-09-21 23:39 UTC",
+      "kb": 2424,
+      "name": "J.04_Selat Badung.json"
+    }
+  ]
+}
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>TCWC: siklon tropis</t>
+        </is>
+      </c>
+      <c r="C25" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E25" s="58" t="inlineStr">
+        <is>
+          <t>https://cuaca.bmkg.go.id/api/v1/tcwc/cyclone/all</t>
+        </is>
+      </c>
+      <c r="F25" s="68" t="inlineStr">
+        <is>
+          <t>{"status":"OK","data":{"docs":[{"_id":"67b446d42719de8e91f91cd3","technical_bulletin":"https://drive.google.com/file/d/1q6O6OvVvOVV7OsqcPwsWhZG9aB4dyLDv/view?usp=sharing","public_bulletin":"https://drive.google.com/file/d/1srXcaxP7BRgdHKjp6DKCDG5fg8SZdrhq/view?usp=sharing","ocean_gale":["Samudera Hindia selatan Jawa Timur","Samudera Hindia selatan Jawa Tengah","Samudera Hindia selatan Jawa Barat","Samudera Hindia selatan Banten","Perairan selatan Banten","Perairan Sukabumi - Cianjur","Perairan Garut - Pangandaran","Perairan Cilacap","Perairan Kebumen - Purworejo","Perairan Yogyakarta","Perairan selatan Jawa Timur","Samudera Hindia barat Lampung","Selat Sunda bagian selatan","Selat Sunda bagian barat","Perairan barat Lampung","Samudera Hindia selatan Bali","Samudera Hindia selatan NTB","Samudera Hindia selatan Kupang - P. Rote","Samudera Hindia selatan P. Sumba - P. Sabu","Perairan selatan Kupang - P. Rote"],"gale":["JAWA BARAT","LAMPUNG","BANTEN"],"extreme_weather":["JAWA BARAT","LAMPUNG","BANTEN"],"month":1,"year":2025,"area":"bbs","name":"TC BIANCA","description_id":"TC BIANCA (99S)","description":"TC BIANCA (99S)","is_current":false,"track":[{"geometry":{"coordinates":[128.7,-10.8],"type":"Point"},"_id":"67bc89d02719ded8f7f9b8e3","type":"Feature","properties":{"date":"2025-02-18T00:00:00.000Z","pressure":1009,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-18 00:00:00 UTC"}},{"geometry":{"coordinates":[126.5,-11.7],"type":"Point"},"_id":"67bc89d02719de476df9b8e4","type":"Feature","properties":{"date":"2025-02-18T12:00:00.000Z","pressure":1008,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-18 12:00:00 UTC"}},{"geometry":{"coordinates":[126.1,-11.7],"type":"Point"},"_id":"67bc89d02719de43b8f9b8e5","type":"Feature","properties":{"date":"2025-02-19T00:00:00.000Z","pressure":1006,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-19 00:00:00 UTC"}},{"geometry":{"coordinates":[127.4,-11.2],"type":"Point"},"_id":"67bc89d02719de3d1bf9b8e6","type":"Feature","properties":{"date":"2025-02-19T12:00:00.000Z","pressure":1006,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-19 12:00:00 UTC"}},{"geometry":{"coordinates":[121.2,-13.3],"type":"Point"},"_id":"67bc89d02719de5e93f9b8e7","type":"Feature","properties":{"date":"2025-02-20T00:00:00.000Z","pressure":1005,"meanWind":25,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-20 00:00:00 UTC"}},{"geometry":{"coordinates":[116.9,-14.1],"type":"Point"},"_id":"67bc89d02719de27fff9b8e8","type":"Feature","properties":{"date":"2025-02-21T00:00:00.000Z","pressure":1004,"meanWind":30,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-21 00:00:00 UTC"}},{"geometry":{"coordinates":[112.3,-15],"type":"Point"},"_id":"67bc89d02719de29aff9b8e9","type":"Feature","properties":{"date":"2025-02-22T00:00:00.000Z","pressure":1006,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-22 00:00:00 UTC"}},{"geometry":{"coordinates":[108.6,-16.2],"type":"Point"},"_id":"67bc89d02719de78f3f9b8ea","type":"Feature","properties":{"date":"2025-02-23T00:00:00.000Z","pressure":1004,"meanWind":30,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-23 00:00:00 UTC"}},{"geometry":{"coordinates":[105.8,-17.2],"type":"Point"},"_id":"67bc89d02719de0e5ef9b8eb","type":"Feature","properties":{"date":"2025-02-23T12:00:00.000Z","pressure":1000,"meanWind":35,"gust":50,"cat":"1","accuracy":"-","dateString":"2025-02-23 12:00:00 UTC"}},{"geometry":{"coordinates":[104.7,-18.3],"type":"Point"},"_id":"67bc89d02719de7b56f9b8ec","type":"Feature","properties":{"date":"2025-02-24T00:00:00.000Z","pressure":991,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-24 00:00:00 UTC"}},{"geometry":{"coordinates":[103.1,-19.7],"type":"Point"},"_id":"67bc89d02719de2d26f9b8ed","type":"Feature","properties":{"date":"2025-02-24T12:00:00.000Z","pressure":980,"meanWind":65,"gust":90,"cat":"3","accuracy":"-","dateString":"2025-02-24 12:00:00 UTC","name":"TC BIANCA"}}],"forecast":[{"geometry":{"coordinates":[102.4,-20.7],"type":"Point"},"_id":"67bc84dc2719debecdf9b868","type":"Feature","properties":{"date":"2025-02-25T00:00:00Z","pressure":967,"meanWind":80,"gust":"110","cat":"3","dateString":"2025-02-25 00:00:00Z UTC"}},{"geometry":{"coordinates":[101.8,-22.3],"type":"Point"},"_id":"67bc84dc2719de5e69f9b869","type":"Feature","properties":{"date":"2025-02-25T12:00:00Z","pressure":970,"meanWind":75,"gust":"105","cat":"3","dateString":"2025-02-25 12:00:00Z UTC"}},{"geometry":{"coordinates":[101.4,-23.9],"type":"Point"},"_id":"67bc84dc2719de5dc1f9b86a","type":"Feature","properties":{"date":"2025-02-26T00:00:00Z","pressure":990,"meanWind":50,"gust":"70","cat":"2","dateString":"2025-02-26 00:00:00Z UTC"}},{"geometry":{"coordinates":[101.6,-25.1],"type":"Point"},"_id":"67bc84dc2719deb8c4f9b86b","type":"Feature","properties":{"date":"2025-02-26T12:00:00Z","pressure":995,"meanWind":40,"gust":"55","cat":"1","dateString":"2025-02-26 12:00:00Z UTC"}},{"geometry":{"coordinates":[100.8,-25.2],"type":"Point"},"_id":"67bc84dc2719de99caf9b86c","type":"Feature","properties":{"date":"2025-02-27T00:00:00Z","pressure":1002,"meanWind":30,"gust":"45","cat":"0","dateString":"2025-02-27 00:00:00Z UTC"}},{"geometry":{"coordinates":[99.2,-25.3],"type":"Point"},"_id":"67bc84dc2719de8126f9b86d","type":"Feature","properties":{"date":"2025-02-27T12:00:00Z","pressure":1006,"meanWind":25,"gust":"45","cat":"0","dateString":"2025-02-27 12:00:00Z UTC","name":"TC BIANCA"}}],"createdAt":"2025-02-18T08:37:40.011Z","updatedAt":"2025-02-25T02:07:08.968Z","publication":{"movement":false,"movementChoose":{"0h":"","24h":"","48h":"","72h":""},"warningText":"","positionAccuration":"sekitar","intensity":"Storm","intensity24":"Hurricane","windQuadran":"","finalPublication":true,"nextPublicationTime":"29/1300 UTC","accurationArea":{"type":"FeatureCollection","features":[]}},"direct_impact":false},{"_id":"67ac29082719de4b5bf88a09","technical_bulletin":"https://drive.google.com/file/d/1Cf8Y9SEWQh_JHGMp9ldCnNcWkDRO_mkZ/view?usp=drive_link","public_bulletin":"https://drive.google.com/file/d/1JezB3O7shfSRbSmPkaMjDQNzB1Uoq6BN/view?usp=drive_link","ocean_gale":["Samudera Hindia barat Aceh","Samudera Hindia barat Kep. Nias","Samudera Hindia barat Kep. Mentawai","Samudera Hindia barat Bengkulu","Samudera Hindia barat Lampung"],"gale":[],"extreme_weather":[],"month":1,"year":2025,"area":"bbs","name":"TC TALIAH","description_id":"Siklon Tropis Taliah","description":"Tropical Cyclone Taliah","is_current":false,"track":[{"geometry":{"coordinates":[117.7,-14.4],"type":"Point"},"_id":"67ac32492719de25f8f88b97","type":"Feature","properties":{"date":"2025-02-02T00:00:00.000Z","pressure":996,"meanWind":30,"gust":45,"cat":"L","accuracy":"-","dateString":"2025-02-02 00:00:00 UTC"}},{"geometry":{"coordinates":[116.1,-14.3],"type":"Point"},"_id":"67ac32492719de955bf88b98","type":"Feature","properties":{"date":"2025-02-02T12:00:00.000Z","pressure":982,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-02 12:00:00 UTC"}},{"geometry":{"coordinates":[115,-15],"type":"Point"},"_id":"67ac32492719de1449f88b99","type":"Feature","properties":{"date":"2025-02-03T00:00:00.000Z","pressure":983,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-03 00:00:00 UTC"}},{"geometry":{"coordinates":[113.6,-15.1],"type":"Point"},"_id":"67ac32492719deb8ccf88b9a","type":"Feature","properties":{"date":"2025-02-03T12:00:00.000Z","pressure":976,"meanWind":60,"gust":85,"cat":"2","accuracy":"-","dateString":"2025-02-03 12:00:00 UTC"}},{"geometry":{"coordinates":[112.1,-15.2],"type":"Point"},"_id":"67ac32492719de6c6ef88b9b","type":"Feature","properties":{"date":"2025-02-04T00:00:00.000Z","pressure":968,"meanWind":70,"gust":100,"cat":"3","accuracy":"-","dateString":"2025-02-04 00:00:00 UTC"}},{"geometry":{"coordinates":[110.4,-15.7],"type":"Point"},"_id":"67ac32492719de0546f88b9c","type":"Feature","properties":{"date":"2025-02-04T12:00:00.000Z","pressure":968,"meanWind":70,"gust":100,"cat":"3","accuracy":"-","dateString":"2025-02-04 12:00:00 UTC"}},{"geometry":{"coordinates":[108.2,-15.7],"type":"Point"},"_id":"67ac32492719de53ddf88b9d","type":"Feature","properties":{"date":"2025-02-05T00:00:00.000Z","pressure":973,"meanWind":65,"gust":90,"cat":"3","accuracy":"-","dateString":"2025-02-05 00:00:00 UTC"}},{"geometry":{"coordinates":[106,-15.2],"type":"Point"},"_id":"67ac32492719de1e74f88b9e","type":"Feature","properties":{"date":"2025-02-05T12:00:00.000Z","pressure":980,"meanWind":55,"gust":75,"cat":"2","accuracy":"-","dateString":"2025-02-05 12:00:00 UTC"}},{"geometry":{"coordinates":[105.3,-14.8],"type":"Point"},"_id":"67ac32492719deade0f88b9f","type":"Feature","properties":{"date":"2025-02-06T00:00:00.000Z","pressure":982,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-06 00:00:00 UTC"}},{"geometry":{"coordinates":[102.6,-14.9],"type":"Point"},"_id":"67ac32492719de0248f88ba0","type":"Feature","properties":{"date":"2025-02-06T12:00:00.000Z","pressure":987,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-06 12:00:00 UTC"}},{"geometry":{"coordinates":[100.2,-15.2],"type":"Point"},"_id":"67ac32492719de73b0f88ba1","type":"Feature","properties":{"date":"2025-02-07T00:00:00.000Z","pressure":989,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-07 00:00:00 UTC"}},{"geometry":{"coordinates":[98.1,-16.2],"type":"Point"},"_id":"67ac32492719de5433f88ba2","type":"Feature","properties":{"date":"2025-02-07T12:00:00.000Z","pressure":993,"meanWind":40,"gust":55,"cat":"1","accuracy":"-","dateString":"2025-02-07 12:00:00 UTC"}},{"geometry":{"coordinates":[96,-16],"type":"Point"},"_id":"67ac32492719deb676f88ba3","type":"Feature","properties":{"date":"2025-02-08T00:00:00.000Z","pressure":993,"meanWind":45,"gust":65,"cat":"1","accuracy":"-","dateString":"2025-02-08 00:00:00 UTC"}},{"geometry":{"coordinates":[95,-15.7],"type":"Point"},"_id":"67ac32492719dee147f88ba4","type":"Feature","properties":{"date":"2025-02-08T12:00:00.000Z","pressure":990,"meanWind":45,"gust":65,"cat":"1","accuracy":"-","dateString":"2025-02-08 12:00:00 UTC"}},{"geometry":{"coordinates":[94.9,-15.4],"type":"Point"},"_id":"67ac32492719de97d9f88ba5","type":"Feature","properties":{"date":"2025-02-09T00:00:00.000Z","pressure":992,"meanWind":40,"gust":55,"cat":"1","accuracy":"-","dateString":"2025-02-09 00:00:00 UTC"}},{"geometry":{"coordinates":[93.5,-15.3],"type":"Point"},"_id":"67ac32492719de1ecff88ba6","type":"Feature","properties":{"date":"2025-02-09T12:00:00.000Z","pressure":996,"meanWind":35,"gust":50,"cat":"1","accuracy":"-","dateString":"2025-02-09 12:00:00 UTC"}},{"geometry":{"coordinates":[93,-14.7],"type":"Point"},"_id":"67ac32492719de4523f88ba7","type":"Feature","properties":{"date":"2025-02-10T00:00:00.000Z","pressure":995,"meanWind":35,"gust":50,"cat":"1","accuracy":"-","dateString":"2025-02-10 00:00:00 UTC"}},{"geometry":{"coordinates":[92.4,-14.4],"type":"Point"},"_id":"67ac32492719de561ff88ba8","type":"Feature","properties":{"date":"2025-02-10T12:00:00.000Z","pressure":992,"meanWind":40,"gust":55,"cat":"1","accuracy":"-","dateString":"2025-02-10 12:00:00 UTC"}},{"geometry":{"coordinates":[92.1,-14.3],"type":"Point"},"_id":"67ac32492719de74fbf88ba9","type":"Feature","properties":{"date":"2025-02-11T00:00:00.000Z","pressure":993,"meanWind":40,"gust":55,"cat":"1","accuracy":"-","dateString":"2025-02-11 00:00:00 UTC"}},{"geometry":{"coordinates":[91.8,-15.3],"type":"Point"},"_id":"67ac32492719de3b5ef88baa","type":"Feature","properties":{"date":"2025-02-11T12:00:00.000Z","pressure":988,"meanWind":50,"gust":70,"cat":"2","accuracy":"-","dateString":"2025-02-11 12:00:00 UTC"}},{"geometry":{"coordinates":[90.8,-16.8],"type":"Point"},"_id":"67ac32492719de11c3f88bab","type":"Feature","properties":{"date":"2025-02-12T00:00:00.000Z","pressure":980,"meanWind":60,"gust":85,"cat":"2","accuracy":"-","dateString":"2025-02-12 00:00:00 UTC","name":"TC TALIAH"}}],"forecast":[{"geometry":{"coordinates":[89.7,-18.8],"type":"Point"},"_id":"67ac31b92719de1a15f88b24","type":"Feature","properties":{"date":"2025-02-12T12:00:00Z","pressure":976,"meanWind":60,"gust":"85.0","cat":"2.0","dateString":"2025-02-12 12:00:00Z UTC"}},{"geometry":{"coordinates":[88.1,-20.5],"type":"Point"},"_id":"67ac31b92719ded876f88b25","type":"Feature","properties":{"date":"2025-02-13T00:00:00Z","pressure":976,"meanWind":60,"gust":"85.0","cat":"2.0","dateString":"2025-02-13 00:00:00Z UTC"}},{"geometry":{"coordinates":[85,-22.9],"type":"Point"},"_id":"67ac31b92719de7c60f88b26","type":"Feature","properties":{"date":"2025-02-14T00:00:00Z","pressure":982,"meanWind":50,"gust":"70.0","cat":"2.0","dateString":"2025-02-14 00:00:00Z UTC"}},{"geometry":{"coordinates":[83.1,-24],"type":"Point"},"_id":"67ac31b92719de17b6f88b27","type":"Feature","properties":{"date":"2025-02-15T00:00:00Z","pressure":986,"meanWind":45,"gust":"65.0","cat":"1.0","dateString":"2025-02-15 00:00:00Z UTC","name":"TC TALIAH"}}],"createdAt":"2025-02-12T04:52:24.692Z","updatedAt":"2025-02-13T12:23:59.908Z","publication":{"movement":false,"movementChoose":{"0h":"","24h":"","48h":"","72h":""},"warningText":"","positionAccuration":"sekitar","intensity":"Storm","intensity24":"Hurricane","windQuadran":"","finalPublication":true,"nextPublicationTime":"29/1300 UTC","accurationArea":{"type":"FeatureCollection","features":[]}}},{"_id":"67abfa732719de24a7f88523","technical_bulletin":"https://drive.google.com/file/d/1WXxVKwKqmTijSkIjigmLWbUVc9ie4WE2/view?usp=drive_link","public_bulletin":"https://drive.google.com/file/d/16CC7X9lkbp88WODMGo4H_eTqbU_Bx8BD/view?usp=drive_link","ocean_gale":["Samudera Hindia selatan Jawa Tengah","Perairan Cilacap","Perairan Kebumen - Purworejo","Perairan Yogyakarta","Samudera Hindia selatan Jawa Timur","Perairan selatan Jawa Timur","Samudera Hindia selatan Bali","Samudera Hindia selatan NTB","Selat Lombok bagian selatan","Selat Alas bagian selatan","Samudera Hindia selatan P. Sumba - P. Sabu","Samudera Hindia selatan Kupang - P. Rote","Perairan selatan Kupang - P. Rote","Perairan utara Kupang - P. Rote","Laut Sawu bagian selatan","Laut Sawu bagian utara","Selat Sumba bagian barat","Selat Sumba bagian timur","Selat Sape bagian selatan","Selat Sape bagian utara","Perairan Sukabumi - Cianjur","Perairan Garut - Pangandaran","Selat Badung","Selat Bali bagian selatan","Selat Bali bagian utara","Samudera Hindia selatan Jawa Barat"],"gale":["NUSA TENGGARA TIMUR"],"extreme_weather":[],"month":2,"year":2025,"area":"bbs","name":"TC ZELIA","description":"TC Zelia","description_id":"TC Zelia","is_current":false,"direct_impact":false,"track":[{"geometry":{"coordinates":[119.1,-17.9],"type":"Point"},"_id":"67aebacb2719de0ce2f8b9bb","type":"Feature","properties":{"date":"2025-02-11T12:00:00.000Z","pressure":"-","meanWind":35,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-11 12:00:00 UTC"}},{"geometry":{"coordinates":[118.9,-18.5],"type":"Point"},"_id":"67aebacb2719deaad9f8b9bc","type":"Feature","properties":{"date":"2025-02-11T18:00:00.000Z","pressure":"-","meanWind":40,"gust":"-","cat":"1","accuracy":"-","dateString":"2025-02-11 18:00:00 UTC"}},{"geometry":{"coordinates":[119.6,-18.1],"type":"Point"},"_id":"67aebacb2719de0fadf8b9bd","type":"Feature","properties":{"date":"2025-02-12T00:00:00.000Z","pressure":985,"meanWind":45,"gust":"-","cat":"1","accuracy":"-","dateString":"2025-02-12 00:00:00 UTC"}},{"geometry":{"coordinates":[118.6,-19],"type":"Point"},"_id":"67aebacb2719de97cff8b9be","type":"Feature","properties":{"date":"2025-02-12T12:00:00.000Z","pressure":976,"meanWind":55,"gust":"-","cat":"2","accuracy":"-","dateString":"2025-02-12 12:00:00 UTC"}},{"geometry":{"coordinates":[118.1,-19],"type":"Point"},"_id":"67aebacb2719de1181f8b9bf","type":"Feature","properties":{"date":"2025-02-13T00:00:00.000Z","pressure":941,"meanWind":100,"gust":140,"cat":"4","accuracy":"-","dateString":"2025-02-13 00:00:00 UTC"}},{"geometry":{"coordinates":[118.2,-19.3],"type":"Point"},"_id":"67aebacb2719de3d0cf8b9c0","type":"Feature","properties":{"date":"2025-02-13T12:00:00.000Z","pressure":928,"meanWind":110,"gust":155,"cat":"5","accuracy":"-","dateString":"2025-02-13 12:00:00 UTC"}},{"geometry":{"coordinates":[118.6,-19.5],"type":"Point"},"_id":"67aebacb2719de1aa3f8b9c1","type":"Feature","properties":{"date":"2025-02-14T00:00:00.000Z","pressure":927,"meanWind":110,"gust":155,"cat":"5","accuracy":"-","dateString":"2025-02-14 00:00:00 UTC","name":"TC ZELIA"}}],"forecast":[{"geometry":{"coordinates":[118.9,-20.7],"type":"Point"},"_id":"67aebacb2719dea928f8b9b8","type":"Feature","properties":{"date":"2025-02-14T12:00:00.000Z","pressure":948,"meanWind":90,"gust":"-","cat":"4","accuracy":30,"dateString":"2025-02-14 12:00:00 UTC"}},{"geometry":{"coordinates":[118.6,-22.1],"type":"Point"},"_id":"67aebacb2719de7769f8b9b9","type":"Feature","properties":{"date":"2025-02-15T00:00:00.000Z","pressure":982,"meanWind":50,"gust":"-","cat":"2","accuracy":60,"dateString":"2025-02-15 00:00:00 UTC"}},{"geometry":{"coordinates":[117.3,-25.2],"type":"Point"},"_id":"67aebacb2719de549af8b9ba","type":"Feature","properties":{"date":"2025-02-16T00:00:00.000Z","pressure":994,"meanWind":30,"gust":"-","cat":"L","accuracy":85,"dateString":"2025-02-16 00:00:00 UTC","name":"TC ZELIA"}}],"createdAt":"2025-02-12T01:33:39.141Z","updatedAt":"2025-02-14T21:53:19.807Z","publication":{"movement":false,"movementChoose":{"0h":"","24h":"","48h":"","72h":""},"warningText":"","positionAccuration":"sekitar","intensity":"Storm","intensity24":"Hurricane","windQuadran":"","finalPublication":true,"nextPublicationTime":"29/1300 UTC","accurationArea":{"type":"FeatureCollection","features":[]}}},{"_id":"67a9b6c22719de351af85286","technical_bulletin":"","public_bulletin":"","ocean_gale":["Laut Natuna Utara","Perairan selatan Kep. Anambas","Perairan utara Kep. Anambas","Perairan barat Kep. Natuna","Perairan utara Kep. Natuna","Perairan selatan Kep. Natuna - Pulau Midai"],"gale":[],"extreme_weather":[],"month":12,"year":2025,"area":"bbu","name":"Bibit 93W","description":"Bibit 93W","description_id":"Bibit 93W","is_current":false,"direct_impact":false,"track":[{"geometry":{"coordinates":[114.7,8.2],"type":"Point"},"_id":"67b4528d2719de3264f91e0f","type":"Feature","properties":{"date":"2025-02-10T00:00:00.000Z","pressure":1007,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-10 00:00:00 UTC"}},{"geometry":{"coordinates":[114.1,8.1],"type":"Point"},"_id":"67b4528d2719de6e83f91e10","type":"Feature","properties":{"date":"2025-02-10T12:00:00.000Z","pressure":1006,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-10 12:00:00 UTC"}},{"geometry":{"coordinates":[113.3,7.7],"type":"Point"},"_id":"67b4528d2719de1f22f91e11","type":"Feature","properties":{"date":"2025-02-11T00:00:00.000Z","pressure":1006,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-11 00:00:00 UTC"}},{"geometry":{"coordinates":[114.1,11.2],"type":"Point"},"_id":"67b4528d2719ded766f91e12","type":"Feature","properties":{"date":"2025-02-11T12:00:00.000Z","pressure":1008,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-11 12:00:00 UTC"}},{"geometry":{"coordinates":[113.5,11.7],"type":"Point"},"_id":"67b4528d2719de766bf91e13","type":"Feature","properties":{"date":"2025-02-12T00:00:00.000Z","pressure":1008,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-12 00:00:00 UTC"}},{"geometry":{"coordinates":[111.7,13.5],"type":"Point"},"_id":"67b4528d2719de815ef91e14","type":"Feature","properties":{"date":"2025-02-13T00:00:00.000Z","pressure":1006,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-13 00:00:00 UTC"}},{"geometry":{"coordinates":[111.9,13.3],"type":"Point"},"_id":"67b4528d2719de5cb6f91e15","type":"Feature","properties":{"date":"2025-02-13T12:00:00.000Z","pressure":1006,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-13 12:00:00 UTC"}},{"geometry":{"coordinates":[111.9,12.1],"type":"Point"},"_id":"67b4528d2719deddb1f91e16","type":"Feature","properties":{"date":"2025-02-14T00:00:00.000Z","pressure":1006,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-14 00:00:00 UTC"}},{"geometry":{"coordinates":[110.7,9.5],"type":"Point"},"_id":"67b4528d2719de721df91e17","type":"Feature","properties":{"date":"2025-02-15T00:00:00.000Z","pressure":1008,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-15 00:00:00 UTC"}},{"geometry":{"coordinates":[108.6,6.1],"type":"Point"},"_id":"67b4528d2719de3f44f91e18","type":"Feature","properties":{"date":"2025-02-16T00:00:00.000Z","pressure":1008,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-16 00:00:00 UTC"}},{"geometry":{"coordinates":[105.5,3.8],"type":"Point"},"_id":"67b4528d2719de2326f91e19","type":"Feature","properties":{"date":"2025-02-17T00:00:00.000Z","pressure":1009,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-17 00:00:00 UTC"}},{"geometry":{"coordinates":[105.3,1.6],"type":"Point"},"_id":"67b4528d2719de152bf91e1a","type":"Feature","properties":{"date":"2025-02-18T00:00:00.000Z","pressure":1010,"meanWind":20,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-18 00:00:00 UTC","name":"Bibit 93W"}}],"forecast":[],"createdAt":"2025-02-10T08:20:18.396Z","updatedAt":"2025-02-18T12:46:51.524Z","publication":{"movement":false,"movementChoose":{"0h":"","24h":"","48h":"","72h":""},"warningText":"","positionAccuration":"sekitar","intensity":"Storm","intensity24":"Hurricane","windQuadran":"","finalPublication":true,"nextPublicationTime":"29/1300 UTC","accurationArea":{"type":"FeatureCollection","features":[]}}},{"_id":"67a702aa2719de9759f814f8","technical_bulletin":"","public_bulletin":"","ocean_gale":["Samudera Hindia selatan Kupang - P. Rote","Perairan selatan Kupang - P. Rote","Laut Sawu bagian utara","Laut Sawu bagian selatan","Perairan utara Kupang - P. Rote","Samudera Hindia selatan Jawa Timur","Samudera Hindia selatan Bali","Samudera Hindia selatan NTB","Samudera Hindia selatan P. Sumba - P. Sabu","Selat Sumba bagian timur","Selat Sumba bagian barat","Samudera Hindia selatan Banten","Samudera Hindia selatan Jawa Barat","Samudera Hindia selatan Jawa Tengah","Perairan selatan Banten","Perairan Sukabumi - Cianjur","Perairan Garut - Pangandaran","Perairan Cilacap","Perairan Kebumen - Purworejo","Perairan Yogyakarta","Perairan selatan Jawa Timur"],"gale":["NUSA TENGGARA BARAT","NUSA TENGGARA TIMUR","BALI","JAWA TIMUR"],"extreme_weather":["NUSA TENGGARA BARAT","BALI","JAWA TIMUR","NUSA TENGGARA TIMUR"],"month":2,"year":2025,"area":"bbs","name":"Bibit 96S","description":"96S","description_id":"96S","is_current":false,"direct_impact":false,"track":[{"geometry":{"coordinates":[126.4,-13.9],"type":"Point"},"_id":"67ab78272719deb490f87c75","type":"Feature","properties":{"date":"2025-02-08T00:00:00.000Z","pressure":1002,"meanWind":15,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-08 00:00:00 UTC"}},{"geometry":{"coordinates":[124.7,-14.1],"type":"Point"},"_id":"67ab78272719defcecf87c76","type":"Feature","properties":{"date":"2025-02-08T12:00:00.000Z","pressure":999.4,"meanWind":18.9,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-08 12:00:00 UTC"}},{"geometry":{"coordinates":[123.9,-14.9],"type":"Point"},"_id":"67ab78272719de7bcef87c77","type":"Feature","properties":{"date":"2025-02-09T00:00:00.000Z","pressure":998,"meanWind":25,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-09 00:00:00 UTC"}},{"geometry":{"coordinates":[121.8,-15.1],"type":"Point"},"_id":"67ab78272719de04d0f87c78","type":"Feature","properties":{"date":"2025-02-10T00:00:00.000Z","pressure":998,"meanWind":25,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-10 00:00:00 UTC"}},{"geometry":{"coordinates":[120.6,-16],"type":"Point"},"_id":"67ab78272719deeeccf87c79","type":"Feature","properties":{"date":"2025-02-10T12:00:00.000Z","pressure":997,"meanWind":25,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-10 12:00:00 UTC"}},{"geometry":{"coordinates":[120.6,-15.8],"type":"Point"},"_id":"67ab78272719decac8f87c7a","type":"Feature","properties":{"date":"2025-02-11T00:00:00.000Z","pressure":997,"meanWind":25,"gust":"-","cat":"L","accuracy":"-","dateString":"2025-02-11 00:00:00 UTC"}},{"geometry":{"coordinates":[119.6,-17.4],"type":"Point"},"_id":"67ab78272719deebe0f87c7b","type":"Feature","properties":{"date":"2025-02-11T12:00:00.000Z","pressure":990,"meanWind":40,"gust":55,"cat":"L","accuracy":"-","dateString":"2025-02-11 12:00:00 UTC","name":"Bibit 96S"}}],"forecast":[],"createdAt":"2025-02-08T07:07:22.187Z","updatedAt":"2025-02-12T01:32:40.270Z","publication":{"movement":false,"movementChoose":{"0h":"","24h":"","48h":"","72h":""},"warningText":"","positionAccuration":"sekitar","intensity":"Storm","intensity24":"Hurricane","windQuadran":"","finalPublication":true,"nextPublicationTime":"29/1300 UTC","accurationArea":{"type":"FeatureCollection","features":[]}}}],"total":41,"limit":5,"page":1,"pages":9}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>Maritim: detail cuaca/gelombang perairan</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="58" t="n">
+        <v>200</v>
+      </c>
+      <c r="E26" s="58" t="inlineStr">
+        <is>
+          <t>https://maritim.bmkg.go.id/public_api/perairan/F.09_Teluk%20Jakarta.json</t>
+        </is>
+      </c>
+      <c r="F26" s="68" t="inlineStr">
+        <is>
+          <t>{"code": "F.09", "name": "Teluk Jakarta", "issued": "2026-09-21 23:39 UTC", "info": "Per 17 Februari 2025 layanan API ini sepenuhnya menggunakan data digital hasil pemodelan BMKG", "data": [{"valid_from": "2026-09-21 12:00 UTC", "valid_to": "2026-09-22 00:00 UTC", "time_desc": "Hari ini", "weather": "Berawan", "weather_desc": "Hari ini untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 5 - 18 knot bertiup dari arah selatan, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Selatan", "wind_to": "Barat Daya", "wind_speed_min": 5, "wind_speed_max": 18}, {"valid_from": "2026-09-22 00:00 UTC", "valid_to": "2026-09-22 12:00 UTC", "time_desc": "Besok", "weather": "Hujan Ringan", "weather_desc": "Besok untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumnya 11 - 33 knot bertiup dari arah utara, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Utara", "wind_to": "Barat Daya", "wind_speed_min": 11, "wind_speed_max": 33}, {"valid_from": "2026-09-22 12:00 UTC", "valid_to": "2026-09-23 12:00 UTC", "time_desc": "H+2", "weather": "Hujan Ringan", "weather_desc": "Lusa untuk Teluk Jakarta diperkirakan hujan ringan, dengan kecepatan angin pada umumnya 5 - 33 knot bertiup dari arah utara, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Utara", "wind_to": "Selatan", "wind_speed_min": 5, "wind_speed_max": 33}, {"valid_from": "2026-09-23 12:00 UTC", "valid_to": "2026-09-24 12:00 UTC", "time_desc": "H+3", "weather": "Berawan", "weather_desc": "Dalam 3 Hari Lagi untuk Teluk Jakarta diperkirakan berawan, dengan kecepatan angin pada umumnya 7 - 35 knot bertiup dari arah utara, tinggi gelombang laut berkisar 0.5 - 1.25 m", "warning_desc": "Waspada Angin Kencang", "station_remark": "Digital forecast by BMKG", "wave_cat": "Rendah", "wave_desc": "0.5 - 1.25 m", "wind_from": "Utara", "wind_to": "Selatan", "wind_speed_min": 7, "wind_speed_max": 35}]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>